--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sales Comparables" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Related Parcels" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Comparables" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,17 +66,17 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -91,11 +91,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E5496"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -189,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -207,11 +202,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,73 +211,64 @@
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -654,14 +636,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -675,7 +657,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Compiled 2026-07-30  |  All properties in Adams County, Colorado</t>
+          <t>Prepared for Carter Equities  |  Updated 2026-07-30  |  8 subject properties, all Adams County, Colorado</t>
         </is>
       </c>
     </row>
@@ -729,22 +711,22 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Property Tax Appeal — Income Approach &amp; Sale Comps</t>
+          <t>Tax appeal — income approach + sale comps</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>(7194) CO-Aurora — 17608 E. 24th Drive, Aurora</t>
+          <t>17608 E. 24th Drive, Aurora</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Assessment Yr 2025 (Val date 6/30/2024)</t>
+          <t>Assess. Yr 2025</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Ryan LLC (Jamie Hoffman) / CoStar</t>
+          <t>Ryan LLC (J. Hoffman) / CoStar</t>
         </is>
       </c>
     </row>
@@ -759,7 +741,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Property Tax Appeal — Income Approach &amp; Auth Letter</t>
+          <t>Tax appeal — income approach + auth letter</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -769,12 +751,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Assessment Yr 2025 (Val date 6/30/2025)</t>
+          <t>Assess. Yr 2025</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>Ryan LLC (Bennett Mecom)</t>
+          <t>Ryan LLC (B. Mecom)</t>
         </is>
       </c>
     </row>
@@ -789,17 +771,17 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Adams County Commercial-Industrial Income &amp; Expense Survey</t>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TempTee Brand Steaks — 2011 E 58th Ave, Denver</t>
+          <t>2011 E 58th Ave (TempTee), Denver</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>2023-2024 (Received 10/10/2024)</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
@@ -814,22 +796,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>5970_Marion_Drive_2024_PL_Detail.pdf</t>
+          <t>5970_Marion_Drive_2024_PL_Detail.pdf / .xlsx</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Income Statement (Detailed, Cash Basis)</t>
+          <t>Income statement detail (+ income-approach block in xlsx)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>5970 Marion Drive</t>
+          <t>5970 Marion Drive, Denver</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>FY2024 (1/1-12/31/2024)</t>
+          <t>FY2024</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -849,17 +831,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Cash Flow Statement (Cash Basis)</t>
+          <t>Cash flow statement (cash basis)</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>5970 Marion Drive</t>
+          <t>5970 Marion Drive, Denver</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>FY2023 (1/1-12/31/2023)</t>
+          <t>FY2023</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
@@ -868,49 +850,154 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>5650_Washington_St.docx</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Restricted Appraisal Report (Industrial/Flex)</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>5650 Washington St, Denver</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Jason Bennett, MAI (Adams County)</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Notes:</t>
+      <c r="A12" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>R0024442.pdf</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal — income approach (Valuation Protest)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St, Thornton</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (B. Mecom)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>• Four distinct subject properties are covered. 7205 Gilpin Way is part of a 4-parcel North Side Gardens LLC portfolio (see 'Related Parcels' tab).</t>
+      <c r="A13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>R0002819.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Cover letter + IRS Form 8825 + Rent Roll</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St, Brighton</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>2024 (rent roll current)</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates / Broadview LLC</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>• Tabs: Property Master (identity), Tenants &amp; Leases, Assessments &amp; Valuation, Income-Expense Summary, Income-Expense Detail, Sales Comparables, Related Parcels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>• All dollar figures transcribed from the source PDFs. Totals shown with =SUM formulas cross-check the printed totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>• 'in house' on the TempTee survey means the owner performs the service internally (no dollar figure reported).</t>
+      <c r="A14" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>R0092302.pdf</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Appeal of Real Property Valuation — income + market sales</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave, Aurora</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2026</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Property Tax Advisors, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A14:F14"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -922,14 +1009,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="26" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -942,551 +1049,1011 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One record per subject property — identity, physical &amp; valuation summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>One row per subject property — identity, physical characteristics &amp; valuation summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Field</t>
+          <t>Property ID</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>Account / Schedule #</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Parcel / Alt #</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Property Name</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>County</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Owner / Client</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Assessee (Tax Roll)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Property Type / Use</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Tenancy</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>Site (Acres)</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Site (SF)</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>GBA (SF)</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>NRA / NLA (SF)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>Year Built</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>Land:Bldg</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>Latest Assessor / County Value</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>Assessment/Tax Yr</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>Taxpayer / Petitioner Opinion</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>Managed By</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>Source File</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>R0178308</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>R0178308</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>R0178308</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
           <t>7205 Gilpin Way</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>7205 Gilpin Way</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>80229</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Center Land Properties</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>North Side Gardens LLC</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Single (proforma)</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>145055</v>
+      </c>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="8" t="n">
+        <v>34228</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>2013</v>
+      </c>
+      <c r="S5" s="6" t="inlineStr">
+        <is>
+          <t>4.24:1</t>
+        </is>
+      </c>
+      <c r="T5" s="6" t="inlineStr">
+        <is>
+          <t>100% (proforma)</t>
+        </is>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>5150325</v>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="n">
+        <v>4832500</v>
+      </c>
+      <c r="X5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y5" s="6" t="inlineStr">
+        <is>
+          <t>R0178308.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>R0169133</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>R0169133</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>R0169133</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>(7194) CO-Aurora</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>17608 E. 24th Drive</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>ABC Supply Co., Inc.</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>ABC Supply Co., Inc.</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Single (proforma)</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>148104</v>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="8" t="n">
+        <v>20910</v>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v>2006</v>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>7.08:1</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>(as of 06/30/2024)</t>
+        </is>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>3408546</v>
+      </c>
+      <c r="V6" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W6" s="9" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>R0169133.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>R0103792</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>R0103792</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0182511406001</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TempTee Brand Steaks</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2011 E 58th Ave</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>80216-1517</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>TempTee Brand Steaks Inc</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>TempTee Brand Steaks Inc</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Mfg / Food Processing</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="8" t="n">
+        <v>17000</v>
+      </c>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied</t>
+        </is>
+      </c>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y7" s="6" t="inlineStr">
+        <is>
+          <t>R0103792.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>0182511303018</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>5970 Marion Drive</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2011 E 58th Ave (TempTee)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Property ID (Account #)</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>R0178308</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>R0169133</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>(mgmt) 5970 Marion</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>R0103792</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Parcel Number</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>R0178308</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>R0169133</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>0182511303018</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>0182511406001</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Property Name</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>(7194) CO-Aurora</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>5970 Marion Drive</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>TempTee Brand Steaks</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Street Address</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Drive</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>5970 Marion Drive</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>2011 E 58th Ave</t>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>80216 (est.)</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>Ankur Kumar (owner)</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - 2-unit</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Multi (2 units)</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="R8" s="6" t="n"/>
+      <c r="S8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>100% (2 units leased)</t>
+        </is>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>2527915</v>
+      </c>
+      <c r="V8" s="5" t="inlineStr">
+        <is>
+          <t>2025 (assigned)</t>
+        </is>
+      </c>
+      <c r="W8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X8" s="6" t="inlineStr">
+        <is>
+          <t>Deerwoods Management LLC</t>
+        </is>
+      </c>
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion P&amp;L/CF/xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>City, State ZIP</t>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>R0103767</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>Denver, CO 80229</t>
+          <t>R0103767</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Aurora, CO 80011</t>
+          <t>R0103767</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Denver, CO 80216 (est.)</t>
+          <t>Washington Business Park</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Denver, CO 80216-1517</t>
+          <t>5650 Washington St</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>80216 (est.)</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Washington Business Park Property LLC</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Washington Business Park Property LLC</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Industrial / Flex (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>100754</v>
+      </c>
+      <c r="P9" s="8" t="n">
+        <v>35577</v>
+      </c>
+      <c r="Q9" s="8" t="n">
+        <v>34442</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>1988</v>
+      </c>
+      <c r="S9" s="6" t="inlineStr">
+        <is>
+          <t>2.83:1</t>
+        </is>
+      </c>
+      <c r="T9" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (7% vac. assumed)</t>
+        </is>
+      </c>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W9" s="6" t="inlineStr">
+        <is>
+          <t>See appraisal (value in embedded image)</t>
+        </is>
+      </c>
+      <c r="X9" s="6" t="inlineStr">
+        <is>
+          <t>Owner: Bryan Sperry</t>
+        </is>
+      </c>
+      <c r="Y9" s="6" t="inlineStr">
+        <is>
+          <t>5650_Washington_St.docx</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>County</t>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>R0024442</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
+          <t>R0024442</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>R0024442</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>SGS - Pennsylvania Industrial</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Thornton</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>80241 (est.)</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
           <t>Adams</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Trinity Real Estate</t>
+        </is>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>Snyder Family Trust Et Al</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="6" t="n"/>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="8" t="n">
+        <v>23729</v>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v>1984</v>
+      </c>
+      <c r="S10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>(leased; rent $9.50/sf NNN 1/1/24)</t>
+        </is>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>3876387</v>
+      </c>
+      <c r="V10" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="n">
+        <v>2837000</v>
+      </c>
+      <c r="X10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y10" s="6" t="inlineStr">
+        <is>
+          <t>R0024442.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>R0002819</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>R0002819</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>01569-06-3-13-002</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Broadview</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>80602</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Adams</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Broadview LLC</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Broadview LLC</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>Commercial (multi-tenant industrial)</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="6" t="n"/>
+      <c r="R11" s="6" t="n"/>
+      <c r="S11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="6" t="inlineStr">
+        <is>
+          <t>Mostly leased (1-2 units vacant)</t>
+        </is>
+      </c>
+      <c r="U11" s="6" t="n"/>
+      <c r="V11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y11" s="6" t="inlineStr">
+        <is>
+          <t>R0002819.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>R0092302</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>R0092302</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>R0092302</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>80022 (est.)</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Adams</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Adams</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Owner / Client</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Center Land Properties</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>ABC Supply Co., Inc.</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Ankur Kumar (owner)</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>TempTee Brand Steaks Inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Assessee (Tax Roll)</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>North Side Gardens LLC</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>ABC Supply Co., Inc.</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>56th Ave. J Investments LLC et al</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>56th Ave. J Investments LLC et al</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="8" t="n">
+        <v>29620</v>
+      </c>
+      <c r="P12" s="8" t="n">
+        <v>9652</v>
+      </c>
+      <c r="Q12" s="8" t="n">
+        <v>9652</v>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v>1973</v>
+      </c>
+      <c r="S12" s="6" t="inlineStr">
+        <is>
+          <t>3.0:1</t>
+        </is>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>95% (proforma)</t>
+        </is>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>1815434</v>
+      </c>
+      <c r="V12" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="n">
+        <v>1493032</v>
+      </c>
+      <c r="X12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>TempTee Brand Steaks Inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Property Type / Use</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Industrial - Warehouse</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>Industrial - Distribution</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Industrial (2-unit, multi-tenant)</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>Industrial - Manufacturing / Food Processing</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Site Size (Acres)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Site Size (SF)</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>145055</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>148104</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Net Rentable Area (SF)</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>34228</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <v>20910</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>17000</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Year Built</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>2013</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>2006</v>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Land-to-Bldg Ratio</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>4.24 : 1</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>7.08 : 1</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Occupancy</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>100% (proforma)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>(as of 06/30/2024)</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>100% (2 units leased)</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>100% Owner-Occupied</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>2025 Assessor Actual Value</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>5150325</v>
-      </c>
-      <c r="C20" s="11" t="n">
-        <v>3408546</v>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Taxpayer Opinion of Value</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>4832500</v>
-      </c>
-      <c r="C21" s="11" t="n">
-        <v>3050000</v>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Value PSF (Taxpayer)</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>141.19</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>145.86</v>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Managed By</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Deerwoods Management LLC</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>Owner-occupied</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Source File(s)</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>R0178308.pdf</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>R0169133.pdf</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>2024 P&amp;L; 2023 Cash Flow</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>R0103792.pdf</t>
+      <c r="Y12" s="6" t="inlineStr">
+        <is>
+          <t>R0092302.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A1:Y1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1498,18 +2065,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1522,7 +2094,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actual tenants (5970 Marion) and proforma lease assumptions used in tax appeals</t>
+          <t>Actual tenants &amp; rent rolls (125 Bridge St, 5970 Marion) and proforma lease assumptions (tax appeals)</t>
         </is>
       </c>
     </row>
@@ -1539,243 +2111,1030 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Tenant / Basis</t>
+          <t>Tenant</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Lease Type</t>
+          <t>Basis / Lease Type</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Base Rent (Annual)</t>
+          <t>Monthly Rent</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>Annual Rent</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>Rent PSF</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>CAM / Recovery</t>
-        </is>
-      </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Vacancy Assumption</t>
+          <t>Lease Start</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
+          <t>Lease End</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Term / Option</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Monthly CAM</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>5970 Marion Drive</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Unit 1</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Whatever It Takes Transmissions &amp; Parts, Inc.</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Actual lease (NNN w/ CAM)</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>CAM escrows billed</t>
-        </is>
-      </c>
-      <c r="H5" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>2024 rent+CAM ~ largest portion of income; monthly ~$9,135</t>
-        </is>
-      </c>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>125 Bridge St, Brighton (R0002819) — Broadview LLC  |  Rent Roll (monthly, current as of Jan-2024)</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
+      <c r="E5" s="20" t="n"/>
+      <c r="F5" s="20" t="n"/>
+      <c r="G5" s="20" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
+      <c r="J5" s="20" t="n"/>
+      <c r="K5" s="20" t="n"/>
+      <c r="L5" s="20" t="n"/>
+      <c r="M5" s="21" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>5970 Marion Drive</t>
+          <t>125 Bridge St</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>A (Indoor)</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Integrated Turf Solutions LLC</t>
+          <t>Bulldog Tires</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>Actual lease (NNN w/ CAM)</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="12" t="n"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>CAM escrows billed</t>
-        </is>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>Monthly rent varied $3,120-$6,860 across 2024</t>
-        </is>
-      </c>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>4414</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>2/15/2021</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>9/30/2026</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>3-yr option</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>2550</v>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>7205 Gilpin Way</t>
+          <t>125 Bridge St</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Whole</t>
+          <t>B (Indoor)</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Proforma (single-tenant assumption)</t>
+          <t>Manny Mercado</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Appraisal proforma</t>
-        </is>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>359394</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>NNN (OpEx 8% EGI)</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Ryan income-approach proforma, not an executed lease</t>
-        </is>
-      </c>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>2425</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2024</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2029</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>2-yr option</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>2425</v>
+      </c>
+      <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>17608 E. 24th Drive</t>
+          <t>125 Bridge St</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Whole</t>
+          <t>C (Indoor)</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Proforma (single-tenant assumption)</t>
+          <t>Drip and Stitch</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Appraisal proforma</t>
-        </is>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>209100</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>NNN (OpEx 8% EGI)</t>
-        </is>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Ryan income-approach proforma, not an executed lease</t>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>12/15/2024</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>11/30/2025</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>1-yr option</t>
+        </is>
+      </c>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>CAM unit 'Cabinet Connections' vacated 3/31/24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th Ave (TempTee)</t>
+          <t>125 Bridge St</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>D (Indoor)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Galaxy Greens</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>3/1/2024</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>10/31/2033</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>5-yr option</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="L9" s="6" t="n"/>
+      <c r="M9" s="6" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>E (Indoor)</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Intensive Drilling</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>1/1/2025</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>12/1/2029</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>5-yr option</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>3100</v>
+      </c>
+      <c r="M10" s="6" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>F (Indoor)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Intensive Drilling</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="n"/>
+      <c r="L11" s="6" t="n"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Listed; no rent shown (vacant/expansion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="6" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>2/28/2026</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>1-yr option</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="n"/>
+      <c r="M12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Intensive Drilling</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>as above</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="n"/>
+      <c r="L13" s="9" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>El Tacos</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>9/30</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>12 months</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="n"/>
+      <c r="M14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Cabinet</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>month-to-month</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="n"/>
+      <c r="L15" s="6" t="n"/>
+      <c r="M15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Outdoor</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>RV Parking</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>month-to-month</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="n"/>
+      <c r="L16" s="6" t="n"/>
+      <c r="M16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>125 Bridge St</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Total Rental Income (monthly)</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr"/>
+      <c r="E17" s="14">
+        <f>SUM(E6:E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="14">
+        <f>E17*12</f>
+        <v/>
+      </c>
+      <c r="G17" s="13" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="14">
+        <f>SUM(K6:K16)</f>
+        <v/>
+      </c>
+      <c r="L17" s="13" t="inlineStr"/>
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>Monthly CAM total $5,000; annualized gross scheduled income ≈ monthly total × 12. IRS Form 8825 actual 2024 gross rents were $307,817.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>5970 Marion Drive (0182511303018) — actual tenants (FY2024)</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+      <c r="J18" s="20" t="n"/>
+      <c r="K18" s="20" t="n"/>
+      <c r="L18" s="20" t="n"/>
+      <c r="M18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Whatever It Takes Transmissions &amp; Parts, Inc.</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Actual (NNN w/ CAM)</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="n"/>
+      <c r="L19" s="6" t="n"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>2024 monthly rent ~$9,136; billed CAM escrows separately</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Integrated Turf Solutions LLC</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Actual (NNN w/ CAM)</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="n"/>
+      <c r="L20" s="6" t="n"/>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>2024 monthly rent ranged $3,120-$6,860; billed CAM escrows</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Tax-appeal proforma lease assumptions (not executed leases)</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="20" t="n"/>
+      <c r="I21" s="20" t="n"/>
+      <c r="J21" s="20" t="n"/>
+      <c r="K21" s="20" t="n"/>
+      <c r="L21" s="20" t="n"/>
+      <c r="M21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>7205 Gilpin Way</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>Whole</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>Owner-Occupied (no tenant)</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>Owner-occupied</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="H9" s="13" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Proforma single-tenant</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Proforma NNN</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="9" t="n">
+        <v>359394</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>100% owner-occupied by TempTee Brand Steaks; no rental income reported</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="n"/>
+      <c r="L22" s="6" t="n"/>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>OpEx 8% EGI; 5% vacancy (Ryan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>17608 E. 24th Dr</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Proforma single-tenant</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Proforma NNN</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="9" t="n">
+        <v>209100</v>
+      </c>
+      <c r="G23" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n"/>
+      <c r="L23" s="6" t="n"/>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>OpEx 8% EGI; 5% vacancy (Ryan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Proforma single-tenant</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Proforma NNN</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="G24" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="n"/>
+      <c r="L24" s="6" t="n"/>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>Face rent $10; actual tenant $9.50/sf NNN as of 1/1/24; 7% vac, 10% OpEx (Ryan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Proforma single-tenant</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Proforma</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="G25" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="n"/>
+      <c r="L25" s="6" t="n"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>$12/sf; 95% occ; 5% expenses (Property Tax Advisors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>5650 Washington St</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Multiple</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Actual multi-tenant (modified gross)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Modified Gross</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n"/>
+      <c r="L26" s="6" t="n"/>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>Actual rents $10.28-$31.48/sf; majority $13-17/sf; $15/sf applied to vacant space. Detailed rent roll embedded as image in appraisal.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1787,16 +3146,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1809,22 +3169,23 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Historical assessed values and Ryan income-approach proforma (tax appeals)</t>
+          <t>Assessed/county values and income-approach proformas across the tax-appeal &amp; appraisal documents</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>A. Historical Assessed Values (Adams County Assessor)</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>A. Assessed / County Values</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
+      <c r="E4" s="20" t="n"/>
+      <c r="F4" s="20" t="n"/>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="21" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -1834,32 +3195,37 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Assess. Yr</t>
+          <t>Assess/Tax Yr</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Land Value</t>
+          <t>Assessor / County Value</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Improvement Value</t>
+          <t>Value PSF</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>Total Actual Value</t>
+          <t>Taxpayer / Petitioner Opinion</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Total Value PSF</t>
+          <t>Opinion PSF</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>Land Value PSF</t>
+          <t>Prior-Yr Value</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
         </is>
       </c>
     </row>
@@ -1874,53 +3240,61 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
-        <v>1125150</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>4025175</v>
-      </c>
-      <c r="E6" s="11" t="n">
+      <c r="C6" s="9" t="n">
         <v>5150325</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="D6" s="16" t="n">
         <v>150.47</v>
       </c>
-      <c r="G6" s="12" t="n">
-        <v>7.76</v>
+      <c r="E6" s="9" t="n">
+        <v>4832500</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>141.19</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>4999770</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>R0178308</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>7205 Gilpin Way (R0178308)</t>
+          <t>17608 E. 24th Dr (R0169133)</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>675090</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>4324680</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>4999770</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>146.07</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>4.65</v>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>3408546</v>
+      </c>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="9" t="n">
+        <v>3050000</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>145.86</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>2900000</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>R0169133 (cover)</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>17608 E. 24th Dr (R0169133)</t>
+          <t>12260 Pennsylvania St (R0024442)</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
@@ -1928,372 +3302,317 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
-        <v>992519</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>2122296</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>3114815</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>148.96</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>6.7</v>
+      <c r="C8" s="9" t="n">
+        <v>3876387</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>163.36</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>2837000</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>119.56</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>R0024442</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>17608 E. 24th Dr (R0169133)</t>
+          <t>6770 E. 56th Ave (R0092302)</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>924078</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>1975922</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>138.69</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>6.24</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Note: R0169133 cover page lists 2025 Assessor's Actual Value of $3,408,546; the historical-assessment schedule (p.2) shows a 2025 total of $3,114,815. Both are reproduced as printed.</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="28" t="n"/>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="29" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>B. Income-Approach Proforma (Ryan LLC — supports Taxpayer's Opinion of Value)</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Line Item</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>7205 Gilpin — Amount</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>7205 Gilpin — $/SF</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>7205 Gilpin — %</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>17608 E.24th — Amount</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>17608 E.24th — $/SF</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>17608 E.24th — %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Potential Base Rent</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>209100</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G15" s="17" t="n">
-        <v>1</v>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1815434</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <v>188.09</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1493032</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>154.69</v>
+      </c>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>R0092302</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion Drive</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2025 (assigned)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>2527915</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>175.55</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>2460577</v>
+      </c>
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion xlsx (income block)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="20" t="n"/>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="21" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>B. Income-Approach Proformas</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="20" t="n"/>
+      <c r="F14" s="20" t="n"/>
+      <c r="G14" s="20" t="n"/>
+      <c r="H14" s="21" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PGI</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Vacancy</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>EGI</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Operating Exp</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOI</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Cap Rate</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Indicated Value</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>Gross Potential Rent</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
+          <t>7205 Gilpin Way</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
         <v>359394</v>
       </c>
-      <c r="C16" s="12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>209100</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="G16" s="17" t="n">
-        <v>1</v>
+      <c r="C16" s="9" t="n">
+        <v>-17970</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>341424</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>-27314</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>314110</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>4832500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>Less: Vacancy Loss</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>-0.53</v>
-      </c>
-      <c r="D17" s="17" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E17" s="11" t="n">
+          <t>17608 E. 24th Dr</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>209100</v>
+      </c>
+      <c r="C17" s="9" t="n">
         <v>-10455</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="G17" s="17" t="n">
-        <v>0.05</v>
+      <c r="D17" s="9" t="n">
+        <v>198645</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>-15892</v>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>182753</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>3050000</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Effective Gross Income (EGI)</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="n">
-        <v>341424</v>
-      </c>
-      <c r="C18" s="20" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="D18" s="21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="E18" s="19" t="n">
-        <v>198645</v>
-      </c>
-      <c r="F18" s="20" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>0.95</v>
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>-16610</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>220680</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>-22068</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>198612</v>
+      </c>
+      <c r="G18" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>2837000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Less: Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="D19" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>0.08</v>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G19" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>1493302</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Less: Property Taxes</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Total Operating Expenses</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="D21" s="17" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E21" s="11" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="G21" s="17" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="22">
+          <t>5970 Marion Drive (mkt)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>172800</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-8640</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>164160</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-4223</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>159937</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2460577</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>NET OPERATING INCOME (NOI)</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n">
-        <v>314110</v>
-      </c>
-      <c r="C22" s="20" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="D22" s="21" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E22" s="19" t="n">
-        <v>182753</v>
-      </c>
-      <c r="F22" s="20" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="G22" s="21" t="n">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Capitalization Rate</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Indicated FMV</t>
-        </is>
-      </c>
-      <c r="B24" s="11" t="n">
-        <v>4832467</v>
-      </c>
-      <c r="C24" s="22" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="11" t="n">
-        <v>3045890</v>
-      </c>
-      <c r="F24" s="22" t="n"/>
-      <c r="G24" s="22" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
-        <is>
-          <t>Indicated FMV (Rounded)</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="n">
-        <v>4832500</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>141.19</v>
-      </c>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="19" t="n">
-        <v>3050000</v>
-      </c>
-      <c r="F25" s="20" t="n">
-        <v>145.86</v>
-      </c>
-      <c r="G25" s="23" t="n"/>
+          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="20" t="n"/>
+      <c r="G22" s="20" t="n"/>
+      <c r="H22" s="21" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2305,14 +3624,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2325,11 +3644,11 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Operating income &amp; expense by property and year (cash basis unless noted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t>Operating income, expense &amp; net by property and year (cash/tax basis as noted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>Property / Year</t>
@@ -2342,12 +3661,12 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Total Operating Expense</t>
+          <t>Total Expense</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Net Income / (Loss)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -2357,86 +3676,104 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B5" s="25" t="n">
+      <c r="B5" s="22" t="n">
         <v>249672.2</v>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="22" t="n">
         <v>162774.36</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="23">
         <f>B5-C5</f>
         <v/>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>P&amp;L Detail, cash basis (incl. debt svc &amp; taxes)</t>
+          <t>5970_Marion 2024 P&amp;L (cash; incl. debt svc &amp; taxes)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B6" s="25" t="n">
+      <c r="B6" s="22" t="n">
         <v>247311.55</v>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="22" t="n">
         <v>188635.46</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="23">
         <f>B6-C6</f>
         <v/>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Cash Flow Stmt, cash basis (incl. debt svc &amp; taxes)</t>
+          <t>2023 Cash Flow (cash; incl. debt svc &amp; taxes)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>2011 E 58th (TempTee) — 2024 survey</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n"/>
-      <c r="C7" s="25" t="n">
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n">
         <v>138050</v>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Owner-occupied; reported OpEx only (excl. 'in house' items)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Net Income shown = Total Income − Total Expense as printed. 5970 Marion 'expense' includes mortgage P&amp;I and property taxes, so it is a cash-flow figure, not NOI. TempTee reported operating expenses only (owner-occupied, no rental income).</t>
-        </is>
-      </c>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="29" t="n"/>
+          <t>Owner-occupied; reported OpEx only ('in house' items = $0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="n">
+        <v>307817</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>316181</v>
+      </c>
+      <c r="D8" s="23">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>IRS Form 8825 (tax basis; incl. depreciation, amort. &amp; interest)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2448,10 +3785,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -2505,7 +3842,7 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
@@ -2515,7 +3852,7 @@
           <t>4001 - Rent (Units 1 &amp; 2)</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="22" t="n">
         <v>168399.6</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -2530,7 +3867,7 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
@@ -2540,38 +3877,38 @@
           <t>4200 - CAM Escrows</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="22" t="n">
         <v>81272.60000000001</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Common area maintenance recoveries</t>
+          <t>CAM recoveries</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="26" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="23">
         <f>SUM(D5:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>Printed total: $249,672.20</t>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $249,672.20.</t>
         </is>
       </c>
     </row>
@@ -2581,24 +3918,20 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>4901 - Utilities - Water</t>
-        </is>
-      </c>
-      <c r="D8" s="25" t="n">
+          <t>Utilities - Water</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="n">
         <v>2175.55</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>N. Washington St Water &amp; Sanitation</t>
-        </is>
-      </c>
+      <c r="E8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -2606,17 +3939,17 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B9" s="32" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>4906 - Utilities - Sewer</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="n">
+          <t>Utilities - Sewer</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="n">
         <v>394.3</v>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
@@ -2627,24 +3960,20 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>5057 - Inspection &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="D10" s="25" t="n">
+          <t>Inspection &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="n">
         <v>100</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>Backflow test</t>
-        </is>
-      </c>
+      <c r="E10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2652,24 +3981,20 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>5063 - Snow Removal</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="n">
+          <t>Snow Removal</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="n">
         <v>927.47</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Cardenas Landscaping</t>
-        </is>
-      </c>
+      <c r="E11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2677,24 +4002,20 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B12" s="32" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>5064 - Common Area Clean</t>
-        </is>
-      </c>
-      <c r="D12" s="25" t="n">
+          <t>Common Area Clean</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="n">
         <v>200</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>A&amp;W Services</t>
-        </is>
-      </c>
+      <c r="E12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2702,22 +4023,22 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>6020 - Property Management</t>
-        </is>
-      </c>
-      <c r="D13" s="25" t="n">
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="n">
         <v>6000</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Deerwoods Management ($500/mo)</t>
+          <t>Deerwoods</t>
         </is>
       </c>
     </row>
@@ -2727,22 +4048,22 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B14" s="32" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>6044 - Eviction Fees</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="n">
+          <t>Eviction Fees</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Net $0 (reclassed to Legal)</t>
+          <t>net $0</t>
         </is>
       </c>
     </row>
@@ -2752,22 +4073,22 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B15" s="32" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>7010 - Insurance</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="n">
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
         <v>10241.26</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Farmers Insurance</t>
+          <t>Farmers</t>
         </is>
       </c>
     </row>
@@ -2777,22 +4098,22 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B16" s="32" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>7020 - Taxes - Real Property</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="n">
+          <t>Taxes - Real Property</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
         <v>62852.62</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Adams County Treasurer (2 halves)</t>
+          <t>Adams Co.</t>
         </is>
       </c>
     </row>
@@ -2802,24 +4123,20 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>7031 - Taxes Other</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="n">
+          <t>Taxes Other</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
         <v>800</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>CA Franchise reimb.</t>
-        </is>
-      </c>
+      <c r="E17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -2827,17 +4144,17 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B18" s="32" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>8100 - Mortgage Principal</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="n">
+          <t>Mortgage Principal</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
         <v>27586.31</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -2852,17 +4169,17 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B19" s="32" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>8101 - Mortgage Interest</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="n">
+          <t>Mortgage Interest</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
         <v>50738.17</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -2877,24 +4194,20 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B20" s="32" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Legal and Professional Fees</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="n">
+          <t>Legal &amp; Professional</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
         <v>465</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>Halstead Law</t>
-        </is>
-      </c>
+      <c r="E20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2902,48 +4215,44 @@
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B21" s="32" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
-        </is>
-      </c>
-      <c r="D21" s="25" t="n">
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
         <v>293.68</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Owner ticket reimb.</t>
-        </is>
-      </c>
+      <c r="E21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>5970 Marion Drive — FY2024</t>
         </is>
       </c>
-      <c r="B22" s="33" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>TOTAL EXPENSE</t>
         </is>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="23">
         <f>SUM(D8:D21)</f>
         <v/>
       </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>Printed total: $162,774.36 (cash-basis; includes debt service &amp; property taxes)</t>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $162,774.36. cash basis; incl. debt service &amp; property taxes</t>
         </is>
       </c>
     </row>
@@ -2953,17 +4262,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B23" s="30" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>4200 - CAM Escrows</t>
-        </is>
-      </c>
-      <c r="D23" s="25" t="n">
+          <t>CAM Escrows</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="n">
         <v>89143.03999999999</v>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
@@ -2974,17 +4283,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B24" s="30" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>4600 - Prior Year CAM</t>
-        </is>
-      </c>
-      <c r="D24" s="25" t="n">
+          <t>Prior Year CAM</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="n">
         <v>523.01</v>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
@@ -2995,17 +4304,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B25" s="30" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>4750 - Tenant Administrative Fees</t>
-        </is>
-      </c>
-      <c r="D25" s="25" t="n">
+          <t>Tenant Admin Fees</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="n">
         <v>500</v>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
@@ -3016,44 +4325,44 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>4650 - Rent Income</t>
-        </is>
-      </c>
-      <c r="D26" s="25" t="n">
+          <t>Rent Income</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="n">
         <v>157145.5</v>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B27" s="31" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Income</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>TOTAL INCOME</t>
         </is>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="23">
         <f>SUM(D23:D26)</f>
         <v/>
       </c>
-      <c r="E27" s="16" t="inlineStr">
-        <is>
-          <t>Printed total: $247,311.55</t>
+      <c r="E27" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $247,311.55.</t>
         </is>
       </c>
     </row>
@@ -3063,17 +4372,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B28" s="32" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>5010 - Electrical Repairs &amp; Lighting</t>
-        </is>
-      </c>
-      <c r="D28" s="25" t="n">
+          <t>Electrical Repairs &amp; Lighting</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="n">
         <v>1550</v>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3084,17 +4393,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B29" s="32" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>5015 - Roofing Repairs</t>
-        </is>
-      </c>
-      <c r="D29" s="25" t="n">
+          <t>Roofing Repairs</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="n">
         <v>47000</v>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
@@ -3105,17 +4414,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B30" s="32" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5017 - Drywall Repairs</t>
-        </is>
-      </c>
-      <c r="D30" s="25" t="n">
+          <t>Drywall Repairs</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="n">
         <v>810</v>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
@@ -3126,17 +4435,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B31" s="32" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>5029 - Snow Removal</t>
-        </is>
-      </c>
-      <c r="D31" s="25" t="n">
+          <t>Snow Removal</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="n">
         <v>1016.31</v>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
@@ -3147,17 +4456,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B32" s="32" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>5030 - Utilities - Water</t>
-        </is>
-      </c>
-      <c r="D32" s="25" t="n">
+          <t>Utilities - Water</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="n">
         <v>2157.08</v>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3168,17 +4477,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B33" s="32" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>5038 - Trash</t>
-        </is>
-      </c>
-      <c r="D33" s="25" t="n">
+          <t>Trash</t>
+        </is>
+      </c>
+      <c r="D33" s="22" t="n">
         <v>151.01</v>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
@@ -3189,17 +4498,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B34" s="32" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5047 - Inspection &amp; Compliance</t>
-        </is>
-      </c>
-      <c r="D34" s="25" t="n">
+          <t>Inspection &amp; Compliance</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="n">
         <v>110</v>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
@@ -3210,24 +4519,20 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B35" s="32" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>6020 - Property Management</t>
-        </is>
-      </c>
-      <c r="D35" s="25" t="n">
+          <t>Property Management</t>
+        </is>
+      </c>
+      <c r="D35" s="22" t="n">
         <v>6000</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Deerwoods Management</t>
-        </is>
-      </c>
+      <c r="E35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -3235,17 +4540,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B36" s="32" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>6043 - Bank fees</t>
-        </is>
-      </c>
-      <c r="D36" s="25" t="n">
+          <t>Bank fees</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="n">
         <v>180</v>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
@@ -3256,17 +4561,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B37" s="32" t="inlineStr">
+      <c r="B37" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>7010 - Insurance</t>
-        </is>
-      </c>
-      <c r="D37" s="25" t="n">
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D37" s="22" t="n">
         <v>8640.99</v>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
@@ -3277,24 +4582,20 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B38" s="32" t="inlineStr">
+      <c r="B38" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>7020 - Taxes - Real Property</t>
-        </is>
-      </c>
-      <c r="D38" s="25" t="n">
+          <t>Taxes - Real Property</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="n">
         <v>37726.76</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>Parcel 0182511303018</t>
-        </is>
-      </c>
+      <c r="E38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -3302,17 +4603,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B39" s="32" t="inlineStr">
+      <c r="B39" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>7031 - Taxes Other</t>
-        </is>
-      </c>
-      <c r="D39" s="25" t="n">
+          <t>Taxes Other</t>
+        </is>
+      </c>
+      <c r="D39" s="22" t="n">
         <v>4968.83</v>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
@@ -3323,17 +4624,17 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B40" s="32" t="inlineStr">
+      <c r="B40" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>8100 - Mortgage Principal</t>
-        </is>
-      </c>
-      <c r="D40" s="25" t="n">
+          <t>Mortgage Principal</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="n">
         <v>26699.59</v>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
@@ -3344,54 +4645,54 @@
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B41" s="32" t="inlineStr">
+      <c r="B41" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>8101 - Mortgage Interest</t>
-        </is>
-      </c>
-      <c r="D41" s="25" t="n">
+          <t>Mortgage Interest</t>
+        </is>
+      </c>
+      <c r="D41" s="22" t="n">
         <v>51624.89</v>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>5970 Marion Drive — FY2023</t>
         </is>
       </c>
-      <c r="B42" s="33" t="inlineStr">
+      <c r="B42" s="28" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
         <is>
           <t>TOTAL EXPENSE</t>
         </is>
       </c>
-      <c r="D42" s="26">
+      <c r="D42" s="23">
         <f>SUM(D28:D41)</f>
         <v/>
       </c>
-      <c r="E42" s="16" t="inlineStr">
-        <is>
-          <t>Printed total: $188,635.46 (cash-basis; incl. debt svc &amp; taxes. Owner Draw $100,000 financing, not in expense.)</t>
+      <c r="E42" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $188,635.46. cash basis; Owner Draw $100,000 (financing) excluded</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B43" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3401,22 +4702,18 @@
           <t>Advertising (leasing)</t>
         </is>
       </c>
-      <c r="D43" s="25" t="n">
+      <c r="D43" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>Owner-reported</t>
-        </is>
-      </c>
+      <c r="E43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B44" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3426,7 +4723,7 @@
           <t>Building Insurance</t>
         </is>
       </c>
-      <c r="D44" s="25" t="n">
+      <c r="D44" s="22" t="n">
         <v>14050</v>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
@@ -3434,10 +4731,10 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B45" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B45" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3447,7 +4744,7 @@
           <t>Building Repair &amp; Maintenance</t>
         </is>
       </c>
-      <c r="D45" s="25" t="n">
+      <c r="D45" s="22" t="n">
         <v>10000</v>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
@@ -3455,10 +4752,10 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B46" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B46" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3468,47 +4765,47 @@
           <t>Ground Maintenance</t>
         </is>
       </c>
-      <c r="D46" s="25" t="n">
+      <c r="D46" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Reported 'in house' (no $)</t>
+          <t>'in house'</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B47" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B47" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>Janitorial Services</t>
-        </is>
-      </c>
-      <c r="D47" s="25" t="n">
+          <t>Janitorial</t>
+        </is>
+      </c>
+      <c r="D47" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Reported 'in house' (no $)</t>
+          <t>'in house'</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B48" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B48" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3518,7 +4815,7 @@
           <t>Leasing Commissions</t>
         </is>
       </c>
-      <c r="D48" s="25" t="n">
+      <c r="D48" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
@@ -3526,10 +4823,10 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B49" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B49" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3539,7 +4836,7 @@
           <t>Management</t>
         </is>
       </c>
-      <c r="D49" s="25" t="n">
+      <c r="D49" s="22" t="n">
         <v>0</v>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
@@ -3547,10 +4844,10 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B50" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B50" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3560,7 +4857,7 @@
           <t>Snow/Trash Removal</t>
         </is>
       </c>
-      <c r="D50" s="25" t="n">
+      <c r="D50" s="22" t="n">
         <v>12000</v>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
@@ -3568,10 +4865,10 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B51" s="32" t="inlineStr">
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B51" s="27" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
@@ -3581,34 +4878,321 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="D51" s="25" t="n">
+      <c r="D51" s="22" t="n">
         <v>102000</v>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="24" t="inlineStr">
-        <is>
-          <t>2011 E 58th (TempTee) — 2024 survey</t>
-        </is>
-      </c>
-      <c r="B52" s="33" t="inlineStr">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>2011 E 58th (TempTee) — 2024</t>
+        </is>
+      </c>
+      <c r="B52" s="28" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="12" t="inlineStr">
         <is>
           <t>TOTAL EXPENSE</t>
         </is>
       </c>
-      <c r="D52" s="26">
+      <c r="D52" s="23">
         <f>SUM(D43:D51)</f>
         <v/>
       </c>
-      <c r="E52" s="16" t="inlineStr">
-        <is>
-          <t>Printed total: $138,050.00 Adams Co. Income&amp;Expense Survey; 100% owner-occupied (~17,000 SF). 'in house' items entered as $0.</t>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $138,050.00. Adams Co. survey; 100% owner-occupied (~17,000 SF); 'in house' items = $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Gross rents</t>
+        </is>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>307817</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>IRS Form 8825, Property A (125 Bridge St, COMMERCIAL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B54" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D54" s="23">
+        <f>SUM(D53:D53)</f>
+        <v/>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $307,817.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B55" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>776</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>12004</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Legal &amp; professional fees</t>
+        </is>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>10211</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="n">
+        <v>98058</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>100279</v>
+      </c>
+      <c r="E59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>4731</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B61" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D61" s="22" t="n">
+        <v>47109</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B62" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Meals - 100%</t>
+        </is>
+      </c>
+      <c r="D62" s="22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B63" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>2166</v>
+      </c>
+      <c r="E63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B64" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Other (Statement #8A)</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="n">
+        <v>39767</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview) — Form 8825</t>
+        </is>
+      </c>
+      <c r="B65" s="28" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D65" s="23">
+        <f>SUM(D55:D64)</f>
+        <v/>
+      </c>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
         </is>
       </c>
     </row>
@@ -3724,7 +5308,7 @@
       <c r="E5" s="5" t="n">
         <v>1987</v>
       </c>
-      <c r="F5" s="34" t="n">
+      <c r="F5" s="29" t="n">
         <v>15100</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -3732,10 +5316,10 @@
           <t>3/25/2024</t>
         </is>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="9" t="n">
         <v>2500000</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="16" t="n">
         <v>165.56</v>
       </c>
     </row>
@@ -3761,7 +5345,7 @@
       <c r="E6" s="5" t="n">
         <v>1996</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="29" t="n">
         <v>39655</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -3769,10 +5353,10 @@
           <t>1/23/2024</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="9" t="n">
         <v>6700000</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="16" t="n">
         <v>168.96</v>
       </c>
     </row>
@@ -3798,7 +5382,7 @@
       <c r="E7" s="5" t="n">
         <v>1996</v>
       </c>
-      <c r="F7" s="34" t="n">
+      <c r="F7" s="29" t="n">
         <v>35441</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -3806,10 +5390,10 @@
           <t>11/6/2023</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="9" t="n">
         <v>3775000</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="16" t="n">
         <v>106.52</v>
       </c>
     </row>
@@ -3835,7 +5419,7 @@
       <c r="E8" s="5" t="n">
         <v>1982</v>
       </c>
-      <c r="F8" s="34" t="n">
+      <c r="F8" s="29" t="n">
         <v>22000</v>
       </c>
       <c r="G8" s="5" t="inlineStr">
@@ -3843,41 +5427,41 @@
           <t>9/20/2022</t>
         </is>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="9" t="n">
         <v>3685000</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="16" t="n">
         <v>167.5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>Average / Total</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="inlineStr"/>
-      <c r="D9" s="35" t="inlineStr"/>
-      <c r="E9" s="35" t="inlineStr"/>
-      <c r="F9" s="36">
+      <c r="A9" s="13" t="inlineStr"/>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="30">
         <f>AVERAGE(F5:F8)</f>
         <v/>
       </c>
-      <c r="G9" s="35" t="inlineStr"/>
-      <c r="H9" s="19">
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="14">
         <f>AVERAGE(H5:H8)</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="31">
         <f>AVERAGE(I5:I8)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Source: CoStar Sale Comps report (©2025 CoStar, licensed to Marvin F. Poer &amp; Company), included in the R0169133 appeal package. All 100% leased at sale; Adams County submarkets.</t>
+    <row r="11" ht="28" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>Source: CoStar (©2025), included in the R0169133 package. Other appeal files also contain comps: R0092302 &amp; 5650 Washington St include CoStar sale/rent comps; R0024442 &amp; R0178308 include CoStar rent/sale sheets — not itemized here (supporting market data).</t>
         </is>
       </c>
     </row>
@@ -3939,7 +5523,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Assessor / County</t>
+          <t>County</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -3976,27 +5560,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>North Side Gardens LLC</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>R0178308</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>7205 Gilpin Way</t>
         </is>
       </c>
-      <c r="D6" s="27" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Adams County</t>
         </is>
       </c>
-      <c r="E6" s="27" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>CO</t>
         </is>
@@ -4056,10 +5640,10 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary subject of the appeal document; the other three parcels are co-listed on the same authorization/appeal schedule. Owner of record on the appeal letter: Center Land Properties (signed by Ken R. Lombardi, Manager).</t>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager).</t>
         </is>
       </c>
     </row>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -13,8 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales Comparables" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -661,6 +660,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Tax appeal — income approach + sale comps</t>
+          <t>Tax appeal — income approach</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Appeal of Real Property Valuation — income + market sales</t>
+          <t>Appeal of Real Property Valuation — income approach</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
@@ -970,6 +970,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -1053,6 +1054,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2098,6 +2100,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3173,6 +3176,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3381,6 +3385,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -3395,6 +3400,7 @@
       <c r="G12" s="20" t="n"/>
       <c r="H12" s="21" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -3591,6 +3597,7 @@
         <v>2460577</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -3648,6 +3655,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3762,12 +3770,17 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3809,6 +3822,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5206,276 +5220,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>SALES COMPARABLES</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Warehouse sale comps supporting the R0169133 (17608 E. 24th Dr) appraisal — CoStar / Ryan LLC</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Address</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>City, ST ZIP</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>Year Built</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Building SF</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>Sale Date</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Sale Price</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>Price PSF</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>8495 Roslyn St</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Commerce City, CO 80022</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>1987</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>15100</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>3/25/2024</t>
-        </is>
-      </c>
-      <c r="H5" s="9" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="I5" s="16" t="n">
-        <v>165.56</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>11900 E 33rd Ave</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>Aurora, CO 80010</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>1996</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>39655</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>1/23/2024</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>6700000</v>
-      </c>
-      <c r="I6" s="16" t="n">
-        <v>168.96</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>6270 E 50th Ave</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Commerce City, CO 80022</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>1996</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>35441</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>11/6/2023</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="n">
-        <v>3775000</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>106.52</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>7001 E 57th Pl</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Commerce City, CO 80022</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Warehouse</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>1982</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>22000</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>9/20/2022</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>3685000</v>
-      </c>
-      <c r="I8" s="16" t="n">
-        <v>167.5</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr"/>
-      <c r="D9" s="13" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr"/>
-      <c r="F9" s="30">
-        <f>AVERAGE(F5:F8)</f>
-        <v/>
-      </c>
-      <c r="G9" s="13" t="inlineStr"/>
-      <c r="H9" s="14">
-        <f>AVERAGE(H5:H8)</f>
-        <v/>
-      </c>
-      <c r="I9" s="31">
-        <f>AVERAGE(I5:I8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
-        <is>
-          <t>Source: CoStar (©2025), included in the R0169133 package. Other appeal files also contain comps: R0092302 &amp; 5650 Washington St include CoStar sale/rent comps; R0024442 &amp; R0178308 include CoStar rent/sale sheets — not itemized here (supporting market data).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5505,6 +5249,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5640,12 +5385,17 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager).</t>
         </is>
       </c>
+      <c r="B10" s="20" t="n"/>
+      <c r="C10" s="20" t="n"/>
+      <c r="D10" s="20" t="n"/>
+      <c r="E10" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -656,11 +656,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-07-30  |  8 subject properties, all Adams County, Colorado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Prepared for Carter Equities  |  Updated 2026-08-03  |  13 subject properties, all Adams County, Colorado</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,35 +969,192 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0048725.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Cover letter (SB 11-119) + 2023-2024 P&amp;L (QuickBooks, accrual)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>9345 (9335) Elm Ct — TARA LLC</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>FY2023-FY2024</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates / owner</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>500_E_76TH_AVE.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Valuation protest — income &amp; sales approaches + income stmt + rent rolls (scanned)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>460-550 E. 76th Ave 'I-25 Corporate Center'</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>FY2024; protest 5/20/2026</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services (D. George) / Colliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0083953.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Valuation protest — income approach + income stmt + rent roll (scanned)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>20901 E. 32nd Pkwy 'Majestic Commercenter'</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>FY2024; protest 6/5/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services (D. George) / Colliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0084233.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Cover letter (SB 11-119) + income statements + rent rolls (2 bldgs)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>3254 &amp; 3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>FY2023-FY2024</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates / Colliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>R0084237.pdf</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Cover letter (SB 11-119) + Yardi income statements + portfolio rent rolls</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl (Denver Industrial Portfolio)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>FY2023-FY2024</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates / St. Paul F&amp;M</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>St. Paul rent rolls cover the full 17-building 'Denver Industrial Portfolio'; only subject-building (14501 E 35th Pl) leases are stored in Tenants &amp; Leases. CoStar sales-comp pages in the 1st Net protests are out of scope and not stored. 3254/3650 Fraser 'Total Expense' figures include capital expenditures as printed. E 76th Ave county value: protest letter shows $44,788,554; the income-approach sheet and 1st Net protest list show 2025 county value $47,464,870 — both reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1210,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2049,6 +2204,537 @@
       <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>R0092302.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R0048725</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>R0048725</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0171920102027</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct (TARA)</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>9345 (9335) Elm Ct</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>TARA LLC (Patricia Ellison)</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>TARA LLC</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Commercial rental</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>2 rental addresses</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="8" t="n"/>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>Leased (rental income both yrs)</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>2025 (SB 11-119 submission)</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>R0048725.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>R0070622-27</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>R0070622;23;24;25;26;27</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corporate Center</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>460-550 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>80229 (est.)</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse/Mfg</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (14 units)</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>857172</v>
+      </c>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="8" t="n">
+        <v>330935</v>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>1974/77/78/79</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>2.59:1</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>77% (76,733 SF vacant 12/31/24)</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>47464870</v>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>500_E_76TH_AVE.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>R0083953</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0083953</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>20901 E. 32nd Pkwy</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>WPC ABC LLC</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>WPC ABC LLC</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (4 suites)</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (4 suites)</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="8" t="n">
+        <v>200000</v>
+      </c>
+      <c r="R15" s="6" t="n"/>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>100% (0 SF vacant)</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>12539259</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>11306000</v>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>R0083953.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>R0084233</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0084233, R0084262</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>3254 &amp; 3650 Fraser St (2 bldgs)</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>3254-3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co. (Attn J.C. Adams)</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (2 bldgs)</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (3-4 per bldg)</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="8" t="n">
+        <v>240987</v>
+      </c>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>100% both bldgs (Jun-2024)</t>
+        </is>
+      </c>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>2025 (SB 11-119 submission)</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Colliers (rent rolls)</t>
+        </is>
+      </c>
+      <c r="Y16" s="6" t="inlineStr">
+        <is>
+          <t>R0084233.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>R0084237</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0084237</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>01821-30-0-02-005</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse/Distribution</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Single→3 units (re-demised 2024)</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="8" t="n">
+        <v>156838</v>
+      </c>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>21% (CIP 32,556 SF; 124,282 SF vacant 6/30/24)</t>
+        </is>
+      </c>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>2025 (SB 11-119 submission)</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y17" s="6" t="inlineStr">
+        <is>
+          <t>R0084237.pdf</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2096,11 +2782,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actual tenants &amp; rent rolls (125 Bridge St, 5970 Marion) and proforma lease assumptions (tax appeals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Actual tenants &amp; rent rolls (125 Bridge St, 5970 Marion, I-25 Corp Center, Majestic, Fraser, 14501 E 35th) and proforma lease assumptions (tax appeals)</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3131,13 +3816,1966 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>460-550 E. 76th Ave 'I-25 Corporate Center' (R0070622-27) — WPC Corporate LLC  |  Rent Roll as of 12/31/2024 (Colliers). Monthly CAM col = operating-expense billing; tax/ins/admin billings in Notes.</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="20" t="n"/>
+      <c r="M27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>425-101-CU</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>B R Printers, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="n">
+        <v>14830.83</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <v>177969.96</v>
+      </c>
+      <c r="G28" s="16" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2016</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>108 mo</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="n">
+        <v>1244</v>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>22,302 SF; +RE tax $8,169/mo, other $226/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>425-201-CU</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Northglenn Winlectric</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="n">
+        <v>20626.67</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <v>247520.04</v>
+      </c>
+      <c r="G29" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2022</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>2/28/2030</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>95 mo</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="n">
+        <v>3816</v>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>61,880 SF; steps 5/1/25 $21,658 → 5/1/29 $25,783.33; +tax $9,591/mo, other $619/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>425-202,202B-CU</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>** VACANT **</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="16" t="n"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>76,733 SF vacant at 12/31/2024 (23.19% of NRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>425-202D-CU</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Denver Winair</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="n">
+        <v>5290.67</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>63488.04</v>
+      </c>
+      <c r="G31" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>1/1/2024</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>2/28/2030</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>74 mo</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="n">
+        <v>979</v>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>15,872 SF; steps 1/1/25 $5,555.20 → 1/1/29 $6,613.33; +tax $2,460/mo, other $159/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>425-301-CU</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Seed Westcom</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="n">
+        <v>7525.87</v>
+      </c>
+      <c r="F32" s="22" t="n">
+        <v>90310.44</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>10/1/2024</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>4/30/2026</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>19 mo</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="n">
+        <v>760</v>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>8,768 SF; step 5/1/25 $7,788.91; +tax $2,864/mo, other $88/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>425-302-CU</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Radica</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E33" s="22" t="n">
+        <v>15198.52</v>
+      </c>
+      <c r="F33" s="22" t="n">
+        <v>182382.24</v>
+      </c>
+      <c r="G33" s="16" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>11/1/2023</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>12/31/2028</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>62 mo</t>
+        </is>
+      </c>
+      <c r="K33" s="22" t="n">
+        <v>1714</v>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>19,717 SF; steps 1/1/25 $15,724.31 → 1/1/28 $17,449.55; +tax $6,439/mo, other $200/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>425-401-CU</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Kiosk Innovations Corporation</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E34" s="22" t="n">
+        <v>11227.5</v>
+      </c>
+      <c r="F34" s="22" t="n">
+        <v>134730</v>
+      </c>
+      <c r="G34" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>8/1/2018</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>7/31/2025</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>84 mo</t>
+        </is>
+      </c>
+      <c r="K34" s="22" t="n">
+        <v>1060</v>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>13,473 SF; +tax $2,889/mo, other $136/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>425-401A-CU</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>B R Printers, Inc.</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E35" s="22" t="n">
+        <v>12969.5</v>
+      </c>
+      <c r="F35" s="22" t="n">
+        <v>155634</v>
+      </c>
+      <c r="G35" s="16" t="n">
+        <v>7.98</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2016</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>108 mo</t>
+        </is>
+      </c>
+      <c r="K35" s="22" t="n">
+        <v>1532</v>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>19,503 SF; +tax $4,181/mo, other $197/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>425-402-CU</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Bella Restoration Services</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E36" s="22" t="n">
+        <v>8031.54</v>
+      </c>
+      <c r="F36" s="22" t="n">
+        <v>96378.48</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>7/1/2022</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2026</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>50 mo</t>
+        </is>
+      </c>
+      <c r="K36" s="22" t="n">
+        <v>892</v>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>11,352 SF; steps 7/1/25 $8,268.04, 7/1/26 $8,514.00; +tax $2,434/mo, other $115/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>425-502-CU</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Northglenn Winnelson</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E37" s="22" t="n">
+        <v>18728.5</v>
+      </c>
+      <c r="F37" s="22" t="n">
+        <v>224742</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>2/1/2017</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>3/15/2027</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>121 mo</t>
+        </is>
+      </c>
+      <c r="K37" s="22" t="n">
+        <v>2755</v>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>26,755 SF; steps 3/1/25 $18,958.65 → 4/1/26 $19,620.33; +tax $7,617/mo, other $271/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>425-504-CU</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Oak Tree Enterprise, LLC</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E38" s="22" t="n">
+        <v>5375.23</v>
+      </c>
+      <c r="F38" s="22" t="n">
+        <v>64502.76</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2023</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2026</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>34 mo</t>
+        </is>
+      </c>
+      <c r="K38" s="22" t="n">
+        <v>679</v>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>6,592 SF; step 6/1/25 $5,536.48; +tax $1,877/mo, other $67/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>425-505-CU</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Window World Inc.</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E39" s="22" t="n">
+        <v>4262.5</v>
+      </c>
+      <c r="F39" s="22" t="n">
+        <v>51150</v>
+      </c>
+      <c r="G39" s="16" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2019</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2026</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>84 mo</t>
+        </is>
+      </c>
+      <c r="K39" s="22" t="n">
+        <v>680</v>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>6,600 SF; step 4/1/25 $4,372.50; +tax $1,879/mo, other $67/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>425-602,602C-CU</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>North Denver Winair Co.</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E40" s="22" t="n">
+        <v>14080.41</v>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>168964.92</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>1/1/2021</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>12/31/2026</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>72 mo</t>
+        </is>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v>1571</v>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>20,086 SF (2 units; 602 from 2/1/2019); steps 2/1/25 $14,498.97, 2/1/26 $14,925.96; +tax $6,473/mo, other $203/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>425-603-CU</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Environmental Seed Westcom</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E41" s="22" t="n">
+        <v>18284.21</v>
+      </c>
+      <c r="F41" s="22" t="n">
+        <v>219410.52</v>
+      </c>
+      <c r="G41" s="16" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>5/1/2018</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>4/30/2026</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>96 mo</t>
+        </is>
+      </c>
+      <c r="K41" s="22" t="n">
+        <v>1669</v>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>21,302 SF; step 5/1/25 $18,923.27; +tax $6,870/mo, other $213/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center</t>
+        </is>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D42" s="13" t="n"/>
+      <c r="E42" s="23">
+        <f>SUM(E28:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="23">
+        <f>SUM(F28:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="13" t="n"/>
+      <c r="H42" s="13" t="n"/>
+      <c r="I42" s="13" t="n"/>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="23">
+        <f>SUM(K28:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="15" t="inlineStr">
+        <is>
+          <t>Printed roll totals: monthly $156,432 / annual $1,877,183; 330,935 SF total, 254,202 occupied, 76,733 vacant (23%). Avg rent $7.38 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>20901 E. 32nd Pkwy 'Majestic Commercenter' (R0083953) — WPC ABC LLC  |  Rent Roll as of 12/31/2024 (Colliers); 200,000 SF, 0% vacant</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="20" t="n"/>
+      <c r="K43" s="20" t="n"/>
+      <c r="L43" s="20" t="n"/>
+      <c r="M43" s="21" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>455-A-CU</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Zayo Group</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E44" s="22" t="n">
+        <v>16875</v>
+      </c>
+      <c r="F44" s="22" t="n">
+        <v>202500</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>5/1/2020</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>10/31/2027</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>90 mo</t>
+        </is>
+      </c>
+      <c r="K44" s="22" t="n">
+        <v>3004</v>
+      </c>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>50,000 SF; steps 11/1/25 $17,375, 11/1/26 $17,916.67; +RE tax $10,414/mo, other $674/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>455-B-CU</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Tritz Pallet</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E45" s="22" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F45" s="22" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2021</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>2/28/2025</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>47 mo</t>
+        </is>
+      </c>
+      <c r="K45" s="22" t="n">
+        <v>3008</v>
+      </c>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>50,000 SF; +tax $10,414/mo, other $674/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>455-C-CU</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Peco Pallet</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E46" s="22" t="n">
+        <v>16250</v>
+      </c>
+      <c r="F46" s="22" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G46" s="16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2020</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2030</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>120 mo</t>
+        </is>
+      </c>
+      <c r="K46" s="22" t="n">
+        <v>2994</v>
+      </c>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>50,000 SF; steps 4/1/25 $18,542 → 4/1/29 $21,042; +tax $10,414/mo, other $674/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>455-D-CU</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Tritz Pallet</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E47" s="22" t="n">
+        <v>15833</v>
+      </c>
+      <c r="F47" s="22" t="n">
+        <v>189996</v>
+      </c>
+      <c r="G47" s="16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>11/1/2019</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>2/28/2025</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>64 mo</t>
+        </is>
+      </c>
+      <c r="K47" s="22" t="n">
+        <v>2983</v>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>50,000 SF; +tax $10,414/mo, other $674/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="n"/>
+      <c r="E48" s="23">
+        <f>SUM(E44:E47)</f>
+        <v/>
+      </c>
+      <c r="F48" s="23">
+        <f>SUM(F44:F47)</f>
+        <v/>
+      </c>
+      <c r="G48" s="13" t="n"/>
+      <c r="H48" s="13" t="n"/>
+      <c r="I48" s="13" t="n"/>
+      <c r="J48" s="13" t="n"/>
+      <c r="K48" s="23">
+        <f>SUM(K44:K47)</f>
+        <v/>
+      </c>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="15" t="inlineStr">
+        <is>
+          <t>Printed roll totals: monthly $58,958 / annual $707,496; avg rent $3.54 PSF; avg recoverable expense $0.16 PSF other + $2.50 tax + $0.72 CAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>3254 Fraser St (R0084233/R0084262) — St. Paul Fire &amp; Marine  |  Rent Roll as of 6/30/2024 (Colliers); 119,200 SF, 0 vacant</t>
+        </is>
+      </c>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="20" t="n"/>
+      <c r="I49" s="20" t="n"/>
+      <c r="J49" s="20" t="n"/>
+      <c r="K49" s="20" t="n"/>
+      <c r="L49" s="20" t="n"/>
+      <c r="M49" s="21" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>8501-A-CU</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Safelite Fulfillment, Inc.</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="n">
+        <v>26137.5</v>
+      </c>
+      <c r="F50" s="22" t="n">
+        <v>313650</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2011</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>5/31/2026</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>181 mo</t>
+        </is>
+      </c>
+      <c r="K50" s="22" t="n">
+        <v>3806</v>
+      </c>
+      <c r="L50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>51,000 SF; step 6/1/25 $26,775; +RE tax $14,412/mo, other $785/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>8501-B-CU</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>ThyssenKrupp Materials NA Inc.</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E51" s="22" t="n">
+        <v>19452.33</v>
+      </c>
+      <c r="F51" s="22" t="n">
+        <v>233427.96</v>
+      </c>
+      <c r="G51" s="16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>11/1/2018</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>1/31/2029</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>123 mo</t>
+        </is>
+      </c>
+      <c r="K51" s="22" t="n">
+        <v>2600</v>
+      </c>
+      <c r="L51" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>34,840 SF; steps 2/1/25 $20,091.07 → 2/1/28 $22,094.37; +tax $9,846/mo, other $536/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>8501-C-CU</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>2M Company Inc</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="n">
+        <v>16263</v>
+      </c>
+      <c r="F52" s="22" t="n">
+        <v>195156</v>
+      </c>
+      <c r="G52" s="16" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2018</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>6/30/2025</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>87 mo</t>
+        </is>
+      </c>
+      <c r="K52" s="22" t="n">
+        <v>2489</v>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>33,360 SF; rent from 7/1/24 (printed $5.75 PSF reflects pre-7/2024 rent $15,985); +tax $9,427/mo, other $514/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>8501-LOT-CU</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>2M Company Inc (lot)</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="16" t="n"/>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2018</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>6/30/2025</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="n"/>
+      <c r="L53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>Yard/lot lease, no separate rent shown</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St</t>
+        </is>
+      </c>
+      <c r="B54" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="n"/>
+      <c r="E54" s="23">
+        <f>SUM(E50:E53)</f>
+        <v/>
+      </c>
+      <c r="F54" s="23">
+        <f>SUM(F50:F53)</f>
+        <v/>
+      </c>
+      <c r="G54" s="13" t="n"/>
+      <c r="H54" s="13" t="n"/>
+      <c r="I54" s="13" t="n"/>
+      <c r="J54" s="13" t="n"/>
+      <c r="K54" s="23">
+        <f>SUM(K50:K53)</f>
+        <v/>
+      </c>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="15" t="inlineStr">
+        <is>
+          <t>Monthly total $61,852.83 matches Dec-2024 income-statement base rent. FY2024 annualized base $742,234; prorated annual per roll $738,898.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>3650 Fraser St (R0084233/R0084262) — St. Paul Fire &amp; Marine  |  Rent Roll as of 6/30/2024 (Colliers); 121,787 SF, 0 vacant</t>
+        </is>
+      </c>
+      <c r="B55" s="20" t="n"/>
+      <c r="C55" s="20" t="n"/>
+      <c r="D55" s="20" t="n"/>
+      <c r="E55" s="20" t="n"/>
+      <c r="F55" s="20" t="n"/>
+      <c r="G55" s="20" t="n"/>
+      <c r="H55" s="20" t="n"/>
+      <c r="I55" s="20" t="n"/>
+      <c r="J55" s="20" t="n"/>
+      <c r="K55" s="20" t="n"/>
+      <c r="L55" s="20" t="n"/>
+      <c r="M55" s="21" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>8502-A-CU</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>Petco Animal Supplies, Inc.</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="n">
+        <v>21370.61</v>
+      </c>
+      <c r="F56" s="22" t="n">
+        <v>256447.32</v>
+      </c>
+      <c r="G56" s="16" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>5/1/2005</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2025</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>244 mo</t>
+        </is>
+      </c>
+      <c r="K56" s="22" t="n">
+        <v>2921</v>
+      </c>
+      <c r="L56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>40,513 SF; step 9/1/24 $22,012.06; +RE tax $11,375/mo, other $625/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>8502-B-CU</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>Emser Tile LLC</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>15188.38</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>182260.56</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>11/1/2009</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>1/31/2028</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>219 mo</t>
+        </is>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>1759</v>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>24,399 SF; steps 2/1/25 $15,635.69 → 2/1/27 $16,591.32; +tax $6,851/mo, other $376/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>8502-C-CU</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>Turbo Air Inc</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="n">
+        <v>14913.17</v>
+      </c>
+      <c r="F58" s="22" t="n">
+        <v>178958.04</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2014</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>7/31/2029</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>182 mo (extended)</t>
+        </is>
+      </c>
+      <c r="K58" s="22" t="n">
+        <v>1958</v>
+      </c>
+      <c r="L58" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>27,156 SF; extended from 7/31/2024; steps 8/1/24 $15,727.85 → 8/1/28 $18,058.74; +tax $7,625/mo, other $419/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>8502-D-CU</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>Assa Abloy Service Centers Inc</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>15330.05</v>
+      </c>
+      <c r="F59" s="22" t="n">
+        <v>183960.6</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>4/1/2014</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>6/30/2029</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>183 mo (extended)</t>
+        </is>
+      </c>
+      <c r="K59" s="22" t="n">
+        <v>2143</v>
+      </c>
+      <c r="L59" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>29,719 SF; extended from 6/30/2024; steps 7/1/24 $16,716.94 → 7/1/28 $18,995.39; +tax $8,344/mo, other $459/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n"/>
+      <c r="E60" s="23">
+        <f>SUM(E56:E59)</f>
+        <v/>
+      </c>
+      <c r="F60" s="23">
+        <f>SUM(F56:F59)</f>
+        <v/>
+      </c>
+      <c r="G60" s="13" t="n"/>
+      <c r="H60" s="13" t="n"/>
+      <c r="I60" s="13" t="n"/>
+      <c r="J60" s="13" t="n"/>
+      <c r="K60" s="23">
+        <f>SUM(K56:K59)</f>
+        <v/>
+      </c>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="15" t="inlineStr">
+        <is>
+          <t>Rents shown at 6/30/2024 step level; Dec-2024 income-statement base rent was $69,645.23/mo after 2024 steps took effect.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl (R0084237) — St. Paul Fire &amp; Marine  |  From Denver Industrial Portfolio rent rolls (Bldg 20); 156,838 SF</t>
+        </is>
+      </c>
+      <c r="B61" s="20" t="n"/>
+      <c r="C61" s="20" t="n"/>
+      <c r="D61" s="20" t="n"/>
+      <c r="E61" s="20" t="n"/>
+      <c r="F61" s="20" t="n"/>
+      <c r="G61" s="20" t="n"/>
+      <c r="H61" s="20" t="n"/>
+      <c r="I61" s="20" t="n"/>
+      <c r="J61" s="20" t="n"/>
+      <c r="K61" s="20" t="n"/>
+      <c r="L61" s="20" t="n"/>
+      <c r="M61" s="21" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>14501-100 (whole)</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Mountain States Logistics (Symbia Logistics)</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Lease (expired)</t>
+        </is>
+      </c>
+      <c r="E62" s="22" t="n">
+        <v>58160.76</v>
+      </c>
+      <c r="F62" s="22" t="n">
+        <v>697929.12</v>
+      </c>
+      <c r="G62" s="16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>3/1/2017</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2024</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>85 mo</t>
+        </is>
+      </c>
+      <c r="K62" s="22" t="n">
+        <v>4100</v>
+      </c>
+      <c r="L62" s="6" t="n">
+        <v>46870</v>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>156,838 SF; Dec-2023 roll; vacated at expiration. Monthly recoveries incl. RE tax $40,324 &amp; HVAC/R&amp;M billback $51,556.75; admin fee fixed $20,340/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>14501-300</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Colorado Industrial Packaging</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E63" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="16" t="n"/>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2029</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>63 mo / 1×60-mo opt @FMR</t>
+        </is>
+      </c>
+      <c r="K63" s="22" t="n">
+        <v>1844.84</v>
+      </c>
+      <c r="L63" s="6" t="n">
+        <v>33129</v>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>32,556 SF; base rent abated to 8/31/24, $6.90 PSF from 9/1/24 ($18,720/mo), steps to $8.20 PSF 6/1/29; +tax $8,763/mo; audit right 90 days</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. 35th Pl</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>14501-100 &amp; -400</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>** VACANT **</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="16" t="n"/>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="9" t="n"/>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>78,694 + 45,588 = 124,282 SF vacant at 6/30/2024 after re-demising</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A61:M61"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A49:M49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3149,7 +5787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3176,7 +5814,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,26 +6022,70 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>460-550 E 76th Ave (R0070622-27)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>47464870</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <v>143.43</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>32000000</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>500_E_76TH_AVE.pdf</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="21" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>20901 E 32nd Pkwy (R0083953)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>12539259</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>11306000</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>R0083953.pdf</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>B. Income-Approach Proformas</t>
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).  E 76th Ave: protest letter cites county value $44,788,554 &amp; owner opinion $32,000,000; 1st Net protest list shows $47,464,870 county / $21,725,000 1st Net value — all reproduced as printed.</t>
         </is>
       </c>
       <c r="B14" s="20" t="n"/>
@@ -3415,211 +6096,313 @@
       <c r="G14" s="20" t="n"/>
       <c r="H14" s="21" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1"/>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>B. Income-Approach Proformas</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="21" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>4832500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Dr</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>209100</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>-10455</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>198645</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>182753</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>3050000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>12260 Pennsylvania St</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>237290</v>
+        <v>359394</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>-16610</v>
+        <v>-17970</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>220680</v>
+        <v>341424</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-22068</v>
+        <v>-27314</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>198612</v>
+        <v>314110</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>2837000</v>
+        <v>4832500</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>6770 E. 56th Ave</t>
+          <t>17608 E. 24th Dr</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>115824</v>
+        <v>209100</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>-5791</v>
+        <v>-10455</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>110033</v>
+        <v>198645</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>-5502</v>
+        <v>-15892</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>104531</v>
+        <v>182753</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>1493302</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-16610</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>220680</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-22068</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>198612</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>2837000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>1493302</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B22" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C22" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D22" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E22" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F22" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G22" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H22" s="14" t="n">
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="21" t="n"/>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center (2024 actual)</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>2750538</v>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>2750538</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>-1279108</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>1471430</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>22637387</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center (stabilized)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>2442300</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-122115</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>2320185</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-185615</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>2134570</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>32839546</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter (2024)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>1361973</v>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>1361973</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>-627099</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>734874</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>11305758</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
+        <is>
+          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, 1st Net, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915). I-25 Corp Center (1st Net): 2024-actual approach caps net rental income $1,471,430 at 6.5% → $22,637,387; stabilized approach ($7.38 face rent, 5% vac, $0.08 exp) → $32,839,546 less lease-up costs $1,023,935 → FINAL indicated $31,815,611; sales grid selected $32,343,372. Majestic (1st Net): 2024 net income $734,874 at 6.5% → $11,305,758 (2024 mill levy 0.130073).</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +6414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +6438,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +6552,242 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct (TARA) — FY2023</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>211025.04</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>16850.27</v>
+      </c>
+      <c r="D9" s="23">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>R0048725 2023-24 P&amp;L (accrual; incl. mortgage interest)</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct (TARA) — FY2024</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>217426.64</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>32673.88</v>
+      </c>
+      <c r="D10" s="23">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>R0048725 P&amp;L (accrual; incl. $5,162.81 other interest expense)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center (460-550 E 76th) — FY2024</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>2750538.25</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>2601154.02</v>
+      </c>
+      <c r="D11" s="23">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt 12/31/24 (accrual; incl. interest, principal, TI/leasing &amp; capex)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter (20901 E 32nd) — FY2024</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>1361972.79</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>684100.1800000001</v>
+      </c>
+      <c r="D12" s="23">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt 12/31/24 (incl. lease commissions $71,251)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>1219707.89</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>569974.73</v>
+      </c>
+      <c r="D13" s="23">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt (expense incl. step-rent amort. &amp; capex $10,573)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>1346677.13</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>751187.25</v>
+      </c>
+      <c r="D14" s="23">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt (expense incl. capex $235,187; tax consulting $42,664)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n">
+        <v>1319987.26</v>
+      </c>
+      <c r="C15" s="22" t="n">
+        <v>557022.5600000001</v>
+      </c>
+      <c r="D15" s="23">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt (expense incl. capex $23,478)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n">
+        <v>1448378.72</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <v>865480.8100000001</v>
+      </c>
+      <c r="D16" s="23">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt (expense incl. capex $258,452; tax consulting $48,338)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>1286230.12</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>694108.6</v>
+      </c>
+      <c r="D17" s="23">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Yardi income stmt (accrual); net income $592,121.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>515250.99</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>586301.91</v>
+      </c>
+      <c r="D18" s="23">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Yardi income stmt; MSL vacated 3/31/24 → net loss $(71,050.92)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation; I-25 Corp Center, Fraser and Majestic statements include debt service and/or capital expenditures as printed, so they are cash-flow figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +6799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +6823,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5207,6 +8207,5938 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2023</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>40301 - Elm Ct Rental Income</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>211025.04</v>
+      </c>
+      <c r="E66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2023</t>
+        </is>
+      </c>
+      <c r="B67" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D67" s="23">
+        <f>SUM(D66:D66)</f>
+        <v/>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $211,025.04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2023</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>60100 - Bank Service Charges</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>841</v>
+      </c>
+      <c r="E68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2023</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>65015 - 9345 Elm Mortgage Interest</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="n">
+        <v>15436.77</v>
+      </c>
+      <c r="E69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2023</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>65063 - Elm Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>572.5</v>
+      </c>
+      <c r="E70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2023</t>
+        </is>
+      </c>
+      <c r="B71" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D71" s="23">
+        <f>SUM(D68:D70)</f>
+        <v/>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $16,850.27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>40301 - Elm Ct Rental Income</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="n">
+        <v>217426.64</v>
+      </c>
+      <c r="E72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D73" s="23">
+        <f>SUM(D72:D72)</f>
+        <v/>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $217,426.64.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>60100 - Bank Service Charges</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="n">
+        <v>1063.6</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>incl. First Bank fees $69</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>60120 - Computer &amp; Internet</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>1896.91</v>
+      </c>
+      <c r="E75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>64046 - Postage</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>327.57</v>
+      </c>
+      <c r="E76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>65015 - 9345 Elm Mortgage Interest</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>12961.72</v>
+      </c>
+      <c r="E77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>65040 - Professional &amp; Accounting Fees</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>65063 - Elm Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>10011.27</v>
+      </c>
+      <c r="E79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>75010 - Interest Expense (other)</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="n">
+        <v>5162.81</v>
+      </c>
+      <c r="E80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>9345/9335 Elm Ct — FY2024</t>
+        </is>
+      </c>
+      <c r="B81" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D81" s="23">
+        <f>SUM(D74:D80)</f>
+        <v/>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $32,673.88.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="n">
+        <v>1707354.9</v>
+      </c>
+      <c r="E82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>240778.65</v>
+      </c>
+      <c r="E83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>778902.12</v>
+      </c>
+      <c r="E84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>32364.45</v>
+      </c>
+      <c r="E85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B86" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Miscellaneous Income</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="n">
+        <v>-8861.870000000001</v>
+      </c>
+      <c r="E86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B87" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D87" s="23">
+        <f>SUM(D82:D86)</f>
+        <v/>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $2,750,538.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Electricity (recov)</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>56500.13</v>
+      </c>
+      <c r="E88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Storm Drainage (recov)</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>3730</v>
+      </c>
+      <c r="E89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>28627.1</v>
+      </c>
+      <c r="E90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Extermination (recov)</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>4445</v>
+      </c>
+      <c r="E91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Fire Protection/Security (recov)</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>23923.79</v>
+      </c>
+      <c r="E92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B93" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (recov)</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>11555.14</v>
+      </c>
+      <c r="E93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B94" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>23540.76</v>
+      </c>
+      <c r="E94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Grounds/Janitorial (recov)</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>20824.66</v>
+      </c>
+      <c r="E95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape/Sprinkler (recov)</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>19677.75</v>
+      </c>
+      <c r="E96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC (recov)</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>14118.37</v>
+      </c>
+      <c r="E97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>19761.37</v>
+      </c>
+      <c r="E98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>5850</v>
+      </c>
+      <c r="E99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>22947</v>
+      </c>
+      <c r="E100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Plumbing (recov)</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>475</v>
+      </c>
+      <c r="E101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B102" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>7778.98</v>
+      </c>
+      <c r="E102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>84658.78</v>
+      </c>
+      <c r="E103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>69.14</v>
+      </c>
+      <c r="E104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Other Direct Billable</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>-22482.64</v>
+      </c>
+      <c r="E105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>862190.26</v>
+      </c>
+      <c r="E106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>81761</v>
+      </c>
+      <c r="E107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>857474.03</v>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Miscellaneous Expense</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>3407.5</v>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Building (capital)</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>5749</v>
+      </c>
+      <c r="E110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>N/P Principal (Chase)</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>167912.77</v>
+      </c>
+      <c r="E111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Finish</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>147300</v>
+      </c>
+      <c r="E112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Lease Commission</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>149359.13</v>
+      </c>
+      <c r="E113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center — FY2024</t>
+        </is>
+      </c>
+      <c r="B114" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D114" s="23">
+        <f>SUM(D88:D113)</f>
+        <v/>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $2,601,154.02.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>698747.99</v>
+      </c>
+      <c r="E115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>143868</v>
+      </c>
+      <c r="E116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>499872</v>
+      </c>
+      <c r="E117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>32352</v>
+      </c>
+      <c r="E118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Prior-Year Reconciliations</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>-12867.2</v>
+      </c>
+      <c r="E119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B120" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D120" s="23">
+        <f>SUM(D115:D119)</f>
+        <v/>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,361,972.79.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>24928.96</v>
+      </c>
+      <c r="E121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>Extermination (recov)</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>Fire Protection/Security (recov)</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>4079.61</v>
+      </c>
+      <c r="E123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B124" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (recov)</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>4433.48</v>
+      </c>
+      <c r="E124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B125" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>310</v>
+      </c>
+      <c r="E125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B126" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape/Sprinkler (recov)</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="n">
+        <v>10960.97</v>
+      </c>
+      <c r="E126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B127" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC (recov)</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="n">
+        <v>5126.45</v>
+      </c>
+      <c r="E127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B128" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>14956.6</v>
+      </c>
+      <c r="E128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="n">
+        <v>75</v>
+      </c>
+      <c r="E129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B130" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>12925.25</v>
+      </c>
+      <c r="E130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="n">
+        <v>43037.28</v>
+      </c>
+      <c r="E131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n">
+        <v>423808.38</v>
+      </c>
+      <c r="E132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>65797</v>
+      </c>
+      <c r="E133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B134" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Miscellaneous Expense</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Lease Commission</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>71251.2</v>
+      </c>
+      <c r="E135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B136" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D136" s="23">
+        <f>SUM(D121:D135)</f>
+        <v/>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $684,100.18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>682842.54</v>
+      </c>
+      <c r="E137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B138" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expense Recovery</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="n">
+        <v>100596</v>
+      </c>
+      <c r="E138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B139" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expense Recovery - 3301</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="n">
+        <v>11100</v>
+      </c>
+      <c r="E139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B140" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="n">
+        <v>13884</v>
+      </c>
+      <c r="E140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>404173</v>
+      </c>
+      <c r="E141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B142" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>PY CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="n">
+        <v>6929.26</v>
+      </c>
+      <c r="E142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B143" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D143" s="22" t="n">
+        <v>183.09</v>
+      </c>
+      <c r="E143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B144" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D144" s="23">
+        <f>SUM(D137:D143)</f>
+        <v/>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,219,707.89.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B145" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>Electricity (recov)</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="n">
+        <v>622.9299999999999</v>
+      </c>
+      <c r="E145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B146" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="n">
+        <v>17210.76</v>
+      </c>
+      <c r="E146" s="6" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B147" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Contract</t>
+        </is>
+      </c>
+      <c r="D147" s="22" t="n">
+        <v>488.34</v>
+      </c>
+      <c r="E147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B148" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>6691.95</v>
+      </c>
+      <c r="E148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B149" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Other</t>
+        </is>
+      </c>
+      <c r="D149" s="22" t="n">
+        <v>515</v>
+      </c>
+      <c r="E149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B150" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>Trash Removal Contract (recov)</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="n">
+        <v>185</v>
+      </c>
+      <c r="E150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B151" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B152" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>Landscape Contract</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="n">
+        <v>8190</v>
+      </c>
+      <c r="E152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B153" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="n">
+        <v>7341.03</v>
+      </c>
+      <c r="E153" s="6" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B154" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>4760</v>
+      </c>
+      <c r="E154" s="6" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B155" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D155" s="22" t="n">
+        <v>1465</v>
+      </c>
+      <c r="E155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B156" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="n">
+        <v>12306</v>
+      </c>
+      <c r="E156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B157" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D157" s="22" t="n">
+        <v>7126.12</v>
+      </c>
+      <c r="E157" s="6" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B158" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>Trash Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="n">
+        <v>145</v>
+      </c>
+      <c r="E158" s="6" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B159" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D159" s="22" t="n">
+        <v>30519.97</v>
+      </c>
+      <c r="E159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B160" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B161" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>Vacant Lot Expense (non-recov)</t>
+        </is>
+      </c>
+      <c r="D161" s="22" t="n">
+        <v>13376.42</v>
+      </c>
+      <c r="E161" s="6" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B162" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="n">
+        <v>17617.11</v>
+      </c>
+      <c r="E162" s="6" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B163" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D163" s="22" t="n">
+        <v>404173</v>
+      </c>
+      <c r="E163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B164" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - Prior-Yr Adj</t>
+        </is>
+      </c>
+      <c r="D164" s="22" t="n">
+        <v>-11797.64</v>
+      </c>
+      <c r="E164" s="6" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B165" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>Step Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D165" s="22" t="n">
+        <v>35915.7</v>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B166" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>Consultation Fees - General</t>
+        </is>
+      </c>
+      <c r="D166" s="22" t="n">
+        <v>1150.44</v>
+      </c>
+      <c r="E166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B167" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Improvement (capital)</t>
+        </is>
+      </c>
+      <c r="D167" s="22" t="n">
+        <v>10572.6</v>
+      </c>
+      <c r="E167" s="6" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B168" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D168" s="23">
+        <f>SUM(D145:D167)</f>
+        <v/>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $569,974.73.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B169" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D169" s="22" t="n">
+        <v>717926.13</v>
+      </c>
+      <c r="E169" s="6" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B170" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expense Recovery</t>
+        </is>
+      </c>
+      <c r="D170" s="22" t="n">
+        <v>106740</v>
+      </c>
+      <c r="E170" s="6" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B171" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expense Recovery - 3301</t>
+        </is>
+      </c>
+      <c r="D171" s="22" t="n">
+        <v>11400</v>
+      </c>
+      <c r="E171" s="6" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B172" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D172" s="22" t="n">
+        <v>22020</v>
+      </c>
+      <c r="E172" s="6" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B173" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D173" s="22" t="n">
+        <v>404220</v>
+      </c>
+      <c r="E173" s="6" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B174" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>PY CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="n">
+        <v>101792.04</v>
+      </c>
+      <c r="E174" s="6" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B175" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt Allowance</t>
+        </is>
+      </c>
+      <c r="D175" s="22" t="n">
+        <v>-18750</v>
+      </c>
+      <c r="E175" s="6" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B176" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="n">
+        <v>1328.96</v>
+      </c>
+      <c r="E176" s="6" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B177" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D177" s="23">
+        <f>SUM(D169:D176)</f>
+        <v/>
+      </c>
+      <c r="E177" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,346,677.13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B178" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>Electricity (recov)</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="n">
+        <v>693.74</v>
+      </c>
+      <c r="E178" s="6" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B179" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D179" s="22" t="n">
+        <v>19369.95</v>
+      </c>
+      <c r="E179" s="6" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B180" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Contract</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="n">
+        <v>499.92</v>
+      </c>
+      <c r="E180" s="6" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B181" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D181" s="22" t="n">
+        <v>6360.79</v>
+      </c>
+      <c r="E181" s="6" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B182" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Other</t>
+        </is>
+      </c>
+      <c r="D182" s="22" t="n">
+        <v>665</v>
+      </c>
+      <c r="E182" s="6" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B183" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (recov)</t>
+        </is>
+      </c>
+      <c r="D183" s="22" t="n">
+        <v>706.73</v>
+      </c>
+      <c r="E183" s="6" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B184" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D184" s="22" t="n">
+        <v>4114</v>
+      </c>
+      <c r="E184" s="6" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B185" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>Landscape Contract</t>
+        </is>
+      </c>
+      <c r="D185" s="22" t="n">
+        <v>8514</v>
+      </c>
+      <c r="E185" s="6" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B186" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape</t>
+        </is>
+      </c>
+      <c r="D186" s="22" t="n">
+        <v>1490.37</v>
+      </c>
+      <c r="E186" s="6" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B187" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D187" s="22" t="n">
+        <v>630</v>
+      </c>
+      <c r="E187" s="6" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B188" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D188" s="22" t="n">
+        <v>1560</v>
+      </c>
+      <c r="E188" s="6" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B189" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="n">
+        <v>16477</v>
+      </c>
+      <c r="E189" s="6" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B190" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Painting (recov)</t>
+        </is>
+      </c>
+      <c r="D190" s="22" t="n">
+        <v>475</v>
+      </c>
+      <c r="E190" s="6" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B191" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D191" s="22" t="n">
+        <v>13659.8</v>
+      </c>
+      <c r="E191" s="6" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B192" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D192" s="22" t="n">
+        <v>31907.5</v>
+      </c>
+      <c r="E192" s="6" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B193" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D193" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E193" s="6" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B194" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>Vacant Lot Expense (non-recov)</t>
+        </is>
+      </c>
+      <c r="D194" s="22" t="n">
+        <v>7165.06</v>
+      </c>
+      <c r="E194" s="6" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B195" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D195" s="22" t="n">
+        <v>23743.77</v>
+      </c>
+      <c r="E195" s="6" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B196" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="n">
+        <v>357648.94</v>
+      </c>
+      <c r="E196" s="6" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B197" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - Prior-Yr Adj</t>
+        </is>
+      </c>
+      <c r="D197" s="22" t="n">
+        <v>-23279.04</v>
+      </c>
+      <c r="E197" s="6" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B198" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>Tax Consulting</t>
+        </is>
+      </c>
+      <c r="D198" s="22" t="n">
+        <v>42663.51</v>
+      </c>
+      <c r="E198" s="6" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B199" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>Step Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D199" s="22" t="n">
+        <v>-316.23</v>
+      </c>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B200" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>Consultation Fees - General</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="n">
+        <v>1150.44</v>
+      </c>
+      <c r="E200" s="6" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B201" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>Building (capital)</t>
+        </is>
+      </c>
+      <c r="D201" s="22" t="n">
+        <v>161240</v>
+      </c>
+      <c r="E201" s="6" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B202" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Improvement (capital)</t>
+        </is>
+      </c>
+      <c r="D202" s="22" t="n">
+        <v>35304</v>
+      </c>
+      <c r="E202" s="6" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B203" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>Roof (capital)</t>
+        </is>
+      </c>
+      <c r="D203" s="22" t="n">
+        <v>38643</v>
+      </c>
+      <c r="E203" s="6" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="11" t="inlineStr">
+        <is>
+          <t>3254 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B204" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D204" s="23">
+        <f>SUM(D178:D203)</f>
+        <v/>
+      </c>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $751,187.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B205" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D205" s="22" t="n">
+        <v>783130.39</v>
+      </c>
+      <c r="E205" s="6" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B206" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D206" s="22" t="n">
+        <v>97620</v>
+      </c>
+      <c r="E206" s="6" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B207" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D207" s="22" t="n">
+        <v>14196</v>
+      </c>
+      <c r="E207" s="6" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B208" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D208" s="22" t="n">
+        <v>410313</v>
+      </c>
+      <c r="E208" s="6" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B209" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>PY CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D209" s="22" t="n">
+        <v>14581.28</v>
+      </c>
+      <c r="E209" s="6" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B210" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C210" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D210" s="22" t="n">
+        <v>146.59</v>
+      </c>
+      <c r="E210" s="6" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B211" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D211" s="23">
+        <f>SUM(D205:D210)</f>
+        <v/>
+      </c>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,319,987.26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B212" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>Electricity (recov)</t>
+        </is>
+      </c>
+      <c r="D212" s="22" t="n">
+        <v>6226.85</v>
+      </c>
+      <c r="E212" s="6" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B213" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D213" s="22" t="n">
+        <v>21223.73</v>
+      </c>
+      <c r="E213" s="6" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B214" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Contract</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="n">
+        <v>488.34</v>
+      </c>
+      <c r="E214" s="6" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B215" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D215" s="22" t="n">
+        <v>4881.03</v>
+      </c>
+      <c r="E215" s="6" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B216" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Other</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="n">
+        <v>665</v>
+      </c>
+      <c r="E216" s="6" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B217" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>Trash Removal Contract (recov)</t>
+        </is>
+      </c>
+      <c r="D217" s="22" t="n">
+        <v>755</v>
+      </c>
+      <c r="E217" s="6" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B218" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (recov)</t>
+        </is>
+      </c>
+      <c r="D218" s="22" t="n">
+        <v>1381.61</v>
+      </c>
+      <c r="E218" s="6" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B219" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>Landscape Contract</t>
+        </is>
+      </c>
+      <c r="D219" s="22" t="n">
+        <v>6960</v>
+      </c>
+      <c r="E219" s="6" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B220" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape</t>
+        </is>
+      </c>
+      <c r="D220" s="22" t="n">
+        <v>4641.04</v>
+      </c>
+      <c r="E220" s="6" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B221" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>HVAC Contract</t>
+        </is>
+      </c>
+      <c r="D221" s="22" t="n">
+        <v>3072</v>
+      </c>
+      <c r="E221" s="6" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B222" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC</t>
+        </is>
+      </c>
+      <c r="D222" s="22" t="n">
+        <v>2289.53</v>
+      </c>
+      <c r="E222" s="6" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B223" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D223" s="22" t="n">
+        <v>3079.93</v>
+      </c>
+      <c r="E223" s="6" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B224" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D224" s="22" t="n">
+        <v>1310</v>
+      </c>
+      <c r="E224" s="6" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B225" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D225" s="22" t="n">
+        <v>12307.5</v>
+      </c>
+      <c r="E225" s="6" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B226" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Painting (recov)</t>
+        </is>
+      </c>
+      <c r="D226" s="22" t="n">
+        <v>450</v>
+      </c>
+      <c r="E226" s="6" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B227" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D227" s="22" t="n">
+        <v>1337.75</v>
+      </c>
+      <c r="E227" s="6" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B228" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D228" s="22" t="n">
+        <v>33020.31</v>
+      </c>
+      <c r="E228" s="6" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B229" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D229" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E229" s="6" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B230" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D230" s="22" t="n">
+        <v>17999.44</v>
+      </c>
+      <c r="E230" s="6" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B231" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D231" s="22" t="n">
+        <v>410301</v>
+      </c>
+      <c r="E231" s="6" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B232" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - Prior-Yr Adj</t>
+        </is>
+      </c>
+      <c r="D232" s="22" t="n">
+        <v>-11874.62</v>
+      </c>
+      <c r="E232" s="6" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B233" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>Step Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D233" s="22" t="n">
+        <v>11753.78</v>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B234" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>Consultation Fees - General</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="n">
+        <v>1175.41</v>
+      </c>
+      <c r="E234" s="6" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B235" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>Lease Commission (capital)</t>
+        </is>
+      </c>
+      <c r="D235" s="22" t="n">
+        <v>23477.93</v>
+      </c>
+      <c r="E235" s="6" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2023</t>
+        </is>
+      </c>
+      <c r="B236" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D236" s="23">
+        <f>SUM(D212:D235)</f>
+        <v/>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $557,022.56.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B237" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D237" s="22" t="n">
+        <v>816139.74</v>
+      </c>
+      <c r="E237" s="6" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B238" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D238" s="22" t="n">
+        <v>105372</v>
+      </c>
+      <c r="E238" s="6" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B239" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D239" s="22" t="n">
+        <v>22548</v>
+      </c>
+      <c r="E239" s="6" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B240" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D240" s="22" t="n">
+        <v>410340</v>
+      </c>
+      <c r="E240" s="6" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B241" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>PY CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D241" s="22" t="n">
+        <v>111725.19</v>
+      </c>
+      <c r="E241" s="6" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B242" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt Allowance</t>
+        </is>
+      </c>
+      <c r="D242" s="22" t="n">
+        <v>-18750</v>
+      </c>
+      <c r="E242" s="6" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B243" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D243" s="22" t="n">
+        <v>1003.79</v>
+      </c>
+      <c r="E243" s="6" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B244" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C244" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D244" s="23">
+        <f>SUM(D237:D243)</f>
+        <v/>
+      </c>
+      <c r="E244" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,448,378.72.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B245" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C245" s="6" t="inlineStr">
+        <is>
+          <t>Electricity (recov)</t>
+        </is>
+      </c>
+      <c r="D245" s="22" t="n">
+        <v>4819.59</v>
+      </c>
+      <c r="E245" s="6" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B246" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D246" s="22" t="n">
+        <v>31429.14</v>
+      </c>
+      <c r="E246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B247" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Contract</t>
+        </is>
+      </c>
+      <c r="D247" s="22" t="n">
+        <v>499.92</v>
+      </c>
+      <c r="E247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B248" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D248" s="22" t="n">
+        <v>2389.89</v>
+      </c>
+      <c r="E248" s="6" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B249" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C249" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Other</t>
+        </is>
+      </c>
+      <c r="D249" s="22" t="n">
+        <v>490</v>
+      </c>
+      <c r="E249" s="6" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B250" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (recov)</t>
+        </is>
+      </c>
+      <c r="D250" s="22" t="n">
+        <v>6350.08</v>
+      </c>
+      <c r="E250" s="6" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B251" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D251" s="22" t="n">
+        <v>9842.09</v>
+      </c>
+      <c r="E251" s="6" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B252" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>Landscape Contract</t>
+        </is>
+      </c>
+      <c r="D252" s="22" t="n">
+        <v>7238</v>
+      </c>
+      <c r="E252" s="6" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B253" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape</t>
+        </is>
+      </c>
+      <c r="D253" s="22" t="n">
+        <v>10264.6</v>
+      </c>
+      <c r="E253" s="6" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B254" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>HVAC Contract</t>
+        </is>
+      </c>
+      <c r="D254" s="22" t="n">
+        <v>3156</v>
+      </c>
+      <c r="E254" s="6" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B255" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C255" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC</t>
+        </is>
+      </c>
+      <c r="D255" s="22" t="n">
+        <v>3631.17</v>
+      </c>
+      <c r="E255" s="6" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B256" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C256" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D256" s="22" t="n">
+        <v>8279.959999999999</v>
+      </c>
+      <c r="E256" s="6" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B257" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C257" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D257" s="22" t="n">
+        <v>1440</v>
+      </c>
+      <c r="E257" s="6" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B258" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C258" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D258" s="22" t="n">
+        <v>16921</v>
+      </c>
+      <c r="E258" s="6" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B259" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C259" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Painting (recov)</t>
+        </is>
+      </c>
+      <c r="D259" s="22" t="n">
+        <v>450</v>
+      </c>
+      <c r="E259" s="6" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B260" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C260" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D260" s="22" t="n">
+        <v>15510.31</v>
+      </c>
+      <c r="E260" s="6" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B261" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C261" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D261" s="22" t="n">
+        <v>33877.02</v>
+      </c>
+      <c r="E261" s="6" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B262" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C262" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D262" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E262" s="6" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B263" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C263" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D263" s="22" t="n">
+        <v>24259.11</v>
+      </c>
+      <c r="E263" s="6" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B264" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C264" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D264" s="22" t="n">
+        <v>393558.59</v>
+      </c>
+      <c r="E264" s="6" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B265" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C265" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - Prior-Yr Adj</t>
+        </is>
+      </c>
+      <c r="D265" s="22" t="n">
+        <v>-22760.66</v>
+      </c>
+      <c r="E265" s="6" t="n"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B266" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C266" s="6" t="inlineStr">
+        <is>
+          <t>Tax Consulting</t>
+        </is>
+      </c>
+      <c r="D266" s="22" t="n">
+        <v>48337.51</v>
+      </c>
+      <c r="E266" s="6" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B267" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C267" s="6" t="inlineStr">
+        <is>
+          <t>Step Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D267" s="22" t="n">
+        <v>5770.36</v>
+      </c>
+      <c r="E267" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B268" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C268" s="6" t="inlineStr">
+        <is>
+          <t>Consultation Fees - General</t>
+        </is>
+      </c>
+      <c r="D268" s="22" t="n">
+        <v>1175.41</v>
+      </c>
+      <c r="E268" s="6" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B269" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C269" s="6" t="inlineStr">
+        <is>
+          <t>Building (capital)</t>
+        </is>
+      </c>
+      <c r="D269" s="22" t="n">
+        <v>72550</v>
+      </c>
+      <c r="E269" s="6" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B270" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C270" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Improvement (capital)</t>
+        </is>
+      </c>
+      <c r="D270" s="22" t="n">
+        <v>54232.59</v>
+      </c>
+      <c r="E270" s="6" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B271" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C271" s="6" t="inlineStr">
+        <is>
+          <t>Lease Commission (capital)</t>
+        </is>
+      </c>
+      <c r="D271" s="22" t="n">
+        <v>89685.63</v>
+      </c>
+      <c r="E271" s="6" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="6" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B272" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C272" s="6" t="inlineStr">
+        <is>
+          <t>Roof (capital)</t>
+        </is>
+      </c>
+      <c r="D272" s="22" t="n">
+        <v>41983.5</v>
+      </c>
+      <c r="E272" s="6" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="11" t="inlineStr">
+        <is>
+          <t>3650 Fraser St — FY2024</t>
+        </is>
+      </c>
+      <c r="B273" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C273" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D273" s="23">
+        <f>SUM(D245:D272)</f>
+        <v/>
+      </c>
+      <c r="E273" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $865,480.81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B274" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C274" s="6" t="inlineStr">
+        <is>
+          <t>4110 - Base Rent Income - Industrial/Warehouse</t>
+        </is>
+      </c>
+      <c r="D274" s="22" t="n">
+        <v>694008.16</v>
+      </c>
+      <c r="E274" s="6" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B275" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C275" s="6" t="inlineStr">
+        <is>
+          <t>4210 - FASB 13 Rent</t>
+        </is>
+      </c>
+      <c r="D275" s="22" t="n">
+        <v>-78624.52</v>
+      </c>
+      <c r="E275" s="6" t="n"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B276" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C276" s="6" t="inlineStr">
+        <is>
+          <t>4301 - CAM Recovery</t>
+        </is>
+      </c>
+      <c r="D276" s="22" t="n">
+        <v>45408.23</v>
+      </c>
+      <c r="E276" s="6" t="n"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B277" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C277" s="6" t="inlineStr">
+        <is>
+          <t>4318 - Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D277" s="22" t="n">
+        <v>482079.21</v>
+      </c>
+      <c r="E277" s="6" t="n"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B278" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C278" s="6" t="inlineStr">
+        <is>
+          <t>4321 - Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D278" s="22" t="n">
+        <v>22931.18</v>
+      </c>
+      <c r="E278" s="6" t="n"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B279" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C279" s="6" t="inlineStr">
+        <is>
+          <t>4365 - HVAC Overtime Recovery</t>
+        </is>
+      </c>
+      <c r="D279" s="22" t="n">
+        <v>86832.62</v>
+      </c>
+      <c r="E279" s="6" t="n"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B280" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C280" s="6" t="inlineStr">
+        <is>
+          <t>4510 - Administrative Fee</t>
+        </is>
+      </c>
+      <c r="D280" s="22" t="n">
+        <v>20340</v>
+      </c>
+      <c r="E280" s="6" t="n"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B281" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C281" s="6" t="inlineStr">
+        <is>
+          <t>4630 - Late Fee Income</t>
+        </is>
+      </c>
+      <c r="D281" s="22" t="n">
+        <v>13255.24</v>
+      </c>
+      <c r="E281" s="6" t="n"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="11" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B282" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C282" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D282" s="23">
+        <f>SUM(D274:D281)</f>
+        <v/>
+      </c>
+      <c r="E282" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,286,230.12.</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B283" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C283" s="6" t="inlineStr">
+        <is>
+          <t>5033 - R&amp;M HVAC</t>
+        </is>
+      </c>
+      <c r="D283" s="22" t="n">
+        <v>83432.53999999999</v>
+      </c>
+      <c r="E283" s="6" t="n"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B284" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C284" s="6" t="inlineStr">
+        <is>
+          <t>5037 - R&amp;M HVAC Contract</t>
+        </is>
+      </c>
+      <c r="D284" s="22" t="n">
+        <v>1600.08</v>
+      </c>
+      <c r="E284" s="6" t="n"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B285" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C285" s="6" t="inlineStr">
+        <is>
+          <t>5038 - R&amp;M HVAC Air Filters</t>
+        </is>
+      </c>
+      <c r="D285" s="22" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E285" s="6" t="n"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B286" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C286" s="6" t="inlineStr">
+        <is>
+          <t>5049 - R&amp;M Misc Repairs Exterior</t>
+        </is>
+      </c>
+      <c r="D286" s="22" t="n">
+        <v>8540</v>
+      </c>
+      <c r="E286" s="6" t="n"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B287" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C287" s="6" t="inlineStr">
+        <is>
+          <t>5082 - R&amp;M Roof Repair</t>
+        </is>
+      </c>
+      <c r="D287" s="22" t="n">
+        <v>2900</v>
+      </c>
+      <c r="E287" s="6" t="n"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B288" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C288" s="6" t="inlineStr">
+        <is>
+          <t>5100 - Landscape Contract Service</t>
+        </is>
+      </c>
+      <c r="D288" s="22" t="n">
+        <v>32200.23</v>
+      </c>
+      <c r="E288" s="6" t="n"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B289" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C289" s="6" t="inlineStr">
+        <is>
+          <t>5575 - R&amp;M Striping (parking)</t>
+        </is>
+      </c>
+      <c r="D289" s="22" t="n">
+        <v>1768</v>
+      </c>
+      <c r="E289" s="6" t="n"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B290" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C290" s="6" t="inlineStr">
+        <is>
+          <t>5901 - Insurance</t>
+        </is>
+      </c>
+      <c r="D290" s="22" t="n">
+        <v>22931.18</v>
+      </c>
+      <c r="E290" s="6" t="n"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B291" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C291" s="6" t="inlineStr">
+        <is>
+          <t>5950 - Real Estate Tax</t>
+        </is>
+      </c>
+      <c r="D291" s="22" t="n">
+        <v>482079.19</v>
+      </c>
+      <c r="E291" s="6" t="n"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B292" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C292" s="6" t="inlineStr">
+        <is>
+          <t>6040 - R&amp;M Other - N/R</t>
+        </is>
+      </c>
+      <c r="D292" s="22" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E292" s="6" t="n"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B293" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C293" s="6" t="inlineStr">
+        <is>
+          <t>6600 - Management Fees - N/R</t>
+        </is>
+      </c>
+      <c r="D293" s="22" t="n">
+        <v>34717.9</v>
+      </c>
+      <c r="E293" s="6" t="n"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B294" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C294" s="6" t="inlineStr">
+        <is>
+          <t>6611 - Admin Bank Charges - N/R</t>
+        </is>
+      </c>
+      <c r="D294" s="22" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E294" s="6" t="n"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B295" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C295" s="6" t="inlineStr">
+        <is>
+          <t>6640 - Admin Mileage Reimb. - N/R</t>
+        </is>
+      </c>
+      <c r="D295" s="22" t="n">
+        <v>1317.11</v>
+      </c>
+      <c r="E295" s="6" t="n"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B296" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C296" s="6" t="inlineStr">
+        <is>
+          <t>6653 - Admin Postage - N/R</t>
+        </is>
+      </c>
+      <c r="D296" s="22" t="n">
+        <v>37.66</v>
+      </c>
+      <c r="E296" s="6" t="n"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B297" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C297" s="6" t="inlineStr">
+        <is>
+          <t>6656 - Admin Professional Fee - N/R</t>
+        </is>
+      </c>
+      <c r="D297" s="22" t="n">
+        <v>606.75</v>
+      </c>
+      <c r="E297" s="6" t="n"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B298" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C298" s="6" t="inlineStr">
+        <is>
+          <t>6700 - Leasing &amp; Marketing - N/R</t>
+        </is>
+      </c>
+      <c r="D298" s="22" t="n">
+        <v>275.31</v>
+      </c>
+      <c r="E298" s="6" t="n"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B299" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C299" s="6" t="inlineStr">
+        <is>
+          <t>6770 - Space Planning - N/R</t>
+        </is>
+      </c>
+      <c r="D299" s="22" t="n">
+        <v>18359.88</v>
+      </c>
+      <c r="E299" s="6" t="n"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="11" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B300" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C300" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D300" s="23">
+        <f>SUM(D283:D299)</f>
+        <v/>
+      </c>
+      <c r="E300" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $694,108.60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B301" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C301" s="6" t="inlineStr">
+        <is>
+          <t>4110 - Base Rent Income - Industrial/Warehouse</t>
+        </is>
+      </c>
+      <c r="D301" s="22" t="n">
+        <v>305520.18</v>
+      </c>
+      <c r="E301" s="6" t="n"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B302" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C302" s="6" t="inlineStr">
+        <is>
+          <t>4175 - Rent Concessions/Incentives</t>
+        </is>
+      </c>
+      <c r="D302" s="22" t="n">
+        <v>-56159.1</v>
+      </c>
+      <c r="E302" s="6" t="inlineStr">
+        <is>
+          <t>CIP abatement</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B303" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C303" s="6" t="inlineStr">
+        <is>
+          <t>4210 - FASB 13 Rent</t>
+        </is>
+      </c>
+      <c r="D303" s="22" t="n">
+        <v>39502.02</v>
+      </c>
+      <c r="E303" s="6" t="n"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B304" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C304" s="6" t="inlineStr">
+        <is>
+          <t>4301 - CAM Recovery</t>
+        </is>
+      </c>
+      <c r="D304" s="22" t="n">
+        <v>35441.08</v>
+      </c>
+      <c r="E304" s="6" t="n"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B305" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C305" s="6" t="inlineStr">
+        <is>
+          <t>4318 - Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D305" s="22" t="n">
+        <v>161732.35</v>
+      </c>
+      <c r="E305" s="6" t="n"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B306" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C306" s="6" t="inlineStr">
+        <is>
+          <t>4321 - Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D306" s="22" t="n">
+        <v>12485.59</v>
+      </c>
+      <c r="E306" s="6" t="n"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B307" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C307" s="6" t="inlineStr">
+        <is>
+          <t>4365 - HVAC Overtime Recovery</t>
+        </is>
+      </c>
+      <c r="D307" s="22" t="n">
+        <v>14386.54</v>
+      </c>
+      <c r="E307" s="6" t="n"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B308" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C308" s="6" t="inlineStr">
+        <is>
+          <t>4429 - Tax Recovery - Prior Year</t>
+        </is>
+      </c>
+      <c r="D308" s="22" t="n">
+        <v>-40958.91</v>
+      </c>
+      <c r="E308" s="6" t="n"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B309" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C309" s="6" t="inlineStr">
+        <is>
+          <t>4453 - HVAC Recovery - Prior Year</t>
+        </is>
+      </c>
+      <c r="D309" s="22" t="n">
+        <v>2636.1</v>
+      </c>
+      <c r="E309" s="6" t="n"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B310" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C310" s="6" t="inlineStr">
+        <is>
+          <t>4510 - Administrative Fee</t>
+        </is>
+      </c>
+      <c r="D310" s="22" t="n">
+        <v>15281.91</v>
+      </c>
+      <c r="E310" s="6" t="n"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B311" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C311" s="6" t="inlineStr">
+        <is>
+          <t>4590 - Interest Income</t>
+        </is>
+      </c>
+      <c r="D311" s="22" t="n">
+        <v>13681.85</v>
+      </c>
+      <c r="E311" s="6" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B312" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C312" s="6" t="inlineStr">
+        <is>
+          <t>4630 - Late Fee Income</t>
+        </is>
+      </c>
+      <c r="D312" s="22" t="n">
+        <v>11701.38</v>
+      </c>
+      <c r="E312" s="6" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="11" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B313" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C313" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D313" s="23">
+        <f>SUM(D301:D312)</f>
+        <v/>
+      </c>
+      <c r="E313" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $515,250.99.</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B314" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C314" s="6" t="inlineStr">
+        <is>
+          <t>5033 - R&amp;M HVAC</t>
+        </is>
+      </c>
+      <c r="D314" s="22" t="n">
+        <v>15632.05</v>
+      </c>
+      <c r="E314" s="6" t="n"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B315" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C315" s="6" t="inlineStr">
+        <is>
+          <t>5037 - R&amp;M HVAC Contract</t>
+        </is>
+      </c>
+      <c r="D315" s="22" t="n">
+        <v>6017.59</v>
+      </c>
+      <c r="E315" s="6" t="n"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B316" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C316" s="6" t="inlineStr">
+        <is>
+          <t>5038 - R&amp;M HVAC Air Filters</t>
+        </is>
+      </c>
+      <c r="D316" s="22" t="n">
+        <v>1894.68</v>
+      </c>
+      <c r="E316" s="6" t="n"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B317" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C317" s="6" t="inlineStr">
+        <is>
+          <t>5049 - R&amp;M Misc Repairs Exterior</t>
+        </is>
+      </c>
+      <c r="D317" s="22" t="n">
+        <v>11796.22</v>
+      </c>
+      <c r="E317" s="6" t="n"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B318" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C318" s="6" t="inlineStr">
+        <is>
+          <t>5078 - R&amp;M Plumbing</t>
+        </is>
+      </c>
+      <c r="D318" s="22" t="n">
+        <v>470</v>
+      </c>
+      <c r="E318" s="6" t="n"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B319" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C319" s="6" t="inlineStr">
+        <is>
+          <t>5082 - R&amp;M Roof Repair</t>
+        </is>
+      </c>
+      <c r="D319" s="22" t="n">
+        <v>13425</v>
+      </c>
+      <c r="E319" s="6" t="n"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B320" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C320" s="6" t="inlineStr">
+        <is>
+          <t>5100 - Landscape Contract Service</t>
+        </is>
+      </c>
+      <c r="D320" s="22" t="n">
+        <v>16464.17</v>
+      </c>
+      <c r="E320" s="6" t="n"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B321" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C321" s="6" t="inlineStr">
+        <is>
+          <t>5165 - Snow Removal</t>
+        </is>
+      </c>
+      <c r="D321" s="22" t="n">
+        <v>1816.5</v>
+      </c>
+      <c r="E321" s="6" t="n"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B322" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C322" s="6" t="inlineStr">
+        <is>
+          <t>5300 - Security &amp; Safety</t>
+        </is>
+      </c>
+      <c r="D322" s="22" t="n">
+        <v>1976.03</v>
+      </c>
+      <c r="E322" s="6" t="n"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B323" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C323" s="6" t="inlineStr">
+        <is>
+          <t>5335 - Fire Safety R&amp;M</t>
+        </is>
+      </c>
+      <c r="D323" s="22" t="n">
+        <v>11106.48</v>
+      </c>
+      <c r="E323" s="6" t="n"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B324" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C324" s="6" t="inlineStr">
+        <is>
+          <t>5405 - Electric</t>
+        </is>
+      </c>
+      <c r="D324" s="22" t="n">
+        <v>1642.67</v>
+      </c>
+      <c r="E324" s="6" t="n"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B325" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C325" s="6" t="inlineStr">
+        <is>
+          <t>5411 - Water</t>
+        </is>
+      </c>
+      <c r="D325" s="22" t="n">
+        <v>4376.5</v>
+      </c>
+      <c r="E325" s="6" t="n"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B326" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C326" s="6" t="inlineStr">
+        <is>
+          <t>5570 - R&amp;M Lights (parking)</t>
+        </is>
+      </c>
+      <c r="D326" s="22" t="n">
+        <v>683.5599999999999</v>
+      </c>
+      <c r="E326" s="6" t="n"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B327" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C327" s="6" t="inlineStr">
+        <is>
+          <t>5580 - R&amp;M Sweeping (parking)</t>
+        </is>
+      </c>
+      <c r="D327" s="22" t="n">
+        <v>990</v>
+      </c>
+      <c r="E327" s="6" t="n"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B328" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C328" s="6" t="inlineStr">
+        <is>
+          <t>5901 - Insurance</t>
+        </is>
+      </c>
+      <c r="D328" s="22" t="n">
+        <v>33646.02</v>
+      </c>
+      <c r="E328" s="6" t="n"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B329" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C329" s="6" t="inlineStr">
+        <is>
+          <t>5950 - Real Estate Tax</t>
+        </is>
+      </c>
+      <c r="D329" s="22" t="n">
+        <v>393251.78</v>
+      </c>
+      <c r="E329" s="6" t="n"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B330" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C330" s="6" t="inlineStr">
+        <is>
+          <t>5990 - Other Taxes</t>
+        </is>
+      </c>
+      <c r="D330" s="22" t="n">
+        <v>4976.01</v>
+      </c>
+      <c r="E330" s="6" t="n"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B331" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C331" s="6" t="inlineStr">
+        <is>
+          <t>6003 - R&amp;M HVAC - N/R</t>
+        </is>
+      </c>
+      <c r="D331" s="22" t="n">
+        <v>9812.48</v>
+      </c>
+      <c r="E331" s="6" t="n"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B332" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C332" s="6" t="inlineStr">
+        <is>
+          <t>6040 - R&amp;M Other - N/R</t>
+        </is>
+      </c>
+      <c r="D332" s="22" t="n">
+        <v>12124.31</v>
+      </c>
+      <c r="E332" s="6" t="n"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B333" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C333" s="6" t="inlineStr">
+        <is>
+          <t>6470 - Utilities Other - N/R</t>
+        </is>
+      </c>
+      <c r="D333" s="22" t="n">
+        <v>26285.83</v>
+      </c>
+      <c r="E333" s="6" t="n"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B334" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C334" s="6" t="inlineStr">
+        <is>
+          <t>6600 - Management Fees - N/R</t>
+        </is>
+      </c>
+      <c r="D334" s="22" t="n">
+        <v>14230.6</v>
+      </c>
+      <c r="E334" s="6" t="n"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B335" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C335" s="6" t="inlineStr">
+        <is>
+          <t>6634 - Admin Legal - N/R</t>
+        </is>
+      </c>
+      <c r="D335" s="22" t="n">
+        <v>1454.04</v>
+      </c>
+      <c r="E335" s="6" t="n"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B336" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C336" s="6" t="inlineStr">
+        <is>
+          <t>6640 - Admin Mileage Reimb. - N/R</t>
+        </is>
+      </c>
+      <c r="D336" s="22" t="n">
+        <v>601.3</v>
+      </c>
+      <c r="E336" s="6" t="n"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B337" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C337" s="6" t="inlineStr">
+        <is>
+          <t>6653 - Admin Postage - N/R</t>
+        </is>
+      </c>
+      <c r="D337" s="22" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="E337" s="6" t="n"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B338" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C338" s="6" t="inlineStr">
+        <is>
+          <t>6656 - Admin Professional Fee - N/R</t>
+        </is>
+      </c>
+      <c r="D338" s="22" t="n">
+        <v>606.75</v>
+      </c>
+      <c r="E338" s="6" t="n"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B339" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C339" s="6" t="inlineStr">
+        <is>
+          <t>6700 - Leasing &amp; Marketing - N/R</t>
+        </is>
+      </c>
+      <c r="D339" s="22" t="n">
+        <v>983.58</v>
+      </c>
+      <c r="E339" s="6" t="n"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="6" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B340" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C340" s="6" t="inlineStr">
+        <is>
+          <t>6770 - Space Planning - N/R</t>
+        </is>
+      </c>
+      <c r="D340" s="22" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="E340" s="6" t="n"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="11" t="inlineStr">
+        <is>
+          <t>14501 E 35th Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B341" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C341" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D341" s="23">
+        <f>SUM(D314:D340)</f>
+        <v/>
+      </c>
+      <c r="E341" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $586,301.91.</t>
         </is>
       </c>
     </row>
@@ -5225,7 +14157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5245,11 +14177,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>North Side Gardens LLC portfolio — parcel schedule attached to the 7205 Gilpin Way (R0178308) appeal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Co-listed parcel schedules attached to the appeals (North Side Gardens portfolio; WPC / 1st Net Exhibit A; St. Paul Fraser accounts)</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,23 +14316,238 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>R0070624</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>460 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager).</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>R0070625</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>470 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>R0070626</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>480 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>R0070627</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>490 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>R0070622</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>500 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>WPC Corporate LLC</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>R0070623</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>550 E. 76th Ave</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>R0084233</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>3254-3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>R0084262</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>3254-3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager).  WPC/1st Net Exhibit A additionally lists 37 parcels across Adams, Arapahoe, Boulder, Denver &amp; Jefferson counties under related WPC/Watumull entities (incl. 20901 E 32nd Pkwy R0083953, 9500 E 104th Ave R0075306, 6100 E 49th Dr R0092694, 6701 E 50th Ave R0181935/R0092711, 6800 Broadway St R0142131-32); only appeal subjects are broken out above.</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -183,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -269,6 +269,9 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +638,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -656,7 +659,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-08-03  |  13 subject properties, all Adams County, Colorado</t>
+          <t>Prepared for Carter Equities  |  Updated 2026-08-03  |  20 subject properties, all Adams County, Colorado</t>
         </is>
       </c>
     </row>
@@ -1119,42 +1122,261 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>R0103791.pdf</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Appeal of Real Property Valuation (2023) + income approach + IRS 8825s (2021-22) + rent rolls 2019-22 (scanned)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — Arakouzo LLP</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2019-2022; appeal TY2023</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Property Tax Advisors, Inc. / owner (R. Soued)</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>R0084249.pdf</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Cover letter (SB 11-119) + income statements + rent rolls</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>FY2023-FY2024</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates / Colliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>R0084250.pdf + R0084250_2.pdf</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll (as of 6/30/2024) + FY2024 income statement (Yardi, Prior-Owner book)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St (bt42569)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>(owner not stated in docs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>R0084253.pdf + R00842532.pdf</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Rent roll 14509 E 33rd Pl (bt46265, as of 1/1/2024) + FY2024 income statement 14705 E 33rd Pl (bt46267)</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>14509 &amp; 14705 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>(owner not stated in docs; RCM/Yardi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>R0084262.pdf</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>DUPLICATE of R0084233.pdf (3254 &amp; 3650 Fraser St package) — no new data extracted</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>3254 &amp; 3650 Fraser St</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>FY2023-FY2024</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates / Colliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>R0084268.pdf</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Valuation protest — income approach + rent roll (scanned)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. Moncrieff Pl — Peterson Moncrieff LLC</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>protest 5/22/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services (D. George)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>R0086203.pdf</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal — income-approach proforma + salient facts</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>2420 Uravan St 'Aurora - Uravan' — Wagner Equipment Co.</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (J. Hoffman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>St. Paul rent rolls cover the full 17-building 'Denver Industrial Portfolio'; only subject-building (14501 E 35th Pl) leases are stored in Tenants &amp; Leases. CoStar sales-comp pages in the 1st Net protests are out of scope and not stored. 3254/3650 Fraser 'Total Expense' figures include capital expenditures as printed. E 76th Ave county value: protest letter shows $44,788,554; the income-approach sheet and 1st Net protest list show 2025 county value $47,464,870 — both reproduced as printed.</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Batch-3 notes: 3250 Abilene &amp; 14705 E 33rd income statements display whole dollars and carry a source inconsistency (the [NB] Gas Vacancy line is included in the printed Direct-Billable subtotal but excluded from the Property-Operating rollup); their subtotals are entered as printed values, not formulas. R0084253.pdf contains the 14509 E 33rd Pl rent roll while its companion upload R00842532.pdf is the 14705 E 33rd Pl income statement — treated as two properties. 14501 E Moncrieff: rent roll shows 53,200 SF vs 52,606 SF in the 1st Net income approach; both as printed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A24:F24"/>
+  <mergeCells count="7">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1166,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2738,6 +2960,743 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>R0103791</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0103791</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>R0103791</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave (Arakouzo)</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>80216</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Arakouzo LLP (Robert Soued, Mgr)</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Arakouzo</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse/Bakery</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (NNN)</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="8" t="n">
+        <v>30965</v>
+      </c>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>100% (Harlan Bakeries)</t>
+        </is>
+      </c>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>2023 (appeal)</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>2899541</v>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>R0103791.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>R0084249</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>R0084249</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>01821-30-0-04-010</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>St. Paul Fire and Marine Insurance Co.</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (5 units)</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="8" t="n">
+        <v>117329</v>
+      </c>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>100% (0 SF vacant)</t>
+        </is>
+      </c>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>2025 (SB 11-119 submission)</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y19" s="6" t="inlineStr">
+        <is>
+          <t>R0084249.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>R0084250</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>R0084250</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>bt42569</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>(not stated; Yardi Prior-Owner book)</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>3 units (1 occupied)</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="8" t="n">
+        <v>231842</v>
+      </c>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>30% (161,638 SF vacant 6/30/24)</t>
+        </is>
+      </c>
+      <c r="U20" s="9" t="n"/>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y20" s="6" t="inlineStr">
+        <is>
+          <t>R0084250.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>R0084253</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>R0084253</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>bt46265</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>(not stated; RCM rent roll)</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (5 units)</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="8" t="n">
+        <v>151485</v>
+      </c>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>100% (0 SF vacant 1/1/24)</t>
+        </is>
+      </c>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y21" s="6" t="inlineStr">
+        <is>
+          <t>R0084253.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>(not stated)</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>bt46267</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>14705 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>14705 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>(not stated; Yardi Prior-Owner book)</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
+        <is>
+          <t>R00842532.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>R0084268</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>R0084268</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. Moncrieff Pl</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. Moncrieff Pl</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Peterson Moncrieff LLC</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Peterson Moncrieff LLC</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse/Distribution</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (NNN)</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="8" t="n">
+        <v>53200</v>
+      </c>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>100% (Highland Cabinetry)</t>
+        </is>
+      </c>
+      <c r="U23" s="9" t="n">
+        <v>6596403</v>
+      </c>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>R0084268.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>R0086203</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>R0086203</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>R0086203</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Aurora - Uravan (Wagner)</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>2420 Uravan St</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Wagner Equipment Co.</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Wagner Equipment Co.</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>Single (proforma)</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O24" s="8" t="n">
+        <v>91476</v>
+      </c>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="8" t="n">
+        <v>16000</v>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v>1991</v>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>5.72:1</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>90% (proforma)</t>
+        </is>
+      </c>
+      <c r="U24" s="9" t="n">
+        <v>2808794</v>
+      </c>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="n">
+        <v>1573700</v>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>R0086203.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Y2"/>
@@ -2753,7 +3712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5764,18 +6723,1044 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave (R0103791) — Arakouzo LLP  |  Owner rent-roll submissions 2019-2022</t>
+        </is>
+      </c>
+      <c r="B65" s="20" t="n"/>
+      <c r="C65" s="20" t="n"/>
+      <c r="D65" s="20" t="n"/>
+      <c r="E65" s="20" t="n"/>
+      <c r="F65" s="20" t="n"/>
+      <c r="G65" s="20" t="n"/>
+      <c r="H65" s="20" t="n"/>
+      <c r="I65" s="20" t="n"/>
+      <c r="J65" s="20" t="n"/>
+      <c r="K65" s="20" t="n"/>
+      <c r="L65" s="20" t="n"/>
+      <c r="M65" s="21" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>Whole bldg</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Harlan Bakeries</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E66" s="22" t="n">
+        <v>20200.37</v>
+      </c>
+      <c r="F66" s="22" t="n">
+        <v>242404.4</v>
+      </c>
+      <c r="G66" s="16" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>~10 yr</t>
+        </is>
+      </c>
+      <c r="K66" s="9" t="n"/>
+      <c r="L66" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>30,965 SF. Annual base rent history: 2019 $223,980; 2020 $230,689; 2021 $236,521.04; 2022 $242,404.40 (monthly shown = 2022/12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl (R0084249) — St. Paul Fire &amp; Marine  |  Rent Roll as of 6/30/2024 (Colliers); 117,329 SF, 0 vacant</t>
+        </is>
+      </c>
+      <c r="B67" s="20" t="n"/>
+      <c r="C67" s="20" t="n"/>
+      <c r="D67" s="20" t="n"/>
+      <c r="E67" s="20" t="n"/>
+      <c r="F67" s="20" t="n"/>
+      <c r="G67" s="20" t="n"/>
+      <c r="H67" s="20" t="n"/>
+      <c r="I67" s="20" t="n"/>
+      <c r="J67" s="20" t="n"/>
+      <c r="K67" s="20" t="n"/>
+      <c r="L67" s="20" t="n"/>
+      <c r="M67" s="21" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>8500-A-CU</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Talley Inc.</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E68" s="22" t="n">
+        <v>15913.34</v>
+      </c>
+      <c r="F68" s="22" t="n">
+        <v>190960.08</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>5/1/2013</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>7/31/2025</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>147 mo</t>
+        </is>
+      </c>
+      <c r="K68" s="22" t="n">
+        <v>1521</v>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>24,545 SF; step 8/1/24 $16,383.79; +RE tax $6,710/mo, other $378/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>8500-A1-CU</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>Bay Industries Incorporated</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E69" s="22" t="n">
+        <v>9628.379999999999</v>
+      </c>
+      <c r="F69" s="22" t="n">
+        <v>115540.56</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>7/1/2012</t>
+        </is>
+      </c>
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2028</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>194 mo</t>
+        </is>
+      </c>
+      <c r="K69" s="22" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L69" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>20,094 SF; steps 9/1/24 $9,913.04 → 9/1/27 $10,834.02; +tax $5,493/mo, other $309/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>8500-A2-CU</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Bay Insulation Supply</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E70" s="22" t="n">
+        <v>9628.379999999999</v>
+      </c>
+      <c r="F70" s="22" t="n">
+        <v>115540.56</v>
+      </c>
+      <c r="G70" s="16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>7/1/2012</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2028</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>194 mo</t>
+        </is>
+      </c>
+      <c r="K70" s="22" t="n">
+        <v>1245</v>
+      </c>
+      <c r="L70" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>20,094 SF; steps 9/1/24 $9,913.04 → 9/1/27 $10,834.02; +tax $5,493/mo, other $309/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>8500-B-CU</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Bay Industries</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E71" s="22" t="n">
+        <v>10457.49</v>
+      </c>
+      <c r="F71" s="22" t="n">
+        <v>125489.88</v>
+      </c>
+      <c r="G71" s="16" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2013</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2026</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>159 mo</t>
+        </is>
+      </c>
+      <c r="K71" s="22" t="n">
+        <v>1430</v>
+      </c>
+      <c r="L71" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>23,068 SF; steps 9/1/24 $10,745.84, 9/1/25 $11,034.19; +tax $6,306/mo, other $355/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>8500-C-CU</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>True North Management Services</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Lease</t>
+        </is>
+      </c>
+      <c r="E72" s="22" t="n">
+        <v>16855.57</v>
+      </c>
+      <c r="F72" s="22" t="n">
+        <v>202266.84</v>
+      </c>
+      <c r="G72" s="16" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>12/1/2022</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>2/29/2028</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>63 mo</t>
+        </is>
+      </c>
+      <c r="K72" s="22" t="n">
+        <v>1830</v>
+      </c>
+      <c r="L72" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>29,528 SF; steps 3/1/25 $17,347.70 → 3/1/27 $18,405.79; +tax $8,072/mo, other $455/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>14200 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="n"/>
+      <c r="E73" s="23">
+        <f>SUM(E68:E72)</f>
+        <v/>
+      </c>
+      <c r="F73" s="23">
+        <f>SUM(F68:F72)</f>
+        <v/>
+      </c>
+      <c r="G73" s="13" t="n"/>
+      <c r="H73" s="13" t="n"/>
+      <c r="I73" s="13" t="n"/>
+      <c r="J73" s="13" t="n"/>
+      <c r="K73" s="23">
+        <f>SUM(K68:K72)</f>
+        <v/>
+      </c>
+      <c r="L73" s="13" t="n"/>
+      <c r="M73" s="15" t="inlineStr">
+        <is>
+          <t>Rents at 6/30/2024 step level (sum $62,483.16); Dec-2024 income-statement current base rent $63,811.28 after 8-9/2024 steps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="10" t="inlineStr">
+        <is>
+          <t>3250 Abilene St (R0084250 / bt42569)  |  Rent Roll as of 6/30/2024; 231,842 SF, 69.7% vacant</t>
+        </is>
+      </c>
+      <c r="B74" s="20" t="n"/>
+      <c r="C74" s="20" t="n"/>
+      <c r="D74" s="20" t="n"/>
+      <c r="E74" s="20" t="n"/>
+      <c r="F74" s="20" t="n"/>
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20" t="n"/>
+      <c r="I74" s="20" t="n"/>
+      <c r="J74" s="20" t="n"/>
+      <c r="K74" s="20" t="n"/>
+      <c r="L74" s="20" t="n"/>
+      <c r="M74" s="21" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Flexpak, LLC</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Prorata Share</t>
+        </is>
+      </c>
+      <c r="E75" s="22" t="n">
+        <v>26853.03</v>
+      </c>
+      <c r="F75" s="22" t="n">
+        <v>322236.36</v>
+      </c>
+      <c r="G75" s="16" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>2/14/2020</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>5/31/2030</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>124 mo</t>
+        </is>
+      </c>
+      <c r="K75" s="9" t="n"/>
+      <c r="L75" s="32" t="n">
+        <v>119772.32</v>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>70,204 SF; recoveries $4.15/SF/yr; total charges $8.74/SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>A (2 units)</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>** VACANT **</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="16" t="n"/>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K76" s="9" t="n"/>
+      <c r="L76" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>161,638 SF vacant (2 units of 80,819 SF); 69.72% of 231,842 SF total</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>3250 Abilene St</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="n"/>
+      <c r="E77" s="23">
+        <f>SUM(E75:E76)</f>
+        <v/>
+      </c>
+      <c r="F77" s="23">
+        <f>SUM(F75:F76)</f>
+        <v/>
+      </c>
+      <c r="G77" s="13" t="n"/>
+      <c r="H77" s="13" t="n"/>
+      <c r="I77" s="13" t="n"/>
+      <c r="J77" s="13" t="n"/>
+      <c r="K77" s="23">
+        <f>SUM(K75:K76)</f>
+        <v/>
+      </c>
+      <c r="L77" s="13" t="n"/>
+      <c r="M77" s="15" t="inlineStr">
+        <is>
+          <t>Roll summary: occupied 70,204 SF (30.28%), base rent $322,236.36/yr ($4.59 PSF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="10" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl (R0084253 / bt46265)  |  Commercial Rent Roll as of 1/1/2024 (RCM); 151,485 SF, 100% occupied</t>
+        </is>
+      </c>
+      <c r="B78" s="20" t="n"/>
+      <c r="C78" s="20" t="n"/>
+      <c r="D78" s="20" t="n"/>
+      <c r="E78" s="20" t="n"/>
+      <c r="F78" s="20" t="n"/>
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="20" t="n"/>
+      <c r="J78" s="20" t="n"/>
+      <c r="K78" s="20" t="n"/>
+      <c r="L78" s="20" t="n"/>
+      <c r="M78" s="21" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>00509A</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Reliance Steel &amp; Aluminum Co.</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>NNN CAP</t>
+        </is>
+      </c>
+      <c r="E79" s="22" t="n">
+        <v>15878.69</v>
+      </c>
+      <c r="F79" s="22" t="n">
+        <v>190544.28</v>
+      </c>
+      <c r="G79" s="16" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>2/1/2009</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>194 mo (renewed 4/2020, 60 mo)</t>
+        </is>
+      </c>
+      <c r="K79" s="22" t="n">
+        <v>1672.81</v>
+      </c>
+      <c r="L79" s="32" t="n">
+        <v>18204</v>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>27,900 SF (18.42% GLA); step 4/1/24 $16,355.05 ($7.03); recoveries $10,076.86/mo incl. tax $7,372.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>00509C</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>All Packaging Company LLC</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Prorata Share</t>
+        </is>
+      </c>
+      <c r="E80" s="22" t="n">
+        <v>21193.38</v>
+      </c>
+      <c r="F80" s="22" t="n">
+        <v>254320.56</v>
+      </c>
+      <c r="G80" s="16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>9/1/2009</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>4/30/2025</t>
+        </is>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>188 mo (renewed 5/2020, 60 mo)</t>
+        </is>
+      </c>
+      <c r="K80" s="22" t="n">
+        <v>2881.39</v>
+      </c>
+      <c r="L80" s="32" t="n">
+        <v>7000</v>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>47,985 SF (31.68%); step 5/1/24 $21,833.18 ($5.46); recoveries $18,247.98/mo incl. tax $12,679.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>00509E</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Intelligent Designs 2000 Corporation</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Prorata Share</t>
+        </is>
+      </c>
+      <c r="E81" s="22" t="n">
+        <v>9465.75</v>
+      </c>
+      <c r="F81" s="22" t="n">
+        <v>113589</v>
+      </c>
+      <c r="G81" s="16" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>12/13/2012</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>148 mo (renewed 4/2020, 60 mo)</t>
+        </is>
+      </c>
+      <c r="K81" s="22" t="n">
+        <v>1134.9</v>
+      </c>
+      <c r="L81" s="32" t="n">
+        <v>10000</v>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>18,900 SF (12.48%); step 4/1/24 $9,749.72 ($6.19); recoveries $7,222.28/mo incl. tax $4,994.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>00509G</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Uzin UTZ North America, Inc.</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>Prorata Share</t>
+        </is>
+      </c>
+      <c r="E82" s="22" t="n">
+        <v>20578.8</v>
+      </c>
+      <c r="F82" s="22" t="n">
+        <v>246945.6</v>
+      </c>
+      <c r="G82" s="16" t="n">
+        <v>6.47</v>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>9/1/2008</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>4/30/2029</t>
+        </is>
+      </c>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>248 mo (renewed 5/1/2024, 60 mo)</t>
+        </is>
+      </c>
+      <c r="K82" s="22" t="n">
+        <v>2291.36</v>
+      </c>
+      <c r="L82" s="32" t="n">
+        <v>40669.68</v>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>38,159 SF (25.19%); renewal steps 5/1/24 $23,054.40 ($7.25) → 5/1/28 $26,455.45 ($8.32); recoveries $14,662.38/mo incl. tax $10,083.24</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>00509H</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Rosenberger Site Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Prorata Share</t>
+        </is>
+      </c>
+      <c r="E83" s="22" t="n">
+        <v>11402.72</v>
+      </c>
+      <c r="F83" s="22" t="n">
+        <v>136832.64</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>8/1/2018</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2024</t>
+        </is>
+      </c>
+      <c r="J83" s="5" t="inlineStr">
+        <is>
+          <t>73 mo (no options)</t>
+        </is>
+      </c>
+      <c r="K83" s="22" t="n">
+        <v>1079.1</v>
+      </c>
+      <c r="L83" s="32" t="n">
+        <v>13380.42</v>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>18,541 SF (12.24%); recoveries $7,107.79/mo incl. tax $4,899.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>14509 E. 33rd Pl</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Total scheduled monthly rent</t>
+        </is>
+      </c>
+      <c r="D84" s="13" t="n"/>
+      <c r="E84" s="23">
+        <f>SUM(E79:E83)</f>
+        <v/>
+      </c>
+      <c r="F84" s="23">
+        <f>SUM(F79:F83)</f>
+        <v/>
+      </c>
+      <c r="G84" s="13" t="n"/>
+      <c r="H84" s="13" t="n"/>
+      <c r="I84" s="13" t="n"/>
+      <c r="J84" s="13" t="n"/>
+      <c r="K84" s="23">
+        <f>SUM(K79:K83)</f>
+        <v/>
+      </c>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="15" t="inlineStr">
+        <is>
+          <t>Printed roll totals: monthly $78,519.34 / annual $942,232.08 ($6.22 avg PSF); recoveries $57,317.29/mo ($687,807.48/yr).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>14501 E. Moncrieff Pl (R0084268) — Peterson Moncrieff LLC  |  Rent Roll as of 7/1/2024; 0% vacant</t>
+        </is>
+      </c>
+      <c r="B85" s="20" t="n"/>
+      <c r="C85" s="20" t="n"/>
+      <c r="D85" s="20" t="n"/>
+      <c r="E85" s="20" t="n"/>
+      <c r="F85" s="20" t="n"/>
+      <c r="G85" s="20" t="n"/>
+      <c r="H85" s="20" t="n"/>
+      <c r="I85" s="20" t="n"/>
+      <c r="J85" s="20" t="n"/>
+      <c r="K85" s="20" t="n"/>
+      <c r="L85" s="20" t="n"/>
+      <c r="M85" s="21" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>14501 E. Moncrieff Pl</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>5455-1-CU</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Highland Cabinetry, Inc.</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E86" s="22" t="n">
+        <v>21060</v>
+      </c>
+      <c r="F86" s="22" t="n">
+        <v>252720</v>
+      </c>
+      <c r="G86" s="16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2019</t>
+        </is>
+      </c>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>8/31/2029</t>
+        </is>
+      </c>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>123 mo</t>
+        </is>
+      </c>
+      <c r="K86" s="22" t="n">
+        <v>4117</v>
+      </c>
+      <c r="L86" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>53,200 SF per roll (52,606 SF per 1st Net income approach); +RE tax $10,285/mo, ins/other $1,039/mo; year-end total w/ recoveries $438,012</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A67:M67"/>
     <mergeCell ref="A61:M61"/>
+    <mergeCell ref="A74:M74"/>
     <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A78:M78"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="A55:M55"/>
+    <mergeCell ref="A65:M65"/>
     <mergeCell ref="A43:M43"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A49:M49"/>
+    <mergeCell ref="A85:M85"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5787,7 +7772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6082,327 +8067,502 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave (R0103791)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="22" t="n"/>
+      <c r="E13" s="9" t="n">
+        <v>2899541</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>R0103791.pdf (county value not stated in package)</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>14501 E Moncrieff Pl (R0084268)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>6596403</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>124</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>3840000</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>72.18000000000001</v>
+      </c>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>R0084268.pdf (letter $3,840,000; analysis $3,838,140)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2420 Uravan St (R0086203)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>2808794</v>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>175.55</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1573700</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>98.36</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>2139300</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>R0086203.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).  E 76th Ave: protest letter cites county value $44,788,554 &amp; owner opinion $32,000,000; 1st Net protest list shows $47,464,870 county / $21,725,000 1st Net value — all reproduced as printed.</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1"/>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="21" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>4832500</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Dr</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>209100</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>-10455</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>198645</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>182753</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>12260 Pennsylvania St</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="n">
-        <v>237290</v>
-      </c>
-      <c r="C20" s="9" t="n">
-        <v>-16610</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>220680</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>-22068</v>
-      </c>
-      <c r="F20" s="14" t="n">
-        <v>198612</v>
-      </c>
-      <c r="G20" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H20" s="14" t="n">
-        <v>2837000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>6770 E. 56th Ave</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>115824</v>
+        <v>359394</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>-5791</v>
+        <v>-17970</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>110033</v>
+        <v>341424</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>-5502</v>
+        <v>-27314</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>104531</v>
+        <v>314110</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="H21" s="14" t="n">
-        <v>1493302</v>
+        <v>4832500</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>5970 Marion Drive (mkt)</t>
+          <t>17608 E. 24th Dr</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>172800</v>
+        <v>209100</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>-8640</v>
+        <v>-10455</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>164160</v>
+        <v>198645</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>-4223</v>
+        <v>-15892</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>159937</v>
+        <v>182753</v>
       </c>
       <c r="G22" s="19" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="H22" s="14" t="n">
-        <v>2460577</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>I-25 Corp Center (2024 actual)</t>
+          <t>12260 Pennsylvania St</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>2750538</v>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>237290</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>-16610</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>2750538</v>
+        <v>220680</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-1279108</v>
+        <v>-22068</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>1471430</v>
+        <v>198612</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>22637387</v>
+        <v>2837000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>I-25 Corp Center (stabilized)</t>
+          <t>6770 E. 56th Ave</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>2442300</v>
+        <v>115824</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>-122115</v>
+        <v>-5791</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>2320185</v>
+        <v>110033</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-185615</v>
+        <v>-5502</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>2134570</v>
+        <v>104531</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>32839546</v>
+        <v>1493302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Majestic Commercenter (2024)</t>
+          <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1361973</v>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>172800</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-8640</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1361973</v>
+        <v>164160</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>-627099</v>
+        <v>-4223</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>734874</v>
+        <v>159937</v>
       </c>
       <c r="G25" s="19" t="n">
         <v>0.065</v>
       </c>
       <c r="H25" s="14" t="n">
+        <v>2460577</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center (2024 actual)</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>2750538</v>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>2750538</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>-1279108</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>1471430</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>22637387</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>I-25 Corp Center (stabilized)</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>2442300</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>-122115</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>2320185</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>-185615</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>2134570</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>32839546</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter (2024)</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>1361973</v>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>1361973</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>-627099</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>734874</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H28" s="14" t="n">
         <v>11305758</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="18" t="inlineStr">
-        <is>
-          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, 1st Net, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915). I-25 Corp Center (1st Net): 2024-actual approach caps net rental income $1,471,430 at 6.5% → $22,637,387; stabilized approach ($7.38 face rent, 5% vac, $0.08 exp) → $32,839,546 less lease-up costs $1,023,935 → FINAL indicated $31,815,611; sales grid selected $32,343,372. Majestic (1st Net): 2024 net income $734,874 at 6.5% → $11,305,758 (2024 mill levy 0.130073).</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="21" t="n"/>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th (2021-22 actuals)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>303912</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>-13737</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>290175</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>0.100076</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>2899541</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>14501 Moncrieff (contract rent)</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="n">
+        <v>249879</v>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>-12494</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>237385</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>-18991</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <v>218394</v>
+      </c>
+      <c r="G30" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <v>3359905</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>2420 Uravan (proforma)</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>136000</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>-13600</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>122400</v>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>-12240</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>110160</v>
+      </c>
+      <c r="G31" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <v>1573700</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
+        <is>
+          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, 1st Net, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915). I-25 Corp Center (1st Net): 2024-actual approach caps net rental income $1,471,430 at 6.5% → $22,637,387; stabilized approach ($7.38 face rent, 5% vac, $0.08 exp) → $32,839,546 less lease-up costs $1,023,935 → FINAL indicated $31,815,611; sales grid selected $32,343,372. Majestic (1st Net): 2024 net income $734,874 at 6.5% → $11,305,758 (2024 mill levy 0.130073). 1803 E 58th (Property Tax Advisors): EGI = annualized 2021-22 actual income; overall rate 10.0076% = 7.00% cap + 3.01% effective tax rate. 14501 Moncrieff (1st Net): contract-rent NOI $218,394 at 6.5% → $3,359,905, plus PV of below-market rent ($103,450/yr × 4.62288 PW, 6 yrs @8%) $478,236 → final $3,838,140. 2420 Uravan (Ryan): $8.50 face rent, 10% vacancy, 10% EGI expenses, 7.0% cap.</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6414,7 +8574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -6772,22 +8932,154 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave (Arakouzo) — 2021</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n">
+        <v>266063</v>
+      </c>
+      <c r="C19" s="22" t="n">
+        <v>92144</v>
+      </c>
+      <c r="D19" s="23">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>IRS Form 8825 (tax basis; incl. depreciation $643)</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave (Arakouzo) — 2022</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="n">
+        <v>379611</v>
+      </c>
+      <c r="C20" s="22" t="n">
+        <v>103235</v>
+      </c>
+      <c r="D20" s="23">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>IRS Form 8825 (tax basis; incl. depreciation $643)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="n">
+        <v>1171686.53</v>
+      </c>
+      <c r="C21" s="22" t="n">
+        <v>570380.8100000001</v>
+      </c>
+      <c r="D21" s="23">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt (expense incl. capex $129,547; step-rent credit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n">
+        <v>1346707.89</v>
+      </c>
+      <c r="C22" s="22" t="n">
+        <v>581292.78</v>
+      </c>
+      <c r="D22" s="23">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Income stmt (expense incl. roof capex $48,535; tax consulting $43,209)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="n">
+        <v>797212</v>
+      </c>
+      <c r="C23" s="22" t="n">
+        <v>1096249</v>
+      </c>
+      <c r="D23" s="23">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Yardi income stmt (accrual, Prior-Owner book; incl. D&amp;A $505,966) → net loss $(299,037)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="n">
+        <v>714461</v>
+      </c>
+      <c r="C24" s="22" t="n">
+        <v>600106</v>
+      </c>
+      <c r="D24" s="23">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Yardi income stmt (accrual, Prior-Owner book; incl. D&amp;A $333,529) → net income $114,355</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation; I-25 Corp Center, Fraser and Majestic statements include debt service and/or capital expenditures as printed, so they are cash-flow figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="21" t="n"/>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A26:E26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6799,7 +9091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -14139,6 +16431,4772 @@
       <c r="E341" s="6" t="inlineStr">
         <is>
           <t>Printed total: $586,301.91.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B342" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C342" s="6" t="inlineStr">
+        <is>
+          <t>Gross rents</t>
+        </is>
+      </c>
+      <c r="D342" s="22" t="n">
+        <v>266063</v>
+      </c>
+      <c r="E342" s="6" t="n"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="11" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B343" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C343" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D343" s="23">
+        <f>SUM(D342:D342)</f>
+        <v/>
+      </c>
+      <c r="E343" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $266,063.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B344" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C344" s="6" t="inlineStr">
+        <is>
+          <t>Commissions</t>
+        </is>
+      </c>
+      <c r="D344" s="22" t="n">
+        <v>500</v>
+      </c>
+      <c r="E344" s="6" t="n"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B345" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C345" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D345" s="22" t="n">
+        <v>9225</v>
+      </c>
+      <c r="E345" s="6" t="n"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B346" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C346" s="6" t="inlineStr">
+        <is>
+          <t>Legal &amp; other professional fees</t>
+        </is>
+      </c>
+      <c r="D346" s="22" t="n">
+        <v>4309</v>
+      </c>
+      <c r="E346" s="6" t="n"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B347" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C347" s="6" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="D347" s="22" t="n">
+        <v>2794</v>
+      </c>
+      <c r="E347" s="6" t="n"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B348" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C348" s="6" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="D348" s="22" t="n">
+        <v>73777</v>
+      </c>
+      <c r="E348" s="6" t="n"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B349" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C349" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D349" s="22" t="n">
+        <v>643</v>
+      </c>
+      <c r="E349" s="6" t="n"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B350" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C350" s="6" t="inlineStr">
+        <is>
+          <t>Other (STMT 6)</t>
+        </is>
+      </c>
+      <c r="D350" s="22" t="n">
+        <v>896</v>
+      </c>
+      <c r="E350" s="6" t="n"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="11" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2021 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B351" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C351" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D351" s="23">
+        <f>SUM(D344:D350)</f>
+        <v/>
+      </c>
+      <c r="E351" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $92,144.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B352" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C352" s="6" t="inlineStr">
+        <is>
+          <t>Gross rents</t>
+        </is>
+      </c>
+      <c r="D352" s="22" t="n">
+        <v>379611</v>
+      </c>
+      <c r="E352" s="6" t="n"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="11" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B353" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C353" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D353" s="23">
+        <f>SUM(D352:D352)</f>
+        <v/>
+      </c>
+      <c r="E353" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $379,611.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B354" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C354" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D354" s="22" t="n">
+        <v>8380</v>
+      </c>
+      <c r="E354" s="6" t="n"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B355" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C355" s="6" t="inlineStr">
+        <is>
+          <t>Legal &amp; other professional fees</t>
+        </is>
+      </c>
+      <c r="D355" s="22" t="n">
+        <v>5245</v>
+      </c>
+      <c r="E355" s="6" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B356" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C356" s="6" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="D356" s="22" t="n">
+        <v>7597</v>
+      </c>
+      <c r="E356" s="6" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B357" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C357" s="6" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="D357" s="22" t="n">
+        <v>80613</v>
+      </c>
+      <c r="E357" s="6" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B358" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C358" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D358" s="22" t="n">
+        <v>643</v>
+      </c>
+      <c r="E358" s="6" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="6" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B359" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C359" s="6" t="inlineStr">
+        <is>
+          <t>Other (STMT 6)</t>
+        </is>
+      </c>
+      <c r="D359" s="22" t="n">
+        <v>757</v>
+      </c>
+      <c r="E359" s="6" t="n"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="11" t="inlineStr">
+        <is>
+          <t>1803 E 58th Ave — 2022 (Form 8825)</t>
+        </is>
+      </c>
+      <c r="B360" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C360" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D360" s="23">
+        <f>SUM(D354:D359)</f>
+        <v/>
+      </c>
+      <c r="E360" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $103,235.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B361" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C361" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D361" s="22" t="n">
+        <v>681184.7</v>
+      </c>
+      <c r="E361" s="6" t="n"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B362" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C362" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D362" s="22" t="n">
+        <v>79956</v>
+      </c>
+      <c r="E362" s="6" t="n"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B363" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C363" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D363" s="22" t="n">
+        <v>13668</v>
+      </c>
+      <c r="E363" s="6" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B364" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C364" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D364" s="22" t="n">
+        <v>384866</v>
+      </c>
+      <c r="E364" s="6" t="n"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B365" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C365" s="6" t="inlineStr">
+        <is>
+          <t>PY CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D365" s="22" t="n">
+        <v>17474.21</v>
+      </c>
+      <c r="E365" s="6" t="n"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B366" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C366" s="6" t="inlineStr">
+        <is>
+          <t>Direct Billable Income</t>
+        </is>
+      </c>
+      <c r="D366" s="22" t="n">
+        <v>-5574.75</v>
+      </c>
+      <c r="E366" s="6" t="n"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B367" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C367" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D367" s="22" t="n">
+        <v>112.37</v>
+      </c>
+      <c r="E367" s="6" t="n"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="11" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B368" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C368" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D368" s="23">
+        <f>SUM(D361:D367)</f>
+        <v/>
+      </c>
+      <c r="E368" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,171,686.53.</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B369" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C369" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D369" s="22" t="n">
+        <v>16380.17</v>
+      </c>
+      <c r="E369" s="6" t="n"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B370" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C370" s="6" t="inlineStr">
+        <is>
+          <t>Extermination (recov)</t>
+        </is>
+      </c>
+      <c r="D370" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E370" s="6" t="n"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B371" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C371" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Contract</t>
+        </is>
+      </c>
+      <c r="D371" s="22" t="n">
+        <v>484.76</v>
+      </c>
+      <c r="E371" s="6" t="n"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B372" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C372" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D372" s="22" t="n">
+        <v>685</v>
+      </c>
+      <c r="E372" s="6" t="n"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B373" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C373" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Other</t>
+        </is>
+      </c>
+      <c r="D373" s="22" t="n">
+        <v>605</v>
+      </c>
+      <c r="E373" s="6" t="n"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B374" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C374" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D374" s="22" t="n">
+        <v>1107</v>
+      </c>
+      <c r="E374" s="6" t="n"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B375" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C375" s="6" t="inlineStr">
+        <is>
+          <t>Landscape Contract</t>
+        </is>
+      </c>
+      <c r="D375" s="22" t="n">
+        <v>6924</v>
+      </c>
+      <c r="E375" s="6" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B376" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C376" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape</t>
+        </is>
+      </c>
+      <c r="D376" s="22" t="n">
+        <v>2719.92</v>
+      </c>
+      <c r="E376" s="6" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B377" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C377" s="6" t="inlineStr">
+        <is>
+          <t>HVAC Contract</t>
+        </is>
+      </c>
+      <c r="D377" s="22" t="n">
+        <v>3468</v>
+      </c>
+      <c r="E377" s="6" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B378" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C378" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC</t>
+        </is>
+      </c>
+      <c r="D378" s="22" t="n">
+        <v>3064.46</v>
+      </c>
+      <c r="E378" s="6" t="n"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B379" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C379" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (recov)</t>
+        </is>
+      </c>
+      <c r="D379" s="22" t="n">
+        <v>1790</v>
+      </c>
+      <c r="E379" s="6" t="n"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B380" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C380" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D380" s="22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E380" s="6" t="n"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B381" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C381" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D381" s="22" t="n">
+        <v>17475.5</v>
+      </c>
+      <c r="E381" s="6" t="n"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B382" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C382" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Plumbing (recov)</t>
+        </is>
+      </c>
+      <c r="D382" s="22" t="n">
+        <v>655</v>
+      </c>
+      <c r="E382" s="6" t="n"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B383" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C383" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D383" s="22" t="n">
+        <v>2442.39</v>
+      </c>
+      <c r="E383" s="6" t="n"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B384" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C384" s="6" t="inlineStr">
+        <is>
+          <t>Signage (recov)</t>
+        </is>
+      </c>
+      <c r="D384" s="22" t="n">
+        <v>5503.31</v>
+      </c>
+      <c r="E384" s="6" t="n"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B385" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C385" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D385" s="22" t="n">
+        <v>30028.16</v>
+      </c>
+      <c r="E385" s="6" t="n"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B386" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C386" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D386" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E386" s="6" t="n"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B387" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C387" s="6" t="inlineStr">
+        <is>
+          <t>Other Direct Billable</t>
+        </is>
+      </c>
+      <c r="D387" s="22" t="n">
+        <v>1072.25</v>
+      </c>
+      <c r="E387" s="6" t="n"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B388" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C388" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D388" s="22" t="n">
+        <v>17340.64</v>
+      </c>
+      <c r="E388" s="6" t="n"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B389" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C389" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D389" s="22" t="n">
+        <v>384873</v>
+      </c>
+      <c r="E389" s="6" t="n"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B390" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C390" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - Prior-Yr Adj</t>
+        </is>
+      </c>
+      <c r="D390" s="22" t="n">
+        <v>-11503.22</v>
+      </c>
+      <c r="E390" s="6" t="n"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B391" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C391" s="6" t="inlineStr">
+        <is>
+          <t>Step Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D391" s="22" t="n">
+        <v>-47793.59</v>
+      </c>
+      <c r="E391" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B392" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C392" s="6" t="inlineStr">
+        <is>
+          <t>Consultation Fees - General</t>
+        </is>
+      </c>
+      <c r="D392" s="22" t="n">
+        <v>1132.39</v>
+      </c>
+      <c r="E392" s="6" t="n"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B393" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C393" s="6" t="inlineStr">
+        <is>
+          <t>Building (capital)</t>
+        </is>
+      </c>
+      <c r="D393" s="22" t="n">
+        <v>42000</v>
+      </c>
+      <c r="E393" s="6" t="n"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B394" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C394" s="6" t="inlineStr">
+        <is>
+          <t>Lease Commission (capital)</t>
+        </is>
+      </c>
+      <c r="D394" s="22" t="n">
+        <v>87546.67</v>
+      </c>
+      <c r="E394" s="6" t="n"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="11" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2023</t>
+        </is>
+      </c>
+      <c r="B395" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C395" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D395" s="23">
+        <f>SUM(D369:D394)</f>
+        <v/>
+      </c>
+      <c r="E395" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $570,380.81.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B396" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C396" s="6" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D396" s="22" t="n">
+        <v>754596.5699999999</v>
+      </c>
+      <c r="E396" s="6" t="n"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B397" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C397" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D397" s="22" t="n">
+        <v>87252</v>
+      </c>
+      <c r="E397" s="6" t="n"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B398" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C398" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D398" s="22" t="n">
+        <v>21672</v>
+      </c>
+      <c r="E398" s="6" t="n"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B399" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C399" s="6" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D399" s="22" t="n">
+        <v>384888</v>
+      </c>
+      <c r="E399" s="6" t="n"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B400" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C400" s="6" t="inlineStr">
+        <is>
+          <t>PY CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D400" s="22" t="n">
+        <v>115535.66</v>
+      </c>
+      <c r="E400" s="6" t="n"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B401" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C401" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt Allowance</t>
+        </is>
+      </c>
+      <c r="D401" s="22" t="n">
+        <v>-18750</v>
+      </c>
+      <c r="E401" s="6" t="n"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B402" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C402" s="6" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D402" s="22" t="n">
+        <v>1513.66</v>
+      </c>
+      <c r="E402" s="6" t="n"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="11" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B403" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C403" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D403" s="23">
+        <f>SUM(D396:D402)</f>
+        <v/>
+      </c>
+      <c r="E403" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,346,707.89.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B404" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C404" s="6" t="inlineStr">
+        <is>
+          <t>Water/Sewer (recov)</t>
+        </is>
+      </c>
+      <c r="D404" s="22" t="n">
+        <v>11611.84</v>
+      </c>
+      <c r="E404" s="6" t="n"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B405" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C405" s="6" t="inlineStr">
+        <is>
+          <t>Extermination (recov)</t>
+        </is>
+      </c>
+      <c r="D405" s="22" t="n">
+        <v>1250</v>
+      </c>
+      <c r="E405" s="6" t="n"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B406" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C406" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Contract</t>
+        </is>
+      </c>
+      <c r="D406" s="22" t="n">
+        <v>515.4400000000001</v>
+      </c>
+      <c r="E406" s="6" t="n"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B407" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C407" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D407" s="22" t="n">
+        <v>429.26</v>
+      </c>
+      <c r="E407" s="6" t="n"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B408" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C408" s="6" t="inlineStr">
+        <is>
+          <t>Fire Safety Other</t>
+        </is>
+      </c>
+      <c r="D408" s="22" t="n">
+        <v>490</v>
+      </c>
+      <c r="E408" s="6" t="n"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B409" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C409" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (recov)</t>
+        </is>
+      </c>
+      <c r="D409" s="22" t="n">
+        <v>792</v>
+      </c>
+      <c r="E409" s="6" t="n"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B410" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C410" s="6" t="inlineStr">
+        <is>
+          <t>Landscape Contract</t>
+        </is>
+      </c>
+      <c r="D410" s="22" t="n">
+        <v>7202</v>
+      </c>
+      <c r="E410" s="6" t="n"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B411" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C411" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape</t>
+        </is>
+      </c>
+      <c r="D411" s="22" t="n">
+        <v>7757.83</v>
+      </c>
+      <c r="E411" s="6" t="n"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B412" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C412" s="6" t="inlineStr">
+        <is>
+          <t>HVAC Contract</t>
+        </is>
+      </c>
+      <c r="D412" s="22" t="n">
+        <v>3552</v>
+      </c>
+      <c r="E412" s="6" t="n"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B413" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C413" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC</t>
+        </is>
+      </c>
+      <c r="D413" s="22" t="n">
+        <v>2144.82</v>
+      </c>
+      <c r="E413" s="6" t="n"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B414" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C414" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Sweeping (recov)</t>
+        </is>
+      </c>
+      <c r="D414" s="22" t="n">
+        <v>1080</v>
+      </c>
+      <c r="E414" s="6" t="n"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B415" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C415" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Prk Lot Snow Removal (recov)</t>
+        </is>
+      </c>
+      <c r="D415" s="22" t="n">
+        <v>27996.5</v>
+      </c>
+      <c r="E415" s="6" t="n"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B416" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C416" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Plumbing (recov)</t>
+        </is>
+      </c>
+      <c r="D416" s="22" t="n">
+        <v>960</v>
+      </c>
+      <c r="E416" s="6" t="n"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B417" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C417" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (recov)</t>
+        </is>
+      </c>
+      <c r="D417" s="22" t="n">
+        <v>16178.25</v>
+      </c>
+      <c r="E417" s="6" t="n"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B418" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C418" s="6" t="inlineStr">
+        <is>
+          <t>Management Fees (recov)</t>
+        </is>
+      </c>
+      <c r="D418" s="22" t="n">
+        <v>31185.58</v>
+      </c>
+      <c r="E418" s="6" t="n"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B419" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C419" s="6" t="inlineStr">
+        <is>
+          <t>Other Expense (recov)</t>
+        </is>
+      </c>
+      <c r="D419" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E419" s="6" t="n"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B420" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C420" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D420" s="22" t="n">
+        <v>23371.06</v>
+      </c>
+      <c r="E420" s="6" t="n"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B421" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C421" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D421" s="22" t="n">
+        <v>378963.87</v>
+      </c>
+      <c r="E421" s="6" t="n"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B422" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C422" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - Prior-Yr Adj</t>
+        </is>
+      </c>
+      <c r="D422" s="22" t="n">
+        <v>-21411.8</v>
+      </c>
+      <c r="E422" s="6" t="n"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B423" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C423" s="6" t="inlineStr">
+        <is>
+          <t>Tax Consulting</t>
+        </is>
+      </c>
+      <c r="D423" s="22" t="n">
+        <v>43208.74</v>
+      </c>
+      <c r="E423" s="6" t="n"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B424" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C424" s="6" t="inlineStr">
+        <is>
+          <t>Step Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D424" s="22" t="n">
+        <v>-5829.75</v>
+      </c>
+      <c r="E424" s="6" t="inlineStr">
+        <is>
+          <t>G&amp;A</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B425" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C425" s="6" t="inlineStr">
+        <is>
+          <t>Consultation Fees - General</t>
+        </is>
+      </c>
+      <c r="D425" s="22" t="n">
+        <v>1132.39</v>
+      </c>
+      <c r="E425" s="6" t="n"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B426" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C426" s="6" t="inlineStr">
+        <is>
+          <t>Lease Commission (capital)</t>
+        </is>
+      </c>
+      <c r="D426" s="22" t="n">
+        <v>78</v>
+      </c>
+      <c r="E426" s="6" t="n"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="6" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B427" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C427" s="6" t="inlineStr">
+        <is>
+          <t>Roof (capital)</t>
+        </is>
+      </c>
+      <c r="D427" s="22" t="n">
+        <v>48534.75</v>
+      </c>
+      <c r="E427" s="6" t="n"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="11" t="inlineStr">
+        <is>
+          <t>14200 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B428" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C428" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D428" s="23">
+        <f>SUM(D404:D427)</f>
+        <v/>
+      </c>
+      <c r="E428" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $581,292.78.</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B429" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C429" s="6" t="inlineStr">
+        <is>
+          <t>Rental Income-Base</t>
+        </is>
+      </c>
+      <c r="D429" s="22" t="n">
+        <v>406844</v>
+      </c>
+      <c r="E429" s="6" t="n"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B430" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C430" s="6" t="inlineStr">
+        <is>
+          <t>Free Rent</t>
+        </is>
+      </c>
+      <c r="D430" s="22" t="n">
+        <v>-37042</v>
+      </c>
+      <c r="E430" s="6" t="n"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B431" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C431" s="6" t="inlineStr">
+        <is>
+          <t>Holdover Rent</t>
+        </is>
+      </c>
+      <c r="D431" s="22" t="n">
+        <v>5490</v>
+      </c>
+      <c r="E431" s="6" t="n"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B432" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C432" s="6" t="inlineStr">
+        <is>
+          <t>Late Fee Revenue</t>
+        </is>
+      </c>
+      <c r="D432" s="22" t="n">
+        <v>2985</v>
+      </c>
+      <c r="E432" s="6" t="n"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B433" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C433" s="6" t="inlineStr">
+        <is>
+          <t>Rental Income-SLR (non-cash)</t>
+        </is>
+      </c>
+      <c r="D433" s="22" t="n">
+        <v>31520</v>
+      </c>
+      <c r="E433" s="6" t="n"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B434" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C434" s="6" t="inlineStr">
+        <is>
+          <t>Mgmt Fees reimb.</t>
+        </is>
+      </c>
+      <c r="D434" s="22" t="n">
+        <v>19706</v>
+      </c>
+      <c r="E434" s="6" t="n"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B435" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C435" s="6" t="inlineStr">
+        <is>
+          <t>Mgmt Fees - JE</t>
+        </is>
+      </c>
+      <c r="D435" s="22" t="n">
+        <v>444</v>
+      </c>
+      <c r="E435" s="6" t="n"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B436" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C436" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes reimb.</t>
+        </is>
+      </c>
+      <c r="D436" s="22" t="n">
+        <v>222988</v>
+      </c>
+      <c r="E436" s="6" t="n"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B437" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C437" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - JE</t>
+        </is>
+      </c>
+      <c r="D437" s="22" t="n">
+        <v>-8003</v>
+      </c>
+      <c r="E437" s="6" t="n"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B438" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C438" s="6" t="inlineStr">
+        <is>
+          <t>Utilities-Others reimb.</t>
+        </is>
+      </c>
+      <c r="D438" s="22" t="n">
+        <v>7871</v>
+      </c>
+      <c r="E438" s="6" t="n"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B439" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C439" s="6" t="inlineStr">
+        <is>
+          <t>Utilities-Others - JE</t>
+        </is>
+      </c>
+      <c r="D439" s="22" t="n">
+        <v>-89</v>
+      </c>
+      <c r="E439" s="6" t="n"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B440" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C440" s="6" t="inlineStr">
+        <is>
+          <t>Insurance reimb.</t>
+        </is>
+      </c>
+      <c r="D440" s="22" t="n">
+        <v>8804</v>
+      </c>
+      <c r="E440" s="6" t="n"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B441" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C441" s="6" t="inlineStr">
+        <is>
+          <t>Insurance - JE</t>
+        </is>
+      </c>
+      <c r="D441" s="22" t="n">
+        <v>13520</v>
+      </c>
+      <c r="E441" s="6" t="n"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B442" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C442" s="6" t="inlineStr">
+        <is>
+          <t>Other Billable Common Area</t>
+        </is>
+      </c>
+      <c r="D442" s="22" t="n">
+        <v>65458</v>
+      </c>
+      <c r="E442" s="6" t="n"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B443" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C443" s="6" t="inlineStr">
+        <is>
+          <t>Other Billable CA (contra)</t>
+        </is>
+      </c>
+      <c r="D443" s="22" t="n">
+        <v>-5646</v>
+      </c>
+      <c r="E443" s="6" t="n"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B444" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C444" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp Reimb Accrual</t>
+        </is>
+      </c>
+      <c r="D444" s="22" t="n">
+        <v>9080</v>
+      </c>
+      <c r="E444" s="6" t="n"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B445" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C445" s="6" t="inlineStr">
+        <is>
+          <t>Other Direct Billable-Non-FI</t>
+        </is>
+      </c>
+      <c r="D445" s="22" t="n">
+        <v>297</v>
+      </c>
+      <c r="E445" s="6" t="n"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B446" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C446" s="6" t="inlineStr">
+        <is>
+          <t>Tenant Damage Fee</t>
+        </is>
+      </c>
+      <c r="D446" s="22" t="n">
+        <v>52982</v>
+      </c>
+      <c r="E446" s="6" t="n"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="11" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B447" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C447" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D447" s="23" t="n">
+        <v>797212</v>
+      </c>
+      <c r="E447" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $797,212. Statement prints whole dollars; group subtotals entered AS PRINTED (line-item sums differ by small rounding). Source quirk: the [NB] Gas Vacancy line is included in the printed Direct-Billable subtotal but excluded from the Property-Operating rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B448" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C448" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Security</t>
+        </is>
+      </c>
+      <c r="D448" s="22" t="n">
+        <v>7701</v>
+      </c>
+      <c r="E448" s="6" t="n"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B449" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C449" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Security</t>
+        </is>
+      </c>
+      <c r="D449" s="22" t="n">
+        <v>510</v>
+      </c>
+      <c r="E449" s="6" t="n"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B450" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C450" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Property Management</t>
+        </is>
+      </c>
+      <c r="D450" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E450" s="6" t="n"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B451" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C451" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Maintenance Services</t>
+        </is>
+      </c>
+      <c r="D451" s="22" t="n">
+        <v>13592</v>
+      </c>
+      <c r="E451" s="6" t="n"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B452" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C452" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Electrical and Lighting</t>
+        </is>
+      </c>
+      <c r="D452" s="22" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E452" s="6" t="n"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B453" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C453" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Roof Maintenance</t>
+        </is>
+      </c>
+      <c r="D453" s="22" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E453" s="6" t="n"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B454" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C454" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] HVAC and Equipment</t>
+        </is>
+      </c>
+      <c r="D454" s="22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E454" s="6" t="n"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B455" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C455" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Window Cleaning</t>
+        </is>
+      </c>
+      <c r="D455" s="22" t="n">
+        <v>412</v>
+      </c>
+      <c r="E455" s="6" t="n"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B456" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C456" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D456" s="22" t="n">
+        <v>1655</v>
+      </c>
+      <c r="E456" s="6" t="n"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B457" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C457" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Fire Life Safety Repairs</t>
+        </is>
+      </c>
+      <c r="D457" s="22" t="n">
+        <v>1815</v>
+      </c>
+      <c r="E457" s="6" t="n"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B458" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C458" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] General Maintenance</t>
+        </is>
+      </c>
+      <c r="D458" s="22" t="n">
+        <v>1676</v>
+      </c>
+      <c r="E458" s="6" t="n"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B459" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C459" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Cleaning Services</t>
+        </is>
+      </c>
+      <c r="D459" s="22" t="n">
+        <v>3434</v>
+      </c>
+      <c r="E459" s="6" t="n"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B460" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C460" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Debris Removal - Reactive</t>
+        </is>
+      </c>
+      <c r="D460" s="22" t="n">
+        <v>1082</v>
+      </c>
+      <c r="E460" s="6" t="n"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B461" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C461" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Parking Lot Sweeping</t>
+        </is>
+      </c>
+      <c r="D461" s="22" t="n">
+        <v>1587</v>
+      </c>
+      <c r="E461" s="6" t="n"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B462" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C462" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract Landscaping</t>
+        </is>
+      </c>
+      <c r="D462" s="22" t="n">
+        <v>4748</v>
+      </c>
+      <c r="E462" s="6" t="n"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B463" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C463" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Landscaping - Reactive</t>
+        </is>
+      </c>
+      <c r="D463" s="22" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E463" s="6" t="n"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B464" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C464" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Irrigation - Reactive</t>
+        </is>
+      </c>
+      <c r="D464" s="22" t="n">
+        <v>2409</v>
+      </c>
+      <c r="E464" s="6" t="n"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B465" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C465" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Snow Removal</t>
+        </is>
+      </c>
+      <c r="D465" s="22" t="n">
+        <v>30101</v>
+      </c>
+      <c r="E465" s="6" t="n"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B466" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C466" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D466" s="22" t="n">
+        <v>410137</v>
+      </c>
+      <c r="E466" s="6" t="n"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B467" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C467" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Real Estate Tax Mgmt</t>
+        </is>
+      </c>
+      <c r="D467" s="22" t="n">
+        <v>29</v>
+      </c>
+      <c r="E467" s="6" t="n"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B468" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C468" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Electric</t>
+        </is>
+      </c>
+      <c r="D468" s="22" t="n">
+        <v>1496</v>
+      </c>
+      <c r="E468" s="6" t="n"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B469" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C469" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D469" s="22" t="n">
+        <v>12042</v>
+      </c>
+      <c r="E469" s="6" t="n"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B470" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C470" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Gas</t>
+        </is>
+      </c>
+      <c r="D470" s="22" t="n">
+        <v>1722</v>
+      </c>
+      <c r="E470" s="6" t="n"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B471" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C471" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Utility Management Costs</t>
+        </is>
+      </c>
+      <c r="D471" s="22" t="n">
+        <v>256</v>
+      </c>
+      <c r="E471" s="6" t="n"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B472" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C472" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Property &amp; General Liability Ins.</t>
+        </is>
+      </c>
+      <c r="D472" s="22" t="n">
+        <v>20937</v>
+      </c>
+      <c r="E472" s="6" t="n"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B473" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C473" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Environmental Insurance</t>
+        </is>
+      </c>
+      <c r="D473" s="22" t="n">
+        <v>55</v>
+      </c>
+      <c r="E473" s="6" t="n"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B474" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C474" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Insurance Deductible</t>
+        </is>
+      </c>
+      <c r="D474" s="22" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E474" s="6" t="inlineStr">
+        <is>
+          <t>Reimbursable subtotal as printed: $549,620</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B475" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C475" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Dock Door Repairs</t>
+        </is>
+      </c>
+      <c r="D475" s="22" t="n">
+        <v>297</v>
+      </c>
+      <c r="E475" s="6" t="n"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B476" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C476" s="6" t="inlineStr">
+        <is>
+          <t>[NB/DB] Gas Vacancy</t>
+        </is>
+      </c>
+      <c r="D476" s="22" t="n">
+        <v>720</v>
+      </c>
+      <c r="E476" s="6" t="inlineStr">
+        <is>
+          <t>printed in DB subtotal ($1,017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B477" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C477" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Security</t>
+        </is>
+      </c>
+      <c r="D477" s="22" t="n">
+        <v>7649</v>
+      </c>
+      <c r="E477" s="6" t="n"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B478" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C478" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Tenant Moveout Damage</t>
+        </is>
+      </c>
+      <c r="D478" s="22" t="n">
+        <v>1176</v>
+      </c>
+      <c r="E478" s="6" t="n"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B479" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C479" s="6" t="inlineStr">
+        <is>
+          <t>[NB] HVAC and Equipment</t>
+        </is>
+      </c>
+      <c r="D479" s="22" t="n">
+        <v>360</v>
+      </c>
+      <c r="E479" s="6" t="n"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B480" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C480" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Electric Vacancy</t>
+        </is>
+      </c>
+      <c r="D480" s="22" t="n">
+        <v>5596</v>
+      </c>
+      <c r="E480" s="6" t="n"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B481" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C481" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Cleaning &amp; Janitorial</t>
+        </is>
+      </c>
+      <c r="D481" s="22" t="n">
+        <v>178</v>
+      </c>
+      <c r="E481" s="6" t="n"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B482" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C482" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Corporate Management</t>
+        </is>
+      </c>
+      <c r="D482" s="22" t="n">
+        <v>6921</v>
+      </c>
+      <c r="E482" s="6" t="n"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B483" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C483" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Insurance deductible exp</t>
+        </is>
+      </c>
+      <c r="D483" s="22" t="n">
+        <v>337</v>
+      </c>
+      <c r="E483" s="6" t="n"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B484" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C484" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Lock and Access</t>
+        </is>
+      </c>
+      <c r="D484" s="22" t="n">
+        <v>404</v>
+      </c>
+      <c r="E484" s="6" t="n"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B485" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C485" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Marketing/Leasing Costs</t>
+        </is>
+      </c>
+      <c r="D485" s="22" t="n">
+        <v>593</v>
+      </c>
+      <c r="E485" s="6" t="n"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B486" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C486" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Vacancy Repairs &amp; Maint.</t>
+        </is>
+      </c>
+      <c r="D486" s="22" t="n">
+        <v>7858</v>
+      </c>
+      <c r="E486" s="6" t="n"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B487" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C487" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Professional Fees</t>
+        </is>
+      </c>
+      <c r="D487" s="22" t="n">
+        <v>1538</v>
+      </c>
+      <c r="E487" s="6" t="n"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B488" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C488" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Legal Fees</t>
+        </is>
+      </c>
+      <c r="D488" s="22" t="n">
+        <v>9592</v>
+      </c>
+      <c r="E488" s="6" t="inlineStr">
+        <is>
+          <t>Non-billable subtotal as printed: $42,202</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B489" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C489" s="6" t="inlineStr">
+        <is>
+          <t>[REO] Prior Year Real Estate Tax</t>
+        </is>
+      </c>
+      <c r="D489" s="22" t="n">
+        <v>-2321</v>
+      </c>
+      <c r="E489" s="6" t="n"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B490" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C490" s="6" t="inlineStr">
+        <is>
+          <t>Professional Fees (G&amp;A)</t>
+        </is>
+      </c>
+      <c r="D490" s="22" t="n">
+        <v>484</v>
+      </c>
+      <c r="E490" s="6" t="inlineStr">
+        <is>
+          <t>Property-operating total as printed: $590,282</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B491" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C491" s="6" t="inlineStr">
+        <is>
+          <t>Land Improvements Depreciation</t>
+        </is>
+      </c>
+      <c r="D491" s="22" t="n">
+        <v>63617</v>
+      </c>
+      <c r="E491" s="6" t="n"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B492" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C492" s="6" t="inlineStr">
+        <is>
+          <t>Building Additions Depreciation</t>
+        </is>
+      </c>
+      <c r="D492" s="22" t="n">
+        <v>361833</v>
+      </c>
+      <c r="E492" s="6" t="n"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B493" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C493" s="6" t="inlineStr">
+        <is>
+          <t>Equip/Marketing/Signage Depreciation</t>
+        </is>
+      </c>
+      <c r="D493" s="22" t="n">
+        <v>237</v>
+      </c>
+      <c r="E493" s="6" t="n"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B494" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C494" s="6" t="inlineStr">
+        <is>
+          <t>TI Depreciation</t>
+        </is>
+      </c>
+      <c r="D494" s="22" t="n">
+        <v>56463</v>
+      </c>
+      <c r="E494" s="6" t="n"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="6" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B495" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C495" s="6" t="inlineStr">
+        <is>
+          <t>Amort - Deferred Leasing Costs</t>
+        </is>
+      </c>
+      <c r="D495" s="22" t="n">
+        <v>23816</v>
+      </c>
+      <c r="E495" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A total as printed: $505,966</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="11" t="inlineStr">
+        <is>
+          <t>3250 Abilene St — FY2024</t>
+        </is>
+      </c>
+      <c r="B496" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C496" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D496" s="23" t="n">
+        <v>1096249</v>
+      </c>
+      <c r="E496" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,096,249. Statement prints whole dollars; group subtotals entered AS PRINTED (line-item sums differ by small rounding). Source quirk: the [NB] Gas Vacancy line is included in the printed Direct-Billable subtotal but excluded from the Property-Operating rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B497" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C497" s="6" t="inlineStr">
+        <is>
+          <t>Rental Income-Base</t>
+        </is>
+      </c>
+      <c r="D497" s="22" t="n">
+        <v>436928</v>
+      </c>
+      <c r="E497" s="6" t="n"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B498" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C498" s="6" t="inlineStr">
+        <is>
+          <t>Free Rent</t>
+        </is>
+      </c>
+      <c r="D498" s="22" t="n">
+        <v>-38271</v>
+      </c>
+      <c r="E498" s="6" t="n"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B499" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C499" s="6" t="inlineStr">
+        <is>
+          <t>Rental Income-SLR (non-cash)</t>
+        </is>
+      </c>
+      <c r="D499" s="22" t="n">
+        <v>48067</v>
+      </c>
+      <c r="E499" s="6" t="n"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B500" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C500" s="6" t="inlineStr">
+        <is>
+          <t>Mgmt Fees reimb.</t>
+        </is>
+      </c>
+      <c r="D500" s="22" t="n">
+        <v>23852</v>
+      </c>
+      <c r="E500" s="6" t="n"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B501" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C501" s="6" t="inlineStr">
+        <is>
+          <t>Mgmt Fees - JE</t>
+        </is>
+      </c>
+      <c r="D501" s="22" t="n">
+        <v>-307</v>
+      </c>
+      <c r="E501" s="6" t="n"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B502" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C502" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes reimb.</t>
+        </is>
+      </c>
+      <c r="D502" s="22" t="n">
+        <v>168965</v>
+      </c>
+      <c r="E502" s="6" t="n"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B503" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C503" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes - JE</t>
+        </is>
+      </c>
+      <c r="D503" s="22" t="n">
+        <v>-11288</v>
+      </c>
+      <c r="E503" s="6" t="n"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B504" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C504" s="6" t="inlineStr">
+        <is>
+          <t>Utilities-Others reimb.</t>
+        </is>
+      </c>
+      <c r="D504" s="22" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E504" s="6" t="n"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B505" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C505" s="6" t="inlineStr">
+        <is>
+          <t>Utilities-Others - JE</t>
+        </is>
+      </c>
+      <c r="D505" s="22" t="n">
+        <v>-114</v>
+      </c>
+      <c r="E505" s="6" t="n"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B506" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C506" s="6" t="inlineStr">
+        <is>
+          <t>Insurance reimb.</t>
+        </is>
+      </c>
+      <c r="D506" s="22" t="n">
+        <v>5561</v>
+      </c>
+      <c r="E506" s="6" t="n"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B507" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C507" s="6" t="inlineStr">
+        <is>
+          <t>Insurance - JE</t>
+        </is>
+      </c>
+      <c r="D507" s="22" t="n">
+        <v>-166</v>
+      </c>
+      <c r="E507" s="6" t="n"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B508" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C508" s="6" t="inlineStr">
+        <is>
+          <t>Other Billable Common Area</t>
+        </is>
+      </c>
+      <c r="D508" s="22" t="n">
+        <v>66511</v>
+      </c>
+      <c r="E508" s="6" t="n"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B509" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C509" s="6" t="inlineStr">
+        <is>
+          <t>Other Billable Common Area (add'l)</t>
+        </is>
+      </c>
+      <c r="D509" s="22" t="n">
+        <v>12040</v>
+      </c>
+      <c r="E509" s="6" t="n"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B510" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C510" s="6" t="inlineStr">
+        <is>
+          <t>Operating Exp Reimb Accrual</t>
+        </is>
+      </c>
+      <c r="D510" s="22" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E510" s="6" t="n"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B511" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C511" s="6" t="inlineStr">
+        <is>
+          <t>Utilities (direct billable)</t>
+        </is>
+      </c>
+      <c r="D511" s="22" t="n">
+        <v>-113</v>
+      </c>
+      <c r="E511" s="6" t="n"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B512" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C512" s="6" t="inlineStr">
+        <is>
+          <t>Other Direct Billable-Non-FI</t>
+        </is>
+      </c>
+      <c r="D512" s="22" t="n">
+        <v>-45</v>
+      </c>
+      <c r="E512" s="6" t="n"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B513" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C513" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt - Contra Revenue</t>
+        </is>
+      </c>
+      <c r="D513" s="22" t="n">
+        <v>-16167</v>
+      </c>
+      <c r="E513" s="6" t="n"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B514" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C514" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt - Additional Reserve</t>
+        </is>
+      </c>
+      <c r="D514" s="22" t="n">
+        <v>-4111</v>
+      </c>
+      <c r="E514" s="6" t="n"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B515" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C515" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt - Reversal (Cash Coll.)</t>
+        </is>
+      </c>
+      <c r="D515" s="22" t="n">
+        <v>4221</v>
+      </c>
+      <c r="E515" s="6" t="n"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B516" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C516" s="6" t="inlineStr">
+        <is>
+          <t>Bad Debt - Reversal Due to Credit</t>
+        </is>
+      </c>
+      <c r="D516" s="22" t="n">
+        <v>16167</v>
+      </c>
+      <c r="E516" s="6" t="n"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="11" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B517" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C517" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D517" s="23" t="n">
+        <v>714461</v>
+      </c>
+      <c r="E517" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $714,461. Statement prints whole dollars; group subtotals entered AS PRINTED (line-item sums differ by small rounding). Source quirk: the [NB] Gas Vacancy line is included in the printed Direct-Billable subtotal but excluded from the Property-Operating rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B518" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C518" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Security</t>
+        </is>
+      </c>
+      <c r="D518" s="22" t="n">
+        <v>5705</v>
+      </c>
+      <c r="E518" s="6" t="n"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B519" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C519" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Property Management</t>
+        </is>
+      </c>
+      <c r="D519" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E519" s="6" t="n"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B520" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C520" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Maintenance Services</t>
+        </is>
+      </c>
+      <c r="D520" s="22" t="n">
+        <v>5809</v>
+      </c>
+      <c r="E520" s="6" t="n"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B521" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C521" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Electrical and Lighting</t>
+        </is>
+      </c>
+      <c r="D521" s="22" t="n">
+        <v>250</v>
+      </c>
+      <c r="E521" s="6" t="n"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B522" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C522" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Roof Maintenance</t>
+        </is>
+      </c>
+      <c r="D522" s="22" t="n">
+        <v>1864</v>
+      </c>
+      <c r="E522" s="6" t="n"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B523" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C523" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] HVAC and Equipment</t>
+        </is>
+      </c>
+      <c r="D523" s="22" t="n">
+        <v>285</v>
+      </c>
+      <c r="E523" s="6" t="n"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B524" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C524" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Window Cleaning</t>
+        </is>
+      </c>
+      <c r="D524" s="22" t="n">
+        <v>706</v>
+      </c>
+      <c r="E524" s="6" t="n"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B525" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C525" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D525" s="22" t="n">
+        <v>1125</v>
+      </c>
+      <c r="E525" s="6" t="n"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B526" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C526" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] General Maintenance</t>
+        </is>
+      </c>
+      <c r="D526" s="22" t="n">
+        <v>1546</v>
+      </c>
+      <c r="E526" s="6" t="n"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B527" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C527" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Parking Lot Sweeping (a)</t>
+        </is>
+      </c>
+      <c r="D527" s="22" t="n">
+        <v>135</v>
+      </c>
+      <c r="E527" s="6" t="n"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B528" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C528" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract - Cleaning Services</t>
+        </is>
+      </c>
+      <c r="D528" s="22" t="n">
+        <v>2367</v>
+      </c>
+      <c r="E528" s="6" t="n"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B529" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C529" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Parking Lot Sweeping (b)</t>
+        </is>
+      </c>
+      <c r="D529" s="22" t="n">
+        <v>1567</v>
+      </c>
+      <c r="E529" s="6" t="n"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B530" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C530" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Contract Landscaping</t>
+        </is>
+      </c>
+      <c r="D530" s="22" t="n">
+        <v>2628</v>
+      </c>
+      <c r="E530" s="6" t="n"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B531" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C531" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Landscaping - Reactive</t>
+        </is>
+      </c>
+      <c r="D531" s="22" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E531" s="6" t="n"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B532" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C532" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Irrigation - Reactive</t>
+        </is>
+      </c>
+      <c r="D532" s="22" t="n">
+        <v>3293</v>
+      </c>
+      <c r="E532" s="6" t="n"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B533" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C533" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Snow Removal</t>
+        </is>
+      </c>
+      <c r="D533" s="22" t="n">
+        <v>27052</v>
+      </c>
+      <c r="E533" s="6" t="n"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B534" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C534" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D534" s="22" t="n">
+        <v>188633</v>
+      </c>
+      <c r="E534" s="6" t="n"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B535" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C535" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Real Estate Tax Mgmt</t>
+        </is>
+      </c>
+      <c r="D535" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="E535" s="6" t="n"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B536" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C536" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Electric</t>
+        </is>
+      </c>
+      <c r="D536" s="22" t="n">
+        <v>929</v>
+      </c>
+      <c r="E536" s="6" t="n"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B537" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C537" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Utility Management Costs</t>
+        </is>
+      </c>
+      <c r="D537" s="22" t="n">
+        <v>151</v>
+      </c>
+      <c r="E537" s="6" t="n"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B538" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C538" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Property &amp; General Liability Ins.</t>
+        </is>
+      </c>
+      <c r="D538" s="22" t="n">
+        <v>6180</v>
+      </c>
+      <c r="E538" s="6" t="n"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B539" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C539" s="6" t="inlineStr">
+        <is>
+          <t>[CAM] Environmental Insurance</t>
+        </is>
+      </c>
+      <c r="D539" s="22" t="n">
+        <v>276</v>
+      </c>
+      <c r="E539" s="6" t="inlineStr">
+        <is>
+          <t>Reimbursable subtotal as printed: $251,626</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B540" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C540" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D540" s="22" t="n">
+        <v>-1457</v>
+      </c>
+      <c r="E540" s="6" t="n"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B541" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C541" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Plumbing and Sewer Maint.</t>
+        </is>
+      </c>
+      <c r="D541" s="22" t="n">
+        <v>882</v>
+      </c>
+      <c r="E541" s="6" t="n"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B542" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C542" s="6" t="inlineStr">
+        <is>
+          <t>[DB] HVAC and Equipment</t>
+        </is>
+      </c>
+      <c r="D542" s="22" t="n">
+        <v>530</v>
+      </c>
+      <c r="E542" s="6" t="n"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B543" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C543" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Electric</t>
+        </is>
+      </c>
+      <c r="D543" s="22" t="n">
+        <v>102</v>
+      </c>
+      <c r="E543" s="6" t="n"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B544" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C544" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Gas</t>
+        </is>
+      </c>
+      <c r="D544" s="22" t="n">
+        <v>310</v>
+      </c>
+      <c r="E544" s="6" t="n"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B545" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C545" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Accrued Electric Expense</t>
+        </is>
+      </c>
+      <c r="D545" s="22" t="n">
+        <v>-63</v>
+      </c>
+      <c r="E545" s="6" t="n"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B546" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C546" s="6" t="inlineStr">
+        <is>
+          <t>[DB] Accrued Gas Expense</t>
+        </is>
+      </c>
+      <c r="D546" s="22" t="n">
+        <v>-463</v>
+      </c>
+      <c r="E546" s="6" t="n"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B547" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C547" s="6" t="inlineStr">
+        <is>
+          <t>[NB/DB] Gas Vacancy</t>
+        </is>
+      </c>
+      <c r="D547" s="22" t="n">
+        <v>3782</v>
+      </c>
+      <c r="E547" s="6" t="inlineStr">
+        <is>
+          <t>printed in DB subtotal ($3,623)</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B548" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C548" s="6" t="inlineStr">
+        <is>
+          <t>[NB] HVAC and Equipment</t>
+        </is>
+      </c>
+      <c r="D548" s="22" t="n">
+        <v>1685</v>
+      </c>
+      <c r="E548" s="6" t="n"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B549" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C549" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Electric Vacancy</t>
+        </is>
+      </c>
+      <c r="D549" s="22" t="n">
+        <v>490</v>
+      </c>
+      <c r="E549" s="6" t="n"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B550" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C550" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Corporate Management</t>
+        </is>
+      </c>
+      <c r="D550" s="22" t="n">
+        <v>6962</v>
+      </c>
+      <c r="E550" s="6" t="n"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B551" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C551" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Insurance deductible exp</t>
+        </is>
+      </c>
+      <c r="D551" s="22" t="n">
+        <v>337</v>
+      </c>
+      <c r="E551" s="6" t="n"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B552" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C552" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Lock and Access</t>
+        </is>
+      </c>
+      <c r="D552" s="22" t="n">
+        <v>404</v>
+      </c>
+      <c r="E552" s="6" t="n"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B553" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C553" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Tenant Relations</t>
+        </is>
+      </c>
+      <c r="D553" s="22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E553" s="6" t="n"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B554" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C554" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Vacancy Repairs &amp; Maint.</t>
+        </is>
+      </c>
+      <c r="D554" s="22" t="n">
+        <v>2010</v>
+      </c>
+      <c r="E554" s="6" t="n"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B555" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C555" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Professional Fees</t>
+        </is>
+      </c>
+      <c r="D555" s="22" t="n">
+        <v>38</v>
+      </c>
+      <c r="E555" s="6" t="n"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B556" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C556" s="6" t="inlineStr">
+        <is>
+          <t>[NB] Legal Fees</t>
+        </is>
+      </c>
+      <c r="D556" s="22" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E556" s="6" t="inlineStr">
+        <is>
+          <t>Non-billable subtotal as printed: $13,891</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B557" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C557" s="6" t="inlineStr">
+        <is>
+          <t>[REO] Prior Year Real Estate Tax</t>
+        </is>
+      </c>
+      <c r="D557" s="22" t="n">
+        <v>1218</v>
+      </c>
+      <c r="E557" s="6" t="inlineStr">
+        <is>
+          <t>Property-operating total as printed: $266,577</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B558" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C558" s="6" t="inlineStr">
+        <is>
+          <t>Land Improvements Depreciation</t>
+        </is>
+      </c>
+      <c r="D558" s="22" t="n">
+        <v>19714</v>
+      </c>
+      <c r="E558" s="6" t="n"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B559" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C559" s="6" t="inlineStr">
+        <is>
+          <t>Building Additions Depreciation</t>
+        </is>
+      </c>
+      <c r="D559" s="22" t="n">
+        <v>206941</v>
+      </c>
+      <c r="E559" s="6" t="n"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B560" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C560" s="6" t="inlineStr">
+        <is>
+          <t>Equip/Marketing/Signage Depreciation</t>
+        </is>
+      </c>
+      <c r="D560" s="22" t="n">
+        <v>580</v>
+      </c>
+      <c r="E560" s="6" t="n"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B561" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C561" s="6" t="inlineStr">
+        <is>
+          <t>TI Depreciation</t>
+        </is>
+      </c>
+      <c r="D561" s="22" t="n">
+        <v>70015</v>
+      </c>
+      <c r="E561" s="6" t="n"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="6" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B562" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C562" s="6" t="inlineStr">
+        <is>
+          <t>Amort - Deferred Leasing Costs</t>
+        </is>
+      </c>
+      <c r="D562" s="22" t="n">
+        <v>36279</v>
+      </c>
+      <c r="E562" s="6" t="inlineStr">
+        <is>
+          <t>D&amp;A total as printed: $333,529</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="11" t="inlineStr">
+        <is>
+          <t>14705 E 33rd Pl — FY2024</t>
+        </is>
+      </c>
+      <c r="B563" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C563" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D563" s="23" t="n">
+        <v>600106</v>
+      </c>
+      <c r="E563" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $600,106. Statement prints whole dollars; group subtotals entered AS PRINTED (line-item sums differ by small rounding). Source quirk: the [NB] Gas Vacancy line is included in the printed Direct-Billable subtotal but excluded from the Property-Operating rollup.</t>
         </is>
       </c>
     </row>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -656,11 +656,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-07-30  |  8 subject properties, all Adams County, Colorado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Prepared for Carter Equities  |  Updated 2026-08-04  |  11 source documents — lease &amp; income/expense data only (market/comp support excluded)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,35 +969,133 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0085571_1540_Altura_Blvd.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal package — income approach + CubeSmart FY2024 income statement + LOA + parcel schedule</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (CubeSmart #6731), Aurora</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025 (LOV 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / CubeSmart</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0086010_15413_E_18th_Avenue.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Abatement petition + income approach + CubeSmart FY2024 income statement + storEDGE occupancy + LOA</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (CubeSmart #6730), Aurora</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 / Value Yr 2026 (LOV 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / CubeSmart</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0040829_self_storage.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal package — income approach + Mini U Storage FY2024/23 NOI statement + rental activity + LOA</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St (Mini U Storage), Thornton</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Value Yr 2025/2026 (LOV 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / Dahn Corp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1"/>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Self-storage packages: CubeSmart/Mini U income statements are store-level accrual NOI statements (property tax &amp; 3rd-party mgmt fees included; interest/depreciation excluded except where noted). Cushman &amp; Wakefield investor-survey pages in R0040829 (market support) were skipped per database scope.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1151,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2049,6 +2145,339 @@
       <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>R0092302.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R0085571</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>R0085571</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0182131405022</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Aurora Altura Boulevard CS 6731</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 731</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC/PTA USI No 731</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Specialty - Self-Storage</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Multi (storage units, MTM)</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>89298</v>
+      </c>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="8" t="n">
+        <v>27139</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>1978</v>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>3.29:1</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>— (not stated in package)</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>3309468</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>2546900</v>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart (store #6731)</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>R0085571_1540_Altura_Blvd.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>R0086010</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>R0086010</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0182132318001</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Aurora - 18th Avenue - CS - 6730</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 730</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC/PTA USI No 730</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Self Storage</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Multi (478 storage units, MTM)</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>203817</v>
+      </c>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="8" t="n">
+        <v>57742</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>1984</v>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>3.53:1 (calc)</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>87% (Jun 2024); 87.3% of SF (Dec 2024)</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>8187500</v>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>2026 (petition Tax Yr 2025)</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>6610000</v>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart (store #6730)</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>R0086010_15413_E_18th_Avenue.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>R0040829</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0040829</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>0171914201013</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Thornton (TH) - Dahn - 21548 (Mini U Storage)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Thornton</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>80229</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund B</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund B</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Self Storage</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Multi (471 storage units, MTM)</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>127395</v>
+      </c>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="8" t="n">
+        <v>48250</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>2.64:1 (calc)</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>84% (Jun 2024); 83.9% of SF (Dec 2024)</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>5428808</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026 (LOV 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>Dahn Corporation (Mini U Storage)</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>R0040829_self_storage.pdf</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2096,11 +2525,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Actual tenants &amp; rent rolls (125 Bridge St, 5970 Marion) and proforma lease assumptions (tax appeals)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Actual tenants &amp; rent rolls (125 Bridge St, 5970 Marion), tax-appeal proforma assumptions, and self-storage occupancy/unit-mix snapshots</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3131,10 +3559,615 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Self-storage facilities — occupancy &amp; unit-mix snapshots as of 12/31/2024 (month-to-month unit rentals; no individual tenant leases)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="20" t="n"/>
+      <c r="M27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>27,139 SF NLA</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage customers (CubeSmart #6731)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="5" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>No unit-level report in package; FY2024 net rental income $383,166 (see Income-Expense Detail)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>478 units / 57,742 SF</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage customers (CubeSmart #6730)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>62425.7</v>
+      </c>
+      <c r="F29" s="6" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="5" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="9" t="n"/>
+      <c r="L29" s="6" t="n"/>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>storEDGE Consolidated Occupancy 12/31/2024: 395 occupied / 72 vacant / 6 reserved / 5 unrentable; 50,433 SF occupied (87.3% of SF; 82.6% of units); scheduled std rent $54,314/mo; occupied actual $62,425.70/mo ($1.24/SF/mo). Per-size detail in source PDF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>471 units / 48,250 SF</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage customers (Mini U Storage)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>SiteLink Rental Activity 12/31/2024 (drive-up units): 395 rented / 76 vacant; 41,130 SF rented (83.9% of SF); gross potential $65,937/mo; rented avg $1.53/SF/mo. Unit-mix below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>5x5 (25 SF)</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>30 units / 18 rented</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="n">
+        <v>1950</v>
+      </c>
+      <c r="F31" s="6" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="9" t="n"/>
+      <c r="L31" s="6" t="n"/>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $65/unit/mo; 450 SF rented of 750 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>5x10 (50 SF)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>137 units / 120 rented</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n">
+        <v>11645</v>
+      </c>
+      <c r="F32" s="6" t="n"/>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="5" t="n"/>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $85/unit/mo; 6,000 SF rented of 6,850 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>7x10 (70 SF)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>58 units / 49 rented</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n">
+        <v>6670</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="5" t="n"/>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $115/unit/mo; 3,430 SF rented of 4,060 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>5x15 (75 SF)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>30 units / 22 rented</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>3570</v>
+      </c>
+      <c r="F34" s="6" t="n"/>
+      <c r="G34" s="6" t="n"/>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="5" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $119/unit/mo; 1,650 SF rented of 2,250 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>10x10 (100 SF)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>76 units / 66 rented</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>11324</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="5" t="n"/>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $149/unit/mo; 6,600 SF rented of 7,600 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>7x20 (140 SF)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>1 units / 0 rented</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>159</v>
+      </c>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="5" t="n"/>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $159/unit/mo; 0 SF rented of 140 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>10x15 (150 SF)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>68 units / 58 rented</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>11900</v>
+      </c>
+      <c r="F37" s="6" t="n"/>
+      <c r="G37" s="6" t="n"/>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="5" t="n"/>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $175/unit/mo; 8,700 SF rented of 10,200 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>10x20 (200 SF)</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>47 units / 43 rented</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>11703</v>
+      </c>
+      <c r="F38" s="6" t="n"/>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $249/unit/mo; 8,600 SF rented of 9,400 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>20x10 (200 SF)</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>5 units / 3 rented</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>1125</v>
+      </c>
+      <c r="F39" s="6" t="n"/>
+      <c r="G39" s="6" t="n"/>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="5" t="n"/>
+      <c r="K39" s="9" t="n"/>
+      <c r="L39" s="6" t="n"/>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $225/unit/mo; 600 SF rented of 1,000 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>10x30 (300 SF)</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>17 units / 15 rented</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>5083</v>
+      </c>
+      <c r="F40" s="6" t="n"/>
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="5" t="n"/>
+      <c r="K40" s="9" t="n"/>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $299/unit/mo; 4,500 SF rented of 5,100 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>15x20 (300 SF)</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>1 units / 0 rented</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>299</v>
+      </c>
+      <c r="F41" s="6" t="n"/>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="5" t="n"/>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" s="6" t="n"/>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $299/unit/mo; 0 SF rented of 300 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>20x30 (600 SF)</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>1 units / 1 rented</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Storage MTM</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>509</v>
+      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>Std rate $509/unit/mo; 600 SF rented of 600 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="inlineStr">
+        <is>
+          <t>471 units / 395 rented</t>
+        </is>
+      </c>
+      <c r="D43" s="13" t="n"/>
+      <c r="E43" s="14">
+        <f>SUM(E31:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="14" t="n"/>
+      <c r="G43" s="13" t="n"/>
+      <c r="H43" s="13" t="n"/>
+      <c r="I43" s="13" t="n"/>
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="15" t="inlineStr">
+        <is>
+          <t>Gross scheduled (potential) monthly rent; printed total $65,937 (SiteLink Rental Activity 12/31/2024)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A27:M27"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="A2:M2"/>
@@ -3149,7 +4182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3176,7 +4209,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,241 +4417,417 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3309468</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>2546900</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>3571199</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>R0085571</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="21" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>8187500</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>6610000</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>R0086010</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>5428808</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>112.51</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>R0040829</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).  R0085571: 2025 Land $312,543 / Imp $2,996,925; 2024 total $3,571,199 ($131.59/SF). R0086010: 2026 Land $1,834,350 / Imp $6,353,150. R0040829: Land $955,465 / Imp $4,473,343.</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="21" t="n"/>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>4832500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Dr</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>209100</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>-10455</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>198645</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>182753</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>12260 Pennsylvania St</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>237290</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>-16610</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>220680</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>-22068</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>198612</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>2837000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>6770 E. 56th Ave</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>115824</v>
+        <v>359394</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>-5791</v>
+        <v>-17970</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>110033</v>
+        <v>341424</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>-5502</v>
+        <v>-27314</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>104531</v>
+        <v>314110</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>1493302</v>
+        <v>4832500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>17608 E. 24th Dr</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>209100</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-10455</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>198645</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-15892</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>182753</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>3050000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>-16610</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>220680</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-22068</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>198612</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>2837000</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>1493302</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B23" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C23" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D23" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E23" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F23" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G23" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H23" s="14" t="n">
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="21" t="n"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>413870</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>413870</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-248322</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>165548</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <v>2546900</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>750646</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-90078</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>660568</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>-231199</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>429370</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>6610000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>796125</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>-119419</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>676706</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>-372188</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>304518</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>4510000</v>
+      </c>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915). Self-storage proformas (Ryan): Altura EGI at 0% vacancy, OpEx 60% of EGI; 18th Ave base rent $13.00/SF NNN, 12% vacancy, non-reimbursable expenses 35%; Washington St base rent $16.50/SF NNN, 15% vacancy, non-reimbursable expenses 55%. Indicated values rounded by preparer.</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +4839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +4863,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +4977,111 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (CubeSmart #6731) — FY2024</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>414633.83</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>328355.94</v>
+      </c>
+      <c r="D9" s="23">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart consolidated income statement (store-level NOI basis; incl. property tax &amp; 3rd-party mgmt fee)</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (CubeSmart #6730) — FY2024</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>783123.25</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>499759.18</v>
+      </c>
+      <c r="D10" s="23">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart consolidated income statement (store-level NOI basis; incl. property tax &amp; 3rd-party mgmt fee)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>10350 Washington St (Mini U) — FY2024</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>790386.21</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>533121.11</v>
+      </c>
+      <c r="D11" s="23">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Mini U Storage NOI &amp; NI detail (NOI basis; excl. interest/extraordinary — net cash flow before D&amp;A $158,744.75)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>10350 Washington St (Mini U) — FY2023</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>899471.29</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>590318.63</v>
+      </c>
+      <c r="D12" s="23">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Mini U Storage NOI &amp; NI detail, prior year (NOI basis; net cash flow before D&amp;A $162,198.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +5093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +5117,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5207,6 +6501,4117 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>383165.98</v>
+      </c>
+      <c r="E66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>4281 - Admin Fee</t>
+        </is>
+      </c>
+      <c r="D67" s="22" t="n">
+        <v>6322</v>
+      </c>
+      <c r="E67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>4282 - Late Fee Revenue</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>29772.29</v>
+      </c>
+      <c r="E68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>4283 - Other Fee Revenue</t>
+        </is>
+      </c>
+      <c r="D69" s="22" t="n">
+        <v>294.71</v>
+      </c>
+      <c r="E69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>4284 - NSF Fees</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>90</v>
+      </c>
+      <c r="E70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>4286 - Convenience Fee Payments</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="n">
+        <v>2910.49</v>
+      </c>
+      <c r="E71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>4285 - Fees Waived</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="n">
+        <v>-23.55</v>
+      </c>
+      <c r="E72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>4287 - Fees Waived - Admin</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="n">
+        <v>-58</v>
+      </c>
+      <c r="E73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>4288 - Fees Waived - Late Fee</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="n">
+        <v>-1359.52</v>
+      </c>
+      <c r="E74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>4255 - Credit Card Chargebacks</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>-265</v>
+      </c>
+      <c r="E75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>7102 - Fees Written Off</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>-6215.58</v>
+      </c>
+      <c r="E76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>4999 - Miscellaneous</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B78" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D78" s="23">
+        <f>SUM(D66:D77)</f>
+        <v/>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $414,633.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>6100 - Payroll</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>50113.05</v>
+      </c>
+      <c r="E79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>6112 - Medical Expense</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="n">
+        <v>10224</v>
+      </c>
+      <c r="E80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>6118 - 401K Expense</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="n">
+        <v>524.02</v>
+      </c>
+      <c r="E81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>6128 - Teammate Rewards</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="n">
+        <v>120</v>
+      </c>
+      <c r="E82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>6130 - Payroll Tax</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>3255.82</v>
+      </c>
+      <c r="E83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>6135 - Bonus</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>4044.11</v>
+      </c>
+      <c r="E84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>6283 - Workers Comp Premium</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>1196.36</v>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Payroll subtotal $69,477.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B86" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>6150 - Rubbish Removal</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="n">
+        <v>1652.28</v>
+      </c>
+      <c r="E86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>6158 - Exterminating</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>813.21</v>
+      </c>
+      <c r="E87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>6184 - Electric</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>6712.38</v>
+      </c>
+      <c r="E88" s="6" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>6185 - Telephone</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>2590.36</v>
+      </c>
+      <c r="E89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>6186 - Water/Sewer</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>4080.59</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Utilities subtotal $15,848.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>6189 - R &amp; M Roof</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>2103.2</v>
+      </c>
+      <c r="E91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>6192 - Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>1302.17</v>
+      </c>
+      <c r="E92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B93" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>6194 - R &amp; M Doors</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>3589.04</v>
+      </c>
+      <c r="E93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B94" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>6195 - R &amp; M Gates</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>4333.14</v>
+      </c>
+      <c r="E94" s="6" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>6196 - R &amp; M Golf Carts</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>902.36</v>
+      </c>
+      <c r="E95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>6197 - R &amp; M Parking Lot</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>1783.14</v>
+      </c>
+      <c r="E96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>6198 - R &amp; M Cameras</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>597.67</v>
+      </c>
+      <c r="E97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>6199 - R &amp; M Hvac</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>975</v>
+      </c>
+      <c r="E98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>6201 - R &amp; M Fire Protection</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>1446.78</v>
+      </c>
+      <c r="E99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>6203 - R &amp; M Lighting/Electrical</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>4909.65</v>
+      </c>
+      <c r="E100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>6206 - R &amp; M Exterior Building Repair</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>2263.41</v>
+      </c>
+      <c r="E101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B102" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>6321 - R &amp; M Apartment</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>1291.58</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M subtotal $25,497.14</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>6151 - Unit Cleanouts</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>5672.87</v>
+      </c>
+      <c r="E103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>6152 - Uniforms</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>324.8</v>
+      </c>
+      <c r="E104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>6156 - Outside Services</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>435</v>
+      </c>
+      <c r="E105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>6159 - Sales Center</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>4140</v>
+      </c>
+      <c r="E106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>6163 - Help Desk</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>534.12</v>
+      </c>
+      <c r="E107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>6162 - Supplies</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>1572.32</v>
+      </c>
+      <c r="E108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>6164 - Sale Items</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>2869.93</v>
+      </c>
+      <c r="E109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>6168 - Dues &amp; Subscriptions</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="E110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>6170 - Landscaping</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>11211.05</v>
+      </c>
+      <c r="E111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>6174 - Signs</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>454.49</v>
+      </c>
+      <c r="E112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>6176 - Teammate Mileage</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>1645.19</v>
+      </c>
+      <c r="E113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B114" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>6182 - Fees &amp; Licenses</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>235.38</v>
+      </c>
+      <c r="E114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>6190 - Postage</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>628.63</v>
+      </c>
+      <c r="E115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>6212 - Office Supplies</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>1187.66</v>
+      </c>
+      <c r="E116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>6218 - Printing Expense</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>75.59999999999999</v>
+      </c>
+      <c r="E117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>6220 - Equipment</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>99.47</v>
+      </c>
+      <c r="E118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>6224 - Computer Equipment - Non Capex</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>934.8</v>
+      </c>
+      <c r="E119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B120" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>6225 - CMS License Fee</t>
+        </is>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>2347.44</v>
+      </c>
+      <c r="E120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>6228 - Bank Adjustments</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>6232 - Visa/Mastercard Fees</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>4895.03</v>
+      </c>
+      <c r="E122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>6233 - American Express Fees</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>402.88</v>
+      </c>
+      <c r="E123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B124" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>6235 - ACH Fees</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="E124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B125" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>6256 - Legal/Auction</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>589.6799999999999</v>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>Other controllable subtotal $40,436.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B126" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>6365 - Internet/Website Costs</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="n">
+        <v>22463.57</v>
+      </c>
+      <c r="E126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B127" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>6375 - Store Marketing</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="n">
+        <v>2010.82</v>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Marketing subtotal $24,474.39; controllable expenses $175,734.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B128" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>7030 - Sales Tax Collection Allowance (offset)</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>-12.01</v>
+      </c>
+      <c r="E128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>7240 - Gross Receipts Tax (property tax)</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="n">
+        <v>121803.84</v>
+      </c>
+      <c r="E129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B130" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>6280 - Insurance</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>5842.43</v>
+      </c>
+      <c r="E130" s="6" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>6172 - Snow Removal &amp; Salting</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="n">
+        <v>2180</v>
+      </c>
+      <c r="E131" s="6" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>7530 - Professional Fees</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n">
+        <v>350</v>
+      </c>
+      <c r="E132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>6801 - Third Party Management Fees</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>22457.4</v>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Non-controllable expenses $152,621.66</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd — FY2024</t>
+        </is>
+      </c>
+      <c r="B134" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D134" s="23">
+        <f>SUM(D79:D133)</f>
+        <v/>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $328,355.94. NOI per statement $86,277.89 (accrual, store-level).</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>731252.08</v>
+      </c>
+      <c r="E135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B136" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>4281 - Admin Fee</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="n">
+        <v>9889</v>
+      </c>
+      <c r="E136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B137" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>4282 - Late Fee Revenue</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>45687.17</v>
+      </c>
+      <c r="E137" s="6" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B138" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>4283 - Other Fee Revenue</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="n">
+        <v>149.54</v>
+      </c>
+      <c r="E138" s="6" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B139" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>4284 - NSF Fees</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="n">
+        <v>60</v>
+      </c>
+      <c r="E139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B140" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>4286 - Convenience Fee Payments</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="n">
+        <v>4306.11</v>
+      </c>
+      <c r="E140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B141" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>4285 - Fees Waived</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="E141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B142" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>4287 - Fees Waived - Admin</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="n">
+        <v>-116</v>
+      </c>
+      <c r="E142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B143" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>4288 - Fees Waived - Late Fee</t>
+        </is>
+      </c>
+      <c r="D143" s="22" t="n">
+        <v>-787.76</v>
+      </c>
+      <c r="E143" s="6" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B144" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>4255 - Credit Card Chargebacks</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="n">
+        <v>-196.9</v>
+      </c>
+      <c r="E144" s="6" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B145" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>7102 - Fees Written Off</t>
+        </is>
+      </c>
+      <c r="D145" s="22" t="n">
+        <v>-7117.67</v>
+      </c>
+      <c r="E145" s="6" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B146" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D146" s="23">
+        <f>SUM(D135:D145)</f>
+        <v/>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $783,123.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B147" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>6100 - Payroll</t>
+        </is>
+      </c>
+      <c r="D147" s="22" t="n">
+        <v>59074.43</v>
+      </c>
+      <c r="E147" s="6" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B148" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>6112 - Medical Expense</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="n">
+        <v>10224</v>
+      </c>
+      <c r="E148" s="6" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B149" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>6118 - 401K Expense</t>
+        </is>
+      </c>
+      <c r="D149" s="22" t="n">
+        <v>881.88</v>
+      </c>
+      <c r="E149" s="6" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B150" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>6128 - Teammate Rewards</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="n">
+        <v>230</v>
+      </c>
+      <c r="E150" s="6" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B151" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>6130 - Payroll Tax</t>
+        </is>
+      </c>
+      <c r="D151" s="22" t="n">
+        <v>6841.49</v>
+      </c>
+      <c r="E151" s="6" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B152" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>6135 - Bonus</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="n">
+        <v>5105.13</v>
+      </c>
+      <c r="E152" s="6" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B153" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>6283 - Workers Comp Premium</t>
+        </is>
+      </c>
+      <c r="D153" s="22" t="n">
+        <v>2011.32</v>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>Payroll subtotal $84,368.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B154" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>6150 - Rubbish Removal</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="n">
+        <v>1454.88</v>
+      </c>
+      <c r="E154" s="6" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B155" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>6158 - Exterminating</t>
+        </is>
+      </c>
+      <c r="D155" s="22" t="n">
+        <v>76.06999999999999</v>
+      </c>
+      <c r="E155" s="6" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B156" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>6184 - Electric</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="n">
+        <v>7663.98</v>
+      </c>
+      <c r="E156" s="6" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B157" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>6185 - Telephone</t>
+        </is>
+      </c>
+      <c r="D157" s="22" t="n">
+        <v>2983.92</v>
+      </c>
+      <c r="E157" s="6" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B158" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>6186 - Water/Sewer</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="n">
+        <v>8564.280000000001</v>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>Utilities subtotal $20,743.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B159" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>6189 - R &amp; M Roof</t>
+        </is>
+      </c>
+      <c r="D159" s="22" t="n">
+        <v>275</v>
+      </c>
+      <c r="E159" s="6" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B160" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>6192 - Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="n">
+        <v>932.75</v>
+      </c>
+      <c r="E160" s="6" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B161" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>6194 - R &amp; M Doors</t>
+        </is>
+      </c>
+      <c r="D161" s="22" t="n">
+        <v>3276.33</v>
+      </c>
+      <c r="E161" s="6" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B162" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>6195 - R &amp; M Gates</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="n">
+        <v>6755</v>
+      </c>
+      <c r="E162" s="6" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B163" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>6196 - R &amp; M Golf Carts</t>
+        </is>
+      </c>
+      <c r="D163" s="22" t="n">
+        <v>767.09</v>
+      </c>
+      <c r="E163" s="6" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B164" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>6198 - R &amp; M Cameras</t>
+        </is>
+      </c>
+      <c r="D164" s="22" t="n">
+        <v>2228.74</v>
+      </c>
+      <c r="E164" s="6" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B165" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>6201 - R &amp; M Fire Protection</t>
+        </is>
+      </c>
+      <c r="D165" s="22" t="n">
+        <v>85.81</v>
+      </c>
+      <c r="E165" s="6" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B166" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>6203 - R &amp; M Lighting/Electrical</t>
+        </is>
+      </c>
+      <c r="D166" s="22" t="n">
+        <v>575</v>
+      </c>
+      <c r="E166" s="6" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B167" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>6206 - R &amp; M Exterior Building Repair</t>
+        </is>
+      </c>
+      <c r="D167" s="22" t="n">
+        <v>1574.82</v>
+      </c>
+      <c r="E167" s="6" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B168" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>6321 - R &amp; M Apartment</t>
+        </is>
+      </c>
+      <c r="D168" s="22" t="n">
+        <v>892.25</v>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M subtotal $17,362.79</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B169" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>6151 - Unit Cleanouts</t>
+        </is>
+      </c>
+      <c r="D169" s="22" t="n">
+        <v>870</v>
+      </c>
+      <c r="E169" s="6" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B170" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>6152 - Uniforms</t>
+        </is>
+      </c>
+      <c r="D170" s="22" t="n">
+        <v>454.01</v>
+      </c>
+      <c r="E170" s="6" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B171" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>6159 - Sales Center</t>
+        </is>
+      </c>
+      <c r="D171" s="22" t="n">
+        <v>4140</v>
+      </c>
+      <c r="E171" s="6" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B172" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>6163 - Help Desk</t>
+        </is>
+      </c>
+      <c r="D172" s="22" t="n">
+        <v>534.12</v>
+      </c>
+      <c r="E172" s="6" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B173" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>6162 - Supplies</t>
+        </is>
+      </c>
+      <c r="D173" s="22" t="n">
+        <v>465.59</v>
+      </c>
+      <c r="E173" s="6" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B174" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>6164 - Sale Items</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="n">
+        <v>3347.05</v>
+      </c>
+      <c r="E174" s="6" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B175" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>6168 - Dues &amp; Subscriptions</t>
+        </is>
+      </c>
+      <c r="D175" s="22" t="n">
+        <v>133.59</v>
+      </c>
+      <c r="E175" s="6" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B176" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>6170 - Landscaping</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="n">
+        <v>18153.74</v>
+      </c>
+      <c r="E176" s="6" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B177" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C177" s="6" t="inlineStr">
+        <is>
+          <t>6174 - Signs</t>
+        </is>
+      </c>
+      <c r="D177" s="22" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="E177" s="6" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B178" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>6176 - Teammate Mileage</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="n">
+        <v>1430.56</v>
+      </c>
+      <c r="E178" s="6" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B179" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C179" s="6" t="inlineStr">
+        <is>
+          <t>6182 - Fees &amp; Licenses</t>
+        </is>
+      </c>
+      <c r="D179" s="22" t="n">
+        <v>914.6</v>
+      </c>
+      <c r="E179" s="6" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B180" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C180" s="6" t="inlineStr">
+        <is>
+          <t>6190 - Postage</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="n">
+        <v>869.38</v>
+      </c>
+      <c r="E180" s="6" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B181" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>6212 - Office Supplies</t>
+        </is>
+      </c>
+      <c r="D181" s="22" t="n">
+        <v>698.04</v>
+      </c>
+      <c r="E181" s="6" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B182" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C182" s="6" t="inlineStr">
+        <is>
+          <t>6218 - Printing Expense</t>
+        </is>
+      </c>
+      <c r="D182" s="22" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="E182" s="6" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B183" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C183" s="6" t="inlineStr">
+        <is>
+          <t>6220 - Equipment</t>
+        </is>
+      </c>
+      <c r="D183" s="22" t="n">
+        <v>1390.33</v>
+      </c>
+      <c r="E183" s="6" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B184" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>6224 - Computer Equipment - Non Capex</t>
+        </is>
+      </c>
+      <c r="D184" s="22" t="n">
+        <v>1274.08</v>
+      </c>
+      <c r="E184" s="6" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B185" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C185" s="6" t="inlineStr">
+        <is>
+          <t>6225 - CMS License Fee</t>
+        </is>
+      </c>
+      <c r="D185" s="22" t="n">
+        <v>2347.44</v>
+      </c>
+      <c r="E185" s="6" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B186" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C186" s="6" t="inlineStr">
+        <is>
+          <t>6228 - Bank Adjustments</t>
+        </is>
+      </c>
+      <c r="D186" s="22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E186" s="6" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B187" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C187" s="6" t="inlineStr">
+        <is>
+          <t>6231 - Loss &amp; Damage</t>
+        </is>
+      </c>
+      <c r="D187" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E187" s="6" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B188" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>6232 - Visa/Mastercard Fees</t>
+        </is>
+      </c>
+      <c r="D188" s="22" t="n">
+        <v>9072.469999999999</v>
+      </c>
+      <c r="E188" s="6" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B189" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C189" s="6" t="inlineStr">
+        <is>
+          <t>6233 - American Express Fees</t>
+        </is>
+      </c>
+      <c r="D189" s="22" t="n">
+        <v>1033.36</v>
+      </c>
+      <c r="E189" s="6" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B190" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C190" s="6" t="inlineStr">
+        <is>
+          <t>6235 - ACH Fees</t>
+        </is>
+      </c>
+      <c r="D190" s="22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="E190" s="6" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B191" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>6234 - IT - Repairs and Services</t>
+        </is>
+      </c>
+      <c r="D191" s="22" t="n">
+        <v>280</v>
+      </c>
+      <c r="E191" s="6" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B192" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C192" s="6" t="inlineStr">
+        <is>
+          <t>6256 - Legal/Auction</t>
+        </is>
+      </c>
+      <c r="D192" s="22" t="n">
+        <v>589.6799999999999</v>
+      </c>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
+          <t>Other controllable subtotal $48,137.71</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B193" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C193" s="6" t="inlineStr">
+        <is>
+          <t>6365 - Internet/Website Costs</t>
+        </is>
+      </c>
+      <c r="D193" s="22" t="n">
+        <v>25650.11</v>
+      </c>
+      <c r="E193" s="6" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B194" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>6375 - Store Marketing</t>
+        </is>
+      </c>
+      <c r="D194" s="22" t="n">
+        <v>324.55</v>
+      </c>
+      <c r="E194" s="6" t="inlineStr">
+        <is>
+          <t>Marketing subtotal $25,974.66; controllable expenses $196,586.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B195" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C195" s="6" t="inlineStr">
+        <is>
+          <t>7030 - Sales Tax Collection Allowance (offset)</t>
+        </is>
+      </c>
+      <c r="D195" s="22" t="n">
+        <v>-14.31</v>
+      </c>
+      <c r="E195" s="6" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B196" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C196" s="6" t="inlineStr">
+        <is>
+          <t>7240 - Gross Receipts Tax (property tax)</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="n">
+        <v>246826.26</v>
+      </c>
+      <c r="E196" s="6" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B197" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>6280 - Insurance</t>
+        </is>
+      </c>
+      <c r="D197" s="22" t="n">
+        <v>10522.42</v>
+      </c>
+      <c r="E197" s="6" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B198" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>6172 - Snow Removal &amp; Salting</t>
+        </is>
+      </c>
+      <c r="D198" s="22" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E198" s="6" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B199" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C199" s="6" t="inlineStr">
+        <is>
+          <t>7530 - Professional Fees</t>
+        </is>
+      </c>
+      <c r="D199" s="22" t="n">
+        <v>350</v>
+      </c>
+      <c r="E199" s="6" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B200" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C200" s="6" t="inlineStr">
+        <is>
+          <t>6801 - Third Party Management Fees</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="n">
+        <v>41598.27</v>
+      </c>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>Non-controllable expenses $303,172.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave — FY2024</t>
+        </is>
+      </c>
+      <c r="B201" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D201" s="23">
+        <f>SUM(D147:D200)</f>
+        <v/>
+      </c>
+      <c r="E201" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $499,759.18. NOI per statement $283,364.07 (accrual, store-level).</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B202" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C202" s="6" t="inlineStr">
+        <is>
+          <t>45050 - Storage Rents</t>
+        </is>
+      </c>
+      <c r="D202" s="22" t="n">
+        <v>702708.05</v>
+      </c>
+      <c r="E202" s="6" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B203" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C203" s="6" t="inlineStr">
+        <is>
+          <t>45100 - Merchandise Sales</t>
+        </is>
+      </c>
+      <c r="D203" s="22" t="n">
+        <v>5824.04</v>
+      </c>
+      <c r="E203" s="6" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B204" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C204" s="6" t="inlineStr">
+        <is>
+          <t>45125 - Commercial Truck Rental</t>
+        </is>
+      </c>
+      <c r="D204" s="22" t="n">
+        <v>2330.89</v>
+      </c>
+      <c r="E204" s="6" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B205" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C205" s="6" t="inlineStr">
+        <is>
+          <t>45150 - Penske Truck Rental</t>
+        </is>
+      </c>
+      <c r="D205" s="22" t="n">
+        <v>50532.36</v>
+      </c>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>Operating revenue subtotal $761,395.34</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B206" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C206" s="6" t="inlineStr">
+        <is>
+          <t>46050 - Administrative Fee</t>
+        </is>
+      </c>
+      <c r="D206" s="22" t="n">
+        <v>4976</v>
+      </c>
+      <c r="E206" s="6" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B207" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C207" s="6" t="inlineStr">
+        <is>
+          <t>46200 - Late Fee</t>
+        </is>
+      </c>
+      <c r="D207" s="22" t="n">
+        <v>20675</v>
+      </c>
+      <c r="E207" s="6" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B208" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>46300 - NSF Fee</t>
+        </is>
+      </c>
+      <c r="D208" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E208" s="6" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B209" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C209" s="6" t="inlineStr">
+        <is>
+          <t>43500 - Miscellaneous Income</t>
+        </is>
+      </c>
+      <c r="D209" s="22" t="n">
+        <v>3314.87</v>
+      </c>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>Other revenue subtotal $28,990.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="11" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B210" s="26" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C210" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D210" s="23">
+        <f>SUM(D202:D209)</f>
+        <v/>
+      </c>
+      <c r="E210" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $790,386.21.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B211" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>60000 - Salaries and Wages</t>
+        </is>
+      </c>
+      <c r="D211" s="22" t="n">
+        <v>83783.53</v>
+      </c>
+      <c r="E211" s="6" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B212" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C212" s="6" t="inlineStr">
+        <is>
+          <t>60100 - Payroll Taxes</t>
+        </is>
+      </c>
+      <c r="D212" s="22" t="n">
+        <v>9981.33</v>
+      </c>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>Payroll subtotal $93,764.86</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B213" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C213" s="6" t="inlineStr">
+        <is>
+          <t>61000 - General Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="D213" s="22" t="n">
+        <v>10417.18</v>
+      </c>
+      <c r="E213" s="6" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B214" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>61100 - Purchase of Resale Items</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="n">
+        <v>3715.51</v>
+      </c>
+      <c r="E214" s="6" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B215" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C215" s="6" t="inlineStr">
+        <is>
+          <t>61150 - Property Uniforms</t>
+        </is>
+      </c>
+      <c r="D215" s="22" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="E215" s="6" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B216" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C216" s="6" t="inlineStr">
+        <is>
+          <t>61200 - Snow Removal/Power Sweeping</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="n">
+        <v>375</v>
+      </c>
+      <c r="E216" s="6" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B217" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C217" s="6" t="inlineStr">
+        <is>
+          <t>61300 - Trash Services</t>
+        </is>
+      </c>
+      <c r="D217" s="22" t="n">
+        <v>5322.58</v>
+      </c>
+      <c r="E217" s="6" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B218" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C218" s="6" t="inlineStr">
+        <is>
+          <t>61400 - Ground Maintenance</t>
+        </is>
+      </c>
+      <c r="D218" s="22" t="n">
+        <v>1044</v>
+      </c>
+      <c r="E218" s="6" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B219" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>61500 - Truck - Lease</t>
+        </is>
+      </c>
+      <c r="D219" s="22" t="n">
+        <v>15600</v>
+      </c>
+      <c r="E219" s="6" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B220" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C220" s="6" t="inlineStr">
+        <is>
+          <t>61700 - Truck - Maintenance</t>
+        </is>
+      </c>
+      <c r="D220" s="22" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="E220" s="6" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B221" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>61800 - Truck - Commercial Commissions</t>
+        </is>
+      </c>
+      <c r="D221" s="22" t="n">
+        <v>330</v>
+      </c>
+      <c r="E221" s="6" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B222" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>61900 - Truck - Penske Commissions</t>
+        </is>
+      </c>
+      <c r="D222" s="22" t="n">
+        <v>5908.99</v>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>R&amp;M subtotal $43,520.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B223" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>62000 - Utilities - Electric</t>
+        </is>
+      </c>
+      <c r="D223" s="22" t="n">
+        <v>2647.46</v>
+      </c>
+      <c r="E223" s="6" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B224" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C224" s="6" t="inlineStr">
+        <is>
+          <t>62100 - Utilities - Water and Sewer</t>
+        </is>
+      </c>
+      <c r="D224" s="22" t="n">
+        <v>2643.74</v>
+      </c>
+      <c r="E224" s="6" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B225" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C225" s="6" t="inlineStr">
+        <is>
+          <t>62200 - Utilities - Gas</t>
+        </is>
+      </c>
+      <c r="D225" s="22" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="E225" s="6" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B226" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>62500 - Security Alarm Service</t>
+        </is>
+      </c>
+      <c r="D226" s="22" t="n">
+        <v>1857.52</v>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>Utilities subtotal $7,150.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B227" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>63000 - Management Fee</t>
+        </is>
+      </c>
+      <c r="D227" s="22" t="n">
+        <v>47235.68</v>
+      </c>
+      <c r="E227" s="6" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B228" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C228" s="6" t="inlineStr">
+        <is>
+          <t>65000 - Legal and Professional Services</t>
+        </is>
+      </c>
+      <c r="D228" s="22" t="n">
+        <v>10238.1</v>
+      </c>
+      <c r="E228" s="6" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B229" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>66000 - Dues and Subscriptions</t>
+        </is>
+      </c>
+      <c r="D229" s="22" t="n">
+        <v>98.05</v>
+      </c>
+      <c r="E229" s="6" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B230" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C230" s="6" t="inlineStr">
+        <is>
+          <t>66050 - Office Supplies</t>
+        </is>
+      </c>
+      <c r="D230" s="22" t="n">
+        <v>934.66</v>
+      </c>
+      <c r="E230" s="6" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B231" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C231" s="6" t="inlineStr">
+        <is>
+          <t>66100 - Postage &amp; Delivery</t>
+        </is>
+      </c>
+      <c r="D231" s="22" t="n">
+        <v>645.37</v>
+      </c>
+      <c r="E231" s="6" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B232" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C232" s="6" t="inlineStr">
+        <is>
+          <t>66200 - Telephone</t>
+        </is>
+      </c>
+      <c r="D232" s="22" t="n">
+        <v>9403.110000000001</v>
+      </c>
+      <c r="E232" s="6" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B233" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>66300 - Call Center Allocation</t>
+        </is>
+      </c>
+      <c r="D233" s="22" t="n">
+        <v>1399.74</v>
+      </c>
+      <c r="E233" s="6" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B234" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C234" s="6" t="inlineStr">
+        <is>
+          <t>69300 - Petty Cash Expenses</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="n">
+        <v>3422.72</v>
+      </c>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>Administrative subtotal $15,903.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B235" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C235" s="6" t="inlineStr">
+        <is>
+          <t>69000 - Travel</t>
+        </is>
+      </c>
+      <c r="D235" s="22" t="n">
+        <v>53.72</v>
+      </c>
+      <c r="E235" s="6" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B236" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C236" s="6" t="inlineStr">
+        <is>
+          <t>56100 - Travel - Property Management</t>
+        </is>
+      </c>
+      <c r="D236" s="22" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>Travel subtotal $67.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B237" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C237" s="6" t="inlineStr">
+        <is>
+          <t>64000 - Promotional Advertising</t>
+        </is>
+      </c>
+      <c r="D237" s="22" t="n">
+        <v>8781.219999999999</v>
+      </c>
+      <c r="E237" s="6" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B238" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>64100 - Google</t>
+        </is>
+      </c>
+      <c r="D238" s="22" t="n">
+        <v>6532.72</v>
+      </c>
+      <c r="E238" s="6" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B239" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C239" s="6" t="inlineStr">
+        <is>
+          <t>64150 - Sparefoot/Storagefront</t>
+        </is>
+      </c>
+      <c r="D239" s="22" t="n">
+        <v>18968.73</v>
+      </c>
+      <c r="E239" s="6" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B240" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C240" s="6" t="inlineStr">
+        <is>
+          <t>64300 - Employee Promotions</t>
+        </is>
+      </c>
+      <c r="D240" s="22" t="n">
+        <v>4302.18</v>
+      </c>
+      <c r="E240" s="6" t="inlineStr">
+        <is>
+          <t>Advertising subtotal $38,584.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B241" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C241" s="6" t="inlineStr">
+        <is>
+          <t>68000 - Fire and Liability Insurance</t>
+        </is>
+      </c>
+      <c r="D241" s="22" t="n">
+        <v>12049.98</v>
+      </c>
+      <c r="E241" s="6" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B242" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C242" s="6" t="inlineStr">
+        <is>
+          <t>68100 - Workers Compensation</t>
+        </is>
+      </c>
+      <c r="D242" s="22" t="n">
+        <v>2700.3</v>
+      </c>
+      <c r="E242" s="6" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B243" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C243" s="6" t="inlineStr">
+        <is>
+          <t>68200 - Medical Insurance</t>
+        </is>
+      </c>
+      <c r="D243" s="22" t="n">
+        <v>11170.57</v>
+      </c>
+      <c r="E243" s="6" t="inlineStr">
+        <is>
+          <t>Insurance subtotal $25,920.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B244" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C244" s="6" t="inlineStr">
+        <is>
+          <t>67000 - Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D244" s="22" t="n">
+        <v>221073.2</v>
+      </c>
+      <c r="E244" s="6" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B245" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C245" s="6" t="inlineStr">
+        <is>
+          <t>67200 - Other Taxes and Licenses</t>
+        </is>
+      </c>
+      <c r="D245" s="22" t="n">
+        <v>267.73</v>
+      </c>
+      <c r="E245" s="6" t="inlineStr">
+        <is>
+          <t>Taxes subtotal $221,340.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B246" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C246" s="6" t="inlineStr">
+        <is>
+          <t>69100 - Bank Charges and Payroll Fees</t>
+        </is>
+      </c>
+      <c r="D246" s="22" t="n">
+        <v>1348.1</v>
+      </c>
+      <c r="E246" s="6" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B247" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C247" s="6" t="inlineStr">
+        <is>
+          <t>69200 - Credit Card Fees</t>
+        </is>
+      </c>
+      <c r="D247" s="22" t="n">
+        <v>28027.29</v>
+      </c>
+      <c r="E247" s="6" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B248" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C248" s="6" t="inlineStr">
+        <is>
+          <t>57500 - Credit Card Fees</t>
+        </is>
+      </c>
+      <c r="D248" s="22" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="E248" s="6" t="inlineStr">
+        <is>
+          <t>Fees &amp; commissions subtotal $29,392.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="11" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B249" s="26" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C249" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D249" s="23">
+        <f>SUM(D211:D248)</f>
+        <v/>
+      </c>
+      <c r="E249" s="18" t="inlineStr">
+        <is>
+          <t>Printed total: $533,121.11. NOI per statement $257,265.10. FY2023 comparative: revenue $899,471.29 / expenses $590,318.63 / NOI $309,152.66 (see Summary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B250" s="25" t="inlineStr">
+        <is>
+          <t>Memo (below NOI)</t>
+        </is>
+      </c>
+      <c r="C250" s="6" t="inlineStr">
+        <is>
+          <t>Interest Expense (73000/57300)</t>
+        </is>
+      </c>
+      <c r="D250" s="22" t="n">
+        <v>79320.35000000001</v>
+      </c>
+      <c r="E250" s="6" t="inlineStr">
+        <is>
+          <t>Below NOI; not in totals above</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B251" s="25" t="inlineStr">
+        <is>
+          <t>Memo (below NOI)</t>
+        </is>
+      </c>
+      <c r="C251" s="6" t="inlineStr">
+        <is>
+          <t>Extraordinary - Participation Management Fee (63500)</t>
+        </is>
+      </c>
+      <c r="D251" s="22" t="n">
+        <v>19200</v>
+      </c>
+      <c r="E251" s="6" t="inlineStr">
+        <is>
+          <t>Below NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B252" s="25" t="inlineStr">
+        <is>
+          <t>Memo (below NOI)</t>
+        </is>
+      </c>
+      <c r="C252" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation &amp; Amortization</t>
+        </is>
+      </c>
+      <c r="D252" s="22" t="n">
+        <v>8922.84</v>
+      </c>
+      <c r="E252" s="6" t="inlineStr">
+        <is>
+          <t>Below NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B253" s="25" t="inlineStr">
+        <is>
+          <t>Memo (below NOI)</t>
+        </is>
+      </c>
+      <c r="C253" s="6" t="inlineStr">
+        <is>
+          <t>Net Cash Flow Before Dep. &amp; Amort.</t>
+        </is>
+      </c>
+      <c r="D253" s="22" t="n">
+        <v>158744.75</v>
+      </c>
+      <c r="E253" s="6" t="inlineStr">
+        <is>
+          <t>Per statement (FY2023: $162,198.05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St — FY2024</t>
+        </is>
+      </c>
+      <c r="B254" s="25" t="inlineStr">
+        <is>
+          <t>Memo (below NOI)</t>
+        </is>
+      </c>
+      <c r="C254" s="6" t="inlineStr">
+        <is>
+          <t>Net Taxable Income</t>
+        </is>
+      </c>
+      <c r="D254" s="22" t="n">
+        <v>149821.91</v>
+      </c>
+      <c r="E254" s="6" t="inlineStr">
+        <is>
+          <t>Per statement (FY2023: $124,600.41)</t>
         </is>
       </c>
     </row>
@@ -5225,7 +10630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5245,11 +10650,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>North Side Gardens LLC portfolio — parcel schedule attached to the 7205 Gilpin Way (R0178308) appeal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Portfolio parcel schedules attached to source packages (North Side Gardens; Winner Storage/CubeSmart PTA; Dahn Corporation) — subject parcels highlighted</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,7 +10789,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
@@ -5397,11 +10800,1088 @@
       <c r="D10" s="20" t="n"/>
       <c r="E10" s="21" t="n"/>
     </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Winner Storage / CubeSmart PTA portfolio — schedule attached to R0085571 LOA (Ryan LLC, 2025/2026)</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n"/>
+      <c r="C12" s="20" t="n"/>
+      <c r="D12" s="20" t="n"/>
+      <c r="E12" s="21" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Lamar Owner LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>300506230</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>9839 W 60th Ave</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Jefferson County</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC/PTA USI No 730</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>0182132318001</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>033895533</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>033895541</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>14706 E 4th Ave</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC/PTA USI No 731</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>0182131405022</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>033902769</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>1800 S Chambers Rd</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>033902785</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1815 S Helena St</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Neighborhood Self Storage LLC</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>032382996</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>2900 S Havana St</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Neighborhood Self Storage LLC</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>032383003</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>2902 S Havana St</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>032879254</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>5353 E County Line Rd</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>034924396</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>7059 S Kenton St</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>6428404001</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>2310 S Circle Dr</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>U Store It</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>6319402055</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>380 E Garden Of The Gods Rd</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Storage LLC</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>0171925204016</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Blvd</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>07032-00-036-000</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>8930 E Hampden Ave</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Denver County</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>07032-00-038-000</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>3540 S Yosemite St</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Denver County</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>U-store-it/Pta Usi No 769</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>0182505401015</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>6790 Federal Blvd</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>06172-00-031-000</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>6150 Leetsdale Dr</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Denver County</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP C/O PTA - CS #229</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>0171928108008</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>8444 Pecos St</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Cube Smart LP #229</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>0171928108010</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>8444 Pecos St</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>D Beeks Aurora Investments LLC</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>031269288</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>2125 Valentia Street</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>034003967</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>1390 S Valentia St</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>300189566</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>1733 S Wadsworth Blvd</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Jefferson County</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>031265631</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>10303 E Warren Ave</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>031974674</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>4120 S Federal Blvd</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Englewood Owner LLC</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>035308359</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Englewood Owner LLC</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>035511812</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>1090 W Hampden Ave</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Cubesmart LP</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>300001349</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>16845 Mt Vernon Rd</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Jefferson County</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>033284798</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>7650 S Broadway</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Dahn Corporation managed portfolio — schedule attached to R0040829 LOA (Nancy K. Naeve, SVP, 6/12/2025)</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="21" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Mini U Storage AAA Ltd</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>R0361999</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>1400 E County Line Rd</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Douglas County</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>America360 Development LLC</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>034611487</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>16830 Hughes Dr</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Mini U Storage Highlands Ranch Ltd</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>R0374153</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>6678 E County Line Rd</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Douglas County</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Colorado Mini Ltd</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>02241-16-008-000</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>3900 E 45th Ave</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Denver County</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Mini U Storage ILIFF</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>035416691</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>7600 E ILIFF Ave</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>DSI Growth &amp; Income Fund II</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>300422700</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>7322 S Carr St</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Jefferson County</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Mini U Storage Mississippi Ltd</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>032382911</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>8600 E Mississippi Ave</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Arapahoe County</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund II</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>7424105063</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>910 Motor City Dr</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>Parker Tech Storage LLC</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>R0440975</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>18901 Longs Way</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Douglas County</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund B</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>0171914201013</t>
+        </is>
+      </c>
+      <c r="C53" s="12" t="inlineStr">
+        <is>
+          <t>10350 Washington St</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A43:E43"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.###"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);-"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +74,12 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -183,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -270,6 +278,43 @@
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -635,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -660,7 +705,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,23 +1014,173 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>R0110351.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Tax appeal - income approach + rent roll + 2yr income statements + LOA</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave, Aurora (ASB Real Estate)</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Ethan Horn) / CoStar</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>R0111559.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Assessor protest letter - income approach, base-period leases, rent roll, 2yr I&amp;E</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>3590 N Himalaya Rd, Bldg 6, Aurora</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2026 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists (Brenda L. Fearn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>R0111560.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Assessor protest letter - income approach, excess-vacancy discounting, rent roll, 2yr I&amp;E</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>20320 E. 36th Dr, Bldg 7, Aurora</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2026 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists (Brenda L. Fearn)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>R0114026.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>SB 11-119 submission - 2023 &amp; 2024 P&amp;L (excerpt) + 06/24 rent roll</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St, Adams County</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates (Todd J. Stevens)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>R0121833.pdf</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Real property summary analysis - income approach, rent roll, 2yr P&amp;L, executed lease</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>5360 Washington St (Anchor Business Park), Denver</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>As of 1/1/2025 (2023-2024 P&amp;L)</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Joseph C. Sansone Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
@@ -995,10 +1189,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1248,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2049,6 +2242,513 @@
       <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>R0092302.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>R0110351</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>R0110351</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>R0110351</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>80011 (est.)</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J13" s="32" t="inlineStr">
+        <is>
+          <t>ASB Real Estate</t>
+        </is>
+      </c>
+      <c r="K13" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28TH OWNER LLC</t>
+        </is>
+      </c>
+      <c r="L13" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse/Distribution</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>Single tenant</t>
+        </is>
+      </c>
+      <c r="N13" s="33" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="O13" s="34" t="n"/>
+      <c r="P13" s="34" t="n"/>
+      <c r="Q13" s="34" t="n">
+        <v>85604</v>
+      </c>
+      <c r="R13" s="35" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S13" s="32" t="n"/>
+      <c r="T13" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024)</t>
+        </is>
+      </c>
+      <c r="U13" s="36" t="n">
+        <v>10683449</v>
+      </c>
+      <c r="V13" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W13" s="36" t="n">
+        <v>7939000</v>
+      </c>
+      <c r="X13" s="32" t="inlineStr">
+        <is>
+          <t>Allegiance / ASB Allegiance Fund</t>
+        </is>
+      </c>
+      <c r="Y13" s="32" t="inlineStr">
+        <is>
+          <t>R0110351.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>R0111559</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>R0111559</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>R0111559</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter - Building 6</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>3590 N Himalaya Road</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #6 LLC</t>
+        </is>
+      </c>
+      <c r="K14" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #6 LLC</t>
+        </is>
+      </c>
+      <c r="L14" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M14" s="32" t="inlineStr">
+        <is>
+          <t>Multi (3 tenants)</t>
+        </is>
+      </c>
+      <c r="N14" s="33" t="n"/>
+      <c r="O14" s="34" t="n"/>
+      <c r="P14" s="34" t="n"/>
+      <c r="Q14" s="34" t="n">
+        <v>125000</v>
+      </c>
+      <c r="R14" s="35" t="n">
+        <v>1998</v>
+      </c>
+      <c r="S14" s="32" t="n"/>
+      <c r="T14" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024 DOV)</t>
+        </is>
+      </c>
+      <c r="U14" s="36" t="n"/>
+      <c r="V14" s="32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="W14" s="36" t="n">
+        <v>8754500</v>
+      </c>
+      <c r="X14" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Realty Co. (Nicole Creighton, PM)</t>
+        </is>
+      </c>
+      <c r="Y14" s="32" t="inlineStr">
+        <is>
+          <t>R0111559.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>R0111560</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>R0111560</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>R0111560</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter - Building 7</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>20320 E. 36th Drive</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #7 LLC</t>
+        </is>
+      </c>
+      <c r="K15" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #7 LLC</t>
+        </is>
+      </c>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M15" s="32" t="inlineStr">
+        <is>
+          <t>Single tenant (vacant at DOV)</t>
+        </is>
+      </c>
+      <c r="N15" s="33" t="n"/>
+      <c r="O15" s="34" t="n"/>
+      <c r="P15" s="34" t="n"/>
+      <c r="Q15" s="34" t="n">
+        <v>200000</v>
+      </c>
+      <c r="R15" s="35" t="n">
+        <v>1998</v>
+      </c>
+      <c r="S15" s="32" t="n"/>
+      <c r="T15" s="32" t="inlineStr">
+        <is>
+          <t>0% - 100% vacant (6/30/2024 DOV)</t>
+        </is>
+      </c>
+      <c r="U15" s="36" t="n"/>
+      <c r="V15" s="32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="W15" s="36" t="n">
+        <v>10345200</v>
+      </c>
+      <c r="X15" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Realty Co. (Nicole Creighton, PM)</t>
+        </is>
+      </c>
+      <c r="Y15" s="32" t="inlineStr">
+        <is>
+          <t>R0111560.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>R0114026</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>R0114026</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>01825-10-1-02-023</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr">
+        <is>
+          <t>Friesen-Washington Street LLC</t>
+        </is>
+      </c>
+      <c r="K16" s="32" t="inlineStr">
+        <is>
+          <t>Friesen-Washington Street LLC</t>
+        </is>
+      </c>
+      <c r="L16" s="32" t="inlineStr">
+        <is>
+          <t>Commercial / Industrial (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>Multi (3 tenants)</t>
+        </is>
+      </c>
+      <c r="N16" s="33" t="n"/>
+      <c r="O16" s="34" t="n"/>
+      <c r="P16" s="34" t="n"/>
+      <c r="Q16" s="34" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="32" t="n"/>
+      <c r="T16" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="U16" s="36" t="n"/>
+      <c r="V16" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W16" s="36" t="n"/>
+      <c r="X16" s="32" t="inlineStr">
+        <is>
+          <t>Owner (Shannon Friesen, bookkeeping)</t>
+        </is>
+      </c>
+      <c r="Y16" s="32" t="inlineStr">
+        <is>
+          <t>R0114026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>R0121833</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>R0121833</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>25-31459-0001-CO (PTR); Appeal 159402</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>5360 Washington Street</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G17" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H17" s="32" t="inlineStr">
+        <is>
+          <t>80216</t>
+        </is>
+      </c>
+      <c r="I17" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J17" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park LLC</t>
+        </is>
+      </c>
+      <c r="K17" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park LLC</t>
+        </is>
+      </c>
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M17" s="32" t="inlineStr">
+        <is>
+          <t>Multi (4 units / 5 leases)</t>
+        </is>
+      </c>
+      <c r="N17" s="33" t="n"/>
+      <c r="O17" s="34" t="n"/>
+      <c r="P17" s="34" t="n">
+        <v>36472</v>
+      </c>
+      <c r="Q17" s="34" t="n">
+        <v>36472</v>
+      </c>
+      <c r="R17" s="35" t="n">
+        <v>2001</v>
+      </c>
+      <c r="S17" s="32" t="n"/>
+      <c r="T17" s="32" t="inlineStr">
+        <is>
+          <t>100% (5 leases on 2024 rent roll)</t>
+        </is>
+      </c>
+      <c r="U17" s="36" t="n">
+        <v>5487982</v>
+      </c>
+      <c r="V17" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W17" s="36" t="n">
+        <v>3919000</v>
+      </c>
+      <c r="X17" s="32" t="inlineStr">
+        <is>
+          <t>Bart S. Hansen (Property Manager)</t>
+        </is>
+      </c>
+      <c r="Y17" s="32" t="inlineStr">
+        <is>
+          <t>R0121833.pdf</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2100,7 +2800,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3128,6 +3827,895 @@
       <c r="M26" s="6" t="inlineStr">
         <is>
           <t>Actual rents $10.28-$31.48/sf; majority $13-17/sf; $15/sf applied to vacant space. Detailed rent roll embedded as image in appraisal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave (R0110351)</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>0100 (Bldg 01115B)</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Old West Mattress Co., LLC</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN (industrial)</t>
+        </is>
+      </c>
+      <c r="E27" s="37" t="n">
+        <v>45512.79</v>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>546153.48</v>
+      </c>
+      <c r="G27" s="37" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>10/10/2018</t>
+        </is>
+      </c>
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>4/30/2028</t>
+        </is>
+      </c>
+      <c r="J27" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="37" t="n">
+        <v>34564.79</v>
+      </c>
+      <c r="L27" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" s="32" t="inlineStr">
+        <is>
+          <t>85,604 SF, 100% occupied; rent roll as of 6/30/2024. $34,564.79/mo is cost recovery, not CAM. Scheduled base-rent increases: 2/1/2025 $46,654.18 ($6.54 PSF); 2/1/2026 $47,795.57 ($6.70); 2/1/2027 $49,008.29 ($6.87); 2/1/2028 $50,221.01 ($7.04). Recovery categories eff. 1/1/2025: CAM $1,839.61, INS $3,338.15, RET $23,941.67 per month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>Exhibits USA, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E28" s="37" t="n">
+        <v>22933.42</v>
+      </c>
+      <c r="F28" s="37" t="n">
+        <v>275201.04</v>
+      </c>
+      <c r="G28" s="37" t="n">
+        <v>4.9943</v>
+      </c>
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>7/13/2007</t>
+        </is>
+      </c>
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>7/31/2027</t>
+        </is>
+      </c>
+      <c r="J28" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>55,103 SF = 44.08% of building. Rent roll as of 06/30/22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>Colorado Roofing Products, LLC</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="n">
+        <v>20855.35</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>250264.2</v>
+      </c>
+      <c r="G29" s="37" t="n">
+        <v>5.7434</v>
+      </c>
+      <c r="H29" s="32" t="inlineStr">
+        <is>
+          <t>3/1/2015</t>
+        </is>
+      </c>
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>2/28/2025</t>
+        </is>
+      </c>
+      <c r="J29" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>43,574 SF = 34.86% of building. Rent roll as of 06/30/22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>Suite 200</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>Invisible Structures, Inc.</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="n">
+        <v>14428.48</v>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>173141.76</v>
+      </c>
+      <c r="G30" s="37" t="n">
+        <v>6.5776</v>
+      </c>
+      <c r="H30" s="32" t="inlineStr">
+        <is>
+          <t>2/1/2020</t>
+        </is>
+      </c>
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>1/31/2027</t>
+        </is>
+      </c>
+      <c r="J30" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" s="32" t="inlineStr">
+        <is>
+          <t>26,323 SF = 21.06% of building. Rent roll as of 06/30/22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>3 tenants - 100% occupied</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E31" s="37" t="n">
+        <v>58217.25</v>
+      </c>
+      <c r="F31" s="37" t="n">
+        <v>698607</v>
+      </c>
+      <c r="G31" s="37" t="n">
+        <v>5.5889</v>
+      </c>
+      <c r="H31" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>125,000 SF total, 0 SF vacant. Printed rent-roll totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>FedEx Ground Package System, Inc.</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Single Tenant Net</t>
+        </is>
+      </c>
+      <c r="E32" s="37" t="n">
+        <v>105833.33</v>
+      </c>
+      <c r="F32" s="37" t="n">
+        <v>1269999.96</v>
+      </c>
+      <c r="G32" s="37" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>4/15/2012</t>
+        </is>
+      </c>
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>4/30/2024</t>
+        </is>
+      </c>
+      <c r="J32" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" s="32" t="inlineStr">
+        <is>
+          <t>200,000 SF. Rent roll as of 06/30/22. Lease expired 4/30/2024, which is why the property was 100% vacant at the 6/30/2024 date of value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St (R0114026)</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>Colorado Signs</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>Actual - lease rate &amp; term only</t>
+        </is>
+      </c>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+      <c r="G33" s="37" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="H33" s="32" t="inlineStr">
+        <is>
+          <t>7/1/2021</t>
+        </is>
+      </c>
+      <c r="I33" s="32" t="inlineStr">
+        <is>
+          <t>6/30/2025</t>
+        </is>
+      </c>
+      <c r="J33" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" s="32" t="inlineStr">
+        <is>
+          <t>Rent roll (06/24) reports only tenant, rate PSF and term - no SF or monthly rent. Corresponding P&amp;L income account is named 'Colorado Wrap'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St (R0114026)</t>
+        </is>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>CPI / Thorp</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>Actual - lease rate &amp; term only</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n"/>
+      <c r="G34" s="37" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="H34" s="32" t="inlineStr">
+        <is>
+          <t>7/1/2023</t>
+        </is>
+      </c>
+      <c r="I34" s="32" t="inlineStr">
+        <is>
+          <t>6/30/2030</t>
+        </is>
+      </c>
+      <c r="J34" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M34" s="32" t="inlineStr">
+        <is>
+          <t>Rent roll (06/24) reports only tenant, rate PSF and term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St (R0114026)</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>Touch Stone Granite &amp; Marble</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>Actual (details not legible)</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n"/>
+      <c r="G35" s="37" t="n"/>
+      <c r="H35" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" s="32" t="inlineStr">
+        <is>
+          <t>Third rent-roll row is obliterated by a black scan artifact; tenant identified only from the P&amp;L rent accounts. Rate and term NOT recoverable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Building Products LLC</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E36" s="37" t="n">
+        <v>1399</v>
+      </c>
+      <c r="F36" s="37" t="n">
+        <v>16788</v>
+      </c>
+      <c r="G36" s="37" t="n"/>
+      <c r="H36" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J36" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" s="32" t="inlineStr">
+        <is>
+          <t>2024 rent roll; date of change 4/1/24. Term end shown as N/A (owner-affiliated tenant).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B37" s="32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C37" s="32" t="inlineStr">
+        <is>
+          <t>Consolidated Electrical Distributors</t>
+        </is>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E37" s="37" t="n">
+        <v>5660</v>
+      </c>
+      <c r="F37" s="37" t="n">
+        <v>67920</v>
+      </c>
+      <c r="G37" s="37" t="n"/>
+      <c r="H37" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" s="32" t="inlineStr">
+        <is>
+          <t>9/30/2026</t>
+        </is>
+      </c>
+      <c r="J37" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" s="32" t="inlineStr">
+        <is>
+          <t>2024 rent roll; date of change 10/1/24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>Integrative Environmental Systems, LLC</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E38" s="37" t="n">
+        <v>5767.29</v>
+      </c>
+      <c r="F38" s="37" t="n">
+        <v>69207.48</v>
+      </c>
+      <c r="G38" s="37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>12/1/2023</t>
+        </is>
+      </c>
+      <c r="I38" s="32" t="inlineStr">
+        <is>
+          <t>11/30/2026</t>
+        </is>
+      </c>
+      <c r="J38" s="32" t="inlineStr">
+        <is>
+          <t>36 mo + option 12/1/2027-11/30/2030</t>
+        </is>
+      </c>
+      <c r="K38" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="37" t="n">
+        <v>5767.29</v>
+      </c>
+      <c r="M38" s="32" t="inlineStr">
+        <is>
+          <t>7,285 SF at $9.50/SF NNN with 3% annual escalations (executed lease dated 10/31/2023). Lease Table 1: Yr1 $9.50/$5,767.29/mo; Yr2 $9.79/$5,943.35; Yr3 $10.08/$6,119.40; total $213,960.48. First-month charges $2,872.60; late fee $250. Rent roll shows term end 10/31/2026 vs 11/30/2026 in the lease body, and Table 1 periods start 11/1/2023 vs the 12/1/2023 commencement - reproduced as printed (source contains typos in the Table 1 period column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>Juniper Overland</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E39" s="37" t="n">
+        <v>5640</v>
+      </c>
+      <c r="F39" s="37" t="n">
+        <v>67680</v>
+      </c>
+      <c r="G39" s="37" t="n"/>
+      <c r="H39" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>3/31/2026</t>
+        </is>
+      </c>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M39" s="32" t="inlineStr">
+        <is>
+          <t>2024 rent roll; date of change 4/1/24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>Restoration Logistics</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E40" s="37" t="n">
+        <v>7190.5</v>
+      </c>
+      <c r="F40" s="37" t="n">
+        <v>86286</v>
+      </c>
+      <c r="G40" s="37" t="n"/>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" s="32" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J40" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" s="32" t="inlineStr">
+        <is>
+          <t>2024 rent roll; date of change 4/1/24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>5 leases - all NNN</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E41" s="37" t="n">
+        <v>25656.79</v>
+      </c>
+      <c r="F41" s="37" t="n">
+        <v>307881.48</v>
+      </c>
+      <c r="G41" s="37" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" s="32" t="inlineStr">
+        <is>
+          <t>Printed rent-roll totals, signed Bart S. Hansen (Property Manager) 4/1/24. PSF = $307,881.48 / 36,472 SF.</t>
         </is>
       </c>
     </row>
@@ -3149,7 +4737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3176,7 +4764,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,241 +4972,541 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave (R0110351)</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="n">
+        <v>10683449</v>
+      </c>
+      <c r="D11" s="37" t="n">
+        <v>124.8</v>
+      </c>
+      <c r="E11" s="36" t="n">
+        <v>7939000</v>
+      </c>
+      <c r="F11" s="37" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="G11" s="36" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>R0110351</t>
+        </is>
+      </c>
+    </row>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="36" t="n">
+        <v>8754500</v>
+      </c>
+      <c r="F12" s="37" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>R0111559</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="36" t="n">
+        <v>10345200</v>
+      </c>
+      <c r="F13" s="37" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="G13" s="36" t="n"/>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>R0111560</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St (R0114026)</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="36" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="36" t="n"/>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>R0114026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park (R0121833)</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C15" s="36" t="n">
+        <v>5487982</v>
+      </c>
+      <c r="D15" s="37" t="n">
+        <v>150</v>
+      </c>
+      <c r="E15" s="36" t="n">
+        <v>3919000</v>
+      </c>
+      <c r="F15" s="37" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>R0121833</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="21" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="21" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B19" s="20" t="n"/>
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20" t="n"/>
+      <c r="E19" s="20" t="n"/>
+      <c r="F19" s="20" t="n"/>
+      <c r="G19" s="20" t="n"/>
+      <c r="H19" s="21" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>7205 Gilpin Way</t>
         </is>
       </c>
-      <c r="B16" s="9" t="n">
+      <c r="B21" s="9" t="n">
         <v>359394</v>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C21" s="9" t="n">
         <v>-17970</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D21" s="9" t="n">
         <v>341424</v>
       </c>
-      <c r="E16" s="9" t="n">
+      <c r="E21" s="9" t="n">
         <v>-27314</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F21" s="14" t="n">
         <v>314110</v>
       </c>
-      <c r="G16" s="19" t="n">
+      <c r="G21" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H21" s="14" t="n">
         <v>4832500</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>17608 E. 24th Dr</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n">
+      <c r="B22" s="9" t="n">
         <v>209100</v>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C22" s="9" t="n">
         <v>-10455</v>
       </c>
-      <c r="D17" s="9" t="n">
+      <c r="D22" s="9" t="n">
         <v>198645</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E22" s="9" t="n">
         <v>-15892</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F22" s="14" t="n">
         <v>182753</v>
       </c>
-      <c r="G17" s="19" t="n">
+      <c r="G22" s="19" t="n">
         <v>0.06</v>
       </c>
-      <c r="H17" s="14" t="n">
+      <c r="H22" s="14" t="n">
         <v>3050000</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>12260 Pennsylvania St</t>
         </is>
       </c>
-      <c r="B18" s="9" t="n">
+      <c r="B23" s="9" t="n">
         <v>237290</v>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C23" s="9" t="n">
         <v>-16610</v>
       </c>
-      <c r="D18" s="9" t="n">
+      <c r="D23" s="9" t="n">
         <v>220680</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E23" s="9" t="n">
         <v>-22068</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F23" s="14" t="n">
         <v>198612</v>
       </c>
-      <c r="G18" s="19" t="n">
+      <c r="G23" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H18" s="14" t="n">
+      <c r="H23" s="14" t="n">
         <v>2837000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>6770 E. 56th Ave</t>
         </is>
       </c>
-      <c r="B19" s="9" t="n">
+      <c r="B24" s="9" t="n">
         <v>115824</v>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C24" s="9" t="n">
         <v>-5791</v>
       </c>
-      <c r="D19" s="9" t="n">
+      <c r="D24" s="9" t="n">
         <v>110033</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E24" s="9" t="n">
         <v>-5502</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F24" s="14" t="n">
         <v>104531</v>
       </c>
-      <c r="G19" s="19" t="n">
+      <c r="G24" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H19" s="14" t="n">
+      <c r="H24" s="14" t="n">
         <v>1493302</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B25" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C25" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D25" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E25" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F25" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G25" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H25" s="14" t="n">
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave (R0110351)</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="n">
+        <v>599228</v>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>-59923</v>
+      </c>
+      <c r="D26" s="36" t="n">
+        <v>539305</v>
+      </c>
+      <c r="E26" s="36" t="n">
+        <v>-43144</v>
+      </c>
+      <c r="F26" s="38" t="n">
+        <v>496161</v>
+      </c>
+      <c r="G26" s="39" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="H26" s="38" t="n">
+        <v>7939000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="n">
+        <v>781250</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>-78125</v>
+      </c>
+      <c r="D27" s="36" t="n">
+        <v>703125</v>
+      </c>
+      <c r="E27" s="36" t="n">
+        <v>-35156</v>
+      </c>
+      <c r="F27" s="38" t="n">
+        <v>667969</v>
+      </c>
+      <c r="G27" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H27" s="38" t="n">
+        <v>8754500</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>-125000</v>
+      </c>
+      <c r="D28" s="36" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="E28" s="36" t="n">
+        <v>-56250</v>
+      </c>
+      <c r="F28" s="38" t="n">
+        <v>1068750</v>
+      </c>
+      <c r="G28" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H28" s="38" t="n">
+        <v>14007200</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - market (R0121833)</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="n">
+        <v>346484</v>
+      </c>
+      <c r="C29" s="36" t="n">
+        <v>-17324</v>
+      </c>
+      <c r="D29" s="36" t="n">
+        <v>329160</v>
+      </c>
+      <c r="E29" s="36" t="n">
+        <v>-49374</v>
+      </c>
+      <c r="F29" s="38" t="n">
+        <v>279786</v>
+      </c>
+      <c r="G29" s="39" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H29" s="38" t="n">
+        <v>3919000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - actual 2024 (R0121833)</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="E30" s="36" t="n">
+        <v>-110337</v>
+      </c>
+      <c r="F30" s="38" t="n">
+        <v>347380</v>
+      </c>
+      <c r="G30" s="39" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H30" s="38" t="n">
+        <v>3510000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - actual 2023 (R0121833)</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>401204</v>
+      </c>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n">
+        <v>401204</v>
+      </c>
+      <c r="E31" s="36" t="n">
+        <v>-119063</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>282140</v>
+      </c>
+      <c r="G31" s="39" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H31" s="38" t="n">
+        <v>2851000</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="21" t="n"/>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +5542,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +5656,242 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="40" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="n">
+        <v>943294.95</v>
+      </c>
+      <c r="C9" s="37" t="n">
+        <v>390362.08</v>
+      </c>
+      <c r="D9" s="41">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. True NOI: no debt service, depreciation or capex in operating expenses. R0110351</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="40" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B10" s="37" t="n">
+        <v>883682.08</v>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>361874.61</v>
+      </c>
+      <c r="D10" s="41">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. True NOI. R0110351</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B11" s="37" t="n">
+        <v>1631357.84</v>
+      </c>
+      <c r="C11" s="37" t="n">
+        <v>642378.16</v>
+      </c>
+      <c r="D11" s="41">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>Operating income before interest ($276,132.81) and other/depreciation ($548,107.94); net income after those = $164,738.93. R0111559</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B12" s="37" t="n">
+        <v>1809817.41</v>
+      </c>
+      <c r="C12" s="37" t="n">
+        <v>975170.45</v>
+      </c>
+      <c r="D12" s="41">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>Operating income before interest ($284,797.60) and other/depreciation ($592,527.05); net income after those = ($42,677.69). R0111559</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B13" s="37" t="n">
+        <v>601617.52</v>
+      </c>
+      <c r="C13" s="37" t="n">
+        <v>856598.01</v>
+      </c>
+      <c r="D13" s="41">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>Operating LOSS - FedEx lease expired 4/30/2024. Before interest ($443,845.39) and other/depr ($721,647.35); net = ($1,420,473.23). R0111560</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B14" s="37" t="n">
+        <v>2280295</v>
+      </c>
+      <c r="C14" s="37" t="n">
+        <v>1162402.67</v>
+      </c>
+      <c r="D14" s="41">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>Operating income before interest ($457,772.92) and other/depr ($795,716.24); net = ($135,596.83). Expenses include $887,022.00 real estate taxes. R0111560</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B15" s="37" t="n">
+        <v>282582.82</v>
+      </c>
+      <c r="C15" s="37" t="n">
+        <v>125492.28</v>
+      </c>
+      <c r="D15" s="41">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Cash basis. NOT a true NOI: expenses include depreciation $78,017.21 + amortization $5,811.58 and lease commissions $34,701.00, while property tax is $0.00. R0114026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B16" s="37" t="n">
+        <v>216726</v>
+      </c>
+      <c r="C16" s="37" t="n"/>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>Cash basis, EXCERPT ONLY. Income total as printed; itemised rents total $214,254.27, so $2,471.73 sits on a page not included in the submission. Expense detail incomplete (only accounting $3,006.92, amortization $855.00, bank fees $30.00 shown). R0114026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B17" s="37" t="n">
+        <v>457717.43</v>
+      </c>
+      <c r="C17" s="37" t="n">
+        <v>290220.4</v>
+      </c>
+      <c r="D17" s="41">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. NOT a true NOI: includes interest expense $44,300.59. Total expense $289,750.40 + other expense $470.00. Net income $167,497.03. R0121833</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B18" s="37" t="n">
+        <v>401203.65</v>
+      </c>
+      <c r="C18" s="37" t="n">
+        <v>285540.55</v>
+      </c>
+      <c r="D18" s="41">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. NOT a true NOI: includes interest expense $46,920.74. Net income $115,663.10. R0121833</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +5903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E341"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +5927,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5207,6 +7311,5986 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B66" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent - Industrial</t>
+        </is>
+      </c>
+      <c r="D66" s="37" t="n">
+        <v>545012.1</v>
+      </c>
+      <c r="E66" s="32" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B67" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Current Yr CAM/Operating Exp</t>
+        </is>
+      </c>
+      <c r="D67" s="37" t="n">
+        <v>21372.13</v>
+      </c>
+      <c r="E67" s="32" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B68" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Current Yr Insurance</t>
+        </is>
+      </c>
+      <c r="D68" s="37" t="n">
+        <v>37117.43</v>
+      </c>
+      <c r="E68" s="32" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B69" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Current Yr Taxes</t>
+        </is>
+      </c>
+      <c r="D69" s="37" t="n">
+        <v>348999.96</v>
+      </c>
+      <c r="E69" s="32" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B70" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Prior Yr CAM/Operating Exp</t>
+        </is>
+      </c>
+      <c r="D70" s="37" t="n">
+        <v>7784.82</v>
+      </c>
+      <c r="E70" s="32" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B71" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Prior Yr Insurance</t>
+        </is>
+      </c>
+      <c r="D71" s="37" t="n">
+        <v>197.31</v>
+      </c>
+      <c r="E71" s="32" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B72" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Prior Yr Taxes</t>
+        </is>
+      </c>
+      <c r="D72" s="37" t="n">
+        <v>-17188.8</v>
+      </c>
+      <c r="E72" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B73" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C73" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D73" s="43">
+        <f>SUM(D66:D72)</f>
+        <v/>
+      </c>
+      <c r="E73" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $943,294.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B74" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>Admin - General</t>
+        </is>
+      </c>
+      <c r="D74" s="37" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E74" s="32" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B75" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>Admin - Full-Time Salaries</t>
+        </is>
+      </c>
+      <c r="D75" s="37" t="n">
+        <v>5638.74</v>
+      </c>
+      <c r="E75" s="32" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B76" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>Admin - Office Supplies &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D76" s="37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E76" s="32" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B77" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>Professional Fee - MRI</t>
+        </is>
+      </c>
+      <c r="D77" s="37" t="n">
+        <v>3236.14</v>
+      </c>
+      <c r="E77" s="32" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B78" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>Cleaning - Pest Control</t>
+        </is>
+      </c>
+      <c r="D78" s="37" t="n">
+        <v>165</v>
+      </c>
+      <c r="E78" s="32" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B79" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>Professional Fee - Sustainability</t>
+        </is>
+      </c>
+      <c r="D79" s="37" t="n">
+        <v>1627.76</v>
+      </c>
+      <c r="E79" s="32" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B80" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+      <c r="D80" s="37" t="n">
+        <v>2519.66</v>
+      </c>
+      <c r="E80" s="32" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B81" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="D81" s="37" t="n">
+        <v>8175.16</v>
+      </c>
+      <c r="E81" s="32" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B82" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D82" s="37" t="n">
+        <v>348999.96</v>
+      </c>
+      <c r="E82" s="32" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B83" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>Prior Year Taxes</t>
+        </is>
+      </c>
+      <c r="D83" s="37" t="n">
+        <v>-17188.8</v>
+      </c>
+      <c r="E83" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B84" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Property</t>
+        </is>
+      </c>
+      <c r="D84" s="37" t="n">
+        <v>25578.36</v>
+      </c>
+      <c r="E84" s="32" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B85" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Liability</t>
+        </is>
+      </c>
+      <c r="D85" s="37" t="n">
+        <v>3521.23</v>
+      </c>
+      <c r="E85" s="32" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B86" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Other</t>
+        </is>
+      </c>
+      <c r="D86" s="37" t="n">
+        <v>8017.84</v>
+      </c>
+      <c r="E86" s="32" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B87" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>Nonrecoverable - R&amp;M Other</t>
+        </is>
+      </c>
+      <c r="D87" s="37" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="E87" s="32" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2024</t>
+        </is>
+      </c>
+      <c r="B88" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D88" s="43">
+        <f>SUM(D74:D87)</f>
+        <v/>
+      </c>
+      <c r="E88" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $390,362.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B89" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent - Industrial</t>
+        </is>
+      </c>
+      <c r="D89" s="37" t="n">
+        <v>531386.87</v>
+      </c>
+      <c r="E89" s="32" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B90" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Current Yr CAM/Operating Exp</t>
+        </is>
+      </c>
+      <c r="D90" s="37" t="n">
+        <v>18538.35</v>
+      </c>
+      <c r="E90" s="32" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B91" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Current Yr Insurance</t>
+        </is>
+      </c>
+      <c r="D91" s="37" t="n">
+        <v>29594.51</v>
+      </c>
+      <c r="E91" s="32" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B92" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Current Yr Taxes</t>
+        </is>
+      </c>
+      <c r="D92" s="37" t="n">
+        <v>308202.9</v>
+      </c>
+      <c r="E92" s="32" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B93" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Prior Yr CAM/Operating Exp</t>
+        </is>
+      </c>
+      <c r="D93" s="37" t="n">
+        <v>-766.53</v>
+      </c>
+      <c r="E93" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B94" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C94" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Prior Yr Insurance</t>
+        </is>
+      </c>
+      <c r="D94" s="37" t="n">
+        <v>-312.24</v>
+      </c>
+      <c r="E94" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B95" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>Recovery - Prior Yr Taxes</t>
+        </is>
+      </c>
+      <c r="D95" s="37" t="n">
+        <v>-2961.78</v>
+      </c>
+      <c r="E95" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B96" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C96" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D96" s="43">
+        <f>SUM(D89:D95)</f>
+        <v/>
+      </c>
+      <c r="E96" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $883,682.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B97" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C97" s="32" t="inlineStr">
+        <is>
+          <t>Admin - General</t>
+        </is>
+      </c>
+      <c r="D97" s="37" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="E97" s="32" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B98" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C98" s="32" t="inlineStr">
+        <is>
+          <t>Admin - Full-Time Salaries</t>
+        </is>
+      </c>
+      <c r="D98" s="37" t="n">
+        <v>6546.36</v>
+      </c>
+      <c r="E98" s="32" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B99" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>Admin - Office Supplies &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="D99" s="37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="E99" s="32" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B100" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="32" t="inlineStr">
+        <is>
+          <t>Professional Fee - MRI</t>
+        </is>
+      </c>
+      <c r="D100" s="37" t="n">
+        <v>2752.6</v>
+      </c>
+      <c r="E100" s="32" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B101" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="32" t="inlineStr">
+        <is>
+          <t>Professional Fee - Audit and Tax Filing</t>
+        </is>
+      </c>
+      <c r="D101" s="37" t="n">
+        <v>7310.78</v>
+      </c>
+      <c r="E101" s="32" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B102" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>Professional Fee - Legal</t>
+        </is>
+      </c>
+      <c r="D102" s="37" t="n">
+        <v>518.5</v>
+      </c>
+      <c r="E102" s="32" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B103" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="32" t="inlineStr">
+        <is>
+          <t>Professional Fee - Sustainability</t>
+        </is>
+      </c>
+      <c r="D103" s="37" t="n">
+        <v>915.86</v>
+      </c>
+      <c r="E103" s="32" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B104" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+      <c r="D104" s="37" t="n">
+        <v>768.0700000000001</v>
+      </c>
+      <c r="E104" s="32" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B105" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="D105" s="37" t="n">
+        <v>7970.79</v>
+      </c>
+      <c r="E105" s="32" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B106" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D106" s="37" t="n">
+        <v>308202.9</v>
+      </c>
+      <c r="E106" s="32" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B107" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>Prior Year Taxes</t>
+        </is>
+      </c>
+      <c r="D107" s="37" t="n">
+        <v>-2961.78</v>
+      </c>
+      <c r="E107" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B108" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Property</t>
+        </is>
+      </c>
+      <c r="D108" s="37" t="n">
+        <v>20559.31</v>
+      </c>
+      <c r="E108" s="32" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B109" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Liability</t>
+        </is>
+      </c>
+      <c r="D109" s="37" t="n">
+        <v>3820.7</v>
+      </c>
+      <c r="E109" s="32" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B110" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Other</t>
+        </is>
+      </c>
+      <c r="D110" s="37" t="n">
+        <v>5411.81</v>
+      </c>
+      <c r="E110" s="32" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>18300 E 28th Ave - CY2023</t>
+        </is>
+      </c>
+      <c r="B111" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C111" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D111" s="43">
+        <f>SUM(D97:D110)</f>
+        <v/>
+      </c>
+      <c r="E111" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $361,874.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B112" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
+      <c r="D112" s="37" t="n">
+        <v>295017.1</v>
+      </c>
+      <c r="E112" s="32" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B113" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes - Tenant</t>
+        </is>
+      </c>
+      <c r="D113" s="37" t="n">
+        <v>118960.59</v>
+      </c>
+      <c r="E113" s="32" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B114" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D114" s="37" t="n">
+        <v>20106</v>
+      </c>
+      <c r="E114" s="32" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B115" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C115" s="32" t="inlineStr">
+        <is>
+          <t>Gas &amp; Electric</t>
+        </is>
+      </c>
+      <c r="D115" s="37" t="n">
+        <v>8448.940000000001</v>
+      </c>
+      <c r="E115" s="32" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B116" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>Community Area Maintenance</t>
+        </is>
+      </c>
+      <c r="D116" s="37" t="n">
+        <v>5487.8</v>
+      </c>
+      <c r="E116" s="32" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B117" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C117" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D117" s="37" t="n">
+        <v>5097</v>
+      </c>
+      <c r="E117" s="32" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B118" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C118" s="32" t="inlineStr">
+        <is>
+          <t>Trash</t>
+        </is>
+      </c>
+      <c r="D118" s="37" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E118" s="32" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B119" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C119" s="32" t="inlineStr">
+        <is>
+          <t>Misc. Tenant Repairs</t>
+        </is>
+      </c>
+      <c r="D119" s="37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E119" s="32" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B120" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C120" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D120" s="43">
+        <f>SUM(D112:D119)</f>
+        <v/>
+      </c>
+      <c r="E120" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $457,717.43</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B121" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C121" s="32" t="inlineStr">
+        <is>
+          <t>Property Tax Expense</t>
+        </is>
+      </c>
+      <c r="D121" s="37" t="n">
+        <v>133608.36</v>
+      </c>
+      <c r="E121" s="32" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B122" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C122" s="32" t="inlineStr">
+        <is>
+          <t>Interest Expense - Loan</t>
+        </is>
+      </c>
+      <c r="D122" s="37" t="n">
+        <v>44300.59</v>
+      </c>
+      <c r="E122" s="32" t="inlineStr">
+        <is>
+          <t>Debt service - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B123" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C123" s="32" t="inlineStr">
+        <is>
+          <t>Property Management Fees</t>
+        </is>
+      </c>
+      <c r="D123" s="37" t="n">
+        <v>31500</v>
+      </c>
+      <c r="E123" s="32" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B124" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C124" s="32" t="inlineStr">
+        <is>
+          <t>Building Maintenance</t>
+        </is>
+      </c>
+      <c r="D124" s="37" t="n">
+        <v>29130.84</v>
+      </c>
+      <c r="E124" s="32" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B125" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C125" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Expense</t>
+        </is>
+      </c>
+      <c r="D125" s="37" t="n">
+        <v>18520.09</v>
+      </c>
+      <c r="E125" s="32" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B126" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" s="32" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D126" s="37" t="n">
+        <v>9783.049999999999</v>
+      </c>
+      <c r="E126" s="32" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B127" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" s="32" t="inlineStr">
+        <is>
+          <t>Trash Removal</t>
+        </is>
+      </c>
+      <c r="D127" s="37" t="n">
+        <v>5821.82</v>
+      </c>
+      <c r="E127" s="32" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B128" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C128" s="32" t="inlineStr">
+        <is>
+          <t>Common Area Maintenance</t>
+        </is>
+      </c>
+      <c r="D128" s="37" t="n">
+        <v>5750</v>
+      </c>
+      <c r="E128" s="32" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B129" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C129" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer Expense</t>
+        </is>
+      </c>
+      <c r="D129" s="37" t="n">
+        <v>4616.57</v>
+      </c>
+      <c r="E129" s="32" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B130" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C130" s="32" t="inlineStr">
+        <is>
+          <t>Telephone Expense</t>
+        </is>
+      </c>
+      <c r="D130" s="37" t="n">
+        <v>1780.94</v>
+      </c>
+      <c r="E130" s="32" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B131" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C131" s="32" t="inlineStr">
+        <is>
+          <t>Automobile Expense</t>
+        </is>
+      </c>
+      <c r="D131" s="37" t="n">
+        <v>1504.2</v>
+      </c>
+      <c r="E131" s="32" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B132" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" s="32" t="inlineStr">
+        <is>
+          <t>Accounting Expense</t>
+        </is>
+      </c>
+      <c r="D132" s="37" t="n">
+        <v>1062.5</v>
+      </c>
+      <c r="E132" s="32" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B133" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" s="32" t="inlineStr">
+        <is>
+          <t>Adams Co Stormwater Utility Fee</t>
+        </is>
+      </c>
+      <c r="D133" s="37" t="n">
+        <v>886</v>
+      </c>
+      <c r="E133" s="32" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B134" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C134" s="32" t="inlineStr">
+        <is>
+          <t>Fire Alarm Monitoring</t>
+        </is>
+      </c>
+      <c r="D134" s="37" t="n">
+        <v>830.4400000000001</v>
+      </c>
+      <c r="E134" s="32" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B135" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C135" s="32" t="inlineStr">
+        <is>
+          <t>Fire Alarm Inspection &amp; Repairs</t>
+        </is>
+      </c>
+      <c r="D135" s="37" t="n">
+        <v>655</v>
+      </c>
+      <c r="E135" s="32" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B136" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C136" s="32" t="inlineStr">
+        <is>
+          <t>Ask My Accountant (other expense)</t>
+        </is>
+      </c>
+      <c r="D136" s="37" t="n">
+        <v>470</v>
+      </c>
+      <c r="E136" s="32" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2024</t>
+        </is>
+      </c>
+      <c r="B137" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C137" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE (incl. other)</t>
+        </is>
+      </c>
+      <c r="D137" s="43">
+        <f>SUM(D121:D136)</f>
+        <v/>
+      </c>
+      <c r="E137" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $290,220.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B138" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C138" s="32" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
+      <c r="D138" s="37" t="n">
+        <v>279618.69</v>
+      </c>
+      <c r="E138" s="32" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B139" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C139" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes - Tenant</t>
+        </is>
+      </c>
+      <c r="D139" s="37" t="n">
+        <v>80179.09</v>
+      </c>
+      <c r="E139" s="32" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B140" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C140" s="32" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D140" s="37" t="n">
+        <v>18863.75</v>
+      </c>
+      <c r="E140" s="32" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B141" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C141" s="32" t="inlineStr">
+        <is>
+          <t>Gas &amp; Electric</t>
+        </is>
+      </c>
+      <c r="D141" s="37" t="n">
+        <v>9403.07</v>
+      </c>
+      <c r="E141" s="32" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B142" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C142" s="32" t="inlineStr">
+        <is>
+          <t>Community Area Maintenance</t>
+        </is>
+      </c>
+      <c r="D142" s="37" t="n">
+        <v>7474.61</v>
+      </c>
+      <c r="E142" s="32" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B143" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C143" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D143" s="37" t="n">
+        <v>3485.67</v>
+      </c>
+      <c r="E143" s="32" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B144" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C144" s="32" t="inlineStr">
+        <is>
+          <t>Trash</t>
+        </is>
+      </c>
+      <c r="D144" s="37" t="n">
+        <v>2847.77</v>
+      </c>
+      <c r="E144" s="32" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B145" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C145" s="32" t="inlineStr">
+        <is>
+          <t>Misc. Tenant Repairs</t>
+        </is>
+      </c>
+      <c r="D145" s="37" t="n">
+        <v>-669</v>
+      </c>
+      <c r="E145" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B146" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C146" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D146" s="43">
+        <f>SUM(D138:D145)</f>
+        <v/>
+      </c>
+      <c r="E146" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $401,203.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B147" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C147" s="32" t="inlineStr">
+        <is>
+          <t>Property Tax Expense</t>
+        </is>
+      </c>
+      <c r="D147" s="37" t="n">
+        <v>117601.18</v>
+      </c>
+      <c r="E147" s="32" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B148" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C148" s="32" t="inlineStr">
+        <is>
+          <t>Interest Expense - Loan</t>
+        </is>
+      </c>
+      <c r="D148" s="37" t="n">
+        <v>46920.74</v>
+      </c>
+      <c r="E148" s="32" t="inlineStr">
+        <is>
+          <t>Debt service - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B149" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C149" s="32" t="inlineStr">
+        <is>
+          <t>Building Maintenance</t>
+        </is>
+      </c>
+      <c r="D149" s="37" t="n">
+        <v>21081.48</v>
+      </c>
+      <c r="E149" s="32" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B150" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C150" s="32" t="inlineStr">
+        <is>
+          <t>Property Management Fees</t>
+        </is>
+      </c>
+      <c r="D150" s="37" t="n">
+        <v>19500</v>
+      </c>
+      <c r="E150" s="32" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B151" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C151" s="32" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D151" s="37" t="n">
+        <v>18166.07</v>
+      </c>
+      <c r="E151" s="32" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B152" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C152" s="32" t="inlineStr">
+        <is>
+          <t>Commission Expense</t>
+        </is>
+      </c>
+      <c r="D152" s="37" t="n">
+        <v>17116.84</v>
+      </c>
+      <c r="E152" s="32" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B153" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C153" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Expense</t>
+        </is>
+      </c>
+      <c r="D153" s="37" t="n">
+        <v>15675.73</v>
+      </c>
+      <c r="E153" s="32" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B154" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C154" s="32" t="inlineStr">
+        <is>
+          <t>Common Area Maintenance</t>
+        </is>
+      </c>
+      <c r="D154" s="37" t="n">
+        <v>6990</v>
+      </c>
+      <c r="E154" s="32" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B155" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C155" s="32" t="inlineStr">
+        <is>
+          <t>Tenant Repairs</t>
+        </is>
+      </c>
+      <c r="D155" s="37" t="n">
+        <v>5957.21</v>
+      </c>
+      <c r="E155" s="32" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B156" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C156" s="32" t="inlineStr">
+        <is>
+          <t>Trash Removal</t>
+        </is>
+      </c>
+      <c r="D156" s="37" t="n">
+        <v>5314.77</v>
+      </c>
+      <c r="E156" s="32" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B157" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C157" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer Expense</t>
+        </is>
+      </c>
+      <c r="D157" s="37" t="n">
+        <v>3690.16</v>
+      </c>
+      <c r="E157" s="32" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B158" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C158" s="32" t="inlineStr">
+        <is>
+          <t>Automobile Expense</t>
+        </is>
+      </c>
+      <c r="D158" s="37" t="n">
+        <v>1955.46</v>
+      </c>
+      <c r="E158" s="32" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B159" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C159" s="32" t="inlineStr">
+        <is>
+          <t>Telephone Expense</t>
+        </is>
+      </c>
+      <c r="D159" s="37" t="n">
+        <v>1629.46</v>
+      </c>
+      <c r="E159" s="32" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B160" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C160" s="32" t="inlineStr">
+        <is>
+          <t>Accounting Expense</t>
+        </is>
+      </c>
+      <c r="D160" s="37" t="n">
+        <v>1525</v>
+      </c>
+      <c r="E160" s="32" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B161" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C161" s="32" t="inlineStr">
+        <is>
+          <t>Adams Co Stormwater Utility Fee</t>
+        </is>
+      </c>
+      <c r="D161" s="37" t="n">
+        <v>886</v>
+      </c>
+      <c r="E161" s="32" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B162" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C162" s="32" t="inlineStr">
+        <is>
+          <t>Fire Alarm Inspection &amp; Repairs</t>
+        </is>
+      </c>
+      <c r="D162" s="37" t="n">
+        <v>820.65</v>
+      </c>
+      <c r="E162" s="32" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B163" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C163" s="32" t="inlineStr">
+        <is>
+          <t>Fire Alarm Monitoring</t>
+        </is>
+      </c>
+      <c r="D163" s="37" t="n">
+        <v>673.92</v>
+      </c>
+      <c r="E163" s="32" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B164" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C164" s="32" t="inlineStr">
+        <is>
+          <t>Office Supplies</t>
+        </is>
+      </c>
+      <c r="D164" s="37" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="E164" s="32" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B165" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C165" s="32" t="inlineStr">
+        <is>
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D165" s="37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E165" s="32" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - CY2023</t>
+        </is>
+      </c>
+      <c r="B166" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C166" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D166" s="43">
+        <f>SUM(D147:D165)</f>
+        <v/>
+      </c>
+      <c r="E166" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $285,540.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B167" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C167" s="32" t="inlineStr">
+        <is>
+          <t>Rent - CPI</t>
+        </is>
+      </c>
+      <c r="D167" s="37" t="n">
+        <v>153780</v>
+      </c>
+      <c r="E167" s="32" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B168" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C168" s="32" t="inlineStr">
+        <is>
+          <t>Rent - Colorado Wrap</t>
+        </is>
+      </c>
+      <c r="D168" s="37" t="n">
+        <v>63525</v>
+      </c>
+      <c r="E168" s="32" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B169" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C169" s="32" t="inlineStr">
+        <is>
+          <t>Rent - Touch Stone</t>
+        </is>
+      </c>
+      <c r="D169" s="37" t="n">
+        <v>62480</v>
+      </c>
+      <c r="E169" s="32" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B170" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C170" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee - CPI</t>
+        </is>
+      </c>
+      <c r="D170" s="37" t="n">
+        <v>1537.8</v>
+      </c>
+      <c r="E170" s="32" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B171" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C171" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee - Colorado Wrap</t>
+        </is>
+      </c>
+      <c r="D171" s="37" t="n">
+        <v>635.22</v>
+      </c>
+      <c r="E171" s="32" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B172" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C172" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees - Touchstone</t>
+        </is>
+      </c>
+      <c r="D172" s="37" t="n">
+        <v>624.8</v>
+      </c>
+      <c r="E172" s="32" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B173" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C173" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D173" s="43">
+        <f>SUM(D167:D172)</f>
+        <v/>
+      </c>
+      <c r="E173" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $282,582.82</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B174" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C174" s="32" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D174" s="37" t="n">
+        <v>78017.21000000001</v>
+      </c>
+      <c r="E174" s="32" t="inlineStr">
+        <is>
+          <t>Non-cash - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B175" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C175" s="32" t="inlineStr">
+        <is>
+          <t>Lease Commissions</t>
+        </is>
+      </c>
+      <c r="D175" s="37" t="n">
+        <v>34701</v>
+      </c>
+      <c r="E175" s="32" t="inlineStr">
+        <is>
+          <t>Capital/leasing cost - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B176" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C176" s="32" t="inlineStr">
+        <is>
+          <t>Amortization expense</t>
+        </is>
+      </c>
+      <c r="D176" s="37" t="n">
+        <v>5811.58</v>
+      </c>
+      <c r="E176" s="32" t="inlineStr">
+        <is>
+          <t>Non-cash - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B177" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C177" s="32" t="inlineStr">
+        <is>
+          <t>Accounting Expense</t>
+        </is>
+      </c>
+      <c r="D177" s="37" t="n">
+        <v>4675</v>
+      </c>
+      <c r="E177" s="32" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B178" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C178" s="32" t="inlineStr">
+        <is>
+          <t>Roof Maintenance - CAM</t>
+        </is>
+      </c>
+      <c r="D178" s="37" t="n">
+        <v>875</v>
+      </c>
+      <c r="E178" s="32" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B179" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C179" s="32" t="inlineStr">
+        <is>
+          <t>Owner Expense</t>
+        </is>
+      </c>
+      <c r="D179" s="37" t="n">
+        <v>527.24</v>
+      </c>
+      <c r="E179" s="32" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B180" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C180" s="32" t="inlineStr">
+        <is>
+          <t>Repair and Maintenance - CAM</t>
+        </is>
+      </c>
+      <c r="D180" s="37" t="n">
+        <v>525.25</v>
+      </c>
+      <c r="E180" s="32" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B181" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C181" s="32" t="inlineStr">
+        <is>
+          <t>Legal Expense</t>
+        </is>
+      </c>
+      <c r="D181" s="37" t="n">
+        <v>345</v>
+      </c>
+      <c r="E181" s="32" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B182" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C182" s="32" t="inlineStr">
+        <is>
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D182" s="37" t="n">
+        <v>15</v>
+      </c>
+      <c r="E182" s="32" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B183" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C183" s="32" t="inlineStr">
+        <is>
+          <t>Property Tax</t>
+        </is>
+      </c>
+      <c r="D183" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E183" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B184" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C184" s="32" t="inlineStr">
+        <is>
+          <t>HVAC / Insurance / Landscape / Trash / Utilities / Water - CAM</t>
+        </is>
+      </c>
+      <c r="D184" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E184" s="32" t="inlineStr">
+        <is>
+          <t>All reported as $0.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2024</t>
+        </is>
+      </c>
+      <c r="B185" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C185" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D185" s="43">
+        <f>SUM(D174:D184)</f>
+        <v/>
+      </c>
+      <c r="E185" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $125,492.28</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B186" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C186" s="32" t="inlineStr">
+        <is>
+          <t>Rent - CPI</t>
+        </is>
+      </c>
+      <c r="D186" s="37" t="n">
+        <v>124025</v>
+      </c>
+      <c r="E186" s="32" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B187" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C187" s="32" t="inlineStr">
+        <is>
+          <t>Rent - Colorado Wrap</t>
+        </is>
+      </c>
+      <c r="D187" s="37" t="n">
+        <v>61425.84</v>
+      </c>
+      <c r="E187" s="32" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B188" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C188" s="32" t="inlineStr">
+        <is>
+          <t>Rent - Touch Stone</t>
+        </is>
+      </c>
+      <c r="D188" s="37" t="n">
+        <v>28803.43</v>
+      </c>
+      <c r="E188" s="32" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B189" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C189" s="40" t="inlineStr">
+        <is>
+          <t>SUBTOTAL of itemised rents (printed 'Total for Income with sub-accounts' = $216,726.00; $2,471.73 is on a page not included)</t>
+        </is>
+      </c>
+      <c r="D189" s="43">
+        <f>SUM(D186:D188)</f>
+        <v/>
+      </c>
+      <c r="E189" s="32" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B190" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C190" s="32" t="inlineStr">
+        <is>
+          <t>Accounting Expense</t>
+        </is>
+      </c>
+      <c r="D190" s="37" t="n">
+        <v>3006.92</v>
+      </c>
+      <c r="E190" s="32" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B191" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C191" s="32" t="inlineStr">
+        <is>
+          <t>Amortization expense</t>
+        </is>
+      </c>
+      <c r="D191" s="37" t="n">
+        <v>855</v>
+      </c>
+      <c r="E191" s="32" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B192" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C192" s="32" t="inlineStr">
+        <is>
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D192" s="37" t="n">
+        <v>30</v>
+      </c>
+      <c r="E192" s="32" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="32" t="inlineStr">
+        <is>
+          <t>6051 Washington St - CY2023</t>
+        </is>
+      </c>
+      <c r="B193" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C193" s="40" t="inlineStr">
+        <is>
+          <t>PARTIAL - expense detail truncated; no printed total in the submitted excerpt</t>
+        </is>
+      </c>
+      <c r="D193" s="43">
+        <f>SUM(D190:D192)</f>
+        <v/>
+      </c>
+      <c r="E193" s="32" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B194" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C194" s="32" t="inlineStr">
+        <is>
+          <t>Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D194" s="37" t="n">
+        <v>816290.11</v>
+      </c>
+      <c r="E194" s="32" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B195" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C195" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D195" s="37" t="n">
+        <v>370458.18</v>
+      </c>
+      <c r="E195" s="32" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B196" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C196" s="32" t="inlineStr">
+        <is>
+          <t>Utilities Reimbursement</t>
+        </is>
+      </c>
+      <c r="D196" s="37" t="n">
+        <v>237036.4</v>
+      </c>
+      <c r="E196" s="32" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B197" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C197" s="32" t="inlineStr">
+        <is>
+          <t>Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D197" s="37" t="n">
+        <v>112044.62</v>
+      </c>
+      <c r="E197" s="32" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B198" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C198" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D198" s="37" t="n">
+        <v>51268.75</v>
+      </c>
+      <c r="E198" s="32" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B199" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C199" s="32" t="inlineStr">
+        <is>
+          <t>Reserve Income</t>
+        </is>
+      </c>
+      <c r="D199" s="37" t="n">
+        <v>34477.56</v>
+      </c>
+      <c r="E199" s="32" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B200" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C200" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Reimbursement</t>
+        </is>
+      </c>
+      <c r="D200" s="37" t="n">
+        <v>18409.99</v>
+      </c>
+      <c r="E200" s="32" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B201" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C201" s="32" t="inlineStr">
+        <is>
+          <t>Rent Above/Below Market</t>
+        </is>
+      </c>
+      <c r="D201" s="37" t="n">
+        <v>11134.68</v>
+      </c>
+      <c r="E201" s="32" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B202" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C202" s="32" t="inlineStr">
+        <is>
+          <t>Direct Tenant Reimbursement</t>
+        </is>
+      </c>
+      <c r="D202" s="37" t="n">
+        <v>3874.98</v>
+      </c>
+      <c r="E202" s="32" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B203" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C203" s="32" t="inlineStr">
+        <is>
+          <t>Tenant TI Reimb Income</t>
+        </is>
+      </c>
+      <c r="D203" s="37" t="n">
+        <v>2545.32</v>
+      </c>
+      <c r="E203" s="32" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B204" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C204" s="32" t="inlineStr">
+        <is>
+          <t>Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D204" s="37" t="n">
+        <v>-26182.75</v>
+      </c>
+      <c r="E204" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B205" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C205" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D205" s="43">
+        <f>SUM(D194:D204)</f>
+        <v/>
+      </c>
+      <c r="E205" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,631,357.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B206" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C206" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D206" s="37" t="n">
+        <v>238177.79</v>
+      </c>
+      <c r="E206" s="32" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B207" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C207" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - DTR</t>
+        </is>
+      </c>
+      <c r="D207" s="37" t="n">
+        <v>190655.91</v>
+      </c>
+      <c r="E207" s="32" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B208" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C208" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees</t>
+        </is>
+      </c>
+      <c r="D208" s="37" t="n">
+        <v>48115.93</v>
+      </c>
+      <c r="E208" s="32" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B209" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C209" s="32" t="inlineStr">
+        <is>
+          <t>Parking Lot</t>
+        </is>
+      </c>
+      <c r="D209" s="37" t="n">
+        <v>27882.26</v>
+      </c>
+      <c r="E209" s="32" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B210" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C210" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Water</t>
+        </is>
+      </c>
+      <c r="D210" s="37" t="n">
+        <v>26890.9</v>
+      </c>
+      <c r="E210" s="32" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B211" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C211" s="32" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="D211" s="37" t="n">
+        <v>19468.01</v>
+      </c>
+      <c r="E211" s="32" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B212" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C212" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D212" s="37" t="n">
+        <v>14262</v>
+      </c>
+      <c r="E212" s="32" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B213" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C213" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal</t>
+        </is>
+      </c>
+      <c r="D213" s="37" t="n">
+        <v>13056.61</v>
+      </c>
+      <c r="E213" s="32" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B214" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C214" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Gas/Heating</t>
+        </is>
+      </c>
+      <c r="D214" s="37" t="n">
+        <v>12760.66</v>
+      </c>
+      <c r="E214" s="32" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B215" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C215" s="32" t="inlineStr">
+        <is>
+          <t>Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D215" s="37" t="n">
+        <v>8339.4</v>
+      </c>
+      <c r="E215" s="32" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B216" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C216" s="32" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="D216" s="37" t="n">
+        <v>6315</v>
+      </c>
+      <c r="E216" s="32" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B217" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C217" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Legal (Leasing)</t>
+        </is>
+      </c>
+      <c r="D217" s="37" t="n">
+        <v>4730</v>
+      </c>
+      <c r="E217" s="32" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B218" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C218" s="32" t="inlineStr">
+        <is>
+          <t>Roof</t>
+        </is>
+      </c>
+      <c r="D218" s="37" t="n">
+        <v>4541.24</v>
+      </c>
+      <c r="E218" s="32" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B219" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C219" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Tax Prep</t>
+        </is>
+      </c>
+      <c r="D219" s="37" t="n">
+        <v>4206</v>
+      </c>
+      <c r="E219" s="32" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B220" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C220" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Liability</t>
+        </is>
+      </c>
+      <c r="D220" s="37" t="n">
+        <v>4138</v>
+      </c>
+      <c r="E220" s="32" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B221" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C221" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Electricity</t>
+        </is>
+      </c>
+      <c r="D221" s="37" t="n">
+        <v>3791.07</v>
+      </c>
+      <c r="E221" s="32" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B222" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C222" s="32" t="inlineStr">
+        <is>
+          <t>Other-DTR</t>
+        </is>
+      </c>
+      <c r="D222" s="37" t="n">
+        <v>3661.72</v>
+      </c>
+      <c r="E222" s="32" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B223" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C223" s="32" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D223" s="37" t="n">
+        <v>2100</v>
+      </c>
+      <c r="E223" s="32" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B224" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C224" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Telephone</t>
+        </is>
+      </c>
+      <c r="D224" s="37" t="n">
+        <v>1907.55</v>
+      </c>
+      <c r="E224" s="32" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B225" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C225" s="32" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="D225" s="37" t="n">
+        <v>1731.19</v>
+      </c>
+      <c r="E225" s="32" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B226" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C226" s="32" t="inlineStr">
+        <is>
+          <t>Sweeping</t>
+        </is>
+      </c>
+      <c r="D226" s="37" t="n">
+        <v>1694.89</v>
+      </c>
+      <c r="E226" s="32" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B227" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C227" s="32" t="inlineStr">
+        <is>
+          <t>Other line items (backflow 270.00, HVAC 616.79, keys 179.58, repairs 169.00, signs 600.45, window washing 460.00, other utilities 15.00, tenant relations 380.69, misc admin (0.01), legal 80.68, prof svc other 732.22, environmental 447.63)</t>
+        </is>
+      </c>
+      <c r="D227" s="37" t="n">
+        <v>3952.03</v>
+      </c>
+      <c r="E227" s="32" t="inlineStr">
+        <is>
+          <t>Aggregated minor accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2024</t>
+        </is>
+      </c>
+      <c r="B228" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C228" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D228" s="43">
+        <f>SUM(D206:D227)</f>
+        <v/>
+      </c>
+      <c r="E228" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $642,378.16</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B229" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C229" s="32" t="inlineStr">
+        <is>
+          <t>Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D229" s="37" t="n">
+        <v>794984.9300000001</v>
+      </c>
+      <c r="E229" s="32" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B230" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C230" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D230" s="37" t="n">
+        <v>556975.99</v>
+      </c>
+      <c r="E230" s="32" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B231" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C231" s="32" t="inlineStr">
+        <is>
+          <t>Utilities Reimbursement</t>
+        </is>
+      </c>
+      <c r="D231" s="37" t="n">
+        <v>224211.78</v>
+      </c>
+      <c r="E231" s="32" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B232" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C232" s="32" t="inlineStr">
+        <is>
+          <t>Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D232" s="37" t="n">
+        <v>81142.14999999999</v>
+      </c>
+      <c r="E232" s="32" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B233" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C233" s="32" t="inlineStr">
+        <is>
+          <t>Direct Tenant Reimbursement</t>
+        </is>
+      </c>
+      <c r="D233" s="37" t="n">
+        <v>48969.89</v>
+      </c>
+      <c r="E233" s="32" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B234" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C234" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D234" s="37" t="n">
+        <v>39899.18</v>
+      </c>
+      <c r="E234" s="32" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B235" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C235" s="32" t="inlineStr">
+        <is>
+          <t>Reserve Income</t>
+        </is>
+      </c>
+      <c r="D235" s="37" t="n">
+        <v>34477.56</v>
+      </c>
+      <c r="E235" s="32" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B236" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C236" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Reimbursement</t>
+        </is>
+      </c>
+      <c r="D236" s="37" t="n">
+        <v>16596</v>
+      </c>
+      <c r="E236" s="32" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B237" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C237" s="32" t="inlineStr">
+        <is>
+          <t>Rent Above/Below Market</t>
+        </is>
+      </c>
+      <c r="D237" s="37" t="n">
+        <v>11134.68</v>
+      </c>
+      <c r="E237" s="32" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B238" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C238" s="32" t="inlineStr">
+        <is>
+          <t>Rent Concessions</t>
+        </is>
+      </c>
+      <c r="D238" s="37" t="n">
+        <v>4125.91</v>
+      </c>
+      <c r="E238" s="32" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B239" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C239" s="32" t="inlineStr">
+        <is>
+          <t>Other Reimbursements</t>
+        </is>
+      </c>
+      <c r="D239" s="37" t="n">
+        <v>3757.5</v>
+      </c>
+      <c r="E239" s="32" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B240" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C240" s="32" t="inlineStr">
+        <is>
+          <t>Tenant TI Reimb Income</t>
+        </is>
+      </c>
+      <c r="D240" s="37" t="n">
+        <v>2545.32</v>
+      </c>
+      <c r="E240" s="32" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B241" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C241" s="32" t="inlineStr">
+        <is>
+          <t>Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D241" s="37" t="n">
+        <v>-9003.48</v>
+      </c>
+      <c r="E241" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B242" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C242" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D242" s="43">
+        <f>SUM(D229:D241)</f>
+        <v/>
+      </c>
+      <c r="E242" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,809,817.41</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B243" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C243" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D243" s="37" t="n">
+        <v>556976</v>
+      </c>
+      <c r="E243" s="32" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B244" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C244" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - DTR</t>
+        </is>
+      </c>
+      <c r="D244" s="37" t="n">
+        <v>197089.44</v>
+      </c>
+      <c r="E244" s="32" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B245" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C245" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees</t>
+        </is>
+      </c>
+      <c r="D245" s="37" t="n">
+        <v>51072.56</v>
+      </c>
+      <c r="E245" s="32" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B246" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C246" s="32" t="inlineStr">
+        <is>
+          <t>Other-DTR</t>
+        </is>
+      </c>
+      <c r="D246" s="37" t="n">
+        <v>31648.03</v>
+      </c>
+      <c r="E246" s="32" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B247" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C247" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Water</t>
+        </is>
+      </c>
+      <c r="D247" s="37" t="n">
+        <v>18658.55</v>
+      </c>
+      <c r="E247" s="32" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B248" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C248" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Gas/Heating</t>
+        </is>
+      </c>
+      <c r="D248" s="37" t="n">
+        <v>18061.78</v>
+      </c>
+      <c r="E248" s="32" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B249" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C249" s="32" t="inlineStr">
+        <is>
+          <t>Parking Lot</t>
+        </is>
+      </c>
+      <c r="D249" s="37" t="n">
+        <v>15959.73</v>
+      </c>
+      <c r="E249" s="32" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B250" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C250" s="32" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="D250" s="37" t="n">
+        <v>13081.96</v>
+      </c>
+      <c r="E250" s="32" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B251" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C251" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D251" s="37" t="n">
+        <v>12342</v>
+      </c>
+      <c r="E251" s="32" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B252" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C252" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal</t>
+        </is>
+      </c>
+      <c r="D252" s="37" t="n">
+        <v>12119.43</v>
+      </c>
+      <c r="E252" s="32" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B253" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C253" s="32" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="D253" s="37" t="n">
+        <v>10957.08</v>
+      </c>
+      <c r="E253" s="32" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B254" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C254" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Legal (Leasing)</t>
+        </is>
+      </c>
+      <c r="D254" s="37" t="n">
+        <v>6953.93</v>
+      </c>
+      <c r="E254" s="32" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B255" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C255" s="32" t="inlineStr">
+        <is>
+          <t>Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D255" s="37" t="n">
+        <v>5466.57</v>
+      </c>
+      <c r="E255" s="32" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B256" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C256" s="32" t="inlineStr">
+        <is>
+          <t>Roof</t>
+        </is>
+      </c>
+      <c r="D256" s="37" t="n">
+        <v>5407.5</v>
+      </c>
+      <c r="E256" s="32" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B257" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C257" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Electricity</t>
+        </is>
+      </c>
+      <c r="D257" s="37" t="n">
+        <v>4680.18</v>
+      </c>
+      <c r="E257" s="32" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B258" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C258" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Liability</t>
+        </is>
+      </c>
+      <c r="D258" s="37" t="n">
+        <v>4496</v>
+      </c>
+      <c r="E258" s="32" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B259" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C259" s="32" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D259" s="37" t="n">
+        <v>2154.16</v>
+      </c>
+      <c r="E259" s="32" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B260" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C260" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Telephone</t>
+        </is>
+      </c>
+      <c r="D260" s="37" t="n">
+        <v>1618.5</v>
+      </c>
+      <c r="E260" s="32" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B261" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C261" s="32" t="inlineStr">
+        <is>
+          <t>Sweeping</t>
+        </is>
+      </c>
+      <c r="D261" s="37" t="n">
+        <v>1473.97</v>
+      </c>
+      <c r="E261" s="32" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B262" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C262" s="32" t="inlineStr">
+        <is>
+          <t>Bank Service Fees</t>
+        </is>
+      </c>
+      <c r="D262" s="37" t="n">
+        <v>1242.82</v>
+      </c>
+      <c r="E262" s="32" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B263" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C263" s="32" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="D263" s="37" t="n">
+        <v>1023.14</v>
+      </c>
+      <c r="E263" s="32" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B264" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C264" s="32" t="inlineStr">
+        <is>
+          <t>Other line items (backflow, glass, painting, signs, window washing, other utilities, other prof svc, environmental)</t>
+        </is>
+      </c>
+      <c r="D264" s="37" t="n">
+        <v>2687.12</v>
+      </c>
+      <c r="E264" s="32" t="inlineStr">
+        <is>
+          <t>Aggregated minor accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 6 - CY2023</t>
+        </is>
+      </c>
+      <c r="B265" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C265" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D265" s="43">
+        <f>SUM(D243:D264)</f>
+        <v/>
+      </c>
+      <c r="E265" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $975,170.45</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B266" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C266" s="32" t="inlineStr">
+        <is>
+          <t>Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D266" s="37" t="n">
+        <v>433916.64</v>
+      </c>
+      <c r="E266" s="32" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B267" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C267" s="32" t="inlineStr">
+        <is>
+          <t>Other Reimbursements</t>
+        </is>
+      </c>
+      <c r="D267" s="37" t="n">
+        <v>158900</v>
+      </c>
+      <c r="E267" s="32" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B268" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C268" s="32" t="inlineStr">
+        <is>
+          <t>Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D268" s="37" t="n">
+        <v>30792.45</v>
+      </c>
+      <c r="E268" s="32" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B269" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C269" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Reimbursement</t>
+        </is>
+      </c>
+      <c r="D269" s="37" t="n">
+        <v>21542.79</v>
+      </c>
+      <c r="E269" s="32" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B270" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C270" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D270" s="37" t="n">
+        <v>12984.33</v>
+      </c>
+      <c r="E270" s="32" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B271" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C271" s="32" t="inlineStr">
+        <is>
+          <t>Direct Tenant Reimbursement</t>
+        </is>
+      </c>
+      <c r="D271" s="37" t="n">
+        <v>12100</v>
+      </c>
+      <c r="E271" s="32" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B272" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C272" s="32" t="inlineStr">
+        <is>
+          <t>Reserve Income</t>
+        </is>
+      </c>
+      <c r="D272" s="37" t="n">
+        <v>8666.68</v>
+      </c>
+      <c r="E272" s="32" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B273" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C273" s="32" t="inlineStr">
+        <is>
+          <t>Utilities Reimbursement</t>
+        </is>
+      </c>
+      <c r="D273" s="37" t="n">
+        <v>1113.72</v>
+      </c>
+      <c r="E273" s="32" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B274" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C274" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D274" s="37" t="n">
+        <v>-53610.69</v>
+      </c>
+      <c r="E274" s="32" t="inlineStr">
+        <is>
+          <t>Credit - reversal on tenant departure</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B275" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C275" s="32" t="inlineStr">
+        <is>
+          <t>Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D275" s="37" t="n">
+        <v>-24788.4</v>
+      </c>
+      <c r="E275" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B276" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C276" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D276" s="43">
+        <f>SUM(D266:D275)</f>
+        <v/>
+      </c>
+      <c r="E276" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $601,617.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B277" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C277" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes (6500)</t>
+        </is>
+      </c>
+      <c r="D277" s="37" t="n">
+        <v>416274.89</v>
+      </c>
+      <c r="E277" s="32" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B278" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C278" s="32" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="D278" s="37" t="n">
+        <v>75423.11</v>
+      </c>
+      <c r="E278" s="32" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B279" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C279" s="32" t="inlineStr">
+        <is>
+          <t>Fire Life Safety (6250)</t>
+        </is>
+      </c>
+      <c r="D279" s="37" t="n">
+        <v>59287.01</v>
+      </c>
+      <c r="E279" s="32" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B280" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C280" s="32" t="inlineStr">
+        <is>
+          <t>Concrete Repairs</t>
+        </is>
+      </c>
+      <c r="D280" s="37" t="n">
+        <v>32885</v>
+      </c>
+      <c r="E280" s="32" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B281" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C281" s="32" t="inlineStr">
+        <is>
+          <t>Leasing - Ground Lease</t>
+        </is>
+      </c>
+      <c r="D281" s="37" t="n">
+        <v>29315</v>
+      </c>
+      <c r="E281" s="32" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B282" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C282" s="32" t="inlineStr">
+        <is>
+          <t>Parking Lot (6320)</t>
+        </is>
+      </c>
+      <c r="D282" s="37" t="n">
+        <v>29326.63</v>
+      </c>
+      <c r="E282" s="32" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B283" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C283" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Water (6635)</t>
+        </is>
+      </c>
+      <c r="D283" s="37" t="n">
+        <v>21194.33</v>
+      </c>
+      <c r="E283" s="32" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B284" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C284" s="32" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="D284" s="37" t="n">
+        <v>20720</v>
+      </c>
+      <c r="E284" s="32" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B285" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C285" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees</t>
+        </is>
+      </c>
+      <c r="D285" s="37" t="n">
+        <v>20123.21</v>
+      </c>
+      <c r="E285" s="32" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B286" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C286" s="32" t="inlineStr">
+        <is>
+          <t>Other-DTR</t>
+        </is>
+      </c>
+      <c r="D286" s="37" t="n">
+        <v>19050.15</v>
+      </c>
+      <c r="E286" s="32" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B287" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C287" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D287" s="37" t="n">
+        <v>17999</v>
+      </c>
+      <c r="E287" s="32" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B288" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C288" s="32" t="inlineStr">
+        <is>
+          <t>HVAC (6275)</t>
+        </is>
+      </c>
+      <c r="D288" s="37" t="n">
+        <v>17159.38</v>
+      </c>
+      <c r="E288" s="32" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B289" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C289" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Electricity</t>
+        </is>
+      </c>
+      <c r="D289" s="37" t="n">
+        <v>15456.85</v>
+      </c>
+      <c r="E289" s="32" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B290" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C290" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal (5370)</t>
+        </is>
+      </c>
+      <c r="D290" s="37" t="n">
+        <v>13374.26</v>
+      </c>
+      <c r="E290" s="32" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B291" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C291" s="32" t="inlineStr">
+        <is>
+          <t>Fire Life Safety (5250)</t>
+        </is>
+      </c>
+      <c r="D291" s="37" t="n">
+        <v>12824.29</v>
+      </c>
+      <c r="E291" s="32" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B292" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C292" s="32" t="inlineStr">
+        <is>
+          <t>Parking Lot (5320)</t>
+        </is>
+      </c>
+      <c r="D292" s="37" t="n">
+        <v>12938.36</v>
+      </c>
+      <c r="E292" s="32" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B293" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C293" s="32" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D293" s="37" t="n">
+        <v>12258.24</v>
+      </c>
+      <c r="E293" s="32" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B294" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C294" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Gas/Heating</t>
+        </is>
+      </c>
+      <c r="D294" s="37" t="n">
+        <v>10275.31</v>
+      </c>
+      <c r="E294" s="32" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B295" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C295" s="32" t="inlineStr">
+        <is>
+          <t>Roof (5350)</t>
+        </is>
+      </c>
+      <c r="D295" s="37" t="n">
+        <v>10428</v>
+      </c>
+      <c r="E295" s="32" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B296" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C296" s="32" t="inlineStr">
+        <is>
+          <t>Landscaping (5290)</t>
+        </is>
+      </c>
+      <c r="D296" s="37" t="n">
+        <v>10027.04</v>
+      </c>
+      <c r="E296" s="32" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B297" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C297" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal (6370)</t>
+        </is>
+      </c>
+      <c r="D297" s="37" t="n">
+        <v>8979.6</v>
+      </c>
+      <c r="E297" s="32" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B298" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C298" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Liability</t>
+        </is>
+      </c>
+      <c r="D298" s="37" t="n">
+        <v>6631</v>
+      </c>
+      <c r="E298" s="32" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B299" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C299" s="32" t="inlineStr">
+        <is>
+          <t>Landscaping (6290)</t>
+        </is>
+      </c>
+      <c r="D299" s="37" t="n">
+        <v>6686.44</v>
+      </c>
+      <c r="E299" s="32" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B300" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C300" s="32" t="inlineStr">
+        <is>
+          <t>HVAC (5275)</t>
+        </is>
+      </c>
+      <c r="D300" s="37" t="n">
+        <v>4732</v>
+      </c>
+      <c r="E300" s="32" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B301" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C301" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Tax Prep</t>
+        </is>
+      </c>
+      <c r="D301" s="37" t="n">
+        <v>4206</v>
+      </c>
+      <c r="E301" s="32" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B302" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C302" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Water (5635)</t>
+        </is>
+      </c>
+      <c r="D302" s="37" t="n">
+        <v>4131.02</v>
+      </c>
+      <c r="E302" s="32" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B303" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C303" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Legal (Leasing)</t>
+        </is>
+      </c>
+      <c r="D303" s="37" t="n">
+        <v>2710</v>
+      </c>
+      <c r="E303" s="32" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B304" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C304" s="32" t="inlineStr">
+        <is>
+          <t>Door Repairs</t>
+        </is>
+      </c>
+      <c r="D304" s="37" t="n">
+        <v>2575.31</v>
+      </c>
+      <c r="E304" s="32" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B305" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C305" s="32" t="inlineStr">
+        <is>
+          <t>Plumbing</t>
+        </is>
+      </c>
+      <c r="D305" s="37" t="n">
+        <v>1944.32</v>
+      </c>
+      <c r="E305" s="32" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B306" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C306" s="32" t="inlineStr">
+        <is>
+          <t>Sweeping</t>
+        </is>
+      </c>
+      <c r="D306" s="37" t="n">
+        <v>2711.83</v>
+      </c>
+      <c r="E306" s="32" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B307" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C307" s="32" t="inlineStr">
+        <is>
+          <t>Other minor accounts (lighting 484.80+852.67, signs 493.46+398.77, window washing 130.00+390.00, backflow 435.00, electrical 476.32, keys 779.00, pest 280.00, roof 6350 1,596.75, repairs 5345 797.50, other utilities 500.92, legal 80.68, prof svc other 732.22)</t>
+        </is>
+      </c>
+      <c r="D307" s="37" t="n">
+        <v>8428.09</v>
+      </c>
+      <c r="E307" s="32" t="inlineStr">
+        <is>
+          <t>Aggregated</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B308" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C308" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes (5500)</t>
+        </is>
+      </c>
+      <c r="D308" s="37" t="n">
+        <v>-53477.66</v>
+      </c>
+      <c r="E308" s="32" t="inlineStr">
+        <is>
+          <t>Credit - reversal</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2024</t>
+        </is>
+      </c>
+      <c r="B309" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C309" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D309" s="43">
+        <f>SUM(D277:D308)</f>
+        <v/>
+      </c>
+      <c r="E309" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $856,598.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B310" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C310" s="32" t="inlineStr">
+        <is>
+          <t>Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D310" s="37" t="n">
+        <v>1291166.6</v>
+      </c>
+      <c r="E310" s="32" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B311" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C311" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D311" s="37" t="n">
+        <v>887022</v>
+      </c>
+      <c r="E311" s="32" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B312" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C312" s="32" t="inlineStr">
+        <is>
+          <t>Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D312" s="37" t="n">
+        <v>112314.39</v>
+      </c>
+      <c r="E312" s="32" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B313" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C313" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D313" s="37" t="n">
+        <v>27573.73</v>
+      </c>
+      <c r="E313" s="32" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B314" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C314" s="32" t="inlineStr">
+        <is>
+          <t>Reserve Income</t>
+        </is>
+      </c>
+      <c r="D314" s="37" t="n">
+        <v>26000.04</v>
+      </c>
+      <c r="E314" s="32" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B315" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C315" s="32" t="inlineStr">
+        <is>
+          <t>Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D315" s="37" t="n">
+        <v>-63781.76</v>
+      </c>
+      <c r="E315" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B316" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C316" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D316" s="43">
+        <f>SUM(D310:D315)</f>
+        <v/>
+      </c>
+      <c r="E316" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $2,280,295.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B317" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C317" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D317" s="37" t="n">
+        <v>887022</v>
+      </c>
+      <c r="E317" s="32" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B318" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C318" s="32" t="inlineStr">
+        <is>
+          <t>Leasing - Ground Lease</t>
+        </is>
+      </c>
+      <c r="D318" s="37" t="n">
+        <v>87230</v>
+      </c>
+      <c r="E318" s="32" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B319" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C319" s="32" t="inlineStr">
+        <is>
+          <t>Parking Lot</t>
+        </is>
+      </c>
+      <c r="D319" s="37" t="n">
+        <v>56960.31</v>
+      </c>
+      <c r="E319" s="32" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B320" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C320" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees</t>
+        </is>
+      </c>
+      <c r="D320" s="37" t="n">
+        <v>39763.87</v>
+      </c>
+      <c r="E320" s="32" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B321" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C321" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal</t>
+        </is>
+      </c>
+      <c r="D321" s="37" t="n">
+        <v>24526.92</v>
+      </c>
+      <c r="E321" s="32" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B322" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C322" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D322" s="37" t="n">
+        <v>15576</v>
+      </c>
+      <c r="E322" s="32" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B323" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C323" s="32" t="inlineStr">
+        <is>
+          <t>Landscaping</t>
+        </is>
+      </c>
+      <c r="D323" s="37" t="n">
+        <v>13090.67</v>
+      </c>
+      <c r="E323" s="32" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B324" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C324" s="32" t="inlineStr">
+        <is>
+          <t>HVAC</t>
+        </is>
+      </c>
+      <c r="D324" s="37" t="n">
+        <v>9664</v>
+      </c>
+      <c r="E324" s="32" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B325" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C325" s="32" t="inlineStr">
+        <is>
+          <t>Insurance - Liability</t>
+        </is>
+      </c>
+      <c r="D325" s="37" t="n">
+        <v>7206</v>
+      </c>
+      <c r="E325" s="32" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B326" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C326" s="32" t="inlineStr">
+        <is>
+          <t>Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D326" s="37" t="n">
+        <v>6193.09</v>
+      </c>
+      <c r="E326" s="32" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B327" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C327" s="32" t="inlineStr">
+        <is>
+          <t>Roof</t>
+        </is>
+      </c>
+      <c r="D327" s="37" t="n">
+        <v>4195</v>
+      </c>
+      <c r="E327" s="32" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B328" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C328" s="32" t="inlineStr">
+        <is>
+          <t>Repairs</t>
+        </is>
+      </c>
+      <c r="D328" s="37" t="n">
+        <v>3267.42</v>
+      </c>
+      <c r="E328" s="32" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B329" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C329" s="32" t="inlineStr">
+        <is>
+          <t>Sweeping</t>
+        </is>
+      </c>
+      <c r="D329" s="37" t="n">
+        <v>2352.16</v>
+      </c>
+      <c r="E329" s="32" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B330" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C330" s="32" t="inlineStr">
+        <is>
+          <t>Lighting</t>
+        </is>
+      </c>
+      <c r="D330" s="37" t="n">
+        <v>1385.67</v>
+      </c>
+      <c r="E330" s="32" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B331" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C331" s="32" t="inlineStr">
+        <is>
+          <t>Bank Service Fees</t>
+        </is>
+      </c>
+      <c r="D331" s="37" t="n">
+        <v>1274.17</v>
+      </c>
+      <c r="E331" s="32" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B332" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C332" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Other</t>
+        </is>
+      </c>
+      <c r="D332" s="37" t="n">
+        <v>733.55</v>
+      </c>
+      <c r="E332" s="32" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B333" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C333" s="32" t="inlineStr">
+        <is>
+          <t>Window Washing</t>
+        </is>
+      </c>
+      <c r="D333" s="37" t="n">
+        <v>520</v>
+      </c>
+      <c r="E333" s="32" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B334" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C334" s="32" t="inlineStr">
+        <is>
+          <t>Backflow Testing &amp; Repair</t>
+        </is>
+      </c>
+      <c r="D334" s="37" t="n">
+        <v>491.29</v>
+      </c>
+      <c r="E334" s="32" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B335" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C335" s="32" t="inlineStr">
+        <is>
+          <t>Prof Service - Other Environ</t>
+        </is>
+      </c>
+      <c r="D335" s="37" t="n">
+        <v>400</v>
+      </c>
+      <c r="E335" s="32" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B336" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C336" s="32" t="inlineStr">
+        <is>
+          <t>Keys/Card Access</t>
+        </is>
+      </c>
+      <c r="D336" s="37" t="n">
+        <v>252.01</v>
+      </c>
+      <c r="E336" s="32" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B337" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C337" s="32" t="inlineStr">
+        <is>
+          <t>Other-DTR</t>
+        </is>
+      </c>
+      <c r="D337" s="37" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="E337" s="32" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B338" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C338" s="32" t="inlineStr">
+        <is>
+          <t>Signs</t>
+        </is>
+      </c>
+      <c r="D338" s="37" t="n">
+        <v>81.70999999999999</v>
+      </c>
+      <c r="E338" s="32" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B339" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C339" s="32" t="inlineStr">
+        <is>
+          <t>Painting</t>
+        </is>
+      </c>
+      <c r="D339" s="37" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="E339" s="32" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B340" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C340" s="32" t="inlineStr">
+        <is>
+          <t>Utilities - Other / Misc admin</t>
+        </is>
+      </c>
+      <c r="D340" s="37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E340" s="32" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 7 - CY2023</t>
+        </is>
+      </c>
+      <c r="B341" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C341" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D341" s="43">
+        <f>SUM(D317:D340)</f>
+        <v/>
+      </c>
+      <c r="E341" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,162,402.67</t>
         </is>
       </c>
     </row>
@@ -5225,7 +13309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5249,7 +13333,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,7 +13468,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
@@ -5396,6 +13478,67 @@
       <c r="C10" s="20" t="n"/>
       <c r="D10" s="20" t="n"/>
       <c r="E10" s="21" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="44" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter - buildings protested together by Sterling Property Tax Specialists (2026):</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #6 LLC</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>R0111559</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>3590 N Himalaya Road, Building 6, Aurora</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #7 LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>R0111560</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>20320 E. 36th Drive, Building 7, Aurora</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -22,13 +22,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="#,##0.###"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);-"/>
     <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="169" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
+    <numFmt numFmtId="171" formatCode="0.000%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -191,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -315,6 +317,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -680,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1164,23 +1172,173 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>R0103518.pdf</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Tax appeal - income approach + 2 rent rolls + CY2023 income statement + 3 lease comps + LOA/40-parcel schedule</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N. Broadway, Denver (First Industrial)</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2024</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Kim Lust) / CoStar</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>R0103519.pdf</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Valuation protest letter + LOA + 2023 &amp; 2024 P&amp;L + 5-date rent roll</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (P &amp; J Trujillo LLLP)</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services (Mike Walter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>R0103704.pdf</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey (handwritten)</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St, Denver (CB Resources LLC)</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>R0103779.pdf</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey (handwritten)</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave, Denver (Federal Partners LLC)</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Owner</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>R0104122.pdf</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>SB 11-119 submission - 06/24 rent roll only</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>550 W 53rd Pl (WSDB 550 LLC)</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates (Todd J. Stevens)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
@@ -1189,10 +1347,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1204,7 +1362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y17"/>
+  <dimension ref="A1:Y22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2752,6 +2910,507 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>R0103518</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>R0103518</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>R0103518</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>11459 5977-5995 N Broadway</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N. Broadway</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G18" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>80216 (per rent roll; cover sheet prints 80012)</t>
+        </is>
+      </c>
+      <c r="I18" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J18" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial Colorado</t>
+        </is>
+      </c>
+      <c r="K18" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial LP</t>
+        </is>
+      </c>
+      <c r="L18" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution</t>
+        </is>
+      </c>
+      <c r="M18" s="32" t="inlineStr">
+        <is>
+          <t>Multi (2 tenants)</t>
+        </is>
+      </c>
+      <c r="N18" s="45" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="O18" s="34" t="n">
+        <v>216058</v>
+      </c>
+      <c r="P18" s="34" t="n"/>
+      <c r="Q18" s="34" t="n">
+        <v>54431</v>
+      </c>
+      <c r="R18" s="35" t="n">
+        <v>1970</v>
+      </c>
+      <c r="S18" s="32" t="inlineStr">
+        <is>
+          <t>3.97 : 1</t>
+        </is>
+      </c>
+      <c r="T18" s="32" t="inlineStr">
+        <is>
+          <t>100% (rent rolls 1/1/2023 &amp; 1/1/2024)</t>
+        </is>
+      </c>
+      <c r="U18" s="36" t="n">
+        <v>6885558</v>
+      </c>
+      <c r="V18" s="32" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W18" s="36" t="n">
+        <v>5794600</v>
+      </c>
+      <c r="X18" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial Realty Trust, Inc.</t>
+        </is>
+      </c>
+      <c r="Y18" s="32" t="inlineStr">
+        <is>
+          <t>R0103518.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>R0103519</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>R0103519</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>R0103519</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>5945 Broadway</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G19" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H19" s="32" t="inlineStr">
+        <is>
+          <t>80216 (est.)</t>
+        </is>
+      </c>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J19" s="32" t="inlineStr">
+        <is>
+          <t>P &amp; J Trujillo LLLP</t>
+        </is>
+      </c>
+      <c r="K19" s="32" t="inlineStr">
+        <is>
+          <t>P &amp; J Trujillo LLLP</t>
+        </is>
+      </c>
+      <c r="L19" s="32" t="inlineStr">
+        <is>
+          <t>Commercial / Industrial (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>Multi (5 spaces)</t>
+        </is>
+      </c>
+      <c r="N19" s="45" t="n"/>
+      <c r="O19" s="34" t="n"/>
+      <c r="P19" s="34" t="n"/>
+      <c r="Q19" s="34" t="n">
+        <v>65227</v>
+      </c>
+      <c r="R19" s="35" t="n"/>
+      <c r="S19" s="32" t="n"/>
+      <c r="T19" s="32" t="inlineStr">
+        <is>
+          <t>100% - 'No vacant space' at all 5 rent-roll dates</t>
+        </is>
+      </c>
+      <c r="U19" s="36" t="n">
+        <v>7902868</v>
+      </c>
+      <c r="V19" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W19" s="36" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="X19" s="32" t="inlineStr">
+        <is>
+          <t>P &amp; J Trujillo LLLP (Peggy L. Trujillo, GP)</t>
+        </is>
+      </c>
+      <c r="Y19" s="32" t="inlineStr">
+        <is>
+          <t>R0103519.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>R0103704</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>R0103704</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>0182511300068</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G20" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H20" s="32" t="inlineStr">
+        <is>
+          <t>80216-1322</t>
+        </is>
+      </c>
+      <c r="I20" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J20" s="32" t="inlineStr">
+        <is>
+          <t>CB Resources LLC</t>
+        </is>
+      </c>
+      <c r="K20" s="32" t="inlineStr">
+        <is>
+          <t>CB Resources LLC</t>
+        </is>
+      </c>
+      <c r="L20" s="32" t="inlineStr">
+        <is>
+          <t>Office / Warehouse ('office spaces')</t>
+        </is>
+      </c>
+      <c r="M20" s="32" t="inlineStr">
+        <is>
+          <t>Owner-occupied</t>
+        </is>
+      </c>
+      <c r="N20" s="45" t="n"/>
+      <c r="O20" s="34" t="n"/>
+      <c r="P20" s="34" t="n"/>
+      <c r="Q20" s="34" t="n">
+        <v>18000</v>
+      </c>
+      <c r="R20" s="35" t="n"/>
+      <c r="S20" s="32" t="n"/>
+      <c r="T20" s="32" t="inlineStr">
+        <is>
+          <t>100% owner-occupied</t>
+        </is>
+      </c>
+      <c r="U20" s="36" t="n"/>
+      <c r="V20" s="32" t="inlineStr">
+        <is>
+          <t>2024 survey (2025 reappraisal)</t>
+        </is>
+      </c>
+      <c r="W20" s="36" t="n"/>
+      <c r="X20" s="32" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y20" s="32" t="inlineStr">
+        <is>
+          <t>R0103704.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>R0103779</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>R0103779</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>0182511400063</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G21" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H21" s="32" t="inlineStr">
+        <is>
+          <t>80216</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J21" s="32" t="inlineStr">
+        <is>
+          <t>Federal Partners LLC</t>
+        </is>
+      </c>
+      <c r="K21" s="32" t="inlineStr">
+        <is>
+          <t>Federal Partners LLC</t>
+        </is>
+      </c>
+      <c r="L21" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M21" s="32" t="inlineStr">
+        <is>
+          <t>Part owner-occupied (~50%) / multi-tenant</t>
+        </is>
+      </c>
+      <c r="N21" s="45" t="n"/>
+      <c r="O21" s="34" t="n"/>
+      <c r="P21" s="34" t="n"/>
+      <c r="Q21" s="34" t="n"/>
+      <c r="R21" s="35" t="n"/>
+      <c r="S21" s="32" t="n"/>
+      <c r="T21" s="32" t="inlineStr">
+        <is>
+          <t>Owner occupies ~50% (47,000 SF); balance multi-tenant; 100% of building rented or subject to lease</t>
+        </is>
+      </c>
+      <c r="U21" s="36" t="n"/>
+      <c r="V21" s="32" t="inlineStr">
+        <is>
+          <t>2024 survey (2025 reappraisal)</t>
+        </is>
+      </c>
+      <c r="W21" s="36" t="n"/>
+      <c r="X21" s="32" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y21" s="32" t="inlineStr">
+        <is>
+          <t>R0103779.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>R0104122</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>R0104122</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>0182515202002</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>550 W 53rd Pl</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>550 W 53rd Pl</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="G22" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H22" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I22" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J22" s="32" t="inlineStr">
+        <is>
+          <t>WSDB 550 LLC</t>
+        </is>
+      </c>
+      <c r="K22" s="32" t="inlineStr">
+        <is>
+          <t>WSDB 550 LLC</t>
+        </is>
+      </c>
+      <c r="L22" s="32" t="inlineStr">
+        <is>
+          <t>Industrial / Retail (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M22" s="32" t="inlineStr">
+        <is>
+          <t>Multi (2 tenants)</t>
+        </is>
+      </c>
+      <c r="N22" s="45" t="n"/>
+      <c r="O22" s="34" t="n"/>
+      <c r="P22" s="34" t="n"/>
+      <c r="Q22" s="34" t="n">
+        <v>127000</v>
+      </c>
+      <c r="R22" s="35" t="n"/>
+      <c r="S22" s="32" t="n"/>
+      <c r="T22" s="32" t="inlineStr">
+        <is>
+          <t>100% (2 tenants on 06/24 rent roll)</t>
+        </is>
+      </c>
+      <c r="U22" s="36" t="n"/>
+      <c r="V22" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W22" s="36" t="n"/>
+      <c r="X22" s="32" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y22" s="32" t="inlineStr">
+        <is>
+          <t>R0104122.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Y2"/>
@@ -2767,7 +3426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4719,6 +5378,884 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B42" s="32" t="inlineStr">
+        <is>
+          <t>5977-81</t>
+        </is>
+      </c>
+      <c r="C42" s="32" t="inlineStr">
+        <is>
+          <t>EDGEBANDING SERVICES INC</t>
+        </is>
+      </c>
+      <c r="D42" s="32" t="inlineStr">
+        <is>
+          <t>Actual - industrial net</t>
+        </is>
+      </c>
+      <c r="E42" s="37" t="n">
+        <v>22904.43</v>
+      </c>
+      <c r="F42" s="37" t="n">
+        <v>274853.16</v>
+      </c>
+      <c r="G42" s="37" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="H42" s="32" t="inlineStr">
+        <is>
+          <t>11/1/2019</t>
+        </is>
+      </c>
+      <c r="I42" s="32" t="inlineStr">
+        <is>
+          <t>10/31/2024</t>
+        </is>
+      </c>
+      <c r="J42" s="32" t="inlineStr">
+        <is>
+          <t>Lease 8580-4 ver; orig. exec. 9/14/2005</t>
+        </is>
+      </c>
+      <c r="K42" s="37" t="n"/>
+      <c r="L42" s="37" t="n">
+        <v>22053.08</v>
+      </c>
+      <c r="M42" s="32" t="inlineStr">
+        <is>
+          <t>40,140 SF. Rent roll as of 1/1/2023. Monthly net rent = base rent. O/E estimate $12,917.99/mo ($3.86 PSF). Move-in 11/1/2019.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B43" s="32" t="inlineStr">
+        <is>
+          <t>005995</t>
+        </is>
+      </c>
+      <c r="C43" s="32" t="inlineStr">
+        <is>
+          <t>SPEC 7 INSULATION CO.</t>
+        </is>
+      </c>
+      <c r="D43" s="32" t="inlineStr">
+        <is>
+          <t>Actual - industrial net</t>
+        </is>
+      </c>
+      <c r="E43" s="37" t="n">
+        <v>7110.29</v>
+      </c>
+      <c r="F43" s="37" t="n">
+        <v>85323.48</v>
+      </c>
+      <c r="G43" s="37" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="H43" s="32" t="inlineStr">
+        <is>
+          <t>11/1/2021</t>
+        </is>
+      </c>
+      <c r="I43" s="32" t="inlineStr">
+        <is>
+          <t>10/31/2024</t>
+        </is>
+      </c>
+      <c r="J43" s="32" t="inlineStr">
+        <is>
+          <t>Lease 15546-2 ver; orig. exec. 6/16/2016</t>
+        </is>
+      </c>
+      <c r="K43" s="37" t="n"/>
+      <c r="L43" s="37" t="n">
+        <v>8426.58</v>
+      </c>
+      <c r="M43" s="32" t="inlineStr">
+        <is>
+          <t>10,140 SF. Rent roll as of 1/1/2023. O/E estimate $3,320.93/mo ($3.93 PSF). Move-in 10/15/2016.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B44" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL 1/1/2023</t>
+        </is>
+      </c>
+      <c r="C44" s="32" t="inlineStr">
+        <is>
+          <t>2 tenants - 100% occupied</t>
+        </is>
+      </c>
+      <c r="D44" s="32" t="inlineStr">
+        <is>
+          <t>Actual - industrial net</t>
+        </is>
+      </c>
+      <c r="E44" s="37" t="n">
+        <v>30014.72</v>
+      </c>
+      <c r="F44" s="37" t="n">
+        <v>360176.64</v>
+      </c>
+      <c r="G44" s="37" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="H44" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J44" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="37" t="n"/>
+      <c r="L44" s="37" t="n">
+        <v>30479.66</v>
+      </c>
+      <c r="M44" s="32" t="inlineStr">
+        <is>
+          <t>50,280 SF occupied, 0 SF vacant. Printed rent-roll totals as of 1/1/2023. NOTE: project SF on the rent roll is 50,280 while the appeal's stated NLA is 54,431 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>5977-81</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>EDGEBANDING SERVICES INC</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr">
+        <is>
+          <t>Actual - industrial net</t>
+        </is>
+      </c>
+      <c r="E45" s="37" t="n">
+        <v>23591.45</v>
+      </c>
+      <c r="F45" s="37" t="n">
+        <v>283097.4</v>
+      </c>
+      <c r="G45" s="37" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="H45" s="32" t="inlineStr">
+        <is>
+          <t>11/1/2019</t>
+        </is>
+      </c>
+      <c r="I45" s="32" t="inlineStr">
+        <is>
+          <t>10/31/2024</t>
+        </is>
+      </c>
+      <c r="J45" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="37" t="n"/>
+      <c r="L45" s="37" t="n">
+        <v>22053.08</v>
+      </c>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>40,140 SF. Rent roll as of 1/1/2024 (escalated). O/E estimate $15,263.38/mo ($4.56 PSF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>005995</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>SPEC 7 INSULATION CO.</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>Actual - industrial net</t>
+        </is>
+      </c>
+      <c r="E46" s="37" t="n">
+        <v>7359.16</v>
+      </c>
+      <c r="F46" s="37" t="n">
+        <v>88309.92</v>
+      </c>
+      <c r="G46" s="37" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H46" s="32" t="inlineStr">
+        <is>
+          <t>11/1/2021</t>
+        </is>
+      </c>
+      <c r="I46" s="32" t="inlineStr">
+        <is>
+          <t>10/31/2024</t>
+        </is>
+      </c>
+      <c r="J46" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="37" t="n"/>
+      <c r="L46" s="37" t="n">
+        <v>8426.58</v>
+      </c>
+      <c r="M46" s="32" t="inlineStr">
+        <is>
+          <t>10,140 SF. Rent roll as of 1/1/2024. O/E estimate $3,999.94/mo ($4.73 PSF). Flagged '*' - a future lease version had been entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL 1/1/2024</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>2 tenants - 100% occupied</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
+        <is>
+          <t>Actual - industrial net</t>
+        </is>
+      </c>
+      <c r="E47" s="37" t="n">
+        <v>30950.61</v>
+      </c>
+      <c r="F47" s="37" t="n">
+        <v>371407.32</v>
+      </c>
+      <c r="G47" s="37" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="H47" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J47" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="37" t="n"/>
+      <c r="L47" s="37" t="n">
+        <v>30479.66</v>
+      </c>
+      <c r="M47" s="32" t="inlineStr">
+        <is>
+          <t>50,280 SF occupied, 0 SF vacant. Printed rent-roll totals as of 1/1/2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>Space 1 (19,712 SF)</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>(tenant not named on rent roll)</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E48" s="37" t="n">
+        <v>11909.34</v>
+      </c>
+      <c r="F48" s="37" t="n">
+        <v>142912.08</v>
+      </c>
+      <c r="G48" s="37" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="H48" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J48" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="37" t="n">
+        <v>4632.32</v>
+      </c>
+      <c r="L48" s="37" t="n"/>
+      <c r="M48" s="32" t="inlineStr">
+        <is>
+          <t>Rent roll gives SF, monthly base rent and CAM only - no tenant names, lease dates or terms. Figures shown are the latest snapshot, 1/1/2025. Prior snapshots: 1/1/23 $8,845.31; 6/30/23 $9,856.00; 1/1/24 and 6/30/24 $11,088.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B49" s="32" t="inlineStr">
+        <is>
+          <t>Space 2 (12,000 SF)</t>
+        </is>
+      </c>
+      <c r="C49" s="32" t="inlineStr">
+        <is>
+          <t>(tenant not named on rent roll)</t>
+        </is>
+      </c>
+      <c r="D49" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E49" s="37" t="n">
+        <v>6268.78</v>
+      </c>
+      <c r="F49" s="37" t="n">
+        <v>75225.36</v>
+      </c>
+      <c r="G49" s="37" t="n">
+        <v>6.27</v>
+      </c>
+      <c r="H49" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="37" t="n">
+        <v>2820</v>
+      </c>
+      <c r="L49" s="37" t="n"/>
+      <c r="M49" s="32" t="inlineStr">
+        <is>
+          <t>1/1/2025 snapshot. Prior: 1/1/23 $6,008.92; 6/30/23 and 1/1/24 $6,186.19; 6/30/24 $6,368.78 (the 1/1/25 figure is $100 lower than 6/30/24, as printed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>Space 3 (10,000 SF)</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>(tenant not named on rent roll)</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E50" s="37" t="n">
+        <v>7918.33</v>
+      </c>
+      <c r="F50" s="37" t="n">
+        <v>95019.96000000001</v>
+      </c>
+      <c r="G50" s="37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H50" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J50" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="37" t="n">
+        <v>2289.61</v>
+      </c>
+      <c r="L50" s="37" t="n"/>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>1/1/2025 snapshot. Prior: 1/1/23 $7,463.33; 6/30/23 through 6/30/24 $7,687.50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>Space 4 (11,015 SF)</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>(tenant not named on rent roll)</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E51" s="37" t="n">
+        <v>8772.040000000001</v>
+      </c>
+      <c r="F51" s="37" t="n">
+        <v>105264.48</v>
+      </c>
+      <c r="G51" s="37" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="H51" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J51" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="37" t="n">
+        <v>2588.53</v>
+      </c>
+      <c r="L51" s="37" t="n"/>
+      <c r="M51" s="32" t="inlineStr">
+        <is>
+          <t>1/1/2025 snapshot. Prior: 1/1/23 through 6/30/23 $8,220.86; 1/1/24 and 6/30/24 $8,467.78.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>Space 5 (12,500 SF)</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>(tenant not named on rent roll)</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E52" s="37" t="n">
+        <v>9897.92</v>
+      </c>
+      <c r="F52" s="37" t="n">
+        <v>118775.04</v>
+      </c>
+      <c r="G52" s="37" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="H52" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J52" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="37" t="n">
+        <v>2937.5</v>
+      </c>
+      <c r="L52" s="37" t="n"/>
+      <c r="M52" s="32" t="inlineStr">
+        <is>
+          <t>1/1/2025 snapshot. Prior: 1/1/23 through 6/30/23 $9,329.17; 1/1/24 and 6/30/24 $9,609.38.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B53" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL 1/1/2025</t>
+        </is>
+      </c>
+      <c r="C53" s="32" t="inlineStr">
+        <is>
+          <t>5 spaces - no vacant space</t>
+        </is>
+      </c>
+      <c r="D53" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E53" s="37" t="n">
+        <v>44766.41</v>
+      </c>
+      <c r="F53" s="37" t="n">
+        <v>537196.92</v>
+      </c>
+      <c r="G53" s="37" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="H53" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J53" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="37" t="n">
+        <v>15267.96</v>
+      </c>
+      <c r="L53" s="37" t="n"/>
+      <c r="M53" s="32" t="inlineStr">
+        <is>
+          <t>65,227 SF across 5 spaces. Monthly base-rent totals by date: 1/1/23 $39,867.59; 6/30/23 $41,279.72; 1/1/24 $43,038.85; 6/30/24 $43,221.44; 1/1/25 $44,766.41. CAM total $15,267.96/mo at every date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave (R0103779)</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>Leased portion</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>(multi-tenant; tenants not named)</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Gross</t>
+        </is>
+      </c>
+      <c r="E54" s="37" t="n">
+        <v>55906</v>
+      </c>
+      <c r="F54" s="37" t="n">
+        <v>670872</v>
+      </c>
+      <c r="G54" s="37" t="n">
+        <v>14</v>
+      </c>
+      <c r="H54" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J54" s="32" t="inlineStr">
+        <is>
+          <t>Years; 9 years remaining as of 2024</t>
+        </is>
+      </c>
+      <c r="K54" s="37" t="n"/>
+      <c r="L54" s="37" t="n"/>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>County I&amp;E survey: scheduled rent $14.00/SF for 12 months beginning 1/1/2023; actual rent received $670,872 (= $55,906 x 12). Owner reports 100% of the building rented or subject to lease, while also reporting ~50% (47,000 SF) owner-occupancy - reproduced as printed. New lease(s) signed between 7/1/22 and 6/30/24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>550 W 53rd Pl (R0104122)</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>Monarch Metal Mfg.</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E55" s="37" t="n">
+        <v>32000</v>
+      </c>
+      <c r="F55" s="37" t="n">
+        <v>384000</v>
+      </c>
+      <c r="G55" s="37" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="H55" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="37" t="n">
+        <v>10000</v>
+      </c>
+      <c r="L55" s="37" t="n"/>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t>87,000 SF. 06/24 rent roll. Lease date left blank on the rent roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>550 W 53rd Pl (R0104122)</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>Arc Thrift Store</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E56" s="37" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F56" s="37" t="n">
+        <v>240000</v>
+      </c>
+      <c r="G56" s="37" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="32" t="inlineStr">
+        <is>
+          <t>9/1/2020</t>
+        </is>
+      </c>
+      <c r="I56" s="32" t="inlineStr">
+        <is>
+          <t>9/30/2025</t>
+        </is>
+      </c>
+      <c r="J56" s="32" t="inlineStr">
+        <is>
+          <t>September 2020 - September 2025</t>
+        </is>
+      </c>
+      <c r="K56" s="37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L56" s="37" t="n"/>
+      <c r="M56" s="32" t="inlineStr">
+        <is>
+          <t>40,000 SF. 06/24 rent roll. Lease dates shown only as month/year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>550 W 53rd Pl (R0104122)</t>
+        </is>
+      </c>
+      <c r="B57" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C57" s="32" t="inlineStr">
+        <is>
+          <t>2 tenants</t>
+        </is>
+      </c>
+      <c r="D57" s="32" t="inlineStr">
+        <is>
+          <t>Actual - base + CAM</t>
+        </is>
+      </c>
+      <c r="E57" s="37" t="n">
+        <v>52000</v>
+      </c>
+      <c r="F57" s="37" t="n">
+        <v>624000</v>
+      </c>
+      <c r="G57" s="37" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="H57" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="37" t="n">
+        <v>15000</v>
+      </c>
+      <c r="L57" s="37" t="n"/>
+      <c r="M57" s="32" t="inlineStr">
+        <is>
+          <t>127,000 SF combined. Rent roll reports no vacancy, no lease PSF and no expiry for Monarch.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
@@ -4737,7 +6274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -5108,26 +6645,71 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C16" s="36" t="n">
+        <v>6885558</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>127</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>5794600</v>
+      </c>
+      <c r="F16" s="37" t="n">
+        <v>106.46</v>
+      </c>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>R0103518</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
-        <is>
-          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="21" t="n"/>
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519)</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C17" s="36" t="n">
+        <v>7902868</v>
+      </c>
+      <c r="D17" s="37" t="n">
+        <v>121.16</v>
+      </c>
+      <c r="E17" s="36" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="F17" s="37" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="G17" s="36" t="n"/>
+      <c r="H17" s="32" t="inlineStr">
+        <is>
+          <t>R0103519</t>
+        </is>
+      </c>
     </row>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
-        <is>
-          <t>B. Income-Approach Proformas</t>
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
         </is>
       </c>
       <c r="B19" s="20" t="n"/>
@@ -5138,375 +6720,438 @@
       <c r="G19" s="20" t="n"/>
       <c r="H19" s="21" t="n"/>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
+        <is>
+          <t>B. Income-Approach Proformas</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="20" t="n"/>
+      <c r="G21" s="20" t="n"/>
+      <c r="H21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C21" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G21" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <v>4832500</v>
-      </c>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Dr</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n">
-        <v>209100</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>-10455</v>
-      </c>
-      <c r="D22" s="9" t="n">
-        <v>198645</v>
-      </c>
-      <c r="E22" s="9" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <v>182753</v>
-      </c>
-      <c r="G22" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <v>3050000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>12260 Pennsylvania St</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>237290</v>
+        <v>359394</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>-16610</v>
+        <v>-17970</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>220680</v>
+        <v>341424</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>-22068</v>
+        <v>-27314</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>198612</v>
+        <v>314110</v>
       </c>
       <c r="G23" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="H23" s="14" t="n">
-        <v>2837000</v>
+        <v>4832500</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>6770 E. 56th Ave</t>
+          <t>17608 E. 24th Dr</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>115824</v>
+        <v>209100</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>-5791</v>
+        <v>-10455</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>110033</v>
+        <v>198645</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>-5502</v>
+        <v>-15892</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>104531</v>
+        <v>182753</v>
       </c>
       <c r="G24" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H24" s="14" t="n">
-        <v>1493302</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-16610</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>220680</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>-22068</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <v>198612</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <v>2837000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>1493302</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B27" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C27" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D27" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E27" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F27" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G27" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H27" s="14" t="n">
         <v>2460577</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="32" t="inlineStr">
-        <is>
-          <t>18300 E 28th Ave (R0110351)</t>
-        </is>
-      </c>
-      <c r="B26" s="36" t="n">
-        <v>599228</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>-59923</v>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>539305</v>
-      </c>
-      <c r="E26" s="36" t="n">
-        <v>-43144</v>
-      </c>
-      <c r="F26" s="38" t="n">
-        <v>496161</v>
-      </c>
-      <c r="G26" s="39" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="H26" s="38" t="n">
-        <v>7939000</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="32" t="inlineStr">
-        <is>
-          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
-        </is>
-      </c>
-      <c r="B27" s="36" t="n">
-        <v>781250</v>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>-78125</v>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>703125</v>
-      </c>
-      <c r="E27" s="36" t="n">
-        <v>-35156</v>
-      </c>
-      <c r="F27" s="38" t="n">
-        <v>667969</v>
-      </c>
-      <c r="G27" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H27" s="38" t="n">
-        <v>8754500</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="32" t="inlineStr">
         <is>
-          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
+          <t>18300 E 28th Ave (R0110351)</t>
         </is>
       </c>
       <c r="B28" s="36" t="n">
-        <v>1250000</v>
+        <v>599228</v>
       </c>
       <c r="C28" s="36" t="n">
-        <v>-125000</v>
+        <v>-59923</v>
       </c>
       <c r="D28" s="36" t="n">
-        <v>1125000</v>
+        <v>539305</v>
       </c>
       <c r="E28" s="36" t="n">
-        <v>-56250</v>
+        <v>-43144</v>
       </c>
       <c r="F28" s="38" t="n">
-        <v>1068750</v>
+        <v>496161</v>
       </c>
       <c r="G28" s="39" t="n">
-        <v>0.07630000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="H28" s="38" t="n">
-        <v>14007200</v>
+        <v>7939000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="32" t="inlineStr">
         <is>
-          <t>Anchor Business Park - market (R0121833)</t>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
         </is>
       </c>
       <c r="B29" s="36" t="n">
-        <v>346484</v>
+        <v>781250</v>
       </c>
       <c r="C29" s="36" t="n">
-        <v>-17324</v>
+        <v>-78125</v>
       </c>
       <c r="D29" s="36" t="n">
-        <v>329160</v>
+        <v>703125</v>
       </c>
       <c r="E29" s="36" t="n">
-        <v>-49374</v>
+        <v>-35156</v>
       </c>
       <c r="F29" s="38" t="n">
-        <v>279786</v>
+        <v>667969</v>
       </c>
       <c r="G29" s="39" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H29" s="38" t="n">
-        <v>3919000</v>
+        <v>8754500</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="32" t="inlineStr">
         <is>
-          <t>Anchor Business Park - actual 2024 (R0121833)</t>
+          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
         </is>
       </c>
       <c r="B30" s="36" t="n">
-        <v>457717</v>
-      </c>
-      <c r="C30" s="36" t="n"/>
+        <v>1250000</v>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>-125000</v>
+      </c>
       <c r="D30" s="36" t="n">
-        <v>457717</v>
+        <v>1125000</v>
       </c>
       <c r="E30" s="36" t="n">
-        <v>-110337</v>
+        <v>-56250</v>
       </c>
       <c r="F30" s="38" t="n">
-        <v>347380</v>
+        <v>1068750</v>
       </c>
       <c r="G30" s="39" t="n">
-        <v>0.099</v>
+        <v>0.07630000000000001</v>
       </c>
       <c r="H30" s="38" t="n">
-        <v>3510000</v>
+        <v>14007200</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="32" t="inlineStr">
         <is>
+          <t>Anchor Business Park - market (R0121833)</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>346484</v>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>-17324</v>
+      </c>
+      <c r="D31" s="36" t="n">
+        <v>329160</v>
+      </c>
+      <c r="E31" s="36" t="n">
+        <v>-49374</v>
+      </c>
+      <c r="F31" s="38" t="n">
+        <v>279786</v>
+      </c>
+      <c r="G31" s="39" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H31" s="38" t="n">
+        <v>3919000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - actual 2024 (R0121833)</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="C32" s="36" t="n"/>
+      <c r="D32" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>-110337</v>
+      </c>
+      <c r="F32" s="38" t="n">
+        <v>347380</v>
+      </c>
+      <c r="G32" s="39" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H32" s="38" t="n">
+        <v>3510000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
           <t>Anchor Business Park - actual 2023 (R0121833)</t>
         </is>
       </c>
-      <c r="B31" s="36" t="n">
+      <c r="B33" s="36" t="n">
         <v>401204</v>
       </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n">
+      <c r="C33" s="36" t="n"/>
+      <c r="D33" s="36" t="n">
         <v>401204</v>
       </c>
-      <c r="E31" s="36" t="n">
+      <c r="E33" s="36" t="n">
         <v>-119063</v>
       </c>
-      <c r="F31" s="38" t="n">
+      <c r="F33" s="38" t="n">
         <v>282140</v>
       </c>
-      <c r="G31" s="39" t="n">
+      <c r="G33" s="39" t="n">
         <v>0.099</v>
       </c>
-      <c r="H31" s="38" t="n">
+      <c r="H33" s="38" t="n">
         <v>2851000</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="n">
+        <v>489879</v>
+      </c>
+      <c r="C34" s="36" t="n">
+        <v>-39190</v>
+      </c>
+      <c r="D34" s="36" t="n">
+        <v>450689</v>
+      </c>
+      <c r="E34" s="36" t="n">
+        <v>-45069</v>
+      </c>
+      <c r="F34" s="38" t="n">
+        <v>405620</v>
+      </c>
+      <c r="G34" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H34" s="38" t="n">
+        <v>5794600</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519) - agent capitalization</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="38" t="n">
+        <v>550000</v>
+      </c>
+      <c r="G35" s="46" t="n">
+        <v>0.09331</v>
+      </c>
+      <c r="H35" s="38" t="n">
+        <v>5894300</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
         </is>
       </c>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="20" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="21" t="n"/>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="20" t="n"/>
+      <c r="D37" s="20" t="n"/>
+      <c r="E37" s="20" t="n"/>
+      <c r="F37" s="20" t="n"/>
+      <c r="G37" s="20" t="n"/>
+      <c r="H37" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5518,7 +7163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5875,23 +7520,132 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B19" s="37" t="n">
+        <v>550031</v>
+      </c>
+      <c r="C19" s="37" t="n">
+        <v>250528</v>
+      </c>
+      <c r="D19" s="41">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. TRUE NOI - depreciation ($71,686) and lease-cost amortization ($9,843) sit below the NOI line; net income after those = $217,973. R0103518</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="40" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B20" s="37" t="n">
+        <v>704810.59</v>
+      </c>
+      <c r="C20" s="37" t="n">
+        <v>524505.21</v>
+      </c>
+      <c r="D20" s="41">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>Cash basis. NOT a true NOI: expenses include loan interest $140,115.06, income tax $71,185.00 and property tax $169,029.80. Agent's stated 2024 NOI excluding those = $560,634. R0103519</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B21" s="37" t="n">
+        <v>655107.84</v>
+      </c>
+      <c r="C21" s="37" t="n">
+        <v>453235.5</v>
+      </c>
+      <c r="D21" s="41">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Cash basis. NOT a true NOI: includes loan interest $142,547.72, income tax $50,000.00, property tax $148,047.68. Agent's stated 2023 NOI = $542,466. R0103519</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="inlineStr">
+        <is>
+          <t>5720 Washington St - 2023/2024 survey</t>
+        </is>
+      </c>
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="37" t="n">
+        <v>71980</v>
+      </c>
+      <c r="D22" s="41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>100% owner-occupied, so no rental income is reported. Operating expenses only, and they were written into the TENANT column of the survey grid despite the owner-occupancy. R0103704</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B23" s="37" t="n">
+        <v>670872</v>
+      </c>
+      <c r="C23" s="37" t="n">
+        <v>244295.66</v>
+      </c>
+      <c r="D23" s="41">
+        <f>B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>County I&amp;E survey, Gross lease. Owner-paid expenses only; janitorial and snow/trash were marked 'T' rather than given a dollar amount, and no property tax or management line was reported. R0103779</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="21" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A25:E25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5903,7 +7657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E341"/>
+  <dimension ref="A1:E420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -13291,6 +15045,1749 @@
       <c r="E341" s="32" t="inlineStr">
         <is>
           <t>Printed total: $1,162,402.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B342" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C342" s="32" t="inlineStr">
+        <is>
+          <t>401000 Base Rent Income</t>
+        </is>
+      </c>
+      <c r="D342" s="37" t="n">
+        <v>362048</v>
+      </c>
+      <c r="E342" s="32" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B343" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C343" s="32" t="inlineStr">
+        <is>
+          <t>408010 S/L Rent Revenue Adjustment</t>
+        </is>
+      </c>
+      <c r="D343" s="37" t="n">
+        <v>-31913</v>
+      </c>
+      <c r="E343" s="32" t="inlineStr">
+        <is>
+          <t>Straight-line adjustment</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B344" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C344" s="32" t="inlineStr">
+        <is>
+          <t>410100 Monthly Estimated CAM</t>
+        </is>
+      </c>
+      <c r="D344" s="37" t="n">
+        <v>194867</v>
+      </c>
+      <c r="E344" s="32" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B345" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C345" s="32" t="inlineStr">
+        <is>
+          <t>412060 Tenant Direct Billed CAM</t>
+        </is>
+      </c>
+      <c r="D345" s="37" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E345" s="32" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B346" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C346" s="32" t="inlineStr">
+        <is>
+          <t>413030 Current Year CAM Accrual</t>
+        </is>
+      </c>
+      <c r="D346" s="37" t="n">
+        <v>22328</v>
+      </c>
+      <c r="E346" s="32" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B347" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C347" s="32" t="inlineStr">
+        <is>
+          <t>415000 Prior Year CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D347" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E347" s="32" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B348" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C348" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D348" s="43">
+        <f>SUM(D342:D347)</f>
+        <v/>
+      </c>
+      <c r="E348" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $550,031. Sum of the printed line items is $550,030 - the source's own Total Rent Revenue subtotal ($330,136) is $1 above its components ($330,135). Both reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B349" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C349" s="32" t="inlineStr">
+        <is>
+          <t>500030 C/A Water/Sewer</t>
+        </is>
+      </c>
+      <c r="D349" s="37" t="n">
+        <v>10493</v>
+      </c>
+      <c r="E349" s="32" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B350" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C350" s="32" t="inlineStr">
+        <is>
+          <t>500035 C/A Other Utilities</t>
+        </is>
+      </c>
+      <c r="D350" s="37" t="n">
+        <v>846</v>
+      </c>
+      <c r="E350" s="32" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B351" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C351" s="32" t="inlineStr">
+        <is>
+          <t>500045 C/A Exterior Light</t>
+        </is>
+      </c>
+      <c r="D351" s="37" t="n">
+        <v>2860</v>
+      </c>
+      <c r="E351" s="32" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B352" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C352" s="32" t="inlineStr">
+        <is>
+          <t>500010 C/A Electric</t>
+        </is>
+      </c>
+      <c r="D352" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E352" s="32" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B353" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C353" s="32" t="inlineStr">
+        <is>
+          <t>501035 C/A Fire Prevention</t>
+        </is>
+      </c>
+      <c r="D353" s="37" t="n">
+        <v>4891</v>
+      </c>
+      <c r="E353" s="32" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B354" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C354" s="32" t="inlineStr">
+        <is>
+          <t>501040 C/A MC Landscaping</t>
+        </is>
+      </c>
+      <c r="D354" s="37" t="n">
+        <v>1737</v>
+      </c>
+      <c r="E354" s="32" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B355" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C355" s="32" t="inlineStr">
+        <is>
+          <t>501050 C/A MC HVAC</t>
+        </is>
+      </c>
+      <c r="D355" s="37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E355" s="32" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B356" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C356" s="32" t="inlineStr">
+        <is>
+          <t>501060 C/A Other Exterior</t>
+        </is>
+      </c>
+      <c r="D356" s="37" t="n">
+        <v>5324</v>
+      </c>
+      <c r="E356" s="32" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B357" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C357" s="32" t="inlineStr">
+        <is>
+          <t>501075 C/A Parking Lot</t>
+        </is>
+      </c>
+      <c r="D357" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E357" s="32" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B358" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C358" s="32" t="inlineStr">
+        <is>
+          <t>501090 C/A Roofing</t>
+        </is>
+      </c>
+      <c r="D358" s="37" t="n">
+        <v>1334</v>
+      </c>
+      <c r="E358" s="32" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B359" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C359" s="32" t="inlineStr">
+        <is>
+          <t>501100 C/A Snow Removal</t>
+        </is>
+      </c>
+      <c r="D359" s="37" t="n">
+        <v>13465</v>
+      </c>
+      <c r="E359" s="32" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B360" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C360" s="32" t="inlineStr">
+        <is>
+          <t>501135 C/A Other Repair/Maintenance</t>
+        </is>
+      </c>
+      <c r="D360" s="37" t="n">
+        <v>3268</v>
+      </c>
+      <c r="E360" s="32" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B361" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C361" s="32" t="inlineStr">
+        <is>
+          <t>501160 C/A Sweeping</t>
+        </is>
+      </c>
+      <c r="D361" s="37" t="n">
+        <v>873</v>
+      </c>
+      <c r="E361" s="32" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B362" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C362" s="32" t="inlineStr">
+        <is>
+          <t>502025 C/A Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D362" s="37" t="n">
+        <v>139832</v>
+      </c>
+      <c r="E362" s="32" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B363" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C363" s="32" t="inlineStr">
+        <is>
+          <t>502020 C/A Real Estate Tax Appeals</t>
+        </is>
+      </c>
+      <c r="D363" s="37" t="n">
+        <v>615</v>
+      </c>
+      <c r="E363" s="32" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B364" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C364" s="32" t="inlineStr">
+        <is>
+          <t>580025 Real Estate Tax Appeal Contra</t>
+        </is>
+      </c>
+      <c r="D364" s="37" t="n">
+        <v>-615</v>
+      </c>
+      <c r="E364" s="32" t="inlineStr">
+        <is>
+          <t>Offsets the appeal fee</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B365" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C365" s="32" t="inlineStr">
+        <is>
+          <t>503010 C/A Insurance</t>
+        </is>
+      </c>
+      <c r="D365" s="37" t="n">
+        <v>7696</v>
+      </c>
+      <c r="E365" s="32" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B366" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C366" s="32" t="inlineStr">
+        <is>
+          <t>504015 C/A Management Fees-Internal</t>
+        </is>
+      </c>
+      <c r="D366" s="37" t="n">
+        <v>22462</v>
+      </c>
+      <c r="E366" s="32" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B367" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C367" s="32" t="inlineStr">
+        <is>
+          <t>521060 D/B Other Exterior</t>
+        </is>
+      </c>
+      <c r="D367" s="37" t="n">
+        <v>2700</v>
+      </c>
+      <c r="E367" s="32" t="inlineStr">
+        <is>
+          <t>Direct-billed</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B368" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C368" s="32" t="inlineStr">
+        <is>
+          <t>530010 L/L Utilities</t>
+        </is>
+      </c>
+      <c r="D368" s="37" t="n">
+        <v>100</v>
+      </c>
+      <c r="E368" s="32" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B369" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C369" s="32" t="inlineStr">
+        <is>
+          <t>530020 L/L Maintenance &amp; Repairs</t>
+        </is>
+      </c>
+      <c r="D369" s="37" t="n">
+        <v>197</v>
+      </c>
+      <c r="E369" s="32" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B370" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C370" s="32" t="inlineStr">
+        <is>
+          <t>530285 L/L Real Estate Tax True Up</t>
+        </is>
+      </c>
+      <c r="D370" s="37" t="n">
+        <v>9385</v>
+      </c>
+      <c r="E370" s="32" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B371" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C371" s="32" t="inlineStr">
+        <is>
+          <t>530290 L/L RE Tax Accrual</t>
+        </is>
+      </c>
+      <c r="D371" s="37" t="n">
+        <v>21566</v>
+      </c>
+      <c r="E371" s="32" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B372" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C372" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D372" s="43">
+        <f>SUM(D349:D371)</f>
+        <v/>
+      </c>
+      <c r="E372" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $250,528. Sum of the printed line items is $250,529 - the source's own Total Common Area Repair/Maint. subtotal ($32,391) is $1 below its components ($32,392). Both reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B373" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C373" s="32" t="inlineStr">
+        <is>
+          <t>4000 Rent Income</t>
+        </is>
+      </c>
+      <c r="D373" s="37" t="n">
+        <v>521595.07</v>
+      </c>
+      <c r="E373" s="32" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B374" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C374" s="32" t="inlineStr">
+        <is>
+          <t>4045 Cam Charge Income</t>
+        </is>
+      </c>
+      <c r="D374" s="37" t="n">
+        <v>183215.52</v>
+      </c>
+      <c r="E374" s="32" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B375" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C375" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D375" s="43">
+        <f>SUM(D373:D374)</f>
+        <v/>
+      </c>
+      <c r="E375" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $704,810.59</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B376" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C376" s="32" t="inlineStr">
+        <is>
+          <t>6500/6520 Property Tax</t>
+        </is>
+      </c>
+      <c r="D376" s="37" t="n">
+        <v>169029.8</v>
+      </c>
+      <c r="E376" s="32" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B377" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C377" s="32" t="inlineStr">
+        <is>
+          <t>6220 Loan Interest</t>
+        </is>
+      </c>
+      <c r="D377" s="37" t="n">
+        <v>140115.06</v>
+      </c>
+      <c r="E377" s="32" t="inlineStr">
+        <is>
+          <t>Debt service - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B378" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C378" s="32" t="inlineStr">
+        <is>
+          <t>6510 Income Tax</t>
+        </is>
+      </c>
+      <c r="D378" s="37" t="n">
+        <v>71185</v>
+      </c>
+      <c r="E378" s="32" t="inlineStr">
+        <is>
+          <t>Entity tax - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B379" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C379" s="32" t="inlineStr">
+        <is>
+          <t>6300 Repairs - Building Repairs</t>
+        </is>
+      </c>
+      <c r="D379" s="37" t="n">
+        <v>32738</v>
+      </c>
+      <c r="E379" s="32" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B380" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C380" s="32" t="inlineStr">
+        <is>
+          <t>6182 Insurance - Bus Owners Pkg</t>
+        </is>
+      </c>
+      <c r="D380" s="37" t="n">
+        <v>40823.02</v>
+      </c>
+      <c r="E380" s="32" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B381" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C381" s="32" t="inlineStr">
+        <is>
+          <t>6235 Management Fees</t>
+        </is>
+      </c>
+      <c r="D381" s="37" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E381" s="32" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B382" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C382" s="32" t="inlineStr">
+        <is>
+          <t>6333 Repairs - Painting &amp; Drywall</t>
+        </is>
+      </c>
+      <c r="D382" s="37" t="n">
+        <v>19750</v>
+      </c>
+      <c r="E382" s="32" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B383" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C383" s="32" t="inlineStr">
+        <is>
+          <t>6335 Repairs - Plbg, Htg &amp; A/C</t>
+        </is>
+      </c>
+      <c r="D383" s="37" t="n">
+        <v>10771.62</v>
+      </c>
+      <c r="E383" s="32" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B384" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C384" s="32" t="inlineStr">
+        <is>
+          <t>6410 Water</t>
+        </is>
+      </c>
+      <c r="D384" s="37" t="n">
+        <v>3926.42</v>
+      </c>
+      <c r="E384" s="32" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B385" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C385" s="32" t="inlineStr">
+        <is>
+          <t>6270 Professional Fees - Other</t>
+        </is>
+      </c>
+      <c r="D385" s="37" t="n">
+        <v>3608.29</v>
+      </c>
+      <c r="E385" s="32" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B386" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C386" s="32" t="inlineStr">
+        <is>
+          <t>6280 Legal Fees</t>
+        </is>
+      </c>
+      <c r="D386" s="37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E386" s="32" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B387" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C387" s="32" t="inlineStr">
+        <is>
+          <t>6275 Accounting</t>
+        </is>
+      </c>
+      <c r="D387" s="37" t="n">
+        <v>800</v>
+      </c>
+      <c r="E387" s="32" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B388" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C388" s="32" t="inlineStr">
+        <is>
+          <t>6232 Lawn &amp; Garden</t>
+        </is>
+      </c>
+      <c r="D388" s="37" t="n">
+        <v>200</v>
+      </c>
+      <c r="E388" s="32" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B389" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C389" s="32" t="inlineStr">
+        <is>
+          <t>6120 Bank Service Charges</t>
+        </is>
+      </c>
+      <c r="D389" s="37" t="n">
+        <v>33</v>
+      </c>
+      <c r="E389" s="32" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B390" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C390" s="32" t="inlineStr">
+        <is>
+          <t>6160 Dues and Subscriptions</t>
+        </is>
+      </c>
+      <c r="D390" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="E390" s="32" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2024</t>
+        </is>
+      </c>
+      <c r="B391" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C391" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D391" s="43">
+        <f>SUM(D376:D390)</f>
+        <v/>
+      </c>
+      <c r="E391" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $524,505.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B392" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C392" s="32" t="inlineStr">
+        <is>
+          <t>4000 Rent Income</t>
+        </is>
+      </c>
+      <c r="D392" s="37" t="n">
+        <v>495442.14</v>
+      </c>
+      <c r="E392" s="32" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B393" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C393" s="32" t="inlineStr">
+        <is>
+          <t>4045 Cam Charge Income</t>
+        </is>
+      </c>
+      <c r="D393" s="37" t="n">
+        <v>159665.7</v>
+      </c>
+      <c r="E393" s="32" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B394" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C394" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D394" s="43">
+        <f>SUM(D392:D393)</f>
+        <v/>
+      </c>
+      <c r="E394" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $655,107.84</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B395" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C395" s="32" t="inlineStr">
+        <is>
+          <t>6520 Property Tax</t>
+        </is>
+      </c>
+      <c r="D395" s="37" t="n">
+        <v>148047.68</v>
+      </c>
+      <c r="E395" s="32" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B396" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C396" s="32" t="inlineStr">
+        <is>
+          <t>6220 Loan Interest</t>
+        </is>
+      </c>
+      <c r="D396" s="37" t="n">
+        <v>142547.72</v>
+      </c>
+      <c r="E396" s="32" t="inlineStr">
+        <is>
+          <t>Debt service - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B397" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C397" s="32" t="inlineStr">
+        <is>
+          <t>6182 Insurance - Bus Owners Pkg</t>
+        </is>
+      </c>
+      <c r="D397" s="37" t="n">
+        <v>62455.69</v>
+      </c>
+      <c r="E397" s="32" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B398" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C398" s="32" t="inlineStr">
+        <is>
+          <t>6510 Income Tax</t>
+        </is>
+      </c>
+      <c r="D398" s="37" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E398" s="32" t="inlineStr">
+        <is>
+          <t>Entity tax - excluded from a true NOI</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B399" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C399" s="32" t="inlineStr">
+        <is>
+          <t>6235 Management Fees</t>
+        </is>
+      </c>
+      <c r="D399" s="37" t="n">
+        <v>33487.46</v>
+      </c>
+      <c r="E399" s="32" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B400" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C400" s="32" t="inlineStr">
+        <is>
+          <t>6410 Water</t>
+        </is>
+      </c>
+      <c r="D400" s="37" t="n">
+        <v>8870.16</v>
+      </c>
+      <c r="E400" s="32" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B401" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C401" s="32" t="inlineStr">
+        <is>
+          <t>6335 Repairs - Plbg, Htg &amp; A/C</t>
+        </is>
+      </c>
+      <c r="D401" s="37" t="n">
+        <v>5086.62</v>
+      </c>
+      <c r="E401" s="32" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B402" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C402" s="32" t="inlineStr">
+        <is>
+          <t>6236 Maintenance - Parking Lot</t>
+        </is>
+      </c>
+      <c r="D402" s="37" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E402" s="32" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B403" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C403" s="32" t="inlineStr">
+        <is>
+          <t>6275 Accounting</t>
+        </is>
+      </c>
+      <c r="D403" s="37" t="n">
+        <v>1100</v>
+      </c>
+      <c r="E403" s="32" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B404" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C404" s="32" t="inlineStr">
+        <is>
+          <t>6310 Building Repairs</t>
+        </is>
+      </c>
+      <c r="D404" s="37" t="n">
+        <v>89.87</v>
+      </c>
+      <c r="E404" s="32" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B405" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C405" s="32" t="inlineStr">
+        <is>
+          <t>6120 Bank Service Charges</t>
+        </is>
+      </c>
+      <c r="D405" s="37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E405" s="32" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway - CY2023</t>
+        </is>
+      </c>
+      <c r="B406" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C406" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D406" s="43">
+        <f>SUM(D395:D405)</f>
+        <v/>
+      </c>
+      <c r="E406" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $453,235.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St - 2023/2024 survey</t>
+        </is>
+      </c>
+      <c r="B407" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C407" s="32" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D407" s="37" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E407" s="32" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St - 2023/2024 survey</t>
+        </is>
+      </c>
+      <c r="B408" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C408" s="32" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D408" s="37" t="n">
+        <v>16380</v>
+      </c>
+      <c r="E408" s="32" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St - 2023/2024 survey</t>
+        </is>
+      </c>
+      <c r="B409" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C409" s="32" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D409" s="37" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E409" s="32" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St - 2023/2024 survey</t>
+        </is>
+      </c>
+      <c r="B410" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C410" s="32" t="inlineStr">
+        <is>
+          <t>Snow/Trash Removal</t>
+        </is>
+      </c>
+      <c r="D410" s="37" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E410" s="32" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="32" t="inlineStr">
+        <is>
+          <t>5720 Washington St - 2023/2024 survey</t>
+        </is>
+      </c>
+      <c r="B411" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C411" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REPORTED OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D411" s="43">
+        <f>SUM(D407:D410)</f>
+        <v/>
+      </c>
+      <c r="E411" s="32" t="inlineStr">
+        <is>
+          <t>No printed total on the survey form - this is the sum of the four handwritten entries. All four were written in the Tenant-Expenses column even though the owner reported 100% owner-occupancy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B412" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C412" s="32" t="inlineStr">
+        <is>
+          <t>Actual rent received (12 months from 1/1/2023)</t>
+        </is>
+      </c>
+      <c r="D412" s="37" t="n">
+        <v>670872</v>
+      </c>
+      <c r="E412" s="32">
+        <f> $55,906.00 monthly x 12; scheduled rent $14.00/SF</f>
+        <v/>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B413" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C413" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D413" s="43">
+        <f>SUM(D412:D412)</f>
+        <v/>
+      </c>
+      <c r="E413" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $670,872.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B414" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C414" s="32" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D414" s="37" t="n">
+        <v>122995.66</v>
+      </c>
+      <c r="E414" s="32" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B415" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C415" s="32" t="inlineStr">
+        <is>
+          <t>Building Repair &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D415" s="37" t="n">
+        <v>100803</v>
+      </c>
+      <c r="E415" s="32" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B416" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C416" s="32" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D416" s="37" t="n">
+        <v>18057</v>
+      </c>
+      <c r="E416" s="32" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B417" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C417" s="32" t="inlineStr">
+        <is>
+          <t>Ground Maintenance</t>
+        </is>
+      </c>
+      <c r="D417" s="37" t="n">
+        <v>2440</v>
+      </c>
+      <c r="E417" s="32" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B418" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C418" s="32" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D418" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E418" s="32" t="inlineStr">
+        <is>
+          <t>Marked 'T' on the form, not a dollar amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B419" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C419" s="32" t="inlineStr">
+        <is>
+          <t>Snow/Trash Removal</t>
+        </is>
+      </c>
+      <c r="D419" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E419" s="32" t="inlineStr">
+        <is>
+          <t>Marked 'T' on the form, not a dollar amount</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="32" t="inlineStr">
+        <is>
+          <t>1890 E 58th Ave - 12 mo from 1/1/2023</t>
+        </is>
+      </c>
+      <c r="B420" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C420" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REPORTED OWNER EXPENSES</t>
+        </is>
+      </c>
+      <c r="D420" s="43">
+        <f>SUM(D414:D419)</f>
+        <v/>
+      </c>
+      <c r="E420" s="32" t="inlineStr">
+        <is>
+          <t>No printed total on the survey form - sum of the owner/landlord column. Gross lease, so the owner pays expenses; no property-tax or management line was reported.</t>
         </is>
       </c>
     </row>
@@ -13309,7 +16806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -13540,6 +17037,445 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="44" t="inlineStr">
+        <is>
+          <t>First Industrial Realty Trust - Adams County parcels on the R0103518 letter-of-authorization schedule (40 parcels total across 6 CO counties):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial LP</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>R0103518</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>5977 Broadway St.</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial LP</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>R0103559</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>5952 Broadway St.</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="32" t="inlineStr">
+        <is>
+          <t>FR MASSACHUSETTS 7 LLC</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>R0103523</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>5909 Broadway St.</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial LP</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>R0024470</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>451 E. 124th Ave.</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>First Industrial LP</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>R0024474</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Thornton CO</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>FR Massachusettes 7 LLC</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>R0111259</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>18150 E. 32nd Pl., Aurora</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>FRASER AURORA LLC</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>R0084260</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>3400 Fraser St</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>FR Park Plaza LLC</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>R0177662</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>21301 E 33rd Dr</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>FR AURORA COMMERCE CENTER PHASE I LLC</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>R0198530</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>22300 E 26th Ave</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>FR Aurora Commerce Center Phase I LLC</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>R0203646</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>22000 E 26th Ave</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>FR Aurora Commerce Center Phase I LLC</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>R0203647</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>22010 E 26th Ave</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>FR Aurora Commerce Center Phase I LLC</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>R0205071</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>22600 E 26th Ave</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>FR 21110 E 31st LLC</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>R0083949</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>21110 E 31st Circle</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>First industrial LP</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>R0180952</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>3350 ODESSA WAY</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>FR 8000 EAST 96 LLC</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>R0215909</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>8000 E 96th Ave</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>FR 8000 EAST 96 LLC</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>R0215910</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>8000 E 96th Ave</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1322,23 +1322,172 @@
         </is>
       </c>
     </row>
-    <row r="25"/>
+    <row r="25">
+      <c r="A25" s="32" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>R0187789.pdf</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>Assessor protest - income approach, recreated rent roll, 2yr expenses, 6 lease comps, 4 sale comps, LOA</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue, Commerce City (KEW Realty)</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists (Paul Leonard)</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="32" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>R0188699.pdf</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>Tax appeal - market proforma + actual 2024 NNN income analysis + 3 lease comps + LOA</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>15100 East 40th Ave, Aurora - Confluent Center 70 (LBA Realty)</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Keegan Conway) / CoStar</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>R0198179.pdf</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>Executed Second Amendment to Lease - State of Colorado (7-step rent schedule, TI allowance, renewal option)</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>17851 E 40th Avenue, Aurora</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Renewal term 7/1/2026 - 6/30/2033</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>CO Dept of Personnel &amp; Administration / Office of the State Architect</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>R0191099.pdf</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>Assessor protest - income approach, 2 rent-roll dates, CY2024 income statement, base-period lease survey</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>3559 N Himalaya Rd, Bldg 5, Aurora (Majestic Commercenter Phase 9)</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>R0200721.pdf</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>Assessor protest - income approach, 3 rent-roll dates, CY2024 income statement, 5 base-period lease comps</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street, Aurora (Majestic Lisbon Buildings LLC)</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
@@ -1347,10 +1496,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1362,7 +1511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y22"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3411,6 +3560,519 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>R0187789</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>R0187789</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="inlineStr">
+        <is>
+          <t>R0187789</t>
+        </is>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue</t>
+        </is>
+      </c>
+      <c r="E23" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue</t>
+        </is>
+      </c>
+      <c r="F23" s="32" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G23" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H23" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J23" s="32" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation (David Spira, President)</t>
+        </is>
+      </c>
+      <c r="K23" s="32" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation</t>
+        </is>
+      </c>
+      <c r="L23" s="32" t="inlineStr">
+        <is>
+          <t>Industrial / Flex (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M23" s="32" t="inlineStr">
+        <is>
+          <t>Multi (3 tenants)</t>
+        </is>
+      </c>
+      <c r="N23" s="33" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O23" s="34" t="n"/>
+      <c r="P23" s="34" t="n"/>
+      <c r="Q23" s="34" t="n">
+        <v>50000</v>
+      </c>
+      <c r="R23" s="35" t="n">
+        <v>2016</v>
+      </c>
+      <c r="S23" s="32" t="n"/>
+      <c r="T23" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024) - stabilized</t>
+        </is>
+      </c>
+      <c r="U23" s="36" t="n">
+        <v>6896593</v>
+      </c>
+      <c r="V23" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W23" s="36" t="n">
+        <v>5440000</v>
+      </c>
+      <c r="X23" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists / Goldstein Law Firm (agents)</t>
+        </is>
+      </c>
+      <c r="Y23" s="32" t="inlineStr">
+        <is>
+          <t>R0187789.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>R0188699</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>R0188699</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="inlineStr">
+        <is>
+          <t>R0188699</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70</t>
+        </is>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>15100 East 40th Avenue</t>
+        </is>
+      </c>
+      <c r="F24" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G24" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H24" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I24" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J24" s="32" t="inlineStr">
+        <is>
+          <t>LBA Realty Fund</t>
+        </is>
+      </c>
+      <c r="K24" s="32" t="inlineStr">
+        <is>
+          <t>LBA NCC2-Company II, LLC</t>
+        </is>
+      </c>
+      <c r="L24" s="32" t="inlineStr">
+        <is>
+          <t>Industrial (30' clear height)</t>
+        </is>
+      </c>
+      <c r="M24" s="32" t="inlineStr">
+        <is>
+          <t>Multi/single not itemized</t>
+        </is>
+      </c>
+      <c r="N24" s="33" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="O24" s="34" t="n"/>
+      <c r="P24" s="34" t="n"/>
+      <c r="Q24" s="34" t="n">
+        <v>105174</v>
+      </c>
+      <c r="R24" s="35" t="n">
+        <v>2016</v>
+      </c>
+      <c r="S24" s="32" t="n"/>
+      <c r="T24" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024)</t>
+        </is>
+      </c>
+      <c r="U24" s="36" t="n">
+        <v>13272555</v>
+      </c>
+      <c r="V24" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W24" s="36" t="n">
+        <v>11498000</v>
+      </c>
+      <c r="X24" s="32" t="inlineStr">
+        <is>
+          <t>LBA Realty (Stephanie Olazabal, VP Property Accounting)</t>
+        </is>
+      </c>
+      <c r="Y24" s="32" t="inlineStr">
+        <is>
+          <t>R0188699.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>R0198179</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>R0198179</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>17851 E 40th Avenue</t>
+        </is>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>17851 E 40th Avenue</t>
+        </is>
+      </c>
+      <c r="F25" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G25" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H25" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I25" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J25" s="32" t="inlineStr">
+        <is>
+          <t>Prologis, L.P. (successor-in-interest to DCT Summit LLC)</t>
+        </is>
+      </c>
+      <c r="K25" s="32" t="inlineStr">
+        <is>
+          <t>Prologis, L.P.</t>
+        </is>
+      </c>
+      <c r="L25" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - leased to the State of Colorado</t>
+        </is>
+      </c>
+      <c r="M25" s="32" t="inlineStr">
+        <is>
+          <t>Single tenant (State of Colorado)</t>
+        </is>
+      </c>
+      <c r="N25" s="33" t="n"/>
+      <c r="O25" s="34" t="n"/>
+      <c r="P25" s="34" t="n"/>
+      <c r="Q25" s="34" t="n">
+        <v>82131</v>
+      </c>
+      <c r="R25" s="35" t="n"/>
+      <c r="S25" s="32" t="n"/>
+      <c r="T25" s="32" t="inlineStr">
+        <is>
+          <t>100% leased (State of Colorado)</t>
+        </is>
+      </c>
+      <c r="U25" s="36" t="n"/>
+      <c r="V25" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="W25" s="36" t="n"/>
+      <c r="X25" s="32" t="inlineStr">
+        <is>
+          <t>Prologis, Inc. (general partner)</t>
+        </is>
+      </c>
+      <c r="Y25" s="32" t="inlineStr">
+        <is>
+          <t>R0198179.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>R0191099</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>R0191099</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="inlineStr">
+        <is>
+          <t>R0191099</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter - Building 5</t>
+        </is>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>3559 N Himalaya Road</t>
+        </is>
+      </c>
+      <c r="F26" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G26" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H26" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I26" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J26" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Phase 9 (bldg 206605)</t>
+        </is>
+      </c>
+      <c r="K26" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Phase 9</t>
+        </is>
+      </c>
+      <c r="L26" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M26" s="32" t="inlineStr">
+        <is>
+          <t>Multi (4 tenants)</t>
+        </is>
+      </c>
+      <c r="N26" s="33" t="n"/>
+      <c r="O26" s="34" t="n"/>
+      <c r="P26" s="34" t="n"/>
+      <c r="Q26" s="34" t="n">
+        <v>159047</v>
+      </c>
+      <c r="R26" s="35" t="n">
+        <v>2017</v>
+      </c>
+      <c r="S26" s="32" t="n"/>
+      <c r="T26" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024 DOV)</t>
+        </is>
+      </c>
+      <c r="U26" s="36" t="n">
+        <v>19943316</v>
+      </c>
+      <c r="V26" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W26" s="36" t="n">
+        <v>11139000</v>
+      </c>
+      <c r="X26" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Realty Co. (Nicole Creighton, PM)</t>
+        </is>
+      </c>
+      <c r="Y26" s="32" t="inlineStr">
+        <is>
+          <t>R0191099.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>R0200721</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>R0200721</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="inlineStr">
+        <is>
+          <t>R0200721</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street</t>
+        </is>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>3420 N. Lisbon Street</t>
+        </is>
+      </c>
+      <c r="F27" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G27" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I27" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J27" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Lisbon Buildings, LLC (bldg 347002)</t>
+        </is>
+      </c>
+      <c r="K27" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Lisbon Buildings, LLC</t>
+        </is>
+      </c>
+      <c r="L27" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="M27" s="32" t="inlineStr">
+        <is>
+          <t>Single tenant</t>
+        </is>
+      </c>
+      <c r="N27" s="33" t="n"/>
+      <c r="O27" s="34" t="n"/>
+      <c r="P27" s="34" t="n"/>
+      <c r="Q27" s="34" t="n">
+        <v>36212</v>
+      </c>
+      <c r="R27" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="S27" s="32" t="n"/>
+      <c r="T27" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024 DOV)</t>
+        </is>
+      </c>
+      <c r="U27" s="36" t="n">
+        <v>5477148</v>
+      </c>
+      <c r="V27" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W27" s="36" t="n">
+        <v>4463600</v>
+      </c>
+      <c r="X27" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Realty Co. (Nicole Creighton, PM)</t>
+        </is>
+      </c>
+      <c r="Y27" s="32" t="inlineStr">
+        <is>
+          <t>R0200721.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Y2"/>
@@ -3426,7 +4088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6256,6 +6918,597 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue (R0187789)</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>5710A</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>Prudential Overall Supply</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E58" s="37" t="n">
+        <v>10259.67</v>
+      </c>
+      <c r="F58" s="37" t="n">
+        <v>123116</v>
+      </c>
+      <c r="G58" s="37" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="H58" s="32" t="inlineStr">
+        <is>
+          <t>12/2017</t>
+        </is>
+      </c>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>4/2026</t>
+        </is>
+      </c>
+      <c r="J58" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="37" t="n">
+        <v>2091.67</v>
+      </c>
+      <c r="L58" s="37" t="n"/>
+      <c r="M58" s="32" t="inlineStr">
+        <is>
+          <t>10,000 SF. Petitioner's recreated rent roll at 6/30/2024. Expense recoveries $25,100/yr ($2.51 PSF); no other income. Gross rent $14.82 PSF. Monthly figures derived from the annual amounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue (R0187789)</t>
+        </is>
+      </c>
+      <c r="B59" s="32" t="inlineStr">
+        <is>
+          <t>5710C</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>United Rentals</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E59" s="37" t="n">
+        <v>8500</v>
+      </c>
+      <c r="F59" s="37" t="n">
+        <v>102000</v>
+      </c>
+      <c r="G59" s="37" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H59" s="32" t="inlineStr">
+        <is>
+          <t>2/2019</t>
+        </is>
+      </c>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>4/2029</t>
+        </is>
+      </c>
+      <c r="J59" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="37" t="n">
+        <v>3650</v>
+      </c>
+      <c r="L59" s="37" t="n"/>
+      <c r="M59" s="32" t="inlineStr">
+        <is>
+          <t>10,000 SF. Recoveries $43,800/yr ($4.38 PSF). Gross rent $14.58 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue (R0187789)</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>5710H</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>Applied Control</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E60" s="37" t="n">
+        <v>31583.33</v>
+      </c>
+      <c r="F60" s="37" t="n">
+        <v>379000</v>
+      </c>
+      <c r="G60" s="37" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="H60" s="32" t="inlineStr">
+        <is>
+          <t>8/2018</t>
+        </is>
+      </c>
+      <c r="I60" s="32" t="inlineStr">
+        <is>
+          <t>12/2026</t>
+        </is>
+      </c>
+      <c r="J60" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="37" t="n">
+        <v>3325</v>
+      </c>
+      <c r="L60" s="37" t="n"/>
+      <c r="M60" s="32" t="inlineStr">
+        <is>
+          <t>30,000 SF. Recoveries $39,900/yr ($1.33 PSF). Gross rent $13.96 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue (R0187789)</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C61" s="32" t="inlineStr">
+        <is>
+          <t>3 tenants - 100% occupied</t>
+        </is>
+      </c>
+      <c r="D61" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN</t>
+        </is>
+      </c>
+      <c r="E61" s="37" t="n">
+        <v>50343</v>
+      </c>
+      <c r="F61" s="37" t="n">
+        <v>604116</v>
+      </c>
+      <c r="G61" s="37" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="H61" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J61" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="37" t="n">
+        <v>9066.67</v>
+      </c>
+      <c r="L61" s="37" t="n"/>
+      <c r="M61" s="32" t="inlineStr">
+        <is>
+          <t>50,000 SF occupied, 0 vacant. Printed totals: scheduled rent $604,116, expense recoveries $108,800, other income $0. Leases have 2 to 5 years remaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>17851 E 40th Avenue (R0198179)</t>
+        </is>
+      </c>
+      <c r="B62" s="32" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C62" s="32" t="inlineStr">
+        <is>
+          <t>State of Colorado - Dept of Public Safety, Division of Homeland Security and Emergency Management</t>
+        </is>
+      </c>
+      <c r="D62" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Gross (State-exempt from property tax)</t>
+        </is>
+      </c>
+      <c r="E62" s="37" t="n">
+        <v>62967.1</v>
+      </c>
+      <c r="F62" s="37" t="n">
+        <v>755605.2</v>
+      </c>
+      <c r="G62" s="37" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H62" s="32" t="inlineStr">
+        <is>
+          <t>7/1/2026</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="inlineStr">
+        <is>
+          <t>6/30/2033</t>
+        </is>
+      </c>
+      <c r="J62" s="32" t="inlineStr">
+        <is>
+          <t>7-yr Second Renewal Term + one 5-yr Third Renewal Option</t>
+        </is>
+      </c>
+      <c r="K62" s="37" t="n"/>
+      <c r="L62" s="37" t="n"/>
+      <c r="M62" s="32" t="inlineStr">
+        <is>
+          <t>82,131 RSF. Executed Second Amendment to a lease dated 12/22/2020 (First Amendment 3/15/2021; first renewal exercised 4/29/2021). Landlord Prologis, L.P. Figures shown are the first paying year. Full schedule (Adjusted Annual Rent PSF / Monthly): 8/1/26-6/30/27 $9.20 / $62,967.10; FY28 $9.47 / $64,815.05; FY29 $9.76 / $66,799.88; FY30 $10.05 / $68,784.71; FY31 $10.36 / $70,906.43; FY32 $10.67 / $73,028.15; FY33 $10.99 / $75,218.31. 7/1/26-7/31/26 is rent-free. Negotiated rent runs $11.52-$13.31 PSF before a $2.32 PSF property-tax credit. TI allowance $205,327.50 ($2.50 PSF); JLL tenant-agent commission $128,648.31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>Suite 100</t>
+        </is>
+      </c>
+      <c r="C63" s="32" t="inlineStr">
+        <is>
+          <t>Erickson Metals of Colorado, Inc. (Randy Adkisson)</t>
+        </is>
+      </c>
+      <c r="D63" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E63" s="37" t="n">
+        <v>29122.88</v>
+      </c>
+      <c r="F63" s="37" t="n">
+        <v>349474.56</v>
+      </c>
+      <c r="G63" s="37" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="H63" s="32" t="inlineStr">
+        <is>
+          <t>12/1/2022</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="inlineStr">
+        <is>
+          <t>1/31/2033</t>
+        </is>
+      </c>
+      <c r="J63" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="37" t="n"/>
+      <c r="L63" s="37" t="n"/>
+      <c r="M63" s="32" t="inlineStr">
+        <is>
+          <t>51,774 SF = 32.55% of building. Rent roll as of 12/31/23. This same lease is used as a comparable in Sterling's own Exhibit F survey for buildings 6 and 7, and in the R0200721 Exhibit C survey, where it is shown at $360,832 / $6.97 PSF rather than the $349,474.56 / $6.75 on this rent roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B64" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C64" s="32" t="inlineStr">
+        <is>
+          <t>Euromarket Designs, Inc.</t>
+        </is>
+      </c>
+      <c r="D64" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E64" s="37" t="n">
+        <v>31693.1</v>
+      </c>
+      <c r="F64" s="37" t="n">
+        <v>380317.2</v>
+      </c>
+      <c r="G64" s="37" t="n">
+        <v>6.879</v>
+      </c>
+      <c r="H64" s="32" t="inlineStr">
+        <is>
+          <t>2/1/2018</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J64" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="37" t="n"/>
+      <c r="L64" s="37" t="n"/>
+      <c r="M64" s="32" t="inlineStr">
+        <is>
+          <t>55,287 SF = 34.76% of building. Rent roll as of 12/31/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>Suite 200</t>
+        </is>
+      </c>
+      <c r="C65" s="32" t="inlineStr">
+        <is>
+          <t>Carbon Chemistry Ltd.</t>
+        </is>
+      </c>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E65" s="37" t="n">
+        <v>12260.4</v>
+      </c>
+      <c r="F65" s="37" t="n">
+        <v>147124.8</v>
+      </c>
+      <c r="G65" s="37" t="n">
+        <v>8.195499999999999</v>
+      </c>
+      <c r="H65" s="32" t="inlineStr">
+        <is>
+          <t>10/1/2020</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>1/31/2025</t>
+        </is>
+      </c>
+      <c r="J65" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="37" t="n"/>
+      <c r="L65" s="37" t="n"/>
+      <c r="M65" s="32" t="inlineStr">
+        <is>
+          <t>17,952 SF = 11.29% of building. Rent roll as of 12/31/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B66" s="32" t="inlineStr">
+        <is>
+          <t>Suite 400</t>
+        </is>
+      </c>
+      <c r="C66" s="32" t="inlineStr">
+        <is>
+          <t>Service Partners, LLC (c/o TopBuild Corp)</t>
+        </is>
+      </c>
+      <c r="D66" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E66" s="37" t="n">
+        <v>19838.25</v>
+      </c>
+      <c r="F66" s="37" t="n">
+        <v>238059</v>
+      </c>
+      <c r="G66" s="37" t="n">
+        <v>6.9947</v>
+      </c>
+      <c r="H66" s="32" t="inlineStr">
+        <is>
+          <t>4/1/2021</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="inlineStr">
+        <is>
+          <t>6/30/2026</t>
+        </is>
+      </c>
+      <c r="J66" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="37" t="n"/>
+      <c r="L66" s="37" t="n"/>
+      <c r="M66" s="32" t="inlineStr">
+        <is>
+          <t>34,034 SF = 21.40% of building. Rent roll as of 12/31/23; at 6/30/23 this lease was $19,260.43/mo, $231,125.16/yr, $6.7910 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL 12/31/23</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>4 tenants - 100% occupied</t>
+        </is>
+      </c>
+      <c r="D67" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E67" s="37" t="n">
+        <v>92914.63</v>
+      </c>
+      <c r="F67" s="37" t="n">
+        <v>1114975.56</v>
+      </c>
+      <c r="G67" s="37" t="n">
+        <v>7.0104</v>
+      </c>
+      <c r="H67" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="37" t="n"/>
+      <c r="L67" s="37" t="n"/>
+      <c r="M67" s="32" t="inlineStr">
+        <is>
+          <t>159,047 SF occupied, 0 vacant. Printed rent-roll totals at 12/31/23. At 6/30/23 the totals were $92,336.81/mo and $1,108,041.72/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street (R0200721)</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>Cameron Ashley Building Products, Inc. (Ryan Beaton)</t>
+        </is>
+      </c>
+      <c r="D68" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Single Tenant Net</t>
+        </is>
+      </c>
+      <c r="E68" s="37" t="n">
+        <v>23370.53</v>
+      </c>
+      <c r="F68" s="37" t="n">
+        <v>280446.36</v>
+      </c>
+      <c r="G68" s="37" t="n">
+        <v>7.7446</v>
+      </c>
+      <c r="H68" s="32" t="inlineStr">
+        <is>
+          <t>10/12/2021</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="inlineStr">
+        <is>
+          <t>12/31/2026</t>
+        </is>
+      </c>
+      <c r="J68" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="37" t="n"/>
+      <c r="L68" s="37" t="n"/>
+      <c r="M68" s="32" t="inlineStr">
+        <is>
+          <t>36,212 SF, 100% of building. Rent roll as of 06/01/24. This annual rent ties exactly to Industrial Rental Income on the CY2024 income statement. Sterling's Exhibit C shows the same lease at $264,348 / $7.30 PSF scheduled with an effective rent of $5.86 PSF after 3 months free rent and $13.14 PSF of tenant improvements, while the letter text describes the commencement rate as $7.60 PSF - three different figures, all reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
@@ -6274,7 +7527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6705,453 +7958,768 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue (R0187789)</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C18" s="36" t="n">
+        <v>6896593</v>
+      </c>
+      <c r="D18" s="37" t="n">
+        <v>137.93</v>
+      </c>
+      <c r="E18" s="36" t="n">
+        <v>5440000</v>
+      </c>
+      <c r="F18" s="37" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="G18" s="36" t="n"/>
+      <c r="H18" s="32" t="inlineStr">
+        <is>
+          <t>R0187789</t>
+        </is>
+      </c>
+    </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 (R0188699)</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C19" s="36" t="n">
+        <v>13272555</v>
+      </c>
+      <c r="D19" s="37" t="n">
+        <v>126.2</v>
+      </c>
+      <c r="E19" s="36" t="n">
+        <v>11498000</v>
+      </c>
+      <c r="F19" s="37" t="n">
+        <v>109.32</v>
+      </c>
+      <c r="G19" s="36" t="n">
+        <v>12707001</v>
+      </c>
+      <c r="H19" s="32" t="inlineStr">
+        <is>
+          <t>R0188699</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>17851 E 40th Avenue (R0198179)</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="C20" s="36" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="36" t="n"/>
+      <c r="F20" s="37" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="32" t="inlineStr">
+        <is>
+          <t>R0198179 - lease document only, no valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C21" s="36" t="n">
+        <v>19943316</v>
+      </c>
+      <c r="D21" s="37" t="n">
+        <v>125.39</v>
+      </c>
+      <c r="E21" s="36" t="n">
+        <v>11139000</v>
+      </c>
+      <c r="F21" s="37" t="n">
+        <v>70.04000000000001</v>
+      </c>
+      <c r="G21" s="36" t="n"/>
+      <c r="H21" s="32" t="inlineStr">
+        <is>
+          <t>R0191099</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street (R0200721)</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>5477148</v>
+      </c>
+      <c r="D22" s="37" t="n">
+        <v>151.25</v>
+      </c>
+      <c r="E22" s="36" t="n">
+        <v>4463600</v>
+      </c>
+      <c r="F22" s="37" t="n">
+        <v>123.26</v>
+      </c>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="32" t="inlineStr">
+        <is>
+          <t>R0200721</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
         </is>
       </c>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="21" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="21" t="n"/>
-    </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="20" t="n"/>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="21" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>7205 Gilpin Way</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n">
+      <c r="B28" s="9" t="n">
         <v>359394</v>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C28" s="9" t="n">
         <v>-17970</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D28" s="9" t="n">
         <v>341424</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E28" s="9" t="n">
         <v>-27314</v>
       </c>
-      <c r="F23" s="14" t="n">
+      <c r="F28" s="14" t="n">
         <v>314110</v>
       </c>
-      <c r="G23" s="19" t="n">
+      <c r="G28" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H23" s="14" t="n">
+      <c r="H28" s="14" t="n">
         <v>4832500</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>17608 E. 24th Dr</t>
         </is>
       </c>
-      <c r="B24" s="9" t="n">
+      <c r="B29" s="9" t="n">
         <v>209100</v>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C29" s="9" t="n">
         <v>-10455</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D29" s="9" t="n">
         <v>198645</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E29" s="9" t="n">
         <v>-15892</v>
       </c>
-      <c r="F24" s="14" t="n">
+      <c r="F29" s="14" t="n">
         <v>182753</v>
       </c>
-      <c r="G24" s="19" t="n">
+      <c r="G29" s="19" t="n">
         <v>0.06</v>
       </c>
-      <c r="H24" s="14" t="n">
+      <c r="H29" s="14" t="n">
         <v>3050000</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>12260 Pennsylvania St</t>
         </is>
       </c>
-      <c r="B25" s="9" t="n">
+      <c r="B30" s="9" t="n">
         <v>237290</v>
       </c>
-      <c r="C25" s="9" t="n">
+      <c r="C30" s="9" t="n">
         <v>-16610</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D30" s="9" t="n">
         <v>220680</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E30" s="9" t="n">
         <v>-22068</v>
       </c>
-      <c r="F25" s="14" t="n">
+      <c r="F30" s="14" t="n">
         <v>198612</v>
       </c>
-      <c r="G25" s="19" t="n">
+      <c r="G30" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H25" s="14" t="n">
+      <c r="H30" s="14" t="n">
         <v>2837000</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>6770 E. 56th Ave</t>
         </is>
       </c>
-      <c r="B26" s="9" t="n">
+      <c r="B31" s="9" t="n">
         <v>115824</v>
       </c>
-      <c r="C26" s="9" t="n">
+      <c r="C31" s="9" t="n">
         <v>-5791</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D31" s="9" t="n">
         <v>110033</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E31" s="9" t="n">
         <v>-5502</v>
       </c>
-      <c r="F26" s="14" t="n">
+      <c r="F31" s="14" t="n">
         <v>104531</v>
       </c>
-      <c r="G26" s="19" t="n">
+      <c r="G31" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H26" s="14" t="n">
+      <c r="H31" s="14" t="n">
         <v>1493302</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B27" s="9" t="n">
+      <c r="B32" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C27" s="9" t="n">
+      <c r="C32" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D27" s="9" t="n">
+      <c r="D32" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E32" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F27" s="14" t="n">
+      <c r="F32" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G27" s="19" t="n">
+      <c r="G32" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H27" s="14" t="n">
+      <c r="H32" s="14" t="n">
         <v>2460577</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>18300 E 28th Ave (R0110351)</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>599228</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>-59923</v>
-      </c>
-      <c r="D28" s="36" t="n">
-        <v>539305</v>
-      </c>
-      <c r="E28" s="36" t="n">
-        <v>-43144</v>
-      </c>
-      <c r="F28" s="38" t="n">
-        <v>496161</v>
-      </c>
-      <c r="G28" s="39" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="H28" s="38" t="n">
-        <v>7939000</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="32" t="inlineStr">
-        <is>
-          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="n">
-        <v>781250</v>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>-78125</v>
-      </c>
-      <c r="D29" s="36" t="n">
-        <v>703125</v>
-      </c>
-      <c r="E29" s="36" t="n">
-        <v>-35156</v>
-      </c>
-      <c r="F29" s="38" t="n">
-        <v>667969</v>
-      </c>
-      <c r="G29" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H29" s="38" t="n">
-        <v>8754500</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>-125000</v>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>1125000</v>
-      </c>
-      <c r="E30" s="36" t="n">
-        <v>-56250</v>
-      </c>
-      <c r="F30" s="38" t="n">
-        <v>1068750</v>
-      </c>
-      <c r="G30" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H30" s="38" t="n">
-        <v>14007200</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>Anchor Business Park - market (R0121833)</t>
-        </is>
-      </c>
-      <c r="B31" s="36" t="n">
-        <v>346484</v>
-      </c>
-      <c r="C31" s="36" t="n">
-        <v>-17324</v>
-      </c>
-      <c r="D31" s="36" t="n">
-        <v>329160</v>
-      </c>
-      <c r="E31" s="36" t="n">
-        <v>-49374</v>
-      </c>
-      <c r="F31" s="38" t="n">
-        <v>279786</v>
-      </c>
-      <c r="G31" s="39" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="H31" s="38" t="n">
-        <v>3919000</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>Anchor Business Park - actual 2024 (R0121833)</t>
-        </is>
-      </c>
-      <c r="B32" s="36" t="n">
-        <v>457717</v>
-      </c>
-      <c r="C32" s="36" t="n"/>
-      <c r="D32" s="36" t="n">
-        <v>457717</v>
-      </c>
-      <c r="E32" s="36" t="n">
-        <v>-110337</v>
-      </c>
-      <c r="F32" s="38" t="n">
-        <v>347380</v>
-      </c>
-      <c r="G32" s="39" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="H32" s="38" t="n">
-        <v>3510000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>Anchor Business Park - actual 2023 (R0121833)</t>
+          <t>18300 E 28th Ave (R0110351)</t>
         </is>
       </c>
       <c r="B33" s="36" t="n">
-        <v>401204</v>
-      </c>
-      <c r="C33" s="36" t="n"/>
+        <v>599228</v>
+      </c>
+      <c r="C33" s="36" t="n">
+        <v>-59923</v>
+      </c>
       <c r="D33" s="36" t="n">
-        <v>401204</v>
+        <v>539305</v>
       </c>
       <c r="E33" s="36" t="n">
-        <v>-119063</v>
+        <v>-43144</v>
       </c>
       <c r="F33" s="38" t="n">
-        <v>282140</v>
+        <v>496161</v>
       </c>
       <c r="G33" s="39" t="n">
-        <v>0.099</v>
+        <v>0.0625</v>
       </c>
       <c r="H33" s="38" t="n">
-        <v>2851000</v>
+        <v>7939000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="32" t="inlineStr">
         <is>
-          <t>5977-5995 N Broadway (R0103518)</t>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
         </is>
       </c>
       <c r="B34" s="36" t="n">
-        <v>489879</v>
+        <v>781250</v>
       </c>
       <c r="C34" s="36" t="n">
-        <v>-39190</v>
+        <v>-78125</v>
       </c>
       <c r="D34" s="36" t="n">
-        <v>450689</v>
+        <v>703125</v>
       </c>
       <c r="E34" s="36" t="n">
-        <v>-45069</v>
+        <v>-35156</v>
       </c>
       <c r="F34" s="38" t="n">
-        <v>405620</v>
-      </c>
-      <c r="G34" s="46" t="n">
-        <v>0.07000000000000001</v>
+        <v>667969</v>
+      </c>
+      <c r="G34" s="39" t="n">
+        <v>0.07630000000000001</v>
       </c>
       <c r="H34" s="38" t="n">
-        <v>5794600</v>
+        <v>8754500</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="32" t="inlineStr">
         <is>
+          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
+        </is>
+      </c>
+      <c r="B35" s="36" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="C35" s="36" t="n">
+        <v>-125000</v>
+      </c>
+      <c r="D35" s="36" t="n">
+        <v>1125000</v>
+      </c>
+      <c r="E35" s="36" t="n">
+        <v>-56250</v>
+      </c>
+      <c r="F35" s="38" t="n">
+        <v>1068750</v>
+      </c>
+      <c r="G35" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H35" s="38" t="n">
+        <v>14007200</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - market (R0121833)</t>
+        </is>
+      </c>
+      <c r="B36" s="36" t="n">
+        <v>346484</v>
+      </c>
+      <c r="C36" s="36" t="n">
+        <v>-17324</v>
+      </c>
+      <c r="D36" s="36" t="n">
+        <v>329160</v>
+      </c>
+      <c r="E36" s="36" t="n">
+        <v>-49374</v>
+      </c>
+      <c r="F36" s="38" t="n">
+        <v>279786</v>
+      </c>
+      <c r="G36" s="39" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H36" s="38" t="n">
+        <v>3919000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - actual 2024 (R0121833)</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="E37" s="36" t="n">
+        <v>-110337</v>
+      </c>
+      <c r="F37" s="38" t="n">
+        <v>347380</v>
+      </c>
+      <c r="G37" s="39" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H37" s="38" t="n">
+        <v>3510000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Anchor Business Park - actual 2023 (R0121833)</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n">
+        <v>401204</v>
+      </c>
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="36" t="n">
+        <v>401204</v>
+      </c>
+      <c r="E38" s="36" t="n">
+        <v>-119063</v>
+      </c>
+      <c r="F38" s="38" t="n">
+        <v>282140</v>
+      </c>
+      <c r="G38" s="39" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="H38" s="38" t="n">
+        <v>2851000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>5977-5995 N Broadway (R0103518)</t>
+        </is>
+      </c>
+      <c r="B39" s="36" t="n">
+        <v>489879</v>
+      </c>
+      <c r="C39" s="36" t="n">
+        <v>-39190</v>
+      </c>
+      <c r="D39" s="36" t="n">
+        <v>450689</v>
+      </c>
+      <c r="E39" s="36" t="n">
+        <v>-45069</v>
+      </c>
+      <c r="F39" s="38" t="n">
+        <v>405620</v>
+      </c>
+      <c r="G39" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H39" s="38" t="n">
+        <v>5794600</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - actual 2023 (R0187789)</t>
+        </is>
+      </c>
+      <c r="B40" s="36" t="n">
+        <v>640426</v>
+      </c>
+      <c r="C40" s="36" t="n">
+        <v>-51234</v>
+      </c>
+      <c r="D40" s="36" t="n">
+        <v>589192</v>
+      </c>
+      <c r="E40" s="36" t="n">
+        <v>-94857</v>
+      </c>
+      <c r="F40" s="38" t="n">
+        <v>494335</v>
+      </c>
+      <c r="G40" s="39" t="n"/>
+      <c r="H40" s="38" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - actual 2024 (R0187789)</t>
+        </is>
+      </c>
+      <c r="B41" s="36" t="n">
+        <v>725742</v>
+      </c>
+      <c r="C41" s="36" t="n">
+        <v>-58059</v>
+      </c>
+      <c r="D41" s="36" t="n">
+        <v>667683</v>
+      </c>
+      <c r="E41" s="36" t="n">
+        <v>-107192</v>
+      </c>
+      <c r="F41" s="38" t="n">
+        <v>560491</v>
+      </c>
+      <c r="G41" s="39" t="n"/>
+      <c r="H41" s="38" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - concluded, avg NOI (R0187789)</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="n"/>
+      <c r="C42" s="36" t="n"/>
+      <c r="D42" s="36" t="n"/>
+      <c r="E42" s="36" t="n"/>
+      <c r="F42" s="38" t="n">
+        <v>527413</v>
+      </c>
+      <c r="G42" s="39" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H42" s="38" t="n">
+        <v>5440000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - market proforma (R0188699)</t>
+        </is>
+      </c>
+      <c r="B43" s="36" t="n">
+        <v>815099</v>
+      </c>
+      <c r="C43" s="36" t="n">
+        <v>-65208</v>
+      </c>
+      <c r="D43" s="36" t="n">
+        <v>749891</v>
+      </c>
+      <c r="E43" s="36" t="n">
+        <v>-59991</v>
+      </c>
+      <c r="F43" s="38" t="n">
+        <v>689899</v>
+      </c>
+      <c r="G43" s="39" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H43" s="38" t="n">
+        <v>11498000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - actual 2024 NNN (R0188699)</t>
+        </is>
+      </c>
+      <c r="B44" s="36" t="n">
+        <v>1536047</v>
+      </c>
+      <c r="C44" s="36" t="n"/>
+      <c r="D44" s="36" t="n">
+        <v>1536047</v>
+      </c>
+      <c r="E44" s="36" t="n">
+        <v>-782165</v>
+      </c>
+      <c r="F44" s="38" t="n">
+        <v>753882</v>
+      </c>
+      <c r="G44" s="39" t="n"/>
+      <c r="H44" s="38" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B45" s="36" t="n">
+        <v>994044</v>
+      </c>
+      <c r="C45" s="36" t="n">
+        <v>-99404</v>
+      </c>
+      <c r="D45" s="36" t="n">
+        <v>894639</v>
+      </c>
+      <c r="E45" s="36" t="n">
+        <v>-44732</v>
+      </c>
+      <c r="F45" s="38" t="n">
+        <v>849907</v>
+      </c>
+      <c r="G45" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H45" s="38" t="n">
+        <v>11139000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street (R0200721)</t>
+        </is>
+      </c>
+      <c r="B46" s="36" t="n">
+        <v>398332</v>
+      </c>
+      <c r="C46" s="36" t="n">
+        <v>-39833</v>
+      </c>
+      <c r="D46" s="36" t="n">
+        <v>358499</v>
+      </c>
+      <c r="E46" s="36" t="n">
+        <v>-17925</v>
+      </c>
+      <c r="F46" s="38" t="n">
+        <v>340574</v>
+      </c>
+      <c r="G46" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H46" s="38" t="n">
+        <v>4463600</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
           <t>5945 &amp; 5957 Broadway (R0103519) - agent capitalization</t>
         </is>
       </c>
-      <c r="B35" s="36" t="n"/>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="38" t="n">
+      <c r="B47" s="36" t="n"/>
+      <c r="C47" s="36" t="n"/>
+      <c r="D47" s="36" t="n"/>
+      <c r="E47" s="36" t="n"/>
+      <c r="F47" s="38" t="n">
         <v>550000</v>
       </c>
-      <c r="G35" s="46" t="n">
+      <c r="G47" s="46" t="n">
         <v>0.09331</v>
       </c>
-      <c r="H35" s="38" t="n">
+      <c r="H47" s="38" t="n">
         <v>5894300</v>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
         </is>
       </c>
-      <c r="B37" s="20" t="n"/>
-      <c r="C37" s="20" t="n"/>
-      <c r="D37" s="20" t="n"/>
-      <c r="E37" s="20" t="n"/>
-      <c r="F37" s="20" t="n"/>
-      <c r="G37" s="20" t="n"/>
-      <c r="H37" s="21" t="n"/>
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="20" t="n"/>
+      <c r="D49" s="20" t="n"/>
+      <c r="E49" s="20" t="n"/>
+      <c r="F49" s="20" t="n"/>
+      <c r="G49" s="20" t="n"/>
+      <c r="H49" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7163,7 +8731,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -7629,23 +9197,132 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="24">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B24" s="37" t="n">
+        <v>640426</v>
+      </c>
+      <c r="C24" s="37" t="n">
+        <v>214395</v>
+      </c>
+      <c r="D24" s="41">
+        <f>B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="32" t="inlineStr">
+        <is>
+          <t>Owner-reported. Total expenses INCLUDE real estate taxes ($137,214); the petitioner's NOI of $494,335 strips taxes out, adds a 3% reserve and applies 8% vacancy. R0187789</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B25" s="37" t="n">
+        <v>725742</v>
+      </c>
+      <c r="C25" s="37" t="n">
+        <v>228330</v>
+      </c>
+      <c r="D25" s="41">
+        <f>B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="32" t="inlineStr">
+        <is>
+          <t>Owner-reported. Includes real estate taxes ($141,168); petitioner's NOI $560,491 on the same basis as 2023. Two-year average NOI $527,413. R0187789</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B26" s="37" t="n">
+        <v>1536047</v>
+      </c>
+      <c r="C26" s="37" t="n">
+        <v>782165</v>
+      </c>
+      <c r="D26" s="41">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN, accrual. Expenses include property taxes $391,900. TRUE NOI $753,882 ($7.17 PSF) - no debt service or depreciation. R0188699</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B27" s="37" t="n">
+        <v>1800360.37</v>
+      </c>
+      <c r="C27" s="37" t="n">
+        <v>628819.46</v>
+      </c>
+      <c r="D27" s="41">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="32" t="inlineStr">
+        <is>
+          <t>Operating income before interest ($331,694.13) and other/depreciation ($559,919.27); net income after those = $279,927.51. R0191099</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B28" s="37" t="n">
+        <v>484482.38</v>
+      </c>
+      <c r="C28" s="37" t="n">
+        <v>205776.75</v>
+      </c>
+      <c r="D28" s="41">
+        <f>B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>Operating income before interest ($86,641.63) and other/depreciation ($233,804.17); net income after those = ($41,740.17). R0200721</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="21" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A30:E30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7657,7 +9334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E420"/>
+  <dimension ref="A1:E516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -16788,6 +18465,2142 @@
       <c r="E420" s="32" t="inlineStr">
         <is>
           <t>No printed total on the survey form - sum of the owner/landlord column. Gross lease, so the owner pays expenses; no property-tax or management line was reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B421" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C421" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D421" s="37" t="n">
+        <v>137214</v>
+      </c>
+      <c r="E421" s="32" t="inlineStr">
+        <is>
+          <t>$2.74 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B422" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C422" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Reimbursable</t>
+        </is>
+      </c>
+      <c r="D422" s="37" t="n">
+        <v>76169</v>
+      </c>
+      <c r="E422" s="32" t="inlineStr">
+        <is>
+          <t>$1.52 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B423" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C423" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Non-Reimbursable</t>
+        </is>
+      </c>
+      <c r="D423" s="37" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E423" s="32" t="inlineStr">
+        <is>
+          <t>$0.02 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B424" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C424" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D424" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E424" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B425" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C425" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D425" s="43">
+        <f>SUM(D421:D424)</f>
+        <v/>
+      </c>
+      <c r="E425" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $214,395.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B426" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C426" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D426" s="37" t="n">
+        <v>141168</v>
+      </c>
+      <c r="E426" s="32" t="inlineStr">
+        <is>
+          <t>$2.82 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B427" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C427" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Reimbursable</t>
+        </is>
+      </c>
+      <c r="D427" s="37" t="n">
+        <v>86637</v>
+      </c>
+      <c r="E427" s="32" t="inlineStr">
+        <is>
+          <t>$1.73 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B428" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C428" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Non-Reimbursable</t>
+        </is>
+      </c>
+      <c r="D428" s="37" t="n">
+        <v>525</v>
+      </c>
+      <c r="E428" s="32" t="inlineStr">
+        <is>
+          <t>$0.01 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B429" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C429" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D429" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E429" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B430" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C430" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D430" s="43">
+        <f>SUM(D426:D429)</f>
+        <v/>
+      </c>
+      <c r="E430" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $228,330.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B431" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C431" s="32" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D431" s="37" t="n">
+        <v>925921</v>
+      </c>
+      <c r="E431" s="32" t="inlineStr">
+        <is>
+          <t>60.3% of EGI, $8.80 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B432" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C432" s="32" t="inlineStr">
+        <is>
+          <t>Reimbursements</t>
+        </is>
+      </c>
+      <c r="D432" s="37" t="n">
+        <v>609219</v>
+      </c>
+      <c r="E432" s="32" t="inlineStr">
+        <is>
+          <t>39.7% of EGI, $5.79 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B433" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C433" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D433" s="37" t="n">
+        <v>908</v>
+      </c>
+      <c r="E433" s="32" t="inlineStr">
+        <is>
+          <t>0.1% of EGI</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B434" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C434" s="32" t="inlineStr">
+        <is>
+          <t>Above/Below Market Rent Income</t>
+        </is>
+      </c>
+      <c r="D434" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E434" s="32" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B435" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C435" s="32" t="inlineStr">
+        <is>
+          <t>Concessions</t>
+        </is>
+      </c>
+      <c r="D435" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" s="32" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B436" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C436" s="40" t="inlineStr">
+        <is>
+          <t>EFFECTIVE GROSS INCOME</t>
+        </is>
+      </c>
+      <c r="D436" s="43">
+        <f>SUM(D431:D435)</f>
+        <v/>
+      </c>
+      <c r="E436" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,536,047. Sum of the printed components is $1,536,048 - a $1 rounding difference in the source. Both reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B437" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C437" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="D437" s="37" t="n">
+        <v>391900</v>
+      </c>
+      <c r="E437" s="32" t="inlineStr">
+        <is>
+          <t>25.5% of EGI, $3.73 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B438" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C438" s="32" t="inlineStr">
+        <is>
+          <t>Reimbursable Operating Expenses</t>
+        </is>
+      </c>
+      <c r="D438" s="37" t="n">
+        <v>264713</v>
+      </c>
+      <c r="E438" s="32" t="inlineStr">
+        <is>
+          <t>17.2% of EGI, $2.52 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B439" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C439" s="32" t="inlineStr">
+        <is>
+          <t>Non-Recoverable Operating Expenses</t>
+        </is>
+      </c>
+      <c r="D439" s="37" t="n">
+        <v>125552</v>
+      </c>
+      <c r="E439" s="32" t="inlineStr">
+        <is>
+          <t>8.2% of EGI, $1.19 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - CY2024</t>
+        </is>
+      </c>
+      <c r="B440" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C440" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D440" s="43">
+        <f>SUM(D437:D439)</f>
+        <v/>
+      </c>
+      <c r="E440" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $782,165.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B441" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C441" s="32" t="inlineStr">
+        <is>
+          <t>4015 Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D441" s="37" t="n">
+        <v>1140134.64</v>
+      </c>
+      <c r="E441" s="32" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B442" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C442" s="32" t="inlineStr">
+        <is>
+          <t>4145 Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D442" s="37" t="n">
+        <v>349367.26</v>
+      </c>
+      <c r="E442" s="32" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B443" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C443" s="32" t="inlineStr">
+        <is>
+          <t>4150 Utilities Reimbursement</t>
+        </is>
+      </c>
+      <c r="D443" s="37" t="n">
+        <v>95769.03</v>
+      </c>
+      <c r="E443" s="32" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B444" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C444" s="32" t="inlineStr">
+        <is>
+          <t>4135 Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D444" s="37" t="n">
+        <v>80939.49000000001</v>
+      </c>
+      <c r="E444" s="32" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B445" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C445" s="32" t="inlineStr">
+        <is>
+          <t>4175 Reserve Income</t>
+        </is>
+      </c>
+      <c r="D445" s="37" t="n">
+        <v>71340.84</v>
+      </c>
+      <c r="E445" s="32" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B446" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C446" s="32" t="inlineStr">
+        <is>
+          <t>4160 Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D446" s="37" t="n">
+        <v>53004.09</v>
+      </c>
+      <c r="E446" s="32" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B447" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C447" s="32" t="inlineStr">
+        <is>
+          <t>4035 Rent Concessions</t>
+        </is>
+      </c>
+      <c r="D447" s="37" t="n">
+        <v>39276.22</v>
+      </c>
+      <c r="E447" s="32" t="inlineStr">
+        <is>
+          <t>Positive as printed</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B448" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C448" s="32" t="inlineStr">
+        <is>
+          <t>4140 Insurance Reimbursement</t>
+        </is>
+      </c>
+      <c r="D448" s="37" t="n">
+        <v>26275.98</v>
+      </c>
+      <c r="E448" s="32" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B449" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C449" s="32" t="inlineStr">
+        <is>
+          <t>4158 Direct Tenant Reimbursement</t>
+        </is>
+      </c>
+      <c r="D449" s="37" t="n">
+        <v>1651.74</v>
+      </c>
+      <c r="E449" s="32" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B450" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C450" s="32" t="inlineStr">
+        <is>
+          <t>4156 Tenant TI Reimb Income</t>
+        </is>
+      </c>
+      <c r="D450" s="37" t="n">
+        <v>-21.94</v>
+      </c>
+      <c r="E450" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B451" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C451" s="32" t="inlineStr">
+        <is>
+          <t>4040 Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D451" s="37" t="n">
+        <v>-57376.98</v>
+      </c>
+      <c r="E451" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B452" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C452" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D452" s="43">
+        <f>SUM(D441:D451)</f>
+        <v/>
+      </c>
+      <c r="E452" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,800,360.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B453" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C453" s="32" t="inlineStr">
+        <is>
+          <t>5500 Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D453" s="37" t="n">
+        <v>349322.3</v>
+      </c>
+      <c r="E453" s="32" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B454" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C454" s="32" t="inlineStr">
+        <is>
+          <t>5400 Management Fees</t>
+        </is>
+      </c>
+      <c r="D454" s="37" t="n">
+        <v>52858.61</v>
+      </c>
+      <c r="E454" s="32" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B455" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C455" s="32" t="inlineStr">
+        <is>
+          <t>5637 Utilities-DTR</t>
+        </is>
+      </c>
+      <c r="D455" s="37" t="n">
+        <v>43479.56</v>
+      </c>
+      <c r="E455" s="32" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B456" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C456" s="32" t="inlineStr">
+        <is>
+          <t>5320 Parking Lot</t>
+        </is>
+      </c>
+      <c r="D456" s="37" t="n">
+        <v>30790.02</v>
+      </c>
+      <c r="E456" s="32" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B457" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C457" s="32" t="inlineStr">
+        <is>
+          <t>5635 Utilities-Water</t>
+        </is>
+      </c>
+      <c r="D457" s="37" t="n">
+        <v>22373.45</v>
+      </c>
+      <c r="E457" s="32" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B458" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C458" s="32" t="inlineStr">
+        <is>
+          <t>5115 Insurance-Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D458" s="37" t="n">
+        <v>20905</v>
+      </c>
+      <c r="E458" s="32" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B459" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C459" s="32" t="inlineStr">
+        <is>
+          <t>5370 Snow Removal</t>
+        </is>
+      </c>
+      <c r="D459" s="37" t="n">
+        <v>19643.13</v>
+      </c>
+      <c r="E459" s="32" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B460" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C460" s="32" t="inlineStr">
+        <is>
+          <t>5290 Landscaping</t>
+        </is>
+      </c>
+      <c r="D460" s="37" t="n">
+        <v>17060.13</v>
+      </c>
+      <c r="E460" s="32" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B461" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C461" s="32" t="inlineStr">
+        <is>
+          <t>5620 Utilities-Gas/Heating</t>
+        </is>
+      </c>
+      <c r="D461" s="37" t="n">
+        <v>16533.91</v>
+      </c>
+      <c r="E461" s="32" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B462" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C462" s="32" t="inlineStr">
+        <is>
+          <t>5610 Utilities-Electricity</t>
+        </is>
+      </c>
+      <c r="D462" s="37" t="n">
+        <v>9700.66</v>
+      </c>
+      <c r="E462" s="32" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B463" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C463" s="32" t="inlineStr">
+        <is>
+          <t>5350 Roof</t>
+        </is>
+      </c>
+      <c r="D463" s="37" t="n">
+        <v>8159.28</v>
+      </c>
+      <c r="E463" s="32" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B464" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C464" s="32" t="inlineStr">
+        <is>
+          <t>5250 Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D464" s="37" t="n">
+        <v>7632.19</v>
+      </c>
+      <c r="E464" s="32" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B465" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C465" s="32" t="inlineStr">
+        <is>
+          <t>8445 Prof Service-Legal (Leasing)</t>
+        </is>
+      </c>
+      <c r="D465" s="37" t="n">
+        <v>6720</v>
+      </c>
+      <c r="E465" s="32" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B466" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C466" s="32" t="inlineStr">
+        <is>
+          <t>5275 HVAC</t>
+        </is>
+      </c>
+      <c r="D466" s="37" t="n">
+        <v>5395.32</v>
+      </c>
+      <c r="E466" s="32" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B467" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C467" s="32" t="inlineStr">
+        <is>
+          <t>5120 Insurance-Liability</t>
+        </is>
+      </c>
+      <c r="D467" s="37" t="n">
+        <v>5268</v>
+      </c>
+      <c r="E467" s="32" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B468" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C468" s="32" t="inlineStr">
+        <is>
+          <t>5615 Utilities-Fire Service</t>
+        </is>
+      </c>
+      <c r="D468" s="37" t="n">
+        <v>2246.08</v>
+      </c>
+      <c r="E468" s="32" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B469" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C469" s="32" t="inlineStr">
+        <is>
+          <t>5312 Other-DTR</t>
+        </is>
+      </c>
+      <c r="D469" s="37" t="n">
+        <v>2679.52</v>
+      </c>
+      <c r="E469" s="32" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B470" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C470" s="32" t="inlineStr">
+        <is>
+          <t>5380 Sweeping</t>
+        </is>
+      </c>
+      <c r="D470" s="37" t="n">
+        <v>2155.91</v>
+      </c>
+      <c r="E470" s="32" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B471" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C471" s="32" t="inlineStr">
+        <is>
+          <t>5630 Utilities-Telephone</t>
+        </is>
+      </c>
+      <c r="D471" s="37" t="n">
+        <v>1752.9</v>
+      </c>
+      <c r="E471" s="32" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B472" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C472" s="32" t="inlineStr">
+        <is>
+          <t>5385 Window Washing</t>
+        </is>
+      </c>
+      <c r="D472" s="37" t="n">
+        <v>1366</v>
+      </c>
+      <c r="E472" s="32" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B473" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C473" s="32" t="inlineStr">
+        <is>
+          <t>5305 Lighting</t>
+        </is>
+      </c>
+      <c r="D473" s="37" t="n">
+        <v>921.76</v>
+      </c>
+      <c r="E473" s="32" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B474" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C474" s="32" t="inlineStr">
+        <is>
+          <t>8450 Prof Service-Other Environ</t>
+        </is>
+      </c>
+      <c r="D474" s="37" t="n">
+        <v>447.63</v>
+      </c>
+      <c r="E474" s="32" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B475" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C475" s="32" t="inlineStr">
+        <is>
+          <t>5335 Plumbing</t>
+        </is>
+      </c>
+      <c r="D475" s="37" t="n">
+        <v>288.85</v>
+      </c>
+      <c r="E475" s="32" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B476" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C476" s="32" t="inlineStr">
+        <is>
+          <t>8435 Prof Service-Other</t>
+        </is>
+      </c>
+      <c r="D476" s="37" t="n">
+        <v>225</v>
+      </c>
+      <c r="E476" s="32" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B477" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C477" s="32" t="inlineStr">
+        <is>
+          <t>5205 Backflow Testing &amp; Repair</t>
+        </is>
+      </c>
+      <c r="D477" s="37" t="n">
+        <v>180</v>
+      </c>
+      <c r="E477" s="32" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B478" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C478" s="32" t="inlineStr">
+        <is>
+          <t>5285 Keys/Card Access</t>
+        </is>
+      </c>
+      <c r="D478" s="37" t="n">
+        <v>179.58</v>
+      </c>
+      <c r="E478" s="32" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B479" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C479" s="32" t="inlineStr">
+        <is>
+          <t>5280 Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D479" s="37" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="E479" s="32" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B480" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C480" s="32" t="inlineStr">
+        <is>
+          <t>5365 Signs</t>
+        </is>
+      </c>
+      <c r="D480" s="37" t="n">
+        <v>160.95</v>
+      </c>
+      <c r="E480" s="32" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B481" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C481" s="32" t="inlineStr">
+        <is>
+          <t>5235 Door Repairs</t>
+        </is>
+      </c>
+      <c r="D481" s="37" t="n">
+        <v>130</v>
+      </c>
+      <c r="E481" s="32" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B482" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C482" s="32" t="inlineStr">
+        <is>
+          <t>8420 Prof Service-Legal</t>
+        </is>
+      </c>
+      <c r="D482" s="37" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="E482" s="32" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 - CY2024</t>
+        </is>
+      </c>
+      <c r="B483" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C483" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D483" s="43">
+        <f>SUM(D453:D482)</f>
+        <v/>
+      </c>
+      <c r="E483" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $628,819.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B484" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C484" s="32" t="inlineStr">
+        <is>
+          <t>4015 Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D484" s="37" t="n">
+        <v>280446.36</v>
+      </c>
+      <c r="E484" s="32" t="inlineStr">
+        <is>
+          <t>Ties exactly to the 06/01/24 rent roll annual rent</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B485" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C485" s="32" t="inlineStr">
+        <is>
+          <t>4145 Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D485" s="37" t="n">
+        <v>149606.51</v>
+      </c>
+      <c r="E485" s="32" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B486" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C486" s="32" t="inlineStr">
+        <is>
+          <t>4135 Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D486" s="37" t="n">
+        <v>29118.48</v>
+      </c>
+      <c r="E486" s="32" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B487" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C487" s="32" t="inlineStr">
+        <is>
+          <t>4160 Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D487" s="37" t="n">
+        <v>14616.96</v>
+      </c>
+      <c r="E487" s="32" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B488" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C488" s="32" t="inlineStr">
+        <is>
+          <t>4175 Reserve Income</t>
+        </is>
+      </c>
+      <c r="D488" s="37" t="n">
+        <v>13579.56</v>
+      </c>
+      <c r="E488" s="32" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B489" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C489" s="32" t="inlineStr">
+        <is>
+          <t>4140 Insurance Reimbursement</t>
+        </is>
+      </c>
+      <c r="D489" s="37" t="n">
+        <v>9974</v>
+      </c>
+      <c r="E489" s="32" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B490" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C490" s="32" t="inlineStr">
+        <is>
+          <t>4158 Direct Tenant Reimbursement</t>
+        </is>
+      </c>
+      <c r="D490" s="37" t="n">
+        <v>261.67</v>
+      </c>
+      <c r="E490" s="32" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B491" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C491" s="32" t="inlineStr">
+        <is>
+          <t>4040 Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D491" s="37" t="n">
+        <v>-13121.16</v>
+      </c>
+      <c r="E491" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B492" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C492" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D492" s="43">
+        <f>SUM(D484:D491)</f>
+        <v/>
+      </c>
+      <c r="E492" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $484,482.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B493" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C493" s="32" t="inlineStr">
+        <is>
+          <t>5500 Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D493" s="37" t="n">
+        <v>150063.24</v>
+      </c>
+      <c r="E493" s="32" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B494" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C494" s="32" t="inlineStr">
+        <is>
+          <t>5400 Management Fees</t>
+        </is>
+      </c>
+      <c r="D494" s="37" t="n">
+        <v>14140.06</v>
+      </c>
+      <c r="E494" s="32" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B495" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C495" s="32" t="inlineStr">
+        <is>
+          <t>5290 Landscaping</t>
+        </is>
+      </c>
+      <c r="D495" s="37" t="n">
+        <v>13736.12</v>
+      </c>
+      <c r="E495" s="32" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B496" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C496" s="32" t="inlineStr">
+        <is>
+          <t>5115 Insurance-Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D496" s="37" t="n">
+        <v>8951</v>
+      </c>
+      <c r="E496" s="32" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B497" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C497" s="32" t="inlineStr">
+        <is>
+          <t>5320 Parking Lot</t>
+        </is>
+      </c>
+      <c r="D497" s="37" t="n">
+        <v>5065.03</v>
+      </c>
+      <c r="E497" s="32" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B498" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C498" s="32" t="inlineStr">
+        <is>
+          <t>5250 Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D498" s="37" t="n">
+        <v>3491.1</v>
+      </c>
+      <c r="E498" s="32" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B499" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C499" s="32" t="inlineStr">
+        <is>
+          <t>5370 Snow Removal</t>
+        </is>
+      </c>
+      <c r="D499" s="37" t="n">
+        <v>2923.75</v>
+      </c>
+      <c r="E499" s="32" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B500" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C500" s="32" t="inlineStr">
+        <is>
+          <t>5350 Roof</t>
+        </is>
+      </c>
+      <c r="D500" s="37" t="n">
+        <v>1794.77</v>
+      </c>
+      <c r="E500" s="32" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B501" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C501" s="32" t="inlineStr">
+        <is>
+          <t>5120 Insurance-Liability</t>
+        </is>
+      </c>
+      <c r="D501" s="37" t="n">
+        <v>1189</v>
+      </c>
+      <c r="E501" s="32" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B502" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C502" s="32" t="inlineStr">
+        <is>
+          <t>5620 Utilities-Gas/Heating</t>
+        </is>
+      </c>
+      <c r="D502" s="37" t="n">
+        <v>1081.59</v>
+      </c>
+      <c r="E502" s="32" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B503" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C503" s="32" t="inlineStr">
+        <is>
+          <t>5280 Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D503" s="37" t="n">
+        <v>750</v>
+      </c>
+      <c r="E503" s="32" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B504" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C504" s="32" t="inlineStr">
+        <is>
+          <t>5380 Sweeping</t>
+        </is>
+      </c>
+      <c r="D504" s="37" t="n">
+        <v>491.25</v>
+      </c>
+      <c r="E504" s="32" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B505" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C505" s="32" t="inlineStr">
+        <is>
+          <t>8450 Prof Service-Other Environ</t>
+        </is>
+      </c>
+      <c r="D505" s="37" t="n">
+        <v>447.63</v>
+      </c>
+      <c r="E505" s="32" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B506" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C506" s="32" t="inlineStr">
+        <is>
+          <t>5385 Window Washing</t>
+        </is>
+      </c>
+      <c r="D506" s="37" t="n">
+        <v>296</v>
+      </c>
+      <c r="E506" s="32" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B507" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C507" s="32" t="inlineStr">
+        <is>
+          <t>5365 Signs</t>
+        </is>
+      </c>
+      <c r="D507" s="37" t="n">
+        <v>272.45</v>
+      </c>
+      <c r="E507" s="32" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B508" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C508" s="32" t="inlineStr">
+        <is>
+          <t>5205 Backflow Testing &amp; Repair</t>
+        </is>
+      </c>
+      <c r="D508" s="37" t="n">
+        <v>270</v>
+      </c>
+      <c r="E508" s="32" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B509" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C509" s="32" t="inlineStr">
+        <is>
+          <t>6290 Landscaping</t>
+        </is>
+      </c>
+      <c r="D509" s="37" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="E509" s="32" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B510" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C510" s="32" t="inlineStr">
+        <is>
+          <t>5312 Other-DTR</t>
+        </is>
+      </c>
+      <c r="D510" s="37" t="n">
+        <v>261.67</v>
+      </c>
+      <c r="E510" s="32" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B511" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C511" s="32" t="inlineStr">
+        <is>
+          <t>8225 Tenant Relations</t>
+        </is>
+      </c>
+      <c r="D511" s="37" t="n">
+        <v>126.9</v>
+      </c>
+      <c r="E511" s="32" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B512" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C512" s="32" t="inlineStr">
+        <is>
+          <t>8420 Prof Service-Legal</t>
+        </is>
+      </c>
+      <c r="D512" s="37" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="E512" s="32" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B513" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C513" s="32" t="inlineStr">
+        <is>
+          <t>5305 Lighting</t>
+        </is>
+      </c>
+      <c r="D513" s="37" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="E513" s="32" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B514" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C514" s="32" t="inlineStr">
+        <is>
+          <t>5285 Keys/Card Access</t>
+        </is>
+      </c>
+      <c r="D514" s="37" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="E514" s="32" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B515" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C515" s="32" t="inlineStr">
+        <is>
+          <t>5275 HVAC</t>
+        </is>
+      </c>
+      <c r="D515" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E515" s="32" t="inlineStr">
+        <is>
+          <t>No amount printed</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street - CY2024</t>
+        </is>
+      </c>
+      <c r="B516" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C516" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D516" s="43">
+        <f>SUM(D493:D515)</f>
+        <v/>
+      </c>
+      <c r="E516" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $205,776.75</t>
         </is>
       </c>
     </row>
@@ -16806,7 +20619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -17476,6 +21289,67 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="44" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter / Majestic Realty - further Adams County buildings protested by Sterling (2025):</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Phase 9</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>R0191099</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>3559 N Himalaya Road, Building 5, Aurora</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Lisbon Buildings, LLC</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>R0200721</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>3420 N. Lisbon Street, Aurora</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -688,7 +688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1472,22 +1472,172 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="32" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>R0187787.pdf</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>Assessor protest - income approach, 2 rent rolls, 2yr expenses, 6 lease comps, sale comps, LOA</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue, Commerce City (KEW Realty)</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists (Paul Leonard)</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="32" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>R0157664.pdf</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>Protest inquiry + LOA + 4-year income analysis + 2024/2023 and 2022/2021 income statements + May 2024 rent roll</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>6045 E 76th Avenue, Commerce City (4711 West Tennessee Avenue LLC)</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (2021-2024 actuals)</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>R.H. Jacobson &amp; Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>R0164588.pdf</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>Tax appeal - market proforma + 5 lease comps + vacant rent roll + income statements</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Way, Commerce City (ASB Real Estate)</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (val 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Ethan Horn) / CoStar</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>R0164287.pdf</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="inlineStr">
+        <is>
+          <t>Owner-filed CBOE appeal + 2024 county I&amp;E survey + 2010-2025 rent schedule + income work sheet</t>
+        </is>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street, Aurora (EDC Holdings LLC)</t>
+        </is>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (rent history 2010-2025)</t>
+        </is>
+      </c>
+      <c r="F33" s="32" t="inlineStr">
+        <is>
+          <t>EDC Holdings LLC (Edward D Chandler, owner)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="32" t="inlineStr">
+        <is>
+          <t>R0180894.pdf</t>
+        </is>
+      </c>
+      <c r="C34" s="32" t="inlineStr">
+        <is>
+          <t>Tax appeal - proforma income analysis + 3-year actual income trends + LOA</t>
+        </is>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>Park 70, 1910 N Gun Club Rd, Aurora (Alpha Industrial Properties)</t>
+        </is>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025 (2022-2024 actuals)</t>
+        </is>
+      </c>
+      <c r="F34" s="32" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Beth Diehl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
@@ -1495,11 +1645,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A38:F38"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1511,7 +1661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:Y32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4073,6 +4223,533 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>R0187787</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>R0187787</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>R0187787</t>
+        </is>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue</t>
+        </is>
+      </c>
+      <c r="E28" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue</t>
+        </is>
+      </c>
+      <c r="F28" s="32" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G28" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H28" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I28" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J28" s="32" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation (David Spira, President)</t>
+        </is>
+      </c>
+      <c r="K28" s="32" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation</t>
+        </is>
+      </c>
+      <c r="L28" s="32" t="inlineStr">
+        <is>
+          <t>Industrial / Flex (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M28" s="32" t="inlineStr">
+        <is>
+          <t>Multi (4 units)</t>
+        </is>
+      </c>
+      <c r="N28" s="45" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O28" s="34" t="n"/>
+      <c r="P28" s="34" t="n"/>
+      <c r="Q28" s="34" t="n">
+        <v>35000</v>
+      </c>
+      <c r="R28" s="35" t="n">
+        <v>2016</v>
+      </c>
+      <c r="S28" s="32" t="n"/>
+      <c r="T28" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30/2024) - stabilized</t>
+        </is>
+      </c>
+      <c r="U28" s="36" t="n">
+        <v>5266489</v>
+      </c>
+      <c r="V28" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W28" s="36" t="n">
+        <v>3930000</v>
+      </c>
+      <c r="X28" s="32" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists / Goldstein Law Firm (agents)</t>
+        </is>
+      </c>
+      <c r="Y28" s="32" t="inlineStr">
+        <is>
+          <t>R0187787.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>R0157664</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>R0157664</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="inlineStr">
+        <is>
+          <t>0172132216014</t>
+        </is>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - 6045 E 76th Avenue</t>
+        </is>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>6045 E 76th Avenue</t>
+        </is>
+      </c>
+      <c r="F29" s="32" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G29" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H29" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I29" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J29" s="32" t="inlineStr">
+        <is>
+          <t>4711 West Tennessee Avenue LLC (Scott Alan McCormick, Manager)</t>
+        </is>
+      </c>
+      <c r="K29" s="32" t="inlineStr">
+        <is>
+          <t>4711 West Tennessee Avenue LLC</t>
+        </is>
+      </c>
+      <c r="L29" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (multi-bay)</t>
+        </is>
+      </c>
+      <c r="M29" s="32" t="inlineStr">
+        <is>
+          <t>Multi (11 bays)</t>
+        </is>
+      </c>
+      <c r="N29" s="45" t="n"/>
+      <c r="O29" s="34" t="n">
+        <v>66700</v>
+      </c>
+      <c r="P29" s="34" t="n"/>
+      <c r="Q29" s="34" t="n">
+        <v>21000</v>
+      </c>
+      <c r="R29" s="35" t="n">
+        <v>1988</v>
+      </c>
+      <c r="S29" s="32" t="n"/>
+      <c r="T29" s="32" t="inlineStr">
+        <is>
+          <t>71.4% - 6,000 SF vacant of 21,000 SF (May 2024 rent roll)</t>
+        </is>
+      </c>
+      <c r="U29" s="36" t="n">
+        <v>3423218</v>
+      </c>
+      <c r="V29" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W29" s="36" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="X29" s="32" t="inlineStr">
+        <is>
+          <t>R.H. Jacobson &amp; Company (agent)</t>
+        </is>
+      </c>
+      <c r="Y29" s="32" t="inlineStr">
+        <is>
+          <t>R0157664.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>R0164588</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>R0164588</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="inlineStr">
+        <is>
+          <t>R0164588</t>
+        </is>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Way</t>
+        </is>
+      </c>
+      <c r="F30" s="32" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G30" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H30" s="32" t="inlineStr">
+        <is>
+          <t>(not stated in document)</t>
+        </is>
+      </c>
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J30" s="32" t="inlineStr">
+        <is>
+          <t>ASB Real Estate</t>
+        </is>
+      </c>
+      <c r="K30" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Owner LLC</t>
+        </is>
+      </c>
+      <c r="L30" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution</t>
+        </is>
+      </c>
+      <c r="M30" s="32" t="inlineStr">
+        <is>
+          <t>Single tenant (vacant)</t>
+        </is>
+      </c>
+      <c r="N30" s="45" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O30" s="34" t="n"/>
+      <c r="P30" s="34" t="n"/>
+      <c r="Q30" s="34" t="n">
+        <v>140630</v>
+      </c>
+      <c r="R30" s="35" t="n">
+        <v>2005</v>
+      </c>
+      <c r="S30" s="32" t="n"/>
+      <c r="T30" s="32" t="inlineStr">
+        <is>
+          <t>0% - 100% vacant at 6/30/2024; Home Depot lease expired Nov 2022</t>
+        </is>
+      </c>
+      <c r="U30" s="36" t="n">
+        <v>17644243</v>
+      </c>
+      <c r="V30" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W30" s="36" t="n">
+        <v>8539000</v>
+      </c>
+      <c r="X30" s="32" t="inlineStr">
+        <is>
+          <t>Allegiance / ASB Allegiance Fund</t>
+        </is>
+      </c>
+      <c r="Y30" s="32" t="inlineStr">
+        <is>
+          <t>R0164588.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>R0164287</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>R0164287</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="inlineStr">
+        <is>
+          <t>0182128401002</t>
+        </is>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street</t>
+        </is>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street</t>
+        </is>
+      </c>
+      <c r="F31" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G31" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H31" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I31" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J31" s="32" t="inlineStr">
+        <is>
+          <t>EDC Holdings LLC (Edward D Chandler, member)</t>
+        </is>
+      </c>
+      <c r="K31" s="32" t="inlineStr">
+        <is>
+          <t>EDC Holdings LLC</t>
+        </is>
+      </c>
+      <c r="L31" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse / Distribution (with admin offices)</t>
+        </is>
+      </c>
+      <c r="M31" s="32" t="inlineStr">
+        <is>
+          <t>Single tenant</t>
+        </is>
+      </c>
+      <c r="N31" s="45" t="n"/>
+      <c r="O31" s="34" t="n"/>
+      <c r="P31" s="34" t="n"/>
+      <c r="Q31" s="34" t="n">
+        <v>27819</v>
+      </c>
+      <c r="R31" s="35" t="n"/>
+      <c r="S31" s="32" t="n"/>
+      <c r="T31" s="32" t="inlineStr">
+        <is>
+          <t>100% - single tenant, 0% vacant</t>
+        </is>
+      </c>
+      <c r="U31" s="36" t="n">
+        <v>4531688</v>
+      </c>
+      <c r="V31" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W31" s="36" t="n">
+        <v>2835000</v>
+      </c>
+      <c r="X31" s="32" t="inlineStr">
+        <is>
+          <t>Owner-managed</t>
+        </is>
+      </c>
+      <c r="Y31" s="32" t="inlineStr">
+        <is>
+          <t>R0164287.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>R0180894</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>R0180894</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="inlineStr">
+        <is>
+          <t>R0180894</t>
+        </is>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - 1910 N Gun Club Rd</t>
+        </is>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>1910 N Gun Club Rd</t>
+        </is>
+      </c>
+      <c r="F32" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G32" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H32" s="32" t="inlineStr">
+        <is>
+          <t>80019</t>
+        </is>
+      </c>
+      <c r="I32" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J32" s="32" t="inlineStr">
+        <is>
+          <t>Alpha Industrial Properties (client); Cherry Owner II LLC (owner of record)</t>
+        </is>
+      </c>
+      <c r="K32" s="32" t="inlineStr">
+        <is>
+          <t>Cherry Owner II LLC</t>
+        </is>
+      </c>
+      <c r="L32" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (Class A)</t>
+        </is>
+      </c>
+      <c r="M32" s="32" t="inlineStr">
+        <is>
+          <t>Not itemized</t>
+        </is>
+      </c>
+      <c r="N32" s="45" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="O32" s="34" t="n">
+        <v>448232</v>
+      </c>
+      <c r="P32" s="34" t="n"/>
+      <c r="Q32" s="34" t="n">
+        <v>163790</v>
+      </c>
+      <c r="R32" s="35" t="n">
+        <v>2019</v>
+      </c>
+      <c r="S32" s="32" t="inlineStr">
+        <is>
+          <t>2.74 : 1</t>
+        </is>
+      </c>
+      <c r="T32" s="32" t="inlineStr">
+        <is>
+          <t>100% (6/30 occupancy, all three actual years)</t>
+        </is>
+      </c>
+      <c r="U32" s="36" t="n">
+        <v>24584873</v>
+      </c>
+      <c r="V32" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W32" s="36" t="n">
+        <v>13214100</v>
+      </c>
+      <c r="X32" s="32" t="inlineStr">
+        <is>
+          <t>Alpha Industrial Properties</t>
+        </is>
+      </c>
+      <c r="Y32" s="32" t="inlineStr">
+        <is>
+          <t>R0180894.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:Y2"/>
@@ -4088,7 +4765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7509,6 +8186,848 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue (R0187787)</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="inlineStr">
+        <is>
+          <t>5690A</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>NOVITECH INC</t>
+        </is>
+      </c>
+      <c r="D69" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Modified Gross Industrial</t>
+        </is>
+      </c>
+      <c r="E69" s="37" t="n">
+        <v>10003.88</v>
+      </c>
+      <c r="F69" s="37" t="n">
+        <v>120046.56</v>
+      </c>
+      <c r="G69" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H69" s="32" t="inlineStr">
+        <is>
+          <t>5/1/2017</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="inlineStr">
+        <is>
+          <t>7/31/2027</t>
+        </is>
+      </c>
+      <c r="J69" s="32" t="inlineStr">
+        <is>
+          <t>123-month term</t>
+        </is>
+      </c>
+      <c r="K69" s="37" t="n"/>
+      <c r="L69" s="37" t="n"/>
+      <c r="M69" s="32" t="inlineStr">
+        <is>
+          <t>10,000 SF. Tenancy Schedule as of 6/30/2024. Annual recoveries $3.31 PSF; no misc income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue (R0187787)</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="inlineStr">
+        <is>
+          <t>5690C</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>CAMSO USA INC</t>
+        </is>
+      </c>
+      <c r="D70" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Modified Gross Industrial</t>
+        </is>
+      </c>
+      <c r="E70" s="37" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F70" s="37" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G70" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H70" s="32" t="inlineStr">
+        <is>
+          <t>8/1/2018</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="inlineStr">
+        <is>
+          <t>9/30/2028</t>
+        </is>
+      </c>
+      <c r="J70" s="32" t="inlineStr">
+        <is>
+          <t>122-month term</t>
+        </is>
+      </c>
+      <c r="K70" s="37" t="n"/>
+      <c r="L70" s="37" t="n"/>
+      <c r="M70" s="32" t="inlineStr">
+        <is>
+          <t>10,000 SF. Annual recoveries $2.59 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue (R0187787)</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t>5690E</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>TECHNEAUX TECHNOLOGY SERVICES LLC</t>
+        </is>
+      </c>
+      <c r="D71" s="32" t="inlineStr">
+        <is>
+          <t>Actual - NNN Industrial</t>
+        </is>
+      </c>
+      <c r="E71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="32" t="inlineStr">
+        <is>
+          <t>5/1/2024</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="inlineStr">
+        <is>
+          <t>7/31/2027</t>
+        </is>
+      </c>
+      <c r="J71" s="32" t="inlineStr">
+        <is>
+          <t>39-month term</t>
+        </is>
+      </c>
+      <c r="K71" s="37" t="n"/>
+      <c r="L71" s="37" t="n"/>
+      <c r="M71" s="32" t="inlineStr">
+        <is>
+          <t>5,000 SF. Rent roll shows $0.00 monthly and annual rent at 6/30/2024 - the lease had commenced two months earlier and was in a rent-abatement period. Annual recoveries $4.95 PSF. The letter cites this as the base-period lease that is 'in-line with market' while calling the three older leases above market.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue (R0187787)</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>5690F</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>REBOUND TECHNOLOGIES INC</t>
+        </is>
+      </c>
+      <c r="D72" s="32" t="inlineStr">
+        <is>
+          <t>Actual - Modified Gross Industrial</t>
+        </is>
+      </c>
+      <c r="E72" s="37" t="n">
+        <v>9791.67</v>
+      </c>
+      <c r="F72" s="37" t="n">
+        <v>117500.04</v>
+      </c>
+      <c r="G72" s="37" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="H72" s="32" t="inlineStr">
+        <is>
+          <t>8/2/2018</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="inlineStr">
+        <is>
+          <t>12/31/2026</t>
+        </is>
+      </c>
+      <c r="J72" s="32" t="inlineStr">
+        <is>
+          <t>101-month term</t>
+        </is>
+      </c>
+      <c r="K72" s="37" t="n"/>
+      <c r="L72" s="37" t="n"/>
+      <c r="M72" s="32" t="inlineStr">
+        <is>
+          <t>10,000 SF. Annual recoveries $2.59 PSF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue (R0187787)</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>4 units - 100% occupied</t>
+        </is>
+      </c>
+      <c r="D73" s="32" t="inlineStr">
+        <is>
+          <t>Actual - mixed MG / NNN</t>
+        </is>
+      </c>
+      <c r="E73" s="37" t="n">
+        <v>29795.55</v>
+      </c>
+      <c r="F73" s="37" t="n">
+        <v>357546.6</v>
+      </c>
+      <c r="G73" s="37" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="H73" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J73" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="37" t="n"/>
+      <c r="L73" s="37" t="n"/>
+      <c r="M73" s="32" t="inlineStr">
+        <is>
+          <t>35,000 SF occupied, 0 SF vacant, 100.00%. Totals are the sum of the four scheduled rents; the Techneaux unit contributes $0 while abated, so PSF is depressed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>1, 2</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>Daisy Window Tint</t>
+        </is>
+      </c>
+      <c r="D74" s="32" t="inlineStr">
+        <is>
+          <t>Actual - 2 unit bay</t>
+        </is>
+      </c>
+      <c r="E74" s="37" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F74" s="37" t="n">
+        <v>43800</v>
+      </c>
+      <c r="G74" s="37" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H74" s="32" t="inlineStr">
+        <is>
+          <t>6/1/2020</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="inlineStr">
+        <is>
+          <t>Month-to-month</t>
+        </is>
+      </c>
+      <c r="J74" s="32" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="K74" s="37" t="n"/>
+      <c r="L74" s="37" t="n"/>
+      <c r="M74" s="32" t="inlineStr">
+        <is>
+          <t>3,000 SF. May 2024 rent roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>ReTyres</t>
+        </is>
+      </c>
+      <c r="D75" s="32" t="inlineStr">
+        <is>
+          <t>Actual - 1 unit bay</t>
+        </is>
+      </c>
+      <c r="E75" s="37" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F75" s="37" t="n">
+        <v>19800</v>
+      </c>
+      <c r="G75" s="37" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H75" s="32" t="inlineStr">
+        <is>
+          <t>12/1/2016</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="inlineStr">
+        <is>
+          <t>Month-to-month</t>
+        </is>
+      </c>
+      <c r="J75" s="32" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="K75" s="37" t="n"/>
+      <c r="L75" s="37" t="n"/>
+      <c r="M75" s="32" t="inlineStr">
+        <is>
+          <t>1,500 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>4, 5</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>TAC Business dba Miracle Service</t>
+        </is>
+      </c>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>Actual - 2 unit bay</t>
+        </is>
+      </c>
+      <c r="E76" s="37" t="n">
+        <v>3700</v>
+      </c>
+      <c r="F76" s="37" t="n">
+        <v>44400</v>
+      </c>
+      <c r="G76" s="37" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H76" s="32" t="inlineStr">
+        <is>
+          <t>7/1/2015</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>Month-to-month</t>
+        </is>
+      </c>
+      <c r="J76" s="32" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="K76" s="37" t="n"/>
+      <c r="L76" s="37" t="n"/>
+      <c r="M76" s="32" t="inlineStr">
+        <is>
+          <t>3,000 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>Drywall, Dorrance</t>
+        </is>
+      </c>
+      <c r="D77" s="32" t="inlineStr">
+        <is>
+          <t>Actual - 1 unit bay</t>
+        </is>
+      </c>
+      <c r="E77" s="37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F77" s="37" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G77" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H77" s="32" t="inlineStr">
+        <is>
+          <t>12/1/2016</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="inlineStr">
+        <is>
+          <t>Month-to-month</t>
+        </is>
+      </c>
+      <c r="J77" s="32" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="K77" s="37" t="n"/>
+      <c r="L77" s="37" t="n"/>
+      <c r="M77" s="32" t="inlineStr">
+        <is>
+          <t>1,500 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B78" s="32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C78" s="32" t="inlineStr">
+        <is>
+          <t>Banchy Welding LLC</t>
+        </is>
+      </c>
+      <c r="D78" s="32" t="inlineStr">
+        <is>
+          <t>Actual - bay</t>
+        </is>
+      </c>
+      <c r="E78" s="37" t="n">
+        <v>2375</v>
+      </c>
+      <c r="F78" s="37" t="n">
+        <v>28500</v>
+      </c>
+      <c r="G78" s="37" t="n">
+        <v>19</v>
+      </c>
+      <c r="H78" s="32" t="inlineStr">
+        <is>
+          <t>12/26/2022</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="J78" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="37" t="n"/>
+      <c r="L78" s="37" t="n"/>
+      <c r="M78" s="32" t="inlineStr">
+        <is>
+          <t>1,500 SF. Labelled '2 unit Bay' on the rent roll but sized 1,500 SF - reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>Dave Mueller</t>
+        </is>
+      </c>
+      <c r="D79" s="32" t="inlineStr">
+        <is>
+          <t>Actual - 1 unit bay</t>
+        </is>
+      </c>
+      <c r="E79" s="37" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F79" s="37" t="n">
+        <v>18000</v>
+      </c>
+      <c r="G79" s="37" t="n">
+        <v>12</v>
+      </c>
+      <c r="H79" s="32" t="inlineStr">
+        <is>
+          <t>4/1/2017</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="inlineStr">
+        <is>
+          <t>Month-to-month</t>
+        </is>
+      </c>
+      <c r="J79" s="32" t="inlineStr">
+        <is>
+          <t>MTM</t>
+        </is>
+      </c>
+      <c r="K79" s="37" t="n"/>
+      <c r="L79" s="37" t="n"/>
+      <c r="M79" s="32" t="inlineStr">
+        <is>
+          <t>1,500 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>13, 14</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>Karl M. Espinoza</t>
+        </is>
+      </c>
+      <c r="D80" s="32" t="inlineStr">
+        <is>
+          <t>Actual - 2 unit bay</t>
+        </is>
+      </c>
+      <c r="E80" s="37" t="n">
+        <v>4150</v>
+      </c>
+      <c r="F80" s="37" t="n">
+        <v>49800</v>
+      </c>
+      <c r="G80" s="37" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="H80" s="32" t="inlineStr">
+        <is>
+          <t>3/15/2023</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="inlineStr">
+        <is>
+          <t>3/31/2026</t>
+        </is>
+      </c>
+      <c r="J80" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="37" t="n"/>
+      <c r="L80" s="37" t="n"/>
+      <c r="M80" s="32" t="inlineStr">
+        <is>
+          <t>3,000 SF. $150 increase scheduled 4/1/25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>6, 8, 10, 11</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>VACANT (4 bays)</t>
+        </is>
+      </c>
+      <c r="D81" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E81" s="37" t="n"/>
+      <c r="F81" s="37" t="n"/>
+      <c r="G81" s="37" t="n"/>
+      <c r="H81" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J81" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="37" t="n"/>
+      <c r="L81" s="37" t="n"/>
+      <c r="M81" s="32" t="inlineStr">
+        <is>
+          <t>6,000 SF vacant = 28.5% of the 21,000 SF building, as noted on the rent roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>7 occupied bays of 11</t>
+        </is>
+      </c>
+      <c r="D82" s="32" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E82" s="37" t="n">
+        <v>18525</v>
+      </c>
+      <c r="F82" s="37" t="n">
+        <v>222300</v>
+      </c>
+      <c r="G82" s="37" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H82" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="37" t="n"/>
+      <c r="L82" s="37" t="n"/>
+      <c r="M82" s="32" t="inlineStr">
+        <is>
+          <t>Printed rent-roll totals: $18,525 scheduled monthly charges, $222,300 annual. PSF is on the 15,000 SF occupied, not the 21,000 SF building ($10.59 PSF building-wide).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Way (R0164588)</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="inlineStr">
+        <is>
+          <t>0100 (Bldg 01115A)</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>VACANT</t>
+        </is>
+      </c>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E83" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="37" t="n"/>
+      <c r="L83" s="37" t="n"/>
+      <c r="M83" s="32" t="inlineStr">
+        <is>
+          <t>140,630 SF, 100% vacant on the 12/31/2024 rent roll and at the 6/30/2024 date of value. Home Depot's lease expired November 2022; the appeal states the space has been listed for lease ~4 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street (R0164287)</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>(single tenant - not named in the filing)</t>
+        </is>
+      </c>
+      <c r="D84" s="32" t="inlineStr">
+        <is>
+          <t>Actual - owner pays property tax only</t>
+        </is>
+      </c>
+      <c r="E84" s="37" t="n">
+        <v>17549.08</v>
+      </c>
+      <c r="F84" s="37" t="n">
+        <v>210589</v>
+      </c>
+      <c r="G84" s="37" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="H84" s="32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="32" t="inlineStr">
+        <is>
+          <t>3 years remaining from 2024</t>
+        </is>
+      </c>
+      <c r="J84" s="32" t="inlineStr">
+        <is>
+          <t>20-year lease term</t>
+        </is>
+      </c>
+      <c r="K84" s="37" t="n"/>
+      <c r="L84" s="37" t="n"/>
+      <c r="M84" s="32" t="inlineStr">
+        <is>
+          <t>27,819 SF. 2025 figures from the owner's rent schedule. The county survey ticks 'Gross' but the comments state the tenant pays every expense except property tax, so it operates as near-NNN. Rent history 2010-2025: $4.86 PSF (2010) rising to $7.57 (2025); 2023 $7.07 / $196,573; 2024 $7.35 / $204,455. The survey reports the building as 27,800 SF against 27,819 SF on the rent schedule and work sheet.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:M1"/>
@@ -7527,7 +9046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8102,586 +9621,616 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue (R0187787)</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>5266489</v>
+      </c>
+      <c r="D23" s="37" t="n">
+        <v>150.47</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>3930000</v>
+      </c>
+      <c r="F23" s="37" t="n">
+        <v>112.29</v>
+      </c>
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="32" t="inlineStr">
+        <is>
+          <t>R0187787</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II (R0157664)</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C24" s="36" t="n">
+        <v>3423218</v>
+      </c>
+      <c r="D24" s="37" t="n">
+        <v>163.01</v>
+      </c>
+      <c r="E24" s="36" t="n">
+        <v>2200000</v>
+      </c>
+      <c r="F24" s="37" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="32" t="inlineStr">
+        <is>
+          <t>R0157664</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Way (R0164588)</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C25" s="36" t="n">
+        <v>17644243</v>
+      </c>
+      <c r="D25" s="37" t="n">
+        <v>125.47</v>
+      </c>
+      <c r="E25" s="36" t="n">
+        <v>8539000</v>
+      </c>
+      <c r="F25" s="37" t="n">
+        <v>60.72</v>
+      </c>
+      <c r="G25" s="36" t="n">
+        <v>12800000</v>
+      </c>
+      <c r="H25" s="32" t="inlineStr">
+        <is>
+          <t>R0164588</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street (R0164287)</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>4531688</v>
+      </c>
+      <c r="D26" s="37" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="E26" s="36" t="n">
+        <v>2835000</v>
+      </c>
+      <c r="F26" s="37" t="n">
+        <v>101.91</v>
+      </c>
+      <c r="G26" s="36" t="n">
+        <v>2834700</v>
+      </c>
+      <c r="H26" s="32" t="inlineStr">
+        <is>
+          <t>R0164287</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 (R0180894)</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>24584873</v>
+      </c>
+      <c r="D27" s="37" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="E27" s="36" t="n">
+        <v>13214100</v>
+      </c>
+      <c r="F27" s="37" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="G27" s="36" t="n">
+        <v>15521000</v>
+      </c>
+      <c r="H27" s="32" t="inlineStr">
+        <is>
+          <t>R0180894</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="21" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="21" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="21" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F32" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>7205 Gilpin Way</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n">
+      <c r="B33" s="9" t="n">
         <v>359394</v>
       </c>
-      <c r="C28" s="9" t="n">
+      <c r="C33" s="9" t="n">
         <v>-17970</v>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D33" s="9" t="n">
         <v>341424</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E33" s="9" t="n">
         <v>-27314</v>
       </c>
-      <c r="F28" s="14" t="n">
+      <c r="F33" s="14" t="n">
         <v>314110</v>
       </c>
-      <c r="G28" s="19" t="n">
+      <c r="G33" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H28" s="14" t="n">
+      <c r="H33" s="14" t="n">
         <v>4832500</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>17608 E. 24th Dr</t>
         </is>
       </c>
-      <c r="B29" s="9" t="n">
+      <c r="B34" s="9" t="n">
         <v>209100</v>
       </c>
-      <c r="C29" s="9" t="n">
+      <c r="C34" s="9" t="n">
         <v>-10455</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D34" s="9" t="n">
         <v>198645</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E34" s="9" t="n">
         <v>-15892</v>
       </c>
-      <c r="F29" s="14" t="n">
+      <c r="F34" s="14" t="n">
         <v>182753</v>
       </c>
-      <c r="G29" s="19" t="n">
+      <c r="G34" s="19" t="n">
         <v>0.06</v>
       </c>
-      <c r="H29" s="14" t="n">
+      <c r="H34" s="14" t="n">
         <v>3050000</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>12260 Pennsylvania St</t>
         </is>
       </c>
-      <c r="B30" s="9" t="n">
+      <c r="B35" s="9" t="n">
         <v>237290</v>
       </c>
-      <c r="C30" s="9" t="n">
+      <c r="C35" s="9" t="n">
         <v>-16610</v>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="D35" s="9" t="n">
         <v>220680</v>
       </c>
-      <c r="E30" s="9" t="n">
+      <c r="E35" s="9" t="n">
         <v>-22068</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F35" s="14" t="n">
         <v>198612</v>
       </c>
-      <c r="G30" s="19" t="n">
+      <c r="G35" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H30" s="14" t="n">
+      <c r="H35" s="14" t="n">
         <v>2837000</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>6770 E. 56th Ave</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
+      <c r="B36" s="9" t="n">
         <v>115824</v>
       </c>
-      <c r="C31" s="9" t="n">
+      <c r="C36" s="9" t="n">
         <v>-5791</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D36" s="9" t="n">
         <v>110033</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E36" s="9" t="n">
         <v>-5502</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F36" s="14" t="n">
         <v>104531</v>
       </c>
-      <c r="G31" s="19" t="n">
+      <c r="G36" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H31" s="14" t="n">
+      <c r="H36" s="14" t="n">
         <v>1493302</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n">
+      <c r="B37" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C32" s="9" t="n">
+      <c r="C37" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D37" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E37" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F32" s="14" t="n">
+      <c r="F37" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G32" s="19" t="n">
+      <c r="G37" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H32" s="14" t="n">
+      <c r="H37" s="14" t="n">
         <v>2460577</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="32" t="inlineStr">
-        <is>
-          <t>18300 E 28th Ave (R0110351)</t>
-        </is>
-      </c>
-      <c r="B33" s="36" t="n">
-        <v>599228</v>
-      </c>
-      <c r="C33" s="36" t="n">
-        <v>-59923</v>
-      </c>
-      <c r="D33" s="36" t="n">
-        <v>539305</v>
-      </c>
-      <c r="E33" s="36" t="n">
-        <v>-43144</v>
-      </c>
-      <c r="F33" s="38" t="n">
-        <v>496161</v>
-      </c>
-      <c r="G33" s="39" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="H33" s="38" t="n">
-        <v>7939000</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="32" t="inlineStr">
-        <is>
-          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
-        </is>
-      </c>
-      <c r="B34" s="36" t="n">
-        <v>781250</v>
-      </c>
-      <c r="C34" s="36" t="n">
-        <v>-78125</v>
-      </c>
-      <c r="D34" s="36" t="n">
-        <v>703125</v>
-      </c>
-      <c r="E34" s="36" t="n">
-        <v>-35156</v>
-      </c>
-      <c r="F34" s="38" t="n">
-        <v>667969</v>
-      </c>
-      <c r="G34" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H34" s="38" t="n">
-        <v>8754500</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="32" t="inlineStr">
-        <is>
-          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
-        </is>
-      </c>
-      <c r="B35" s="36" t="n">
-        <v>1250000</v>
-      </c>
-      <c r="C35" s="36" t="n">
-        <v>-125000</v>
-      </c>
-      <c r="D35" s="36" t="n">
-        <v>1125000</v>
-      </c>
-      <c r="E35" s="36" t="n">
-        <v>-56250</v>
-      </c>
-      <c r="F35" s="38" t="n">
-        <v>1068750</v>
-      </c>
-      <c r="G35" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H35" s="38" t="n">
-        <v>14007200</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="32" t="inlineStr">
-        <is>
-          <t>Anchor Business Park - market (R0121833)</t>
-        </is>
-      </c>
-      <c r="B36" s="36" t="n">
-        <v>346484</v>
-      </c>
-      <c r="C36" s="36" t="n">
-        <v>-17324</v>
-      </c>
-      <c r="D36" s="36" t="n">
-        <v>329160</v>
-      </c>
-      <c r="E36" s="36" t="n">
-        <v>-49374</v>
-      </c>
-      <c r="F36" s="38" t="n">
-        <v>279786</v>
-      </c>
-      <c r="G36" s="39" t="n">
-        <v>0.07140000000000001</v>
-      </c>
-      <c r="H36" s="38" t="n">
-        <v>3919000</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="32" t="inlineStr">
-        <is>
-          <t>Anchor Business Park - actual 2024 (R0121833)</t>
-        </is>
-      </c>
-      <c r="B37" s="36" t="n">
-        <v>457717</v>
-      </c>
-      <c r="C37" s="36" t="n"/>
-      <c r="D37" s="36" t="n">
-        <v>457717</v>
-      </c>
-      <c r="E37" s="36" t="n">
-        <v>-110337</v>
-      </c>
-      <c r="F37" s="38" t="n">
-        <v>347380</v>
-      </c>
-      <c r="G37" s="39" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="H37" s="38" t="n">
-        <v>3510000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="32" t="inlineStr">
         <is>
-          <t>Anchor Business Park - actual 2023 (R0121833)</t>
+          <t>18300 E 28th Ave (R0110351)</t>
         </is>
       </c>
       <c r="B38" s="36" t="n">
-        <v>401204</v>
-      </c>
-      <c r="C38" s="36" t="n"/>
+        <v>599228</v>
+      </c>
+      <c r="C38" s="36" t="n">
+        <v>-59923</v>
+      </c>
       <c r="D38" s="36" t="n">
-        <v>401204</v>
+        <v>539305</v>
       </c>
       <c r="E38" s="36" t="n">
-        <v>-119063</v>
+        <v>-43144</v>
       </c>
       <c r="F38" s="38" t="n">
-        <v>282140</v>
+        <v>496161</v>
       </c>
       <c r="G38" s="39" t="n">
-        <v>0.099</v>
+        <v>0.0625</v>
       </c>
       <c r="H38" s="38" t="n">
-        <v>2851000</v>
+        <v>7939000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="32" t="inlineStr">
         <is>
-          <t>5977-5995 N Broadway (R0103518)</t>
+          <t>Majestic Commercenter Bldg 6 (R0111559)</t>
         </is>
       </c>
       <c r="B39" s="36" t="n">
-        <v>489879</v>
+        <v>781250</v>
       </c>
       <c r="C39" s="36" t="n">
-        <v>-39190</v>
+        <v>-78125</v>
       </c>
       <c r="D39" s="36" t="n">
-        <v>450689</v>
+        <v>703125</v>
       </c>
       <c r="E39" s="36" t="n">
-        <v>-45069</v>
+        <v>-35156</v>
       </c>
       <c r="F39" s="38" t="n">
-        <v>405620</v>
-      </c>
-      <c r="G39" s="46" t="n">
-        <v>0.07000000000000001</v>
+        <v>667969</v>
+      </c>
+      <c r="G39" s="39" t="n">
+        <v>0.07630000000000001</v>
       </c>
       <c r="H39" s="38" t="n">
-        <v>5794600</v>
+        <v>8754500</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="32" t="inlineStr">
         <is>
-          <t>5710 E. 56th Avenue - actual 2023 (R0187789)</t>
+          <t>Majestic Commercenter Bldg 7 (R0111560)</t>
         </is>
       </c>
       <c r="B40" s="36" t="n">
-        <v>640426</v>
+        <v>1250000</v>
       </c>
       <c r="C40" s="36" t="n">
-        <v>-51234</v>
+        <v>-125000</v>
       </c>
       <c r="D40" s="36" t="n">
-        <v>589192</v>
+        <v>1125000</v>
       </c>
       <c r="E40" s="36" t="n">
-        <v>-94857</v>
+        <v>-56250</v>
       </c>
       <c r="F40" s="38" t="n">
-        <v>494335</v>
-      </c>
-      <c r="G40" s="39" t="n"/>
-      <c r="H40" s="38" t="n"/>
+        <v>1068750</v>
+      </c>
+      <c r="G40" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H40" s="38" t="n">
+        <v>14007200</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="32" t="inlineStr">
         <is>
-          <t>5710 E. 56th Avenue - actual 2024 (R0187789)</t>
+          <t>Anchor Business Park - market (R0121833)</t>
         </is>
       </c>
       <c r="B41" s="36" t="n">
-        <v>725742</v>
+        <v>346484</v>
       </c>
       <c r="C41" s="36" t="n">
-        <v>-58059</v>
+        <v>-17324</v>
       </c>
       <c r="D41" s="36" t="n">
-        <v>667683</v>
+        <v>329160</v>
       </c>
       <c r="E41" s="36" t="n">
-        <v>-107192</v>
+        <v>-49374</v>
       </c>
       <c r="F41" s="38" t="n">
-        <v>560491</v>
-      </c>
-      <c r="G41" s="39" t="n"/>
-      <c r="H41" s="38" t="n"/>
+        <v>279786</v>
+      </c>
+      <c r="G41" s="39" t="n">
+        <v>0.07140000000000001</v>
+      </c>
+      <c r="H41" s="38" t="n">
+        <v>3919000</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="32" t="inlineStr">
         <is>
-          <t>5710 E. 56th Avenue - concluded, avg NOI (R0187789)</t>
-        </is>
-      </c>
-      <c r="B42" s="36" t="n"/>
+          <t>Anchor Business Park - actual 2024 (R0121833)</t>
+        </is>
+      </c>
+      <c r="B42" s="36" t="n">
+        <v>457717</v>
+      </c>
       <c r="C42" s="36" t="n"/>
-      <c r="D42" s="36" t="n"/>
-      <c r="E42" s="36" t="n"/>
+      <c r="D42" s="36" t="n">
+        <v>457717</v>
+      </c>
+      <c r="E42" s="36" t="n">
+        <v>-110337</v>
+      </c>
       <c r="F42" s="38" t="n">
-        <v>527413</v>
+        <v>347380</v>
       </c>
       <c r="G42" s="39" t="n">
-        <v>0.097</v>
+        <v>0.099</v>
       </c>
       <c r="H42" s="38" t="n">
-        <v>5440000</v>
+        <v>3510000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="32" t="inlineStr">
         <is>
-          <t>Confluent Center 70 - market proforma (R0188699)</t>
+          <t>Anchor Business Park - actual 2023 (R0121833)</t>
         </is>
       </c>
       <c r="B43" s="36" t="n">
-        <v>815099</v>
-      </c>
-      <c r="C43" s="36" t="n">
-        <v>-65208</v>
-      </c>
+        <v>401204</v>
+      </c>
+      <c r="C43" s="36" t="n"/>
       <c r="D43" s="36" t="n">
-        <v>749891</v>
+        <v>401204</v>
       </c>
       <c r="E43" s="36" t="n">
-        <v>-59991</v>
+        <v>-119063</v>
       </c>
       <c r="F43" s="38" t="n">
-        <v>689899</v>
+        <v>282140</v>
       </c>
       <c r="G43" s="39" t="n">
-        <v>0.06</v>
+        <v>0.099</v>
       </c>
       <c r="H43" s="38" t="n">
-        <v>11498000</v>
+        <v>2851000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="32" t="inlineStr">
         <is>
-          <t>Confluent Center 70 - actual 2024 NNN (R0188699)</t>
+          <t>5977-5995 N Broadway (R0103518)</t>
         </is>
       </c>
       <c r="B44" s="36" t="n">
-        <v>1536047</v>
-      </c>
-      <c r="C44" s="36" t="n"/>
+        <v>489879</v>
+      </c>
+      <c r="C44" s="36" t="n">
+        <v>-39190</v>
+      </c>
       <c r="D44" s="36" t="n">
-        <v>1536047</v>
+        <v>450689</v>
       </c>
       <c r="E44" s="36" t="n">
-        <v>-782165</v>
+        <v>-45069</v>
       </c>
       <c r="F44" s="38" t="n">
-        <v>753882</v>
-      </c>
-      <c r="G44" s="39" t="n"/>
-      <c r="H44" s="38" t="n"/>
+        <v>405620</v>
+      </c>
+      <c r="G44" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H44" s="38" t="n">
+        <v>5794600</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="32" t="inlineStr">
         <is>
-          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+          <t>5710 E. 56th Avenue - actual 2023 (R0187789)</t>
         </is>
       </c>
       <c r="B45" s="36" t="n">
-        <v>994044</v>
+        <v>640426</v>
       </c>
       <c r="C45" s="36" t="n">
-        <v>-99404</v>
+        <v>-51234</v>
       </c>
       <c r="D45" s="36" t="n">
-        <v>894639</v>
+        <v>589192</v>
       </c>
       <c r="E45" s="36" t="n">
-        <v>-44732</v>
+        <v>-94857</v>
       </c>
       <c r="F45" s="38" t="n">
-        <v>849907</v>
-      </c>
-      <c r="G45" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H45" s="38" t="n">
-        <v>11139000</v>
-      </c>
+        <v>494335</v>
+      </c>
+      <c r="G45" s="39" t="n"/>
+      <c r="H45" s="38" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="32" t="inlineStr">
         <is>
-          <t>3420 Lisbon Street (R0200721)</t>
+          <t>5710 E. 56th Avenue - actual 2024 (R0187789)</t>
         </is>
       </c>
       <c r="B46" s="36" t="n">
-        <v>398332</v>
+        <v>725742</v>
       </c>
       <c r="C46" s="36" t="n">
-        <v>-39833</v>
+        <v>-58059</v>
       </c>
       <c r="D46" s="36" t="n">
-        <v>358499</v>
+        <v>667683</v>
       </c>
       <c r="E46" s="36" t="n">
-        <v>-17925</v>
+        <v>-107192</v>
       </c>
       <c r="F46" s="38" t="n">
-        <v>340574</v>
-      </c>
-      <c r="G46" s="39" t="n">
-        <v>0.07630000000000001</v>
-      </c>
-      <c r="H46" s="38" t="n">
-        <v>4463600</v>
-      </c>
+        <v>560491</v>
+      </c>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="38" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="32" t="inlineStr">
         <is>
-          <t>5945 &amp; 5957 Broadway (R0103519) - agent capitalization</t>
+          <t>5710 E. 56th Avenue - concluded, avg NOI (R0187789)</t>
         </is>
       </c>
       <c r="B47" s="36" t="n"/>
@@ -8689,37 +10238,457 @@
       <c r="D47" s="36" t="n"/>
       <c r="E47" s="36" t="n"/>
       <c r="F47" s="38" t="n">
+        <v>527413</v>
+      </c>
+      <c r="G47" s="39" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H47" s="38" t="n">
+        <v>5440000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - market proforma (R0188699)</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n">
+        <v>815099</v>
+      </c>
+      <c r="C48" s="36" t="n">
+        <v>-65208</v>
+      </c>
+      <c r="D48" s="36" t="n">
+        <v>749891</v>
+      </c>
+      <c r="E48" s="36" t="n">
+        <v>-59991</v>
+      </c>
+      <c r="F48" s="38" t="n">
+        <v>689899</v>
+      </c>
+      <c r="G48" s="39" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H48" s="38" t="n">
+        <v>11498000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="inlineStr">
+        <is>
+          <t>Confluent Center 70 - actual 2024 NNN (R0188699)</t>
+        </is>
+      </c>
+      <c r="B49" s="36" t="n">
+        <v>1536047</v>
+      </c>
+      <c r="C49" s="36" t="n"/>
+      <c r="D49" s="36" t="n">
+        <v>1536047</v>
+      </c>
+      <c r="E49" s="36" t="n">
+        <v>-782165</v>
+      </c>
+      <c r="F49" s="38" t="n">
+        <v>753882</v>
+      </c>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="38" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 5 (R0191099)</t>
+        </is>
+      </c>
+      <c r="B50" s="36" t="n">
+        <v>994044</v>
+      </c>
+      <c r="C50" s="36" t="n">
+        <v>-99404</v>
+      </c>
+      <c r="D50" s="36" t="n">
+        <v>894639</v>
+      </c>
+      <c r="E50" s="36" t="n">
+        <v>-44732</v>
+      </c>
+      <c r="F50" s="38" t="n">
+        <v>849907</v>
+      </c>
+      <c r="G50" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H50" s="38" t="n">
+        <v>11139000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>3420 Lisbon Street (R0200721)</t>
+        </is>
+      </c>
+      <c r="B51" s="36" t="n">
+        <v>398332</v>
+      </c>
+      <c r="C51" s="36" t="n">
+        <v>-39833</v>
+      </c>
+      <c r="D51" s="36" t="n">
+        <v>358499</v>
+      </c>
+      <c r="E51" s="36" t="n">
+        <v>-17925</v>
+      </c>
+      <c r="F51" s="38" t="n">
+        <v>340574</v>
+      </c>
+      <c r="G51" s="39" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H51" s="38" t="n">
+        <v>4463600</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - actual 2023 (R0187787)</t>
+        </is>
+      </c>
+      <c r="B52" s="36" t="n">
+        <v>445925</v>
+      </c>
+      <c r="C52" s="36" t="n">
+        <v>-35674</v>
+      </c>
+      <c r="D52" s="36" t="n">
+        <v>410251</v>
+      </c>
+      <c r="E52" s="36" t="n">
+        <v>-65287</v>
+      </c>
+      <c r="F52" s="38" t="n">
+        <v>344964</v>
+      </c>
+      <c r="G52" s="46" t="n"/>
+      <c r="H52" s="38" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - actual 2024 (R0187787)</t>
+        </is>
+      </c>
+      <c r="B53" s="36" t="n">
+        <v>547382</v>
+      </c>
+      <c r="C53" s="36" t="n">
+        <v>-43791</v>
+      </c>
+      <c r="D53" s="36" t="n">
+        <v>503591</v>
+      </c>
+      <c r="E53" s="36" t="n">
+        <v>-86600</v>
+      </c>
+      <c r="F53" s="38" t="n">
+        <v>416991</v>
+      </c>
+      <c r="G53" s="46" t="n"/>
+      <c r="H53" s="38" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - concluded, avg NOI (R0187787)</t>
+        </is>
+      </c>
+      <c r="B54" s="36" t="n"/>
+      <c r="C54" s="36" t="n"/>
+      <c r="D54" s="36" t="n"/>
+      <c r="E54" s="36" t="n"/>
+      <c r="F54" s="38" t="n">
+        <v>380978</v>
+      </c>
+      <c r="G54" s="46" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="H54" s="38" t="n">
+        <v>3930000</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>9410 Heinz Way - market proforma (R0164588)</t>
+        </is>
+      </c>
+      <c r="B55" s="36" t="n">
+        <v>773465</v>
+      </c>
+      <c r="C55" s="36" t="n">
+        <v>-77347</v>
+      </c>
+      <c r="D55" s="36" t="n">
+        <v>696119</v>
+      </c>
+      <c r="E55" s="36" t="n">
+        <v>-55689</v>
+      </c>
+      <c r="F55" s="38" t="n">
+        <v>640429</v>
+      </c>
+      <c r="G55" s="46" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H55" s="38" t="n">
+        <v>8539000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - market proforma (R0180894)</t>
+        </is>
+      </c>
+      <c r="B56" s="36" t="n">
+        <v>982740</v>
+      </c>
+      <c r="C56" s="36" t="n">
+        <v>-49137</v>
+      </c>
+      <c r="D56" s="36" t="n">
+        <v>933603</v>
+      </c>
+      <c r="E56" s="36" t="n">
+        <v>-74688</v>
+      </c>
+      <c r="F56" s="38" t="n">
+        <v>858915</v>
+      </c>
+      <c r="G56" s="46" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H56" s="38" t="n">
+        <v>13214100</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - actual YE2024 (R0180894)</t>
+        </is>
+      </c>
+      <c r="B57" s="36" t="n">
+        <v>2146279</v>
+      </c>
+      <c r="C57" s="36" t="n"/>
+      <c r="D57" s="36" t="n">
+        <v>2146279</v>
+      </c>
+      <c r="E57" s="36" t="n">
+        <v>-1307976</v>
+      </c>
+      <c r="F57" s="38" t="n">
+        <v>838303</v>
+      </c>
+      <c r="G57" s="46" t="n"/>
+      <c r="H57" s="38" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - actual YE2023 (R0180894)</t>
+        </is>
+      </c>
+      <c r="B58" s="36" t="n">
+        <v>2148674</v>
+      </c>
+      <c r="C58" s="36" t="n"/>
+      <c r="D58" s="36" t="n">
+        <v>2148674</v>
+      </c>
+      <c r="E58" s="36" t="n">
+        <v>-1297289</v>
+      </c>
+      <c r="F58" s="38" t="n">
+        <v>851385</v>
+      </c>
+      <c r="G58" s="46" t="n"/>
+      <c r="H58" s="38" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - actual YE2022 (R0180894)</t>
+        </is>
+      </c>
+      <c r="B59" s="36" t="n">
+        <v>1635142</v>
+      </c>
+      <c r="C59" s="36" t="n"/>
+      <c r="D59" s="36" t="n">
+        <v>1635142</v>
+      </c>
+      <c r="E59" s="36" t="n">
+        <v>-765306</v>
+      </c>
+      <c r="F59" s="38" t="n">
+        <v>869836</v>
+      </c>
+      <c r="G59" s="46" t="n"/>
+      <c r="H59" s="38" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - stabilized, taxes in cap rate (R0157664)</t>
+        </is>
+      </c>
+      <c r="B60" s="36" t="n">
+        <v>260000</v>
+      </c>
+      <c r="C60" s="36" t="n"/>
+      <c r="D60" s="36" t="n">
+        <v>260000</v>
+      </c>
+      <c r="E60" s="36" t="n">
+        <v>-42000</v>
+      </c>
+      <c r="F60" s="38" t="n">
+        <v>218000</v>
+      </c>
+      <c r="G60" s="46" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="H60" s="38" t="n">
+        <v>2224490</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - stabilized, taxes in expenses (R0157664)</t>
+        </is>
+      </c>
+      <c r="B61" s="36" t="n">
+        <v>260000</v>
+      </c>
+      <c r="C61" s="36" t="n"/>
+      <c r="D61" s="36" t="n">
+        <v>260000</v>
+      </c>
+      <c r="E61" s="36" t="n">
+        <v>-107000</v>
+      </c>
+      <c r="F61" s="38" t="n">
+        <v>153000</v>
+      </c>
+      <c r="G61" s="46" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H61" s="38" t="n">
+        <v>2185714</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden St - owner work sheet at requested value (R0164287)</t>
+        </is>
+      </c>
+      <c r="B62" s="36" t="n">
+        <v>210590</v>
+      </c>
+      <c r="C62" s="36" t="n"/>
+      <c r="D62" s="36" t="n">
+        <v>210590</v>
+      </c>
+      <c r="E62" s="36" t="n">
+        <v>-103260</v>
+      </c>
+      <c r="F62" s="38" t="n">
+        <v>107330</v>
+      </c>
+      <c r="G62" s="46" t="n">
+        <v>0.03785</v>
+      </c>
+      <c r="H62" s="38" t="n">
+        <v>2835663</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden St - owner work sheet at assessed value (R0164287)</t>
+        </is>
+      </c>
+      <c r="B63" s="36" t="n">
+        <v>210590</v>
+      </c>
+      <c r="C63" s="36" t="n"/>
+      <c r="D63" s="36" t="n">
+        <v>210590</v>
+      </c>
+      <c r="E63" s="36" t="n">
+        <v>-158922</v>
+      </c>
+      <c r="F63" s="38" t="n">
+        <v>51668</v>
+      </c>
+      <c r="G63" s="46" t="n">
+        <v>0.01141</v>
+      </c>
+      <c r="H63" s="38" t="n">
+        <v>4531688</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="inlineStr">
+        <is>
+          <t>5945 &amp; 5957 Broadway (R0103519) - agent capitalization</t>
+        </is>
+      </c>
+      <c r="B64" s="36" t="n"/>
+      <c r="C64" s="36" t="n"/>
+      <c r="D64" s="36" t="n"/>
+      <c r="E64" s="36" t="n"/>
+      <c r="F64" s="38" t="n">
         <v>550000</v>
       </c>
-      <c r="G47" s="46" t="n">
+      <c r="G64" s="46" t="n">
         <v>0.09331</v>
       </c>
-      <c r="H47" s="38" t="n">
+      <c r="H64" s="38" t="n">
         <v>5894300</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
         <is>
           <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
         </is>
       </c>
-      <c r="B49" s="20" t="n"/>
-      <c r="C49" s="20" t="n"/>
-      <c r="D49" s="20" t="n"/>
-      <c r="E49" s="20" t="n"/>
-      <c r="F49" s="20" t="n"/>
-      <c r="G49" s="20" t="n"/>
-      <c r="H49" s="21" t="n"/>
+      <c r="B66" s="20" t="n"/>
+      <c r="C66" s="20" t="n"/>
+      <c r="D66" s="20" t="n"/>
+      <c r="E66" s="20" t="n"/>
+      <c r="F66" s="20" t="n"/>
+      <c r="G66" s="20" t="n"/>
+      <c r="H66" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A66:H66"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8731,7 +10700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -9307,22 +11276,242 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="n">
+        <v>445925</v>
+      </c>
+      <c r="C29" s="37" t="n">
+        <v>169139</v>
+      </c>
+      <c r="D29" s="41">
+        <f>B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="32" t="inlineStr">
+        <is>
+          <t>Owner-reported gross income and expenses. Expenses INCLUDE real estate taxes ($116,160); the petitioner's NOI of $344,964 strips taxes out, adds a 3% reserve and applies 8% vacancy. R0187787</t>
+        </is>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="n">
+        <v>547382</v>
+      </c>
+      <c r="C30" s="37" t="n">
+        <v>194687</v>
+      </c>
+      <c r="D30" s="41">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="32" t="inlineStr">
+        <is>
+          <t>Includes real estate taxes ($123,195); petitioner's NOI $416,991. Two-year average NOI $380,978. R0187787</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="40" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B31" s="37" t="n">
+        <v>229531</v>
+      </c>
+      <c r="C31" s="37" t="n">
+        <v>107553.3</v>
+      </c>
+      <c r="D31" s="41">
+        <f>B31-C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. TRUE NOI $121,977.70 - no debt service or depreciation. Expenses include real property taxes $69,401.60. R0157664</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B32" s="37" t="n">
+        <v>256200</v>
+      </c>
+      <c r="C32" s="37" t="n">
+        <v>91938.17999999999</v>
+      </c>
+      <c r="D32" s="41">
+        <f>B32-C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. TRUE NOI $164,261.82. Real property taxes $59,985.48. R0157664</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B33" s="37" t="n">
+        <v>258992.67</v>
+      </c>
+      <c r="C33" s="37" t="n">
+        <v>96393.71000000001</v>
+      </c>
+      <c r="D33" s="41">
+        <f>B33-C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. NOI $162,598.96; net income after $5,791.72 of capital improvements = $156,807.24. R0157664</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="n">
+        <v>289136.52</v>
+      </c>
+      <c r="C34" s="37" t="n">
+        <v>74778.87</v>
+      </c>
+      <c r="D34" s="41">
+        <f>B34-C34</f>
+        <v/>
+      </c>
+      <c r="E34" s="32" t="inlineStr">
+        <is>
+          <t>Accrual. NOI $214,357.65; net income after $2,642.04 of capital improvements = $211,715.61. R0157664</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B35" s="37" t="n">
+        <v>2146279</v>
+      </c>
+      <c r="C35" s="37" t="n">
+        <v>1307976</v>
+      </c>
+      <c r="D35" s="41">
+        <f>B35-C35</f>
+        <v/>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>Actual. TRUE NOI $838,303 ($5.13 PSF). Expenses include property taxes $912,402 and $1,118 of non-recoverable expense. 100% occupied. R0180894</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B36" s="37" t="n">
+        <v>2148674</v>
+      </c>
+      <c r="C36" s="37" t="n">
+        <v>1297289</v>
+      </c>
+      <c r="D36" s="41">
+        <f>B36-C36</f>
+        <v/>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>Actual. NOI $851,385 ($5.21 PSF). Property taxes $923,586; non-recoverable $17,221. R0180894</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B37" s="37" t="n">
+        <v>1635142</v>
+      </c>
+      <c r="C37" s="37" t="n">
+        <v>765306</v>
+      </c>
+      <c r="D37" s="41">
+        <f>B37-C37</f>
+        <v/>
+      </c>
+      <c r="E37" s="32" t="inlineStr">
+        <is>
+          <t>Actual. NOI $869,836 ($5.32 PSF). Property taxes $533,285; non-recoverable $8,751. R0180894</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t>2850 Walden Street - 2025 (owner schedule)</t>
+        </is>
+      </c>
+      <c r="B38" s="37" t="n">
+        <v>210589</v>
+      </c>
+      <c r="C38" s="37" t="n">
+        <v>158923</v>
+      </c>
+      <c r="D38" s="41">
+        <f>B38-C38</f>
+        <v/>
+      </c>
+      <c r="E38" s="32" t="inlineStr">
+        <is>
+          <t>Owner's rent schedule. The only expense the owner bears is property tax; the tenant pays everything else. Net $51,666 - a 1.14% return on the assessor's $4,531,688. R0164287</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="21" t="n"/>
+      <c r="B40" s="20" t="n"/>
+      <c r="C40" s="20" t="n"/>
+      <c r="D40" s="20" t="n"/>
+      <c r="E40" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A40:E40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9334,7 +11523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E516"/>
+  <dimension ref="A1:E648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -20601,6 +22790,2952 @@
       <c r="E516" s="32" t="inlineStr">
         <is>
           <t>Printed total: $205,776.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B517" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C517" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D517" s="37" t="n">
+        <v>116160</v>
+      </c>
+      <c r="E517" s="32" t="inlineStr">
+        <is>
+          <t>$3.32 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B518" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C518" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Reimbursable</t>
+        </is>
+      </c>
+      <c r="D518" s="37" t="n">
+        <v>51894</v>
+      </c>
+      <c r="E518" s="32" t="inlineStr">
+        <is>
+          <t>$1.48 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B519" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C519" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Non-Reimbursable</t>
+        </is>
+      </c>
+      <c r="D519" s="37" t="n">
+        <v>1085</v>
+      </c>
+      <c r="E519" s="32" t="inlineStr">
+        <is>
+          <t>$0.03 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B520" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C520" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D520" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E520" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2023</t>
+        </is>
+      </c>
+      <c r="B521" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C521" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D521" s="43">
+        <f>SUM(D517:D520)</f>
+        <v/>
+      </c>
+      <c r="E521" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $169,139.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B522" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C522" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D522" s="37" t="n">
+        <v>123195</v>
+      </c>
+      <c r="E522" s="32" t="inlineStr">
+        <is>
+          <t>$3.52 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B523" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C523" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Reimbursable</t>
+        </is>
+      </c>
+      <c r="D523" s="37" t="n">
+        <v>65115</v>
+      </c>
+      <c r="E523" s="32" t="inlineStr">
+        <is>
+          <t>$1.86 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B524" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C524" s="32" t="inlineStr">
+        <is>
+          <t>CAM - Non-Reimbursable</t>
+        </is>
+      </c>
+      <c r="D524" s="37" t="n">
+        <v>6377</v>
+      </c>
+      <c r="E524" s="32" t="inlineStr">
+        <is>
+          <t>$0.18 PSF</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B525" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C525" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D525" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E525" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue - CY2024</t>
+        </is>
+      </c>
+      <c r="B526" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C526" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D526" s="43">
+        <f>SUM(D522:D525)</f>
+        <v/>
+      </c>
+      <c r="E526" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $194,687.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B527" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C527" s="32" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="D527" s="37" t="n">
+        <v>229531</v>
+      </c>
+      <c r="E527" s="32" t="inlineStr">
+        <is>
+          <t>No CAM reimbursements or misc income reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B528" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C528" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D528" s="43">
+        <f>SUM(D527:D527)</f>
+        <v/>
+      </c>
+      <c r="E528" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $229,531.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B529" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C529" s="32" t="inlineStr">
+        <is>
+          <t>Real Property Taxes</t>
+        </is>
+      </c>
+      <c r="D529" s="37" t="n">
+        <v>69401.60000000001</v>
+      </c>
+      <c r="E529" s="32" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B530" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C530" s="32" t="inlineStr">
+        <is>
+          <t>Trash Services</t>
+        </is>
+      </c>
+      <c r="D530" s="37" t="n">
+        <v>8500.75</v>
+      </c>
+      <c r="E530" s="32" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B531" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C531" s="32" t="inlineStr">
+        <is>
+          <t>Fire / Life &amp; Safety R&amp;M</t>
+        </is>
+      </c>
+      <c r="D531" s="37" t="n">
+        <v>8299.799999999999</v>
+      </c>
+      <c r="E531" s="32" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B532" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C532" s="32" t="inlineStr">
+        <is>
+          <t>Exterior R&amp;M</t>
+        </is>
+      </c>
+      <c r="D532" s="37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E532" s="32" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B533" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C533" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D533" s="37" t="n">
+        <v>3438.85</v>
+      </c>
+      <c r="E533" s="32" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B534" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C534" s="32" t="inlineStr">
+        <is>
+          <t>Landscape Services</t>
+        </is>
+      </c>
+      <c r="D534" s="37" t="n">
+        <v>3350</v>
+      </c>
+      <c r="E534" s="32" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B535" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C535" s="32" t="inlineStr">
+        <is>
+          <t>Property Insurance</t>
+        </is>
+      </c>
+      <c r="D535" s="37" t="n">
+        <v>1634.57</v>
+      </c>
+      <c r="E535" s="32" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B536" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C536" s="32" t="inlineStr">
+        <is>
+          <t>Partnership Accounting</t>
+        </is>
+      </c>
+      <c r="D536" s="37" t="n">
+        <v>1550</v>
+      </c>
+      <c r="E536" s="32" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B537" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C537" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal Services</t>
+        </is>
+      </c>
+      <c r="D537" s="37" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E537" s="32" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B538" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C538" s="32" t="inlineStr">
+        <is>
+          <t>Maintenance &amp; Repairs</t>
+        </is>
+      </c>
+      <c r="D538" s="37" t="n">
+        <v>819.88</v>
+      </c>
+      <c r="E538" s="32" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B539" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C539" s="32" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="D539" s="37" t="n">
+        <v>712.77</v>
+      </c>
+      <c r="E539" s="32" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B540" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C540" s="32" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="D540" s="37" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="E540" s="32" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B541" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C541" s="32" t="inlineStr">
+        <is>
+          <t>Merchant Account</t>
+        </is>
+      </c>
+      <c r="D541" s="37" t="n">
+        <v>221.71</v>
+      </c>
+      <c r="E541" s="32" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B542" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C542" s="32" t="inlineStr">
+        <is>
+          <t>Interior Unit R&amp;M</t>
+        </is>
+      </c>
+      <c r="D542" s="37" t="n">
+        <v>175</v>
+      </c>
+      <c r="E542" s="32" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B543" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C543" s="32" t="inlineStr">
+        <is>
+          <t>Marketing Supplies</t>
+        </is>
+      </c>
+      <c r="D543" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="E543" s="32" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B544" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C544" s="32" t="inlineStr">
+        <is>
+          <t>Partnership Admin</t>
+        </is>
+      </c>
+      <c r="D544" s="37" t="n">
+        <v>20</v>
+      </c>
+      <c r="E544" s="32" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B545" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C545" s="32" t="inlineStr">
+        <is>
+          <t>Electrical R&amp;M</t>
+        </is>
+      </c>
+      <c r="D545" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E545" s="32" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B546" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C546" s="32" t="inlineStr">
+        <is>
+          <t>HVAC R&amp;M</t>
+        </is>
+      </c>
+      <c r="D546" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E546" s="32" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B547" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C547" s="32" t="inlineStr">
+        <is>
+          <t>Plumbing R&amp;M</t>
+        </is>
+      </c>
+      <c r="D547" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E547" s="32" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B548" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C548" s="32" t="inlineStr">
+        <is>
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D548" s="37" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E548" s="32" t="inlineStr">
+        <is>
+          <t>Credit</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2024</t>
+        </is>
+      </c>
+      <c r="B549" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C549" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D549" s="43">
+        <f>SUM(D529:D548)</f>
+        <v/>
+      </c>
+      <c r="E549" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $107,553.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B550" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C550" s="32" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="D550" s="37" t="n">
+        <v>256200</v>
+      </c>
+      <c r="E550" s="32" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B551" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C551" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D551" s="43">
+        <f>SUM(D550:D550)</f>
+        <v/>
+      </c>
+      <c r="E551" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $256,200.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B552" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C552" s="32" t="inlineStr">
+        <is>
+          <t>Real Property Taxes</t>
+        </is>
+      </c>
+      <c r="D552" s="37" t="n">
+        <v>59985.48</v>
+      </c>
+      <c r="E552" s="32" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B553" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C553" s="32" t="inlineStr">
+        <is>
+          <t>Trash Services</t>
+        </is>
+      </c>
+      <c r="D553" s="37" t="n">
+        <v>9561.9</v>
+      </c>
+      <c r="E553" s="32" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B554" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C554" s="32" t="inlineStr">
+        <is>
+          <t>Property Insurance</t>
+        </is>
+      </c>
+      <c r="D554" s="37" t="n">
+        <v>5867.85</v>
+      </c>
+      <c r="E554" s="32" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B555" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C555" s="32" t="inlineStr">
+        <is>
+          <t>Fire / Life &amp; Safety R&amp;M</t>
+        </is>
+      </c>
+      <c r="D555" s="37" t="n">
+        <v>3870.75</v>
+      </c>
+      <c r="E555" s="32" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B556" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C556" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal Services</t>
+        </is>
+      </c>
+      <c r="D556" s="37" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E556" s="32" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B557" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C557" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D557" s="37" t="n">
+        <v>2311.97</v>
+      </c>
+      <c r="E557" s="32" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B558" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C558" s="32" t="inlineStr">
+        <is>
+          <t>Landscape Services</t>
+        </is>
+      </c>
+      <c r="D558" s="37" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E558" s="32" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B559" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C559" s="32" t="inlineStr">
+        <is>
+          <t>Plumbing R&amp;M</t>
+        </is>
+      </c>
+      <c r="D559" s="37" t="n">
+        <v>1094.49</v>
+      </c>
+      <c r="E559" s="32" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B560" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C560" s="32" t="inlineStr">
+        <is>
+          <t>Electrical R&amp;M</t>
+        </is>
+      </c>
+      <c r="D560" s="37" t="n">
+        <v>990</v>
+      </c>
+      <c r="E560" s="32" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B561" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C561" s="32" t="inlineStr">
+        <is>
+          <t>Partnership Accounting</t>
+        </is>
+      </c>
+      <c r="D561" s="37" t="n">
+        <v>800</v>
+      </c>
+      <c r="E561" s="32" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B562" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C562" s="32" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="D562" s="37" t="n">
+        <v>760.15</v>
+      </c>
+      <c r="E562" s="32" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B563" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C563" s="32" t="inlineStr">
+        <is>
+          <t>Interior Unit R&amp;M</t>
+        </is>
+      </c>
+      <c r="D563" s="37" t="n">
+        <v>618</v>
+      </c>
+      <c r="E563" s="32" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B564" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C564" s="32" t="inlineStr">
+        <is>
+          <t>HVAC R&amp;M</t>
+        </is>
+      </c>
+      <c r="D564" s="37" t="n">
+        <v>480</v>
+      </c>
+      <c r="E564" s="32" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B565" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C565" s="32" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="D565" s="37" t="n">
+        <v>316.05</v>
+      </c>
+      <c r="E565" s="32" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B566" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C566" s="32" t="inlineStr">
+        <is>
+          <t>Merchant Account</t>
+        </is>
+      </c>
+      <c r="D566" s="37" t="n">
+        <v>281.54</v>
+      </c>
+      <c r="E566" s="32" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2023</t>
+        </is>
+      </c>
+      <c r="B567" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C567" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D567" s="43">
+        <f>SUM(D552:D566)</f>
+        <v/>
+      </c>
+      <c r="E567" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $91,938.18</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B568" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C568" s="32" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="D568" s="37" t="n">
+        <v>255992.67</v>
+      </c>
+      <c r="E568" s="32" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B569" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C569" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D569" s="37" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E569" s="32" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B570" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C570" s="32" t="inlineStr">
+        <is>
+          <t>Damages</t>
+        </is>
+      </c>
+      <c r="D570" s="37" t="n">
+        <v>500</v>
+      </c>
+      <c r="E570" s="32" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B571" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C571" s="32" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D571" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E571" s="32" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B572" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C572" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D572" s="43">
+        <f>SUM(D568:D571)</f>
+        <v/>
+      </c>
+      <c r="E572" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $258,992.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B573" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C573" s="32" t="inlineStr">
+        <is>
+          <t>Real Property Taxes</t>
+        </is>
+      </c>
+      <c r="D573" s="37" t="n">
+        <v>66104.78</v>
+      </c>
+      <c r="E573" s="32" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B574" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C574" s="32" t="inlineStr">
+        <is>
+          <t>Trash Services</t>
+        </is>
+      </c>
+      <c r="D574" s="37" t="n">
+        <v>8303.969999999999</v>
+      </c>
+      <c r="E574" s="32" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B575" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C575" s="32" t="inlineStr">
+        <is>
+          <t>Property Insurance</t>
+        </is>
+      </c>
+      <c r="D575" s="37" t="n">
+        <v>5276</v>
+      </c>
+      <c r="E575" s="32" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B576" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C576" s="32" t="inlineStr">
+        <is>
+          <t>Landscape Services</t>
+        </is>
+      </c>
+      <c r="D576" s="37" t="n">
+        <v>4280</v>
+      </c>
+      <c r="E576" s="32" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B577" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C577" s="32" t="inlineStr">
+        <is>
+          <t>Plumbing R&amp;M</t>
+        </is>
+      </c>
+      <c r="D577" s="37" t="n">
+        <v>4115</v>
+      </c>
+      <c r="E577" s="32" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B578" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C578" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D578" s="37" t="n">
+        <v>3043.11</v>
+      </c>
+      <c r="E578" s="32" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B579" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C579" s="32" t="inlineStr">
+        <is>
+          <t>Exterior R&amp;M</t>
+        </is>
+      </c>
+      <c r="D579" s="37" t="n">
+        <v>2333.33</v>
+      </c>
+      <c r="E579" s="32" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B580" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C580" s="32" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="D580" s="37" t="n">
+        <v>887.54</v>
+      </c>
+      <c r="E580" s="32" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B581" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C581" s="32" t="inlineStr">
+        <is>
+          <t>Interior Common Area R&amp;M</t>
+        </is>
+      </c>
+      <c r="D581" s="37" t="n">
+        <v>780</v>
+      </c>
+      <c r="E581" s="32" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B582" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C582" s="32" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="D582" s="37" t="n">
+        <v>633.98</v>
+      </c>
+      <c r="E582" s="32" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B583" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C583" s="32" t="inlineStr">
+        <is>
+          <t>Electrical R&amp;M</t>
+        </is>
+      </c>
+      <c r="D583" s="37" t="n">
+        <v>611</v>
+      </c>
+      <c r="E583" s="32" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B584" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C584" s="32" t="inlineStr">
+        <is>
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D584" s="37" t="n">
+        <v>25</v>
+      </c>
+      <c r="E584" s="32" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B585" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C585" s="32" t="inlineStr">
+        <is>
+          <t>Interior Unit R&amp;M</t>
+        </is>
+      </c>
+      <c r="D585" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E585" s="32" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B586" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C586" s="32" t="inlineStr">
+        <is>
+          <t>HVAC R&amp;M</t>
+        </is>
+      </c>
+      <c r="D586" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E586" s="32" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B587" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C587" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal Services</t>
+        </is>
+      </c>
+      <c r="D587" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E587" s="32" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B588" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C588" s="32" t="inlineStr">
+        <is>
+          <t>Merchant Account</t>
+        </is>
+      </c>
+      <c r="D588" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E588" s="32" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2022</t>
+        </is>
+      </c>
+      <c r="B589" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C589" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D589" s="43">
+        <f>SUM(D573:D588)</f>
+        <v/>
+      </c>
+      <c r="E589" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $96,393.71. NOTE: the agent's own Income Analysis reports 2022 total income of $258,492 (omitting the $500 damages) and real estate taxes of $59,147 against the $66,104.78 on this statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B590" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C590" s="32" t="inlineStr">
+        <is>
+          <t>Market Rent</t>
+        </is>
+      </c>
+      <c r="D590" s="37" t="n">
+        <v>282764.52</v>
+      </c>
+      <c r="E590" s="32" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B591" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C591" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D591" s="37" t="n">
+        <v>3863.06</v>
+      </c>
+      <c r="E591" s="32" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B592" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C592" s="32" t="inlineStr">
+        <is>
+          <t>Damages</t>
+        </is>
+      </c>
+      <c r="D592" s="37" t="n">
+        <v>2392.04</v>
+      </c>
+      <c r="E592" s="32" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B593" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C593" s="32" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D593" s="37" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="E593" s="32" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B594" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C594" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D594" s="43">
+        <f>SUM(D590:D593)</f>
+        <v/>
+      </c>
+      <c r="E594" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $289,136.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B595" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C595" s="32" t="inlineStr">
+        <is>
+          <t>Real Property Taxes</t>
+        </is>
+      </c>
+      <c r="D595" s="37" t="n">
+        <v>48283.72</v>
+      </c>
+      <c r="E595" s="32" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B596" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C596" s="32" t="inlineStr">
+        <is>
+          <t>Trash Services</t>
+        </is>
+      </c>
+      <c r="D596" s="37" t="n">
+        <v>6710.19</v>
+      </c>
+      <c r="E596" s="32" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B597" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C597" s="32" t="inlineStr">
+        <is>
+          <t>Property Insurance</t>
+        </is>
+      </c>
+      <c r="D597" s="37" t="n">
+        <v>4893</v>
+      </c>
+      <c r="E597" s="32" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B598" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C598" s="32" t="inlineStr">
+        <is>
+          <t>Landscape Services</t>
+        </is>
+      </c>
+      <c r="D598" s="37" t="n">
+        <v>3875</v>
+      </c>
+      <c r="E598" s="32" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B599" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C599" s="32" t="inlineStr">
+        <is>
+          <t>Water &amp; Sewer</t>
+        </is>
+      </c>
+      <c r="D599" s="37" t="n">
+        <v>3344.39</v>
+      </c>
+      <c r="E599" s="32" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B600" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C600" s="32" t="inlineStr">
+        <is>
+          <t>Interior Common Area R&amp;M</t>
+        </is>
+      </c>
+      <c r="D600" s="37" t="n">
+        <v>2923</v>
+      </c>
+      <c r="E600" s="32" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B601" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C601" s="32" t="inlineStr">
+        <is>
+          <t>Plumbing R&amp;M</t>
+        </is>
+      </c>
+      <c r="D601" s="37" t="n">
+        <v>1144</v>
+      </c>
+      <c r="E601" s="32" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B602" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C602" s="32" t="inlineStr">
+        <is>
+          <t>Snow Removal Services</t>
+        </is>
+      </c>
+      <c r="D602" s="37" t="n">
+        <v>870</v>
+      </c>
+      <c r="E602" s="32" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B603" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C603" s="32" t="inlineStr">
+        <is>
+          <t>Interior Unit R&amp;M</t>
+        </is>
+      </c>
+      <c r="D603" s="37" t="n">
+        <v>846</v>
+      </c>
+      <c r="E603" s="32" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B604" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C604" s="32" t="inlineStr">
+        <is>
+          <t>Electric</t>
+        </is>
+      </c>
+      <c r="D604" s="37" t="n">
+        <v>648.33</v>
+      </c>
+      <c r="E604" s="32" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B605" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C605" s="32" t="inlineStr">
+        <is>
+          <t>Merchant Account</t>
+        </is>
+      </c>
+      <c r="D605" s="37" t="n">
+        <v>408.51</v>
+      </c>
+      <c r="E605" s="32" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B606" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C606" s="32" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="D606" s="37" t="n">
+        <v>322.98</v>
+      </c>
+      <c r="E606" s="32" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B607" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C607" s="32" t="inlineStr">
+        <is>
+          <t>HVAC R&amp;M</t>
+        </is>
+      </c>
+      <c r="D607" s="37" t="n">
+        <v>280</v>
+      </c>
+      <c r="E607" s="32" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B608" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C608" s="32" t="inlineStr">
+        <is>
+          <t>Exterior R&amp;M</t>
+        </is>
+      </c>
+      <c r="D608" s="37" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="E608" s="32" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B609" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C609" s="32" t="inlineStr">
+        <is>
+          <t>Bank Fees</t>
+        </is>
+      </c>
+      <c r="D609" s="37" t="n">
+        <v>31</v>
+      </c>
+      <c r="E609" s="32" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B610" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C610" s="32" t="inlineStr">
+        <is>
+          <t>Electrical R&amp;M</t>
+        </is>
+      </c>
+      <c r="D610" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E610" s="32" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="32" t="inlineStr">
+        <is>
+          <t>Alpine Park II - CY2021</t>
+        </is>
+      </c>
+      <c r="B611" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C611" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D611" s="43">
+        <f>SUM(D595:D610)</f>
+        <v/>
+      </c>
+      <c r="E611" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $74,778.87</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B612" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C612" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D612" s="37" t="n">
+        <v>921507</v>
+      </c>
+      <c r="E612" s="32" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B613" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C613" s="32" t="inlineStr">
+        <is>
+          <t>Recoverable Income</t>
+        </is>
+      </c>
+      <c r="D613" s="37" t="n">
+        <v>1224772</v>
+      </c>
+      <c r="E613" s="32" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B614" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C614" s="32" t="inlineStr">
+        <is>
+          <t>Vacancy Loss</t>
+        </is>
+      </c>
+      <c r="D614" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E614" s="32" t="inlineStr">
+        <is>
+          <t>100% occupied</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B615" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C615" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D615" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E615" s="32" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B616" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C616" s="40" t="inlineStr">
+        <is>
+          <t>EFFECTIVE GROSS INCOME</t>
+        </is>
+      </c>
+      <c r="D616" s="43">
+        <f>SUM(D612:D615)</f>
+        <v/>
+      </c>
+      <c r="E616" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $2,146,279.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B617" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C617" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="D617" s="37" t="n">
+        <v>912402</v>
+      </c>
+      <c r="E617" s="32" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B618" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C618" s="32" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="D618" s="37" t="n">
+        <v>394456</v>
+      </c>
+      <c r="E618" s="32" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B619" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C619" s="32" t="inlineStr">
+        <is>
+          <t>Non-Recoverable Expenses</t>
+        </is>
+      </c>
+      <c r="D619" s="37" t="n">
+        <v>1118</v>
+      </c>
+      <c r="E619" s="32" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B620" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C620" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="D620" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E620" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B621" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C621" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D621" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E621" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2024</t>
+        </is>
+      </c>
+      <c r="B622" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C622" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D622" s="43">
+        <f>SUM(D617:D621)</f>
+        <v/>
+      </c>
+      <c r="E622" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,307,976.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B623" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C623" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D623" s="37" t="n">
+        <v>921507</v>
+      </c>
+      <c r="E623" s="32" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B624" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C624" s="32" t="inlineStr">
+        <is>
+          <t>Recoverable Income</t>
+        </is>
+      </c>
+      <c r="D624" s="37" t="n">
+        <v>1227167</v>
+      </c>
+      <c r="E624" s="32" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B625" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C625" s="32" t="inlineStr">
+        <is>
+          <t>Vacancy Loss</t>
+        </is>
+      </c>
+      <c r="D625" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E625" s="32" t="inlineStr">
+        <is>
+          <t>100% occupied</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B626" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C626" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D626" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E626" s="32" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B627" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C627" s="40" t="inlineStr">
+        <is>
+          <t>EFFECTIVE GROSS INCOME</t>
+        </is>
+      </c>
+      <c r="D627" s="43">
+        <f>SUM(D623:D626)</f>
+        <v/>
+      </c>
+      <c r="E627" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $2,148,674.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B628" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C628" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="D628" s="37" t="n">
+        <v>923586</v>
+      </c>
+      <c r="E628" s="32" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B629" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C629" s="32" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="D629" s="37" t="n">
+        <v>356482</v>
+      </c>
+      <c r="E629" s="32" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B630" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C630" s="32" t="inlineStr">
+        <is>
+          <t>Non-Recoverable Expenses</t>
+        </is>
+      </c>
+      <c r="D630" s="37" t="n">
+        <v>17221</v>
+      </c>
+      <c r="E630" s="32" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B631" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C631" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="D631" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E631" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B632" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C632" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D632" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E632" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2023</t>
+        </is>
+      </c>
+      <c r="B633" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C633" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D633" s="43">
+        <f>SUM(D628:D632)</f>
+        <v/>
+      </c>
+      <c r="E633" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,297,289.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B634" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C634" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D634" s="37" t="n">
+        <v>837490</v>
+      </c>
+      <c r="E634" s="32" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B635" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C635" s="32" t="inlineStr">
+        <is>
+          <t>Recoverable Income</t>
+        </is>
+      </c>
+      <c r="D635" s="37" t="n">
+        <v>797652</v>
+      </c>
+      <c r="E635" s="32" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B636" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C636" s="32" t="inlineStr">
+        <is>
+          <t>Vacancy Loss</t>
+        </is>
+      </c>
+      <c r="D636" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E636" s="32" t="inlineStr">
+        <is>
+          <t>100% occupied</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B637" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C637" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D637" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E637" s="32" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B638" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C638" s="40" t="inlineStr">
+        <is>
+          <t>EFFECTIVE GROSS INCOME</t>
+        </is>
+      </c>
+      <c r="D638" s="43">
+        <f>SUM(D634:D637)</f>
+        <v/>
+      </c>
+      <c r="E638" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $1,635,142.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B639" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C639" s="32" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="D639" s="37" t="n">
+        <v>533285</v>
+      </c>
+      <c r="E639" s="32" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B640" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C640" s="32" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
+      <c r="D640" s="37" t="n">
+        <v>223270</v>
+      </c>
+      <c r="E640" s="32" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B641" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C641" s="32" t="inlineStr">
+        <is>
+          <t>Non-Recoverable Expenses</t>
+        </is>
+      </c>
+      <c r="D641" s="37" t="n">
+        <v>8751</v>
+      </c>
+      <c r="E641" s="32" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B642" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C642" s="32" t="inlineStr">
+        <is>
+          <t>Management Fee</t>
+        </is>
+      </c>
+      <c r="D642" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E642" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B643" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C643" s="32" t="inlineStr">
+        <is>
+          <t>Reserves for Replacement</t>
+        </is>
+      </c>
+      <c r="D643" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E643" s="32" t="inlineStr">
+        <is>
+          <t>Reported as $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="32" t="inlineStr">
+        <is>
+          <t>Park 70 - YE2022</t>
+        </is>
+      </c>
+      <c r="B644" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C644" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D644" s="43">
+        <f>SUM(D639:D643)</f>
+        <v/>
+      </c>
+      <c r="E644" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $765,306.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street - 2025 (owner schedule)</t>
+        </is>
+      </c>
+      <c r="B645" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C645" s="32" t="inlineStr">
+        <is>
+          <t>Scheduled rent - single tenant</t>
+        </is>
+      </c>
+      <c r="D645" s="37" t="n">
+        <v>210589</v>
+      </c>
+      <c r="E645" s="32" t="inlineStr">
+        <is>
+          <t>$7.57 PSF on 27,819 SF</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street - 2025 (owner schedule)</t>
+        </is>
+      </c>
+      <c r="B646" s="42" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C646" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D646" s="43">
+        <f>SUM(D645:D645)</f>
+        <v/>
+      </c>
+      <c r="E646" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $210,589.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street - 2025 (owner schedule)</t>
+        </is>
+      </c>
+      <c r="B647" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C647" s="32" t="inlineStr">
+        <is>
+          <t>Real property tax (the only owner-borne expense)</t>
+        </is>
+      </c>
+      <c r="D647" s="37" t="n">
+        <v>158923</v>
+      </c>
+      <c r="E647" s="32" t="inlineStr">
+        <is>
+          <t>Tenant pays all other expenses and improvements per the lease</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="32" t="inlineStr">
+        <is>
+          <t>2850 Walden Street - 2025 (owner schedule)</t>
+        </is>
+      </c>
+      <c r="B648" s="42" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C648" s="40" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="D648" s="43">
+        <f>SUM(D647:D647)</f>
+        <v/>
+      </c>
+      <c r="E648" s="32" t="inlineStr">
+        <is>
+          <t>Printed total: $158,923.00</t>
         </is>
       </c>
     </row>
@@ -20619,7 +25754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -21350,6 +26485,67 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation - 'KEW East, West &amp; Park' industrial/flex buildings, Commerce City (2025/2026 LOA):</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation</t>
+        </is>
+      </c>
+      <c r="B35" s="32" t="inlineStr">
+        <is>
+          <t>R0187787</t>
+        </is>
+      </c>
+      <c r="C35" s="32" t="inlineStr">
+        <is>
+          <t>5690 E. 56th Avenue, Commerce City</t>
+        </is>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E35" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>KEW Realty Corporation</t>
+        </is>
+      </c>
+      <c r="B36" s="32" t="inlineStr">
+        <is>
+          <t>R0187789</t>
+        </is>
+      </c>
+      <c r="C36" s="32" t="inlineStr">
+        <is>
+          <t>5710 E. 56th Avenue, Commerce City</t>
+        </is>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E36" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -22,13 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.###"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);-"/>
+    <numFmt numFmtId="168" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +74,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00808080"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -183,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -270,6 +276,39 @@
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -635,7 +674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -660,7 +699,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,35 +1008,193 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>R0180834_584_Mega_or_447_Cold_Storage_rent_roll_and_income_statement.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>Rent roll + income statement (accrual)</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Center (ct912501) — 553,757 SF</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>RR as of 01/01/2025; IS Dec-2024 YTD</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Owner/manager report (Yardi "ysi_is" tree); printed 06/05/2025</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>R0212546_PL_Showing_8.07PSF_Mega_on_absolute_net_lease_1983_YOC.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss, 2 years (accrual)</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>2780 North Tower Road, LLC — 377,729 SF</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>FY2024 &amp; FY2023</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>Owner (QuickBooks); printed 03/17/2025 — Petitioner's Exhibit G</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>R0212546_2023_and_2024_Operating_Income_statement_showing_8PSF_for_377729_single_tenant_mega_built_1983_on_larger_lot.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="32" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss, 2 years (accrual)</t>
+        </is>
+      </c>
+      <c r="D17" s="32" t="inlineStr">
+        <is>
+          <t>2780 North Tower Road, LLC — 377,729 SF</t>
+        </is>
+      </c>
+      <c r="E17" s="32" t="inlineStr">
+        <is>
+          <t>FY2024 &amp; FY2023</t>
+        </is>
+      </c>
+      <c r="F17" s="32" t="inlineStr">
+        <is>
+          <t>Same P&amp;L as doc #11 — duplicate content, different file</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>R0083953_200000_SF_1985_YOC_Mega_Rent_Roll_20212024.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="inlineStr">
+        <is>
+          <t>Commercial rent rolls, 4 dates</t>
+        </is>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter / WPC ABC LLC — 20901 E. 32nd Pkwy</t>
+        </is>
+      </c>
+      <c r="E18" s="32" t="inlineStr">
+        <is>
+          <t>06/2021, 06/2022, 01/2023, 06/2024</t>
+        </is>
+      </c>
+      <c r="F18" s="32" t="inlineStr">
+        <is>
+          <t>Colliers International (users David, Andy, Jean)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>R0083953_200000_SF_1985_YOC_Mega_Operating_Income_Statement.pdf</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="inlineStr">
+        <is>
+          <t>Income statements + budget/variance</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter / WPC ABC LLC — 20901 E. 32nd Pkwy</t>
+        </is>
+      </c>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>FY2024, FY2023, FY2022</t>
+        </is>
+      </c>
+      <c r="F19" s="32" t="inlineStr">
+        <is>
+          <t>Property manager (Colliers) operating statements</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>R0083953 rent roll: the 6/30/2024 recap page shows Peco Pallet (455-C-CU) expiring 3/31/2030 while the Colliers rent roll for the same date shows 3/31/2025; both dates are reproduced as printed. Docs #11 and #12 are byte-different files with identical content (same P&amp;L), so FY2024/FY2023 for 2780 N. Tower Rd is entered once. No assessor or petitioner opinion of value appears in any of these five documents, so no rows were added to 'Assessments &amp; Valuation'.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1250,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2052,8 +2247,296 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>R0180834</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>R0180834</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Center (ct912501)</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>—  (not stated in document)</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>Adams (assumed)</t>
+        </is>
+      </c>
+      <c r="J13" s="32" t="inlineStr">
+        <is>
+          <t>—  (not stated in document)</t>
+        </is>
+      </c>
+      <c r="K13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse / Distribution</t>
+        </is>
+      </c>
+      <c r="M13" s="32" t="inlineStr">
+        <is>
+          <t>Single-tenant</t>
+        </is>
+      </c>
+      <c r="N13" s="32" t="n"/>
+      <c r="O13" s="32" t="n"/>
+      <c r="P13" s="34" t="n"/>
+      <c r="Q13" s="34" t="n">
+        <v>553757</v>
+      </c>
+      <c r="R13" s="32" t="n"/>
+      <c r="S13" s="32" t="n"/>
+      <c r="T13" s="32" t="inlineStr">
+        <is>
+          <t>100.0% occupied / 100.0% leased</t>
+        </is>
+      </c>
+      <c r="U13" s="35" t="n"/>
+      <c r="V13" s="32" t="n"/>
+      <c r="W13" s="35" t="inlineStr">
+        <is>
+          <t>—  (Yardi-managed; preparer not named)</t>
+        </is>
+      </c>
+      <c r="X13" s="32" t="inlineStr">
+        <is>
+          <t>R0180834 rent roll &amp; income statement.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>R0212546</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>R0212546</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>2780 North Tower Road</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Road</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>Aurora (est.)</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="32" t="inlineStr">
+        <is>
+          <t>2780 North Tower Road, LLC</t>
+        </is>
+      </c>
+      <c r="K14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (mega)</t>
+        </is>
+      </c>
+      <c r="M14" s="32" t="inlineStr">
+        <is>
+          <t>Single-tenant</t>
+        </is>
+      </c>
+      <c r="N14" s="32" t="n"/>
+      <c r="O14" s="32" t="n"/>
+      <c r="P14" s="34" t="n"/>
+      <c r="Q14" s="34" t="n">
+        <v>377729</v>
+      </c>
+      <c r="R14" s="32" t="n">
+        <v>1983</v>
+      </c>
+      <c r="S14" s="32" t="n"/>
+      <c r="T14" s="32" t="inlineStr">
+        <is>
+          <t>100% (single tenant, absolute net)</t>
+        </is>
+      </c>
+      <c r="U14" s="35" t="n"/>
+      <c r="V14" s="32" t="n"/>
+      <c r="W14" s="35" t="inlineStr">
+        <is>
+          <t>—  (owner-managed)</t>
+        </is>
+      </c>
+      <c r="X14" s="32" t="inlineStr">
+        <is>
+          <t>R0212546 P&amp;L 2024 &amp; 2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>R0083953</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>R0083953</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — WPC ABC LLC</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>20901 E. 32nd Pkwy</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="32" t="inlineStr">
+        <is>
+          <t>WPC ABC, LLC</t>
+        </is>
+      </c>
+      <c r="K15" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (4 × 50,000 SF units)</t>
+        </is>
+      </c>
+      <c r="M15" s="32" t="inlineStr">
+        <is>
+          <t>Multi-tenant (4 units)</t>
+        </is>
+      </c>
+      <c r="N15" s="32" t="n"/>
+      <c r="O15" s="32" t="n"/>
+      <c r="P15" s="34" t="n"/>
+      <c r="Q15" s="34" t="n">
+        <v>200000</v>
+      </c>
+      <c r="R15" s="32" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S15" s="32" t="n"/>
+      <c r="T15" s="32" t="inlineStr">
+        <is>
+          <t>100.0% (0 vacant SF at every rent-roll date 2021-2024)</t>
+        </is>
+      </c>
+      <c r="U15" s="35" t="n"/>
+      <c r="V15" s="32" t="n"/>
+      <c r="W15" s="35" t="inlineStr">
+        <is>
+          <t>Colliers International</t>
+        </is>
+      </c>
+      <c r="X15" s="32" t="inlineStr">
+        <is>
+          <t>R0083953 rent roll &amp; income statements.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Year built for R0180834 is not stated in its rent roll or income statement. Addresses/ZIPs marked "—" do not appear in the source document; 2780 N. Tower Rd city is inferred from the street address. Building areas are the leasable areas printed on each rent roll (R0180834: 553,757 SF; R0212546: 377,729 SF per the document title, used for the $/SF checks below; R0083953: 200,000 SF).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A16:Y16"/>
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="A1:Y1"/>
   </mergeCells>
@@ -2067,7 +2550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2100,7 +2583,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3131,13 +3613,749 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="36" t="inlineStr">
+        <is>
+          <t>Denver Distribution Center (R0180834) — rent roll as of 01/01/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="37" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr</t>
+        </is>
+      </c>
+      <c r="B29" s="37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="inlineStr">
+        <is>
+          <t>United Natural Foods Inc (t0201668)</t>
+        </is>
+      </c>
+      <c r="D29" s="37" t="inlineStr">
+        <is>
+          <t>Actual NNN (industrial)</t>
+        </is>
+      </c>
+      <c r="E29" s="37" t="n">
+        <v>300709.67</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>3608516.04</v>
+      </c>
+      <c r="G29" s="37" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="H29" s="37" t="inlineStr">
+        <is>
+          <t>6/15/2012</t>
+        </is>
+      </c>
+      <c r="I29" s="37" t="inlineStr">
+        <is>
+          <t>10/31/2028</t>
+        </is>
+      </c>
+      <c r="J29" s="37" t="inlineStr">
+        <is>
+          <t>1st Renewal Opt 10/31/2027; 2nd Renewal Opt 10/31/2032; Expansion Opt</t>
+        </is>
+      </c>
+      <c r="K29" s="37" t="n">
+        <v>4646.33</v>
+      </c>
+      <c r="L29" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="37" t="inlineStr">
+        <is>
+          <t>Charge code cabrnind @ $0.54/SF/mo. Status Current. CAM shown = ceopex; also ceins $6,943.97/mo and ceretax $186,818.31/mo (both eff. 01/01/2025). AR balance $(14,541.14).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="37" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr</t>
+        </is>
+      </c>
+      <c r="B30" s="37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="inlineStr">
+        <is>
+          <t>United Natural Foods Inc — future rent step</t>
+        </is>
+      </c>
+      <c r="D30" s="37" t="inlineStr">
+        <is>
+          <t>Actual NNN</t>
+        </is>
+      </c>
+      <c r="E30" s="37" t="n">
+        <v>308781.17</v>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>3705374.04</v>
+      </c>
+      <c r="G30" s="37" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="H30" s="37" t="inlineStr">
+        <is>
+          <t>11/1/2025</t>
+        </is>
+      </c>
+      <c r="I30" s="37" t="inlineStr">
+        <is>
+          <t>10/31/2028</t>
+        </is>
+      </c>
+      <c r="J30" s="37" t="inlineStr">
+        <is>
+          <t>Scheduled step</t>
+        </is>
+      </c>
+      <c r="K30" s="37" t="n"/>
+      <c r="L30" s="37" t="n"/>
+      <c r="M30" s="37" t="inlineStr">
+        <is>
+          <t>Future amount $0.56/SF/mo effective 11/01/2025 (printed on the same rent-roll line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="38" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr</t>
+        </is>
+      </c>
+      <c r="B31" s="38" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C31" s="38" t="inlineStr">
+        <is>
+          <t>Total monthly billing (all charge codes)</t>
+        </is>
+      </c>
+      <c r="D31" s="38" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="E31" s="39" t="n">
+        <v>499118.28</v>
+      </c>
+      <c r="F31" s="40">
+        <f>E31*12</f>
+        <v/>
+      </c>
+      <c r="G31" s="39" t="n"/>
+      <c r="H31" s="38" t="n"/>
+      <c r="I31" s="38" t="n"/>
+      <c r="J31" s="38" t="inlineStr">
+        <is>
+          <t>1 unit / 553,757 SF</t>
+        </is>
+      </c>
+      <c r="K31" s="39" t="n"/>
+      <c r="L31" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="38" t="inlineStr">
+        <is>
+          <t>Printed rent-roll total $499,118.28/mo; 100.00% occupied, 100.00% leased, 0 vacant units. Security deposit $0.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="36" t="inlineStr">
+        <is>
+          <t>2780 North Tower Road (R0212546) — absolute net single tenant</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>Single tenant (name not stated in P&amp;L)</t>
+        </is>
+      </c>
+      <c r="D34" s="37" t="inlineStr">
+        <is>
+          <t>Absolute net</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n">
+        <v>3047376</v>
+      </c>
+      <c r="G34" s="37" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="H34" s="37" t="n"/>
+      <c r="I34" s="37" t="n"/>
+      <c r="J34" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="37" t="n"/>
+      <c r="L34" s="37" t="n"/>
+      <c r="M34" s="37" t="inlineStr">
+        <is>
+          <t>FY2024 rent income (acct 42327 "Rent Income SRO Tower Road") ÷ 377,729 SF = $8.07/SF. Tenant pays taxes, insurance, R&amp;M, utilities — all $0 to owner in FY2024.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd</t>
+        </is>
+      </c>
+      <c r="B35" s="37" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>Single tenant (name not stated in P&amp;L)</t>
+        </is>
+      </c>
+      <c r="D35" s="37" t="inlineStr">
+        <is>
+          <t>Absolute net</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="37" t="n">
+        <v>2979661</v>
+      </c>
+      <c r="G35" s="37" t="n">
+        <v>7.89</v>
+      </c>
+      <c r="H35" s="37" t="n"/>
+      <c r="I35" s="37" t="n"/>
+      <c r="J35" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="n"/>
+      <c r="L35" s="37" t="n"/>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>FY2023 rent income ÷ 377,729 SF = $7.89/SF. FY2023 had $687 utilities at owner level; taxes and R&amp;M still $0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="36" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter / WPC ABC LLC (R0083953) — rent roll as of 06/30/2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B38" s="32" t="inlineStr">
+        <is>
+          <t>455-A-CU</t>
+        </is>
+      </c>
+      <c r="C38" s="32" t="inlineStr">
+        <is>
+          <t>Zayo Group</t>
+        </is>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN (CAM/tax/ins billed)</t>
+        </is>
+      </c>
+      <c r="E38" s="41" t="n">
+        <v>16375</v>
+      </c>
+      <c r="F38" s="35" t="n">
+        <v>196500</v>
+      </c>
+      <c r="G38" s="41" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H38" s="32" t="inlineStr">
+        <is>
+          <t>5/1/2020</t>
+        </is>
+      </c>
+      <c r="I38" s="32" t="inlineStr">
+        <is>
+          <t>10/31/2027</t>
+        </is>
+      </c>
+      <c r="J38" s="32" t="inlineStr">
+        <is>
+          <t>90 mo</t>
+        </is>
+      </c>
+      <c r="K38" s="41" t="n">
+        <v>3004</v>
+      </c>
+      <c r="L38" s="41" t="n"/>
+      <c r="M38" s="32" t="inlineStr">
+        <is>
+          <t>Steps: $16,875 (11/01/2024), $17,375 (11/01/2025), $17,916.67 (11/01/2026). Other exp $674/mo. Gross rent $30,467/mo = $7.31/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B39" s="32" t="inlineStr">
+        <is>
+          <t>455-B-CU</t>
+        </is>
+      </c>
+      <c r="C39" s="32" t="inlineStr">
+        <is>
+          <t>Tritz Pallet</t>
+        </is>
+      </c>
+      <c r="D39" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN (CAM/tax/ins billed)</t>
+        </is>
+      </c>
+      <c r="E39" s="41" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F39" s="35" t="n">
+        <v>120000</v>
+      </c>
+      <c r="G39" s="41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H39" s="32" t="inlineStr">
+        <is>
+          <t>4/1/2021</t>
+        </is>
+      </c>
+      <c r="I39" s="32" t="inlineStr">
+        <is>
+          <t>2/28/2025</t>
+        </is>
+      </c>
+      <c r="J39" s="32" t="inlineStr">
+        <is>
+          <t>47 mo</t>
+        </is>
+      </c>
+      <c r="K39" s="41" t="n">
+        <v>3008</v>
+      </c>
+      <c r="L39" s="41" t="n"/>
+      <c r="M39" s="32" t="inlineStr">
+        <is>
+          <t>Last step $10,000 eff. 03/01/2024. Other exp $674/mo. Gross rent $24,096/mo = $5.78/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>455-C-CU</t>
+        </is>
+      </c>
+      <c r="C40" s="32" t="inlineStr">
+        <is>
+          <t>Peco Pallet</t>
+        </is>
+      </c>
+      <c r="D40" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN (CAM/tax/ins billed)</t>
+        </is>
+      </c>
+      <c r="E40" s="41" t="n">
+        <v>16250</v>
+      </c>
+      <c r="F40" s="35" t="n">
+        <v>195000</v>
+      </c>
+      <c r="G40" s="41" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="32" t="inlineStr">
+        <is>
+          <t>4/1/2020</t>
+        </is>
+      </c>
+      <c r="I40" s="32" t="inlineStr">
+        <is>
+          <t>3/31/2025</t>
+        </is>
+      </c>
+      <c r="J40" s="32" t="inlineStr">
+        <is>
+          <t>120 mo</t>
+        </is>
+      </c>
+      <c r="K40" s="41" t="n">
+        <v>2994</v>
+      </c>
+      <c r="L40" s="41" t="n"/>
+      <c r="M40" s="32" t="inlineStr">
+        <is>
+          <t>Last step $16,250 eff. 04/01/2024. Other exp $674/mo. Gross rent $30,332/mo = $7.28/SF. The 6/30/2024 recap page shows this lease ending 3/31/2030 — discrepancy as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B41" s="32" t="inlineStr">
+        <is>
+          <t>455-D-CU</t>
+        </is>
+      </c>
+      <c r="C41" s="32" t="inlineStr">
+        <is>
+          <t>Tritz Pallet</t>
+        </is>
+      </c>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN (CAM/tax/ins billed)</t>
+        </is>
+      </c>
+      <c r="E41" s="41" t="n">
+        <v>15833</v>
+      </c>
+      <c r="F41" s="35" t="n">
+        <v>189996</v>
+      </c>
+      <c r="G41" s="41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H41" s="32" t="inlineStr">
+        <is>
+          <t>11/1/2019</t>
+        </is>
+      </c>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>2/28/2025</t>
+        </is>
+      </c>
+      <c r="J41" s="32" t="inlineStr">
+        <is>
+          <t>64 mo</t>
+        </is>
+      </c>
+      <c r="K41" s="41" t="n">
+        <v>2983</v>
+      </c>
+      <c r="L41" s="41" t="n"/>
+      <c r="M41" s="32" t="inlineStr">
+        <is>
+          <t>Last step $15,833 eff. 03/01/2024. Other exp $674/mo. Gross rent $29,904/mo = $7.18/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B42" s="38" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C42" s="38" t="inlineStr">
+        <is>
+          <t>Property totals — 200,000 SF, 0 vacant</t>
+        </is>
+      </c>
+      <c r="D42" s="38" t="inlineStr">
+        <is>
+          <t>Actual NNN</t>
+        </is>
+      </c>
+      <c r="E42" s="39">
+        <f>SUM(E38:E41)</f>
+        <v/>
+      </c>
+      <c r="F42" s="40">
+        <f>SUM(F38:F41)</f>
+        <v/>
+      </c>
+      <c r="G42" s="39" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H42" s="38" t="n"/>
+      <c r="I42" s="38" t="n"/>
+      <c r="J42" s="38" t="inlineStr">
+        <is>
+          <t>6.69 yr wtd-avg term</t>
+        </is>
+      </c>
+      <c r="K42" s="39">
+        <f>SUM(K38:K41)</f>
+        <v/>
+      </c>
+      <c r="L42" s="39" t="n"/>
+      <c r="M42" s="38" t="inlineStr">
+        <is>
+          <t>Printed property totals 06/2024: base rent $58,458.00/mo, prorated annual $701,496.00, $3.51/SF; OpEx recovery $11,989/mo ($0.72/SF), RE tax $41,656/mo ($2.50/SF), other $2,696/mo ($0.16/SF); gross rents $114,799.00/mo = $6.89/SF. Recap page annualizes year-end rates to $707,496.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="36" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — rent-roll totals by report date (200,000 SF, 100% occupied throughout)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B45" s="32" t="inlineStr">
+        <is>
+          <t>06/2021 (6/1-6/30/2021)</t>
+        </is>
+      </c>
+      <c r="C45" s="32" t="inlineStr">
+        <is>
+          <t>All 4 units (Zayo, Tritz ×2, Peco)</t>
+        </is>
+      </c>
+      <c r="D45" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="n">
+        <v>52083</v>
+      </c>
+      <c r="F45" s="35" t="n">
+        <v>624996</v>
+      </c>
+      <c r="G45" s="41" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="H45" s="32" t="n"/>
+      <c r="I45" s="32" t="n"/>
+      <c r="J45" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K45" s="41" t="n">
+        <v>11013</v>
+      </c>
+      <c r="L45" s="41" t="n"/>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>Monthly RE tax billed $32,381; other exp $1,368; gross rents $96,845.00/mo = $5.81/SF/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B46" s="32" t="inlineStr">
+        <is>
+          <t>06/2022 (6/1-6/30/2022)</t>
+        </is>
+      </c>
+      <c r="C46" s="32" t="inlineStr">
+        <is>
+          <t>All 4 units (Zayo, Tritz ×2, Peco)</t>
+        </is>
+      </c>
+      <c r="D46" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="n">
+        <v>54208</v>
+      </c>
+      <c r="F46" s="35" t="n">
+        <v>650496</v>
+      </c>
+      <c r="G46" s="41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="H46" s="32" t="n"/>
+      <c r="I46" s="32" t="n"/>
+      <c r="J46" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K46" s="41" t="n">
+        <v>11007</v>
+      </c>
+      <c r="L46" s="41" t="n"/>
+      <c r="M46" s="32" t="inlineStr">
+        <is>
+          <t>Monthly RE tax billed $31,348; other exp $1,596; gross rents $98,159.00/mo = $5.89/SF/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B47" s="32" t="inlineStr">
+        <is>
+          <t>01/2023 (1/1-1/31/2023)</t>
+        </is>
+      </c>
+      <c r="C47" s="32" t="inlineStr">
+        <is>
+          <t>All 4 units (Zayo, Tritz ×2, Peco)</t>
+        </is>
+      </c>
+      <c r="D47" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="n">
+        <v>55917.34</v>
+      </c>
+      <c r="F47" s="35" t="n">
+        <v>671008.08</v>
+      </c>
+      <c r="G47" s="41" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="H47" s="32" t="n"/>
+      <c r="I47" s="32" t="n"/>
+      <c r="J47" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K47" s="41" t="n">
+        <v>12683</v>
+      </c>
+      <c r="L47" s="41" t="n"/>
+      <c r="M47" s="32" t="inlineStr">
+        <is>
+          <t>Monthly RE tax billed $36,004; other exp $1,976; gross rents $106,580.34/mo = $6.39/SF/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter</t>
+        </is>
+      </c>
+      <c r="B48" s="32" t="inlineStr">
+        <is>
+          <t>06/2024 (6/1-6/30/2024)</t>
+        </is>
+      </c>
+      <c r="C48" s="32" t="inlineStr">
+        <is>
+          <t>All 4 units (Zayo, Tritz ×2, Peco)</t>
+        </is>
+      </c>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>Actual NNN</t>
+        </is>
+      </c>
+      <c r="E48" s="41" t="n">
+        <v>58458</v>
+      </c>
+      <c r="F48" s="35" t="n">
+        <v>701496</v>
+      </c>
+      <c r="G48" s="41" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H48" s="32" t="n"/>
+      <c r="I48" s="32" t="n"/>
+      <c r="J48" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="41" t="n">
+        <v>11989</v>
+      </c>
+      <c r="L48" s="41" t="n"/>
+      <c r="M48" s="32" t="inlineStr">
+        <is>
+          <t>Monthly RE tax billed $41,656; other exp $2,696; gross rents $114,799.00/mo = $6.89/SF/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="33" t="inlineStr">
+        <is>
+          <t>Rent PSF is annual base rent ÷ leasable SF as printed on each rent roll. Denver Distribution Center rents are billed monthly per SF ($0.54 → $0.56); the annual PSF shown here is 12× that rate. 2780 N. Tower Road has no rent roll in the file — its rent is taken from the P&amp;L income line and divided by the 377,729 SF in the document title.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A49:M49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3176,7 +4394,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,7 +4602,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -3400,7 +4616,6 @@
       <c r="G12" s="20" t="n"/>
       <c r="H12" s="21" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -3597,7 +4812,6 @@
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -3631,7 +4845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +4869,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +4983,155 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="42" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr (R0180834) — FY2024</t>
+        </is>
+      </c>
+      <c r="B9" s="43" t="n">
+        <v>5292302.21</v>
+      </c>
+      <c r="C9" s="43" t="n">
+        <v>2376573.38</v>
+      </c>
+      <c r="D9" s="43">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="44" t="inlineStr">
+        <is>
+          <t>Accrual income statement, Dec-2024 YTD. Net = NOI $2,915,728.83 (printed). Excludes $902,885.40 non-operating financing cost; net income after financing $2,012,843.43.</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="42" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd (R0212546) — FY2024</t>
+        </is>
+      </c>
+      <c r="B10" s="43" t="n">
+        <v>3047376</v>
+      </c>
+      <c r="C10" s="43" t="n">
+        <v>515200</v>
+      </c>
+      <c r="D10" s="43">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="44" t="inlineStr">
+        <is>
+          <t>Accrual P&amp;L. Net = net ordinary income $2,532,176 (printed). Expense incl. depreciation $456,096 &amp; amortization $12,124; excl. interest $613,282. Cash operating expense only $46,980 ($0.12/SF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="42" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd (R0212546) — FY2023</t>
+        </is>
+      </c>
+      <c r="B11" s="43" t="n">
+        <v>2979661</v>
+      </c>
+      <c r="C11" s="43" t="n">
+        <v>497459</v>
+      </c>
+      <c r="D11" s="43">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="44" t="inlineStr">
+        <is>
+          <t>Accrual P&amp;L. Net = net ordinary income $2,482,202 (printed). Net income after $641,014 interest and $18 other income = $1,841,206.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="42" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter (R0083953) — FY2024</t>
+        </is>
+      </c>
+      <c r="B12" s="43" t="n">
+        <v>1361972.79</v>
+      </c>
+      <c r="C12" s="43" t="n">
+        <v>612748.98</v>
+      </c>
+      <c r="D12" s="43">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="44" t="inlineStr">
+        <is>
+          <t>Net = income from operations $749,223.81 (printed). Excludes $71,251.20 lease commission and $100 G&amp;A; operating summary after those = $677,872.61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter (R0083953) — FY2023</t>
+        </is>
+      </c>
+      <c r="B13" s="43" t="n">
+        <v>1332229.95</v>
+      </c>
+      <c r="C13" s="43" t="n">
+        <v>534383.48</v>
+      </c>
+      <c r="D13" s="43">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="44" t="inlineStr">
+        <is>
+          <t>Net = income from operations $797,846.47 (printed). Operating summary after $100 G&amp;A = $797,746.47.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="42" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter (R0083953) — FY2022</t>
+        </is>
+      </c>
+      <c r="B14" s="43" t="n">
+        <v>1158591.35</v>
+      </c>
+      <c r="C14" s="43" t="n">
+        <v>517966.24</v>
+      </c>
+      <c r="D14" s="43">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="44" t="inlineStr">
+        <is>
+          <t>Net = income from operations $640,625.11 (printed). Excludes $24,325.08 lease commission and $100 G&amp;A; operating summary after those = $616,200.03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +5143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +5167,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5210,10 +6554,2913 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B67" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="32" t="inlineStr">
+        <is>
+          <t>4000100-040 Rent - Industrial</t>
+        </is>
+      </c>
+      <c r="D67" s="41" t="n">
+        <v>3608516.04</v>
+      </c>
+      <c r="E67" s="32" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B68" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C68" s="32" t="inlineStr">
+        <is>
+          <t>4010500-000 Bad Debt/Uncollectible Rents (credit)</t>
+        </is>
+      </c>
+      <c r="D68" s="41" t="n">
+        <v>103942.63</v>
+      </c>
+      <c r="E68" s="32" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B69" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C69" s="32" t="inlineStr">
+        <is>
+          <t>4060200-010 OpEx Recovery - Current Yr Estimate</t>
+        </is>
+      </c>
+      <c r="D69" s="41" t="n">
+        <v>56318.16</v>
+      </c>
+      <c r="E69" s="32" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B70" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C70" s="32" t="inlineStr">
+        <is>
+          <t>4060200-020 OpEx Recovery - Prior Yr Reconciliation</t>
+        </is>
+      </c>
+      <c r="D70" s="41" t="n">
+        <v>-290730.22</v>
+      </c>
+      <c r="E70" s="32" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B71" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C71" s="32" t="inlineStr">
+        <is>
+          <t>4060200-030 OpEx Recovery - CY Over/Under Billing</t>
+        </is>
+      </c>
+      <c r="D71" s="41" t="n">
+        <v>-3591.51</v>
+      </c>
+      <c r="E71" s="32" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B72" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C72" s="32" t="inlineStr">
+        <is>
+          <t>4060300-010 Insurance Recovery - Current Yr Estimate</t>
+        </is>
+      </c>
+      <c r="D72" s="41" t="n">
+        <v>90371.16</v>
+      </c>
+      <c r="E72" s="32" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B73" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C73" s="32" t="inlineStr">
+        <is>
+          <t>4060300-020 Insurance Recovery - Prior Yr Reconciliation</t>
+        </is>
+      </c>
+      <c r="D73" s="41" t="n">
+        <v>15236.42</v>
+      </c>
+      <c r="E73" s="32" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B74" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C74" s="32" t="inlineStr">
+        <is>
+          <t>4060300-030 Insurance Recovery - CY Over/Under Billing</t>
+        </is>
+      </c>
+      <c r="D74" s="41" t="n">
+        <v>-11115.1</v>
+      </c>
+      <c r="E74" s="32" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B75" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C75" s="32" t="inlineStr">
+        <is>
+          <t>4060400-010 RE Tax Recovery - Current Yr Estimate</t>
+        </is>
+      </c>
+      <c r="D75" s="41" t="n">
+        <v>2408707.68</v>
+      </c>
+      <c r="E75" s="32" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B76" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C76" s="32" t="inlineStr">
+        <is>
+          <t>4060400-020 RE Tax Recovery - Prior Yr Reconciliation</t>
+        </is>
+      </c>
+      <c r="D76" s="41" t="n">
+        <v>-337524.5</v>
+      </c>
+      <c r="E76" s="32" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B77" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C77" s="32" t="inlineStr">
+        <is>
+          <t>4060400-030 RE Tax Recovery - CY Over/Under Billing</t>
+        </is>
+      </c>
+      <c r="D77" s="41" t="n">
+        <v>-347828.55</v>
+      </c>
+      <c r="E77" s="32" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="38" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B78" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C78" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D78" s="39">
+        <f>SUM(D67:D77)</f>
+        <v/>
+      </c>
+      <c r="E78" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $5,292,302.21. Total Revenues (net commercial rental income $3,712,458.67 + recovery income $1,579,843.54). Bad debt is printed as a positive rent adjustment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B79" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="32" t="inlineStr">
+        <is>
+          <t>5015100-010 Roof - Contract</t>
+        </is>
+      </c>
+      <c r="D79" s="41" t="n">
+        <v>1604.01</v>
+      </c>
+      <c r="E79" s="32" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B80" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="32" t="inlineStr">
+        <is>
+          <t>5015100-020 Roof - R&amp;M</t>
+        </is>
+      </c>
+      <c r="D80" s="41" t="n">
+        <v>1274.85</v>
+      </c>
+      <c r="E80" s="32" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B81" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C81" s="32" t="inlineStr">
+        <is>
+          <t>5030900-000 Utilities - Other</t>
+        </is>
+      </c>
+      <c r="D81" s="41" t="n">
+        <v>34</v>
+      </c>
+      <c r="E81" s="32" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B82" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C82" s="32" t="inlineStr">
+        <is>
+          <t>5050100-000 Insurance - Property Insurance</t>
+        </is>
+      </c>
+      <c r="D82" s="41" t="n">
+        <v>77116.59</v>
+      </c>
+      <c r="E82" s="32" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B83" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C83" s="32" t="inlineStr">
+        <is>
+          <t>5070100-000 Taxes - Real Estate</t>
+        </is>
+      </c>
+      <c r="D83" s="41" t="n">
+        <v>2060754.14</v>
+      </c>
+      <c r="E83" s="32" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
+        <is>
+          <t>5070900-000 Taxes - Other</t>
+        </is>
+      </c>
+      <c r="D84" s="41" t="n">
+        <v>166.65</v>
+      </c>
+      <c r="E84" s="32" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B85" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C85" s="32" t="inlineStr">
+        <is>
+          <t>5080100-000 Building Admin - Management Fees</t>
+        </is>
+      </c>
+      <c r="D85" s="41" t="n">
+        <v>138053.44</v>
+      </c>
+      <c r="E85" s="32" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B86" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="32" t="inlineStr">
+        <is>
+          <t>5080400-030 Building Admin - UPS/FEDEX</t>
+        </is>
+      </c>
+      <c r="D86" s="41" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="E86" s="32" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B87" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C87" s="32" t="inlineStr">
+        <is>
+          <t>5080510-000 Building Admin - Accounting Support</t>
+        </is>
+      </c>
+      <c r="D87" s="41" t="n">
+        <v>69026.74000000001</v>
+      </c>
+      <c r="E87" s="32" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B88" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="32" t="inlineStr">
+        <is>
+          <t>5080530-000 Building Admin - Bank Fees</t>
+        </is>
+      </c>
+      <c r="D88" s="41" t="n">
+        <v>6073.59</v>
+      </c>
+      <c r="E88" s="32" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B89" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C89" s="32" t="inlineStr">
+        <is>
+          <t>5080590-000 Building Admin - Licenses &amp; Fees Required</t>
+        </is>
+      </c>
+      <c r="D89" s="41" t="n">
+        <v>32.75</v>
+      </c>
+      <c r="E89" s="32" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B90" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C90" s="32" t="inlineStr">
+        <is>
+          <t>5080625-010 Building Admin - Sustainability</t>
+        </is>
+      </c>
+      <c r="D90" s="41" t="n">
+        <v>453.89</v>
+      </c>
+      <c r="E90" s="32" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B91" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C91" s="32" t="inlineStr">
+        <is>
+          <t>5101700-000 Marketing - Tenant Retention &amp; Incentives</t>
+        </is>
+      </c>
+      <c r="D91" s="41" t="n">
+        <v>316.98</v>
+      </c>
+      <c r="E91" s="32" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B92" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C92" s="32" t="inlineStr">
+        <is>
+          <t>5132050-000 G&amp;A - Professional Fees - Other</t>
+        </is>
+      </c>
+      <c r="D92" s="41" t="n">
+        <v>100</v>
+      </c>
+      <c r="E92" s="32" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B93" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="32" t="inlineStr">
+        <is>
+          <t>5139300-000 G&amp;A - R&amp;M Nonrecoverable</t>
+        </is>
+      </c>
+      <c r="D93" s="41" t="n">
+        <v>21548.5</v>
+      </c>
+      <c r="E93" s="32" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="38" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B94" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C94" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D94" s="39">
+        <f>SUM(D79:D93)</f>
+        <v/>
+      </c>
+      <c r="E94" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $2,376,573.38. Total Operating Expenses = recoverable $2,354,607.90 + non-recoverable $21,965.48. NOI $2,915,728.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B95" s="32" t="inlineStr">
+        <is>
+          <t>Non-operating</t>
+        </is>
+      </c>
+      <c r="C95" s="32" t="inlineStr">
+        <is>
+          <t>7000200-000 Interest Expense - Note Payable</t>
+        </is>
+      </c>
+      <c r="D95" s="41" t="n">
+        <v>868994.76</v>
+      </c>
+      <c r="E95" s="32" t="inlineStr">
+        <is>
+          <t>Below the NOI line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B96" s="32" t="inlineStr">
+        <is>
+          <t>Non-operating</t>
+        </is>
+      </c>
+      <c r="C96" s="32" t="inlineStr">
+        <is>
+          <t>7011040-000 Amort Exp - Deferred Financing Costs</t>
+        </is>
+      </c>
+      <c r="D96" s="41" t="n">
+        <v>33890.64</v>
+      </c>
+      <c r="E96" s="32" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="38" t="inlineStr">
+        <is>
+          <t>Denver Distribution Ctr — FY2024</t>
+        </is>
+      </c>
+      <c r="B97" s="38" t="inlineStr">
+        <is>
+          <t>Non-operating</t>
+        </is>
+      </c>
+      <c r="C97" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL NON-OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D97" s="39">
+        <f>SUM(D95:D96)</f>
+        <v/>
+      </c>
+      <c r="E97" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $902,885.40. Net income after financing: $2,012,843.43.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B99" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C99" s="32" t="inlineStr">
+        <is>
+          <t>42327 - Rent Income SRO Tower Road</t>
+        </is>
+      </c>
+      <c r="D99" s="41" t="n">
+        <v>3047376</v>
+      </c>
+      <c r="E99" s="32" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="38" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B100" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C100" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D100" s="39">
+        <f>SUM(D99:D99)</f>
+        <v/>
+      </c>
+      <c r="E100" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $3,047,376.00. Total Income as printed (rent only). Rent ÷ 377,729 SF = $8.07/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B101" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="32" t="inlineStr">
+        <is>
+          <t>60400 - Bank Service Charges</t>
+        </is>
+      </c>
+      <c r="D101" s="41" t="n">
+        <v>207</v>
+      </c>
+      <c r="E101" s="32" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B102" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="32" t="inlineStr">
+        <is>
+          <t>62500 - Dues and Subscriptions</t>
+        </is>
+      </c>
+      <c r="D102" s="41" t="n">
+        <v>839</v>
+      </c>
+      <c r="E102" s="32" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B103" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="32" t="inlineStr">
+        <is>
+          <t>64900 - Office Supplies</t>
+        </is>
+      </c>
+      <c r="D103" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="32" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B104" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="32" t="inlineStr">
+        <is>
+          <t>66700 - Professional Fees: Accounting</t>
+        </is>
+      </c>
+      <c r="D104" s="41" t="n">
+        <v>4000</v>
+      </c>
+      <c r="E104" s="32" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B105" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="32" t="inlineStr">
+        <is>
+          <t>66700 - Professional Fees: Service Agreement</t>
+        </is>
+      </c>
+      <c r="D105" s="41" t="n">
+        <v>16962</v>
+      </c>
+      <c r="E105" s="32" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B106" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C106" s="32" t="inlineStr">
+        <is>
+          <t>66700 - Professional Fees - Other</t>
+        </is>
+      </c>
+      <c r="D106" s="41" t="n">
+        <v>-951</v>
+      </c>
+      <c r="E106" s="32" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B107" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C107" s="32" t="inlineStr">
+        <is>
+          <t>67200 - Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="D107" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="32" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B108" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C108" s="32" t="inlineStr">
+        <is>
+          <t>68000 - Taxes - Property</t>
+        </is>
+      </c>
+      <c r="D108" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="32" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B109" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C109" s="32" t="inlineStr">
+        <is>
+          <t>68600 - Utilities</t>
+        </is>
+      </c>
+      <c r="D109" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="32" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B110" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C110" s="32" t="inlineStr">
+        <is>
+          <t>74410 - Outside Services</t>
+        </is>
+      </c>
+      <c r="D110" s="41" t="n">
+        <v>14830</v>
+      </c>
+      <c r="E110" s="32" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B111" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C111" s="32" t="inlineStr">
+        <is>
+          <t>75015 - Legal</t>
+        </is>
+      </c>
+      <c r="D111" s="41" t="n">
+        <v>11093</v>
+      </c>
+      <c r="E111" s="32" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B112" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C112" s="32" t="inlineStr">
+        <is>
+          <t>75020 - Consulting fees</t>
+        </is>
+      </c>
+      <c r="D112" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="32" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B113" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C113" s="32" t="inlineStr">
+        <is>
+          <t>77025 - Depreciation - Bldgs &amp; Improvement</t>
+        </is>
+      </c>
+      <c r="D113" s="41" t="n">
+        <v>456096</v>
+      </c>
+      <c r="E113" s="32" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B114" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C114" s="32" t="inlineStr">
+        <is>
+          <t>77026 - Amortization</t>
+        </is>
+      </c>
+      <c r="D114" s="41" t="n">
+        <v>12124</v>
+      </c>
+      <c r="E114" s="32" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="38" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B115" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C115" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D115" s="39">
+        <f>SUM(D101:D114)</f>
+        <v/>
+      </c>
+      <c r="E115" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $515,200.00. Total Expense as printed. Absolute net lease — property taxes, R&amp;M and utilities are $0 to the owner. Excluding depreciation $456,096 and amortization $12,124, cash operating expense is $46,980 ($0.12/SF). Net ordinary income $2,532,176; less interest $613,282 → net income $1,918,894.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2024</t>
+        </is>
+      </c>
+      <c r="B116" s="32" t="inlineStr">
+        <is>
+          <t>Non-operating</t>
+        </is>
+      </c>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>92000 - Interest Expense - Notes</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="n">
+        <v>613282</v>
+      </c>
+      <c r="E116" s="32" t="inlineStr">
+        <is>
+          <t>Printed Total Other Expense: $613,282. Net income: $1,918,894.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B118" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C118" s="32" t="inlineStr">
+        <is>
+          <t>42327 - Rent Income SRO Tower Road</t>
+        </is>
+      </c>
+      <c r="D118" s="41" t="n">
+        <v>2979661</v>
+      </c>
+      <c r="E118" s="32" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="38" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B119" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C119" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D119" s="39">
+        <f>SUM(D118:D118)</f>
+        <v/>
+      </c>
+      <c r="E119" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $2,979,661.00. Total Income as printed (rent only). Rent ÷ 377,729 SF = $7.89/SF. Separately, Other Income of $18 is reported below the operating section.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B120" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>60400 - Bank Service Charges</t>
+        </is>
+      </c>
+      <c r="D120" s="41" t="n">
+        <v>355</v>
+      </c>
+      <c r="E120" s="32" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B121" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C121" s="32" t="inlineStr">
+        <is>
+          <t>62500 - Dues and Subscriptions</t>
+        </is>
+      </c>
+      <c r="D121" s="41" t="n">
+        <v>800</v>
+      </c>
+      <c r="E121" s="32" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B122" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C122" s="32" t="inlineStr">
+        <is>
+          <t>64900 - Office Supplies</t>
+        </is>
+      </c>
+      <c r="D122" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" s="32" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B123" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C123" s="32" t="inlineStr">
+        <is>
+          <t>66700 - Professional Fees: Accounting</t>
+        </is>
+      </c>
+      <c r="D123" s="41" t="n">
+        <v>3855</v>
+      </c>
+      <c r="E123" s="32" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B124" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C124" s="32" t="inlineStr">
+        <is>
+          <t>66700 - Professional Fees: Service Agreement</t>
+        </is>
+      </c>
+      <c r="D124" s="41" t="n">
+        <v>16596</v>
+      </c>
+      <c r="E124" s="32" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B125" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C125" s="32" t="inlineStr">
+        <is>
+          <t>66700 - Professional Fees - Other</t>
+        </is>
+      </c>
+      <c r="D125" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="32" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B126" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" s="32" t="inlineStr">
+        <is>
+          <t>67200 - Repairs and Maintenance</t>
+        </is>
+      </c>
+      <c r="D126" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="32" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B127" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" s="32" t="inlineStr">
+        <is>
+          <t>68000 - Taxes - Property</t>
+        </is>
+      </c>
+      <c r="D127" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="32" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B128" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C128" s="32" t="inlineStr">
+        <is>
+          <t>68600 - Utilities</t>
+        </is>
+      </c>
+      <c r="D128" s="41" t="n">
+        <v>687</v>
+      </c>
+      <c r="E128" s="32" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B129" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C129" s="32" t="inlineStr">
+        <is>
+          <t>74410 - Outside Services</t>
+        </is>
+      </c>
+      <c r="D129" s="41" t="n">
+        <v>2206</v>
+      </c>
+      <c r="E129" s="32" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B130" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C130" s="32" t="inlineStr">
+        <is>
+          <t>75015 - Legal</t>
+        </is>
+      </c>
+      <c r="D130" s="41" t="n">
+        <v>4730</v>
+      </c>
+      <c r="E130" s="32" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B131" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C131" s="32" t="inlineStr">
+        <is>
+          <t>75020 - Consulting fees</t>
+        </is>
+      </c>
+      <c r="D131" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="32" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B132" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" s="32" t="inlineStr">
+        <is>
+          <t>77025 - Depreciation - Bldgs &amp; Improvement</t>
+        </is>
+      </c>
+      <c r="D132" s="41" t="n">
+        <v>456096</v>
+      </c>
+      <c r="E132" s="32" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B133" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" s="32" t="inlineStr">
+        <is>
+          <t>77026 - Amortization</t>
+        </is>
+      </c>
+      <c r="D133" s="41" t="n">
+        <v>12124</v>
+      </c>
+      <c r="E133" s="32" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="38" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B134" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C134" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D134" s="39">
+        <f>SUM(D120:D133)</f>
+        <v/>
+      </c>
+      <c r="E134" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $497,459.00. Total Expense as printed. Absolute net lease — property taxes, R&amp;M are $0 to the owner. Excluding depreciation $456,096 and amortization $12,124, cash operating expense is $29,239 ($0.08/SF). Net ordinary income $2,482,202; less interest $641,014 → net income $1,841,206.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B135" s="32" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C135" s="32" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D135" s="41" t="n">
+        <v>18</v>
+      </c>
+      <c r="E135" s="32" t="inlineStr">
+        <is>
+          <t>Printed Total Other Income: $18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="32" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Rd — FY2023</t>
+        </is>
+      </c>
+      <c r="B136" s="32" t="inlineStr">
+        <is>
+          <t>Non-operating</t>
+        </is>
+      </c>
+      <c r="C136" s="32" t="inlineStr">
+        <is>
+          <t>92000 - Interest Expense - Notes</t>
+        </is>
+      </c>
+      <c r="D136" s="41" t="n">
+        <v>641014</v>
+      </c>
+      <c r="E136" s="32" t="inlineStr">
+        <is>
+          <t>Printed Total Other Expense: $641,014. Net income: $1,841,206.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B138" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C138" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D138" s="41" t="n">
+        <v>698747.99</v>
+      </c>
+      <c r="E138" s="32" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B139" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C139" s="32" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D139" s="41" t="n">
+        <v>143868</v>
+      </c>
+      <c r="E139" s="32" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B140" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C140" s="32" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D140" s="41" t="n">
+        <v>499872</v>
+      </c>
+      <c r="E140" s="32" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B141" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C141" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D141" s="41" t="n">
+        <v>32352</v>
+      </c>
+      <c r="E141" s="32" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B142" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C142" s="32" t="inlineStr">
+        <is>
+          <t>Prior Year Reconciliations</t>
+        </is>
+      </c>
+      <c r="D142" s="41" t="n">
+        <v>-12867.2</v>
+      </c>
+      <c r="E142" s="32" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B143" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C143" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D143" s="39">
+        <f>SUM(D138:D142)</f>
+        <v/>
+      </c>
+      <c r="E143" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $1,361,972.79. Gross Revenue as printed. Base rent ÷ 200,000 SF = $3.49/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B144" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C144" s="32" t="inlineStr">
+        <is>
+          <t>Water/Sewer (rec)</t>
+        </is>
+      </c>
+      <c r="D144" s="41" t="n">
+        <v>24928.96</v>
+      </c>
+      <c r="E144" s="32" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B145" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C145" s="32" t="inlineStr">
+        <is>
+          <t>Extermination (rec)</t>
+        </is>
+      </c>
+      <c r="D145" s="41" t="n">
+        <v>2310</v>
+      </c>
+      <c r="E145" s="32" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B146" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C146" s="32" t="inlineStr">
+        <is>
+          <t>Fire Protection/Security (rec)</t>
+        </is>
+      </c>
+      <c r="D146" s="41" t="n">
+        <v>4079.61</v>
+      </c>
+      <c r="E146" s="32" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B147" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C147" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (rec)</t>
+        </is>
+      </c>
+      <c r="D147" s="41" t="n">
+        <v>4433.48</v>
+      </c>
+      <c r="E147" s="32" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B148" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C148" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (rec)</t>
+        </is>
+      </c>
+      <c r="D148" s="41" t="n">
+        <v>310</v>
+      </c>
+      <c r="E148" s="32" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B149" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C149" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape/Sprinkler (rec)</t>
+        </is>
+      </c>
+      <c r="D149" s="41" t="n">
+        <v>10960.97</v>
+      </c>
+      <c r="E149" s="32" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B150" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C150" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC (rec)</t>
+        </is>
+      </c>
+      <c r="D150" s="41" t="n">
+        <v>5126.45</v>
+      </c>
+      <c r="E150" s="32" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B151" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C151" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (rec)</t>
+        </is>
+      </c>
+      <c r="D151" s="41" t="n">
+        <v>14956.6</v>
+      </c>
+      <c r="E151" s="32" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B152" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C152" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot Sweeping (rec)</t>
+        </is>
+      </c>
+      <c r="D152" s="41" t="n">
+        <v>75</v>
+      </c>
+      <c r="E152" s="32" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B153" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C153" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot Snow Removal (rec)</t>
+        </is>
+      </c>
+      <c r="D153" s="41" t="n">
+        <v>12925.25</v>
+      </c>
+      <c r="E153" s="32" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B154" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C154" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees (rec)</t>
+        </is>
+      </c>
+      <c r="D154" s="41" t="n">
+        <v>43037.28</v>
+      </c>
+      <c r="E154" s="32" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B155" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C155" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes (fixed)</t>
+        </is>
+      </c>
+      <c r="D155" s="41" t="n">
+        <v>423808.38</v>
+      </c>
+      <c r="E155" s="32" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B156" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C156" s="32" t="inlineStr">
+        <is>
+          <t>Insurance (fixed)</t>
+        </is>
+      </c>
+      <c r="D156" s="41" t="n">
+        <v>65797</v>
+      </c>
+      <c r="E156" s="32" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2024</t>
+        </is>
+      </c>
+      <c r="B157" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C157" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D157" s="39">
+        <f>SUM(D144:D156)</f>
+        <v/>
+      </c>
+      <c r="E157" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $612,748.98. Recoverable OpEx $123,143.60 + fixed $489,605.38. Income from operations $749,223.81. Below that line: G&amp;A misc $100.00 and lease commission $71,251.20 → total expenses $684,100.18, operating summary $677,872.61.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B159" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C159" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D159" s="41" t="n">
+        <v>675674.6800000001</v>
+      </c>
+      <c r="E159" s="32" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B160" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C160" s="32" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D160" s="41" t="n">
+        <v>152196</v>
+      </c>
+      <c r="E160" s="32" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B161" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C161" s="32" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D161" s="41" t="n">
+        <v>506459.28</v>
+      </c>
+      <c r="E161" s="32" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B162" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C162" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D162" s="41" t="n">
+        <v>23712</v>
+      </c>
+      <c r="E162" s="32" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B163" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C163" s="32" t="inlineStr">
+        <is>
+          <t>Prior Year Reconciliations</t>
+        </is>
+      </c>
+      <c r="D163" s="41" t="n">
+        <v>-25812.01</v>
+      </c>
+      <c r="E163" s="32" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B164" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C164" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D164" s="39">
+        <f>SUM(D159:D163)</f>
+        <v/>
+      </c>
+      <c r="E164" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $1,332,229.95. Gross Revenue as printed. Base rent ÷ 200,000 SF = $3.38/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B165" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C165" s="32" t="inlineStr">
+        <is>
+          <t>Water/Sewer (rec)</t>
+        </is>
+      </c>
+      <c r="D165" s="41" t="n">
+        <v>24936.52</v>
+      </c>
+      <c r="E165" s="32" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B166" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C166" s="32" t="inlineStr">
+        <is>
+          <t>Extermination (rec)</t>
+        </is>
+      </c>
+      <c r="D166" s="41" t="n">
+        <v>2910</v>
+      </c>
+      <c r="E166" s="32" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B167" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C167" s="32" t="inlineStr">
+        <is>
+          <t>Fire Protection/Security (rec)</t>
+        </is>
+      </c>
+      <c r="D167" s="41" t="n">
+        <v>1930</v>
+      </c>
+      <c r="E167" s="32" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B168" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C168" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (rec)</t>
+        </is>
+      </c>
+      <c r="D168" s="41" t="n">
+        <v>2154.09</v>
+      </c>
+      <c r="E168" s="32" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B169" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C169" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (rec)</t>
+        </is>
+      </c>
+      <c r="D169" s="41" t="n">
+        <v>1317</v>
+      </c>
+      <c r="E169" s="32" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B170" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C170" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Grounds (rec)</t>
+        </is>
+      </c>
+      <c r="D170" s="41" t="n">
+        <v>1295</v>
+      </c>
+      <c r="E170" s="32" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B171" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C171" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape/Sprinkler (rec)</t>
+        </is>
+      </c>
+      <c r="D171" s="41" t="n">
+        <v>21159.44</v>
+      </c>
+      <c r="E171" s="32" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B172" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C172" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC (rec)</t>
+        </is>
+      </c>
+      <c r="D172" s="41" t="n">
+        <v>19024.59</v>
+      </c>
+      <c r="E172" s="32" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B173" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C173" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (rec)</t>
+        </is>
+      </c>
+      <c r="D173" s="41" t="n">
+        <v>44093.04</v>
+      </c>
+      <c r="E173" s="32" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B174" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C174" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot Snow Removal (rec)</t>
+        </is>
+      </c>
+      <c r="D174" s="41" t="n">
+        <v>12819.5</v>
+      </c>
+      <c r="E174" s="32" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B175" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C175" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (rec)</t>
+        </is>
+      </c>
+      <c r="D175" s="41" t="n">
+        <v>2667.83</v>
+      </c>
+      <c r="E175" s="32" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B176" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C176" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees (rec)</t>
+        </is>
+      </c>
+      <c r="D176" s="41" t="n">
+        <v>38009.45</v>
+      </c>
+      <c r="E176" s="32" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B177" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C177" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (non-recoverable)</t>
+        </is>
+      </c>
+      <c r="D177" s="41" t="n">
+        <v>825</v>
+      </c>
+      <c r="E177" s="32" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B178" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C178" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes (fixed)</t>
+        </is>
+      </c>
+      <c r="D178" s="41" t="n">
+        <v>331843.02</v>
+      </c>
+      <c r="E178" s="32" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B179" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C179" s="32" t="inlineStr">
+        <is>
+          <t>Insurance (fixed)</t>
+        </is>
+      </c>
+      <c r="D179" s="41" t="n">
+        <v>29399</v>
+      </c>
+      <c r="E179" s="32" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2023</t>
+        </is>
+      </c>
+      <c r="B180" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C180" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D180" s="39">
+        <f>SUM(D165:D179)</f>
+        <v/>
+      </c>
+      <c r="E180" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $534,383.48. Recoverable OpEx $172,316.46 + non-recoverable $825.00 + fixed $361,242.02. Income from operations $797,846.47. Below that line: G&amp;A misc $100.00 → total expenses $534,483.48, operating summary $797,746.47.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B182" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C182" s="32" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D182" s="41" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="E182" s="32" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B183" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C183" s="32" t="inlineStr">
+        <is>
+          <t>Base Rent</t>
+        </is>
+      </c>
+      <c r="D183" s="41" t="n">
+        <v>652664.67</v>
+      </c>
+      <c r="E183" s="32" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B184" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C184" s="32" t="inlineStr">
+        <is>
+          <t>Operating Exp. Recovery</t>
+        </is>
+      </c>
+      <c r="D184" s="41" t="n">
+        <v>132892</v>
+      </c>
+      <c r="E184" s="32" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B185" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C185" s="32" t="inlineStr">
+        <is>
+          <t>Tax Recovery</t>
+        </is>
+      </c>
+      <c r="D185" s="41" t="n">
+        <v>378242</v>
+      </c>
+      <c r="E185" s="32" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B186" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C186" s="32" t="inlineStr">
+        <is>
+          <t>Insurance Recovery</t>
+        </is>
+      </c>
+      <c r="D186" s="41" t="n">
+        <v>18696</v>
+      </c>
+      <c r="E186" s="32" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B187" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C187" s="32" t="inlineStr">
+        <is>
+          <t>Prior Year Reconciliations</t>
+        </is>
+      </c>
+      <c r="D187" s="41" t="n">
+        <v>-23912.57</v>
+      </c>
+      <c r="E187" s="32" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B188" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C188" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D188" s="39">
+        <f>SUM(D182:D187)</f>
+        <v/>
+      </c>
+      <c r="E188" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $1,158,591.35. Gross Revenue as printed. Base rent ÷ 200,000 SF = $3.26/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B189" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C189" s="32" t="inlineStr">
+        <is>
+          <t>Electricity (rec)</t>
+        </is>
+      </c>
+      <c r="D189" s="41" t="n">
+        <v>216.16</v>
+      </c>
+      <c r="E189" s="32" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B190" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C190" s="32" t="inlineStr">
+        <is>
+          <t>Water/Sewer (rec)</t>
+        </is>
+      </c>
+      <c r="D190" s="41" t="n">
+        <v>31675.08</v>
+      </c>
+      <c r="E190" s="32" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B191" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C191" s="32" t="inlineStr">
+        <is>
+          <t>Extermination (rec)</t>
+        </is>
+      </c>
+      <c r="D191" s="41" t="n">
+        <v>2240</v>
+      </c>
+      <c r="E191" s="32" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B192" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C192" s="32" t="inlineStr">
+        <is>
+          <t>Fire Protection/Security (rec)</t>
+        </is>
+      </c>
+      <c r="D192" s="41" t="n">
+        <v>3326</v>
+      </c>
+      <c r="E192" s="32" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B193" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C193" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Electrical (rec)</t>
+        </is>
+      </c>
+      <c r="D193" s="41" t="n">
+        <v>646</v>
+      </c>
+      <c r="E193" s="32" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B194" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C194" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - General Building (rec)</t>
+        </is>
+      </c>
+      <c r="D194" s="41" t="n">
+        <v>510</v>
+      </c>
+      <c r="E194" s="32" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B195" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C195" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Grounds (rec)</t>
+        </is>
+      </c>
+      <c r="D195" s="41" t="n">
+        <v>1665</v>
+      </c>
+      <c r="E195" s="32" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B196" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C196" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Landscape/Sprinkler (rec)</t>
+        </is>
+      </c>
+      <c r="D196" s="41" t="n">
+        <v>13440.66</v>
+      </c>
+      <c r="E196" s="32" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B197" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C197" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - HVAC (rec)</t>
+        </is>
+      </c>
+      <c r="D197" s="41" t="n">
+        <v>1022.84</v>
+      </c>
+      <c r="E197" s="32" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B198" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C198" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot (rec)</t>
+        </is>
+      </c>
+      <c r="D198" s="41" t="n">
+        <v>19891.2</v>
+      </c>
+      <c r="E198" s="32" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B199" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C199" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Parking Lot Snow Removal (rec)</t>
+        </is>
+      </c>
+      <c r="D199" s="41" t="n">
+        <v>19352.66</v>
+      </c>
+      <c r="E199" s="32" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B200" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C200" s="32" t="inlineStr">
+        <is>
+          <t>R&amp;M - Roof (rec)</t>
+        </is>
+      </c>
+      <c r="D200" s="41" t="n">
+        <v>861.9299999999999</v>
+      </c>
+      <c r="E200" s="32" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B201" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C201" s="32" t="inlineStr">
+        <is>
+          <t>Management Fees (rec)</t>
+        </is>
+      </c>
+      <c r="D201" s="41" t="n">
+        <v>35162.86</v>
+      </c>
+      <c r="E201" s="32" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B202" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C202" s="32" t="inlineStr">
+        <is>
+          <t>Other Expense (rec)</t>
+        </is>
+      </c>
+      <c r="D202" s="41" t="n">
+        <v>181.59</v>
+      </c>
+      <c r="E202" s="32" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B203" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C203" s="32" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes (fixed)</t>
+        </is>
+      </c>
+      <c r="D203" s="41" t="n">
+        <v>366203.26</v>
+      </c>
+      <c r="E203" s="32" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="32" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B204" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C204" s="32" t="inlineStr">
+        <is>
+          <t>Insurance (fixed)</t>
+        </is>
+      </c>
+      <c r="D204" s="41" t="n">
+        <v>21571</v>
+      </c>
+      <c r="E204" s="32" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="38" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter — FY2022</t>
+        </is>
+      </c>
+      <c r="B205" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C205" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D205" s="39">
+        <f>SUM(D189:D204)</f>
+        <v/>
+      </c>
+      <c r="E205" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $517,966.24. Recoverable OpEx $130,191.98 + fixed $387,774.26. Income from operations $640,625.11. Below that line: G&amp;A misc $100.00 and lease commission $24,325.08 → total expenses $542,391.32, operating summary $616,200.03.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="33" t="inlineStr">
+        <is>
+          <t>Denver Distribution Center and Majestic Commercenter figures are accrual, year-to-date, and exclude debt service from the operating-expense totals (financing is listed separately). 2780 N. Tower Road totals follow the owner's QuickBooks P&amp;L and DO include depreciation and amortization inside Total Expense; interest is shown separately as non-operating.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A206:E206"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5249,7 +9496,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,7 +9631,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -189,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -309,6 +309,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -674,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1158,43 +1161,141 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
+    <row r="20">
+      <c r="A20" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>R0132030_Mega_Rent_roll_and_Operating_income.pdf</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="inlineStr">
+        <is>
+          <t>Rent rolls (3 dates) + 12-month detail income statement + income proforma</t>
+        </is>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 LLC — 200,090 SF, Aurora</t>
+        </is>
+      </c>
+      <c r="E20" s="32" t="inlineStr">
+        <is>
+          <t>RR 06/30/23, 12/31/23, 06/01/24; IS FY2024</t>
+        </is>
+      </c>
+      <c r="F20" s="32" t="inlineStr">
+        <is>
+          <t>Major Properties (R5510DISM1/R5515RRMSI); printed 04/25/2025 — Petitioner's Exhibits G &amp; H</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="32" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>Dollar_General_to_Build_Mega_Warehouse_at_HighPoint_Elevated_Industrial__Logistics_Park__Mile_High_CRE.pdf</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="inlineStr">
+        <is>
+          <t>Trade-press news article (market context only)</t>
+        </is>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>HighPoint Elevated I&amp;L Park, Aurora — not a subject property</t>
+        </is>
+      </c>
+      <c r="E21" s="32" t="inlineStr">
+        <is>
+          <t>Published 08/09/2022 (saved 10/26/2022)</t>
+        </is>
+      </c>
+      <c r="F21" s="32" t="inlineStr">
+        <is>
+          <t>Mile High CRE (milehighcre.com)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>R0180834_584_Mega_or_447_Cold_Storage_rent_roll_and_income_statement_1.pdf</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="inlineStr">
+        <is>
+          <t>Rent roll + income statement (accrual)</t>
+        </is>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>Denver Distribution Center (ct912501) — 553,757 SF</t>
+        </is>
+      </c>
+      <c r="E22" s="32" t="inlineStr">
+        <is>
+          <t>RR as of 01/01/2025; IS Dec-2024 YTD</t>
+        </is>
+      </c>
+      <c r="F22" s="32" t="inlineStr">
+        <is>
+          <t>Duplicate of doc #10 — identical content, not re-entered</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>R0083953 rent roll: the 6/30/2024 recap page shows Peco Pallet (455-C-CU) expiring 3/31/2030 while the Colliers rent roll for the same date shows 3/31/2025; both dates are reproduced as printed. Docs #11 and #12 are byte-different files with identical content (same P&amp;L), so FY2024/FY2023 for 2780 N. Tower Rd is entered once. No assessor or petitioner opinion of value appears in any of these five documents, so no rows were added to 'Assessments &amp; Valuation'.</t>
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Doc #16 (Dollar General / HighPoint Elevated) is a news article about a 919,000 SF build-to-suit at a third-party development in Aurora. It contains no rent roll, lease or income/expense data for any subject property, so it is indexed here for context only and given no Property Master row — consistent with the database scope, which excludes market/comparable support material. Doc #17 is byte-different from doc #10 but its extracted text is identical page-for-page, so R0180834 was not entered twice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1206,7 +1307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2528,7 +2629,104 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="33" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>R0132030</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>R0132030</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 LLC</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>—  (not stated; Aurora, CO 80011)</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I16" s="32" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J16" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 LLC</t>
+        </is>
+      </c>
+      <c r="K16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L16" s="32" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M16" s="32" t="inlineStr">
+        <is>
+          <t>Multi-tenant (2 leased + 1 vacant suite)</t>
+        </is>
+      </c>
+      <c r="N16" s="32" t="n"/>
+      <c r="O16" s="32" t="n"/>
+      <c r="P16" s="34" t="n"/>
+      <c r="Q16" s="34" t="n">
+        <v>200090</v>
+      </c>
+      <c r="R16" s="32" t="n"/>
+      <c r="S16" s="32" t="n"/>
+      <c r="T16" s="32" t="inlineStr">
+        <is>
+          <t>75.01% occupied / 24.99% vacant (50,002 SF) at all 3 rent-roll dates</t>
+        </is>
+      </c>
+      <c r="U16" s="35" t="n"/>
+      <c r="V16" s="32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W16" s="35" t="n">
+        <v>13402900</v>
+      </c>
+      <c r="X16" s="32" t="inlineStr">
+        <is>
+          <t>Major Properties (mgr N. Creighton; broker R. Hertel)</t>
+        </is>
+      </c>
+      <c r="Y16" s="32" t="inlineStr">
+        <is>
+          <t>R0132030 rent roll &amp; operating income.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>Year built for R0180834 is not stated in its rent roll or income statement. Addresses/ZIPs marked "—" do not appear in the source document; 2780 N. Tower Rd city is inferred from the street address. Building areas are the leasable areas printed on each rent roll (R0180834: 553,757 SF; R0212546: 377,729 SF per the document title, used for the $/SF checks below; R0083953: 200,000 SF).</t>
         </is>
@@ -2536,7 +2734,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A16:Y16"/>
+    <mergeCell ref="A17:Y17"/>
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="A1:Y1"/>
   </mergeCells>
@@ -2550,7 +2748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4342,18 +4540,622 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="inlineStr">
+      <c r="A49" s="36" t="inlineStr">
+        <is>
+          <t>Commercenter #22 LLC (R0132030), Aurora — rent roll at three dates; 200,090 SF, 24.99% vacant throughout</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B50" s="32" t="inlineStr">
+        <is>
+          <t>Bldg 22 / 206422</t>
+        </is>
+      </c>
+      <c r="C50" s="32" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington</t>
+        </is>
+      </c>
+      <c r="D50" s="32" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="n">
+        <v>28119.36</v>
+      </c>
+      <c r="F50" s="35" t="n">
+        <v>337432.32</v>
+      </c>
+      <c r="G50" s="41" t="n">
+        <v>5.2045</v>
+      </c>
+      <c r="H50" s="32" t="inlineStr">
+        <is>
+          <t>8/1/2015</t>
+        </is>
+      </c>
+      <c r="I50" s="32" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="J50" s="32" t="inlineStr">
+        <is>
+          <t>As of 06/01/24</t>
+        </is>
+      </c>
+      <c r="K50" s="41" t="n"/>
+      <c r="L50" s="41" t="n"/>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>64,835 SF. 32.40% of building; monthly net rent $0.4337/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B51" s="32" t="inlineStr">
+        <is>
+          <t>Bldg 22 / 206422</t>
+        </is>
+      </c>
+      <c r="C51" s="32" t="inlineStr">
+        <is>
+          <t>Steelcase, Inc.</t>
+        </is>
+      </c>
+      <c r="D51" s="32" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E51" s="41" t="n">
+        <v>39219.25</v>
+      </c>
+      <c r="F51" s="35" t="n">
+        <v>470631</v>
+      </c>
+      <c r="G51" s="41" t="n">
+        <v>5.5204</v>
+      </c>
+      <c r="H51" s="32" t="inlineStr">
+        <is>
+          <t>10/1/2019</t>
+        </is>
+      </c>
+      <c r="I51" s="32" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="J51" s="32" t="inlineStr">
+        <is>
+          <t>As of 06/01/24</t>
+        </is>
+      </c>
+      <c r="K51" s="41" t="n"/>
+      <c r="L51" s="41" t="n"/>
+      <c r="M51" s="32" t="inlineStr">
+        <is>
+          <t>85,253 SF. 42.61% of building; monthly net rent $0.4600/SF. Notice address: Steelcase Global Real Estate, 980 N Michigan Ave #1000, Chicago IL 60611.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B52" s="32" t="inlineStr">
+        <is>
+          <t>VACANT</t>
+        </is>
+      </c>
+      <c r="C52" s="32" t="inlineStr">
+        <is>
+          <t>Vacant suite — 50,002 SF (24.99% of building)</t>
+        </is>
+      </c>
+      <c r="D52" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E52" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="32" t="n"/>
+      <c r="I52" s="32" t="n"/>
+      <c r="J52" s="32" t="inlineStr">
+        <is>
+          <t>As of 06/01/24</t>
+        </is>
+      </c>
+      <c r="K52" s="41" t="n"/>
+      <c r="L52" s="41" t="n"/>
+      <c r="M52" s="32" t="inlineStr">
+        <is>
+          <t>No rent; 150,088 SF occupied of 200,090 SF (75.01%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B53" s="38" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C53" s="38" t="inlineStr">
+        <is>
+          <t>Grand total — Project Commercenter #22 LLC</t>
+        </is>
+      </c>
+      <c r="D53" s="38" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E53" s="39">
+        <f>SUM(E50:E52)</f>
+        <v/>
+      </c>
+      <c r="F53" s="40">
+        <f>SUM(F50:F52)</f>
+        <v/>
+      </c>
+      <c r="G53" s="39" t="n"/>
+      <c r="H53" s="38" t="n"/>
+      <c r="I53" s="38" t="n"/>
+      <c r="J53" s="38" t="inlineStr">
+        <is>
+          <t>As of 06/01/24</t>
+        </is>
+      </c>
+      <c r="K53" s="39" t="n"/>
+      <c r="L53" s="39" t="n"/>
+      <c r="M53" s="38" t="inlineStr">
+        <is>
+          <t>Printed grand total $67,338.61/mo and $808,063.32/yr on 200,090 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B54" s="32" t="inlineStr">
+        <is>
+          <t>Bldg 22 / 206422</t>
+        </is>
+      </c>
+      <c r="C54" s="32" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington</t>
+        </is>
+      </c>
+      <c r="D54" s="32" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E54" s="41" t="n">
+        <v>28119.36</v>
+      </c>
+      <c r="F54" s="35" t="n">
+        <v>337432.32</v>
+      </c>
+      <c r="G54" s="41" t="n">
+        <v>5.2045</v>
+      </c>
+      <c r="H54" s="32" t="inlineStr">
+        <is>
+          <t>8/1/2015</t>
+        </is>
+      </c>
+      <c r="I54" s="32" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="J54" s="32" t="inlineStr">
+        <is>
+          <t>As of 12/31/23</t>
+        </is>
+      </c>
+      <c r="K54" s="41" t="n"/>
+      <c r="L54" s="41" t="n"/>
+      <c r="M54" s="32" t="inlineStr">
+        <is>
+          <t>64,835 SF. Rent unchanged from the 06/30/23 roll onward at $0.4337/SF/mo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B55" s="32" t="inlineStr">
+        <is>
+          <t>Bldg 22 / 206422</t>
+        </is>
+      </c>
+      <c r="C55" s="32" t="inlineStr">
+        <is>
+          <t>Steelcase, Inc.</t>
+        </is>
+      </c>
+      <c r="D55" s="32" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E55" s="41" t="n">
+        <v>38450.25</v>
+      </c>
+      <c r="F55" s="35" t="n">
+        <v>461403</v>
+      </c>
+      <c r="G55" s="41" t="n">
+        <v>5.4122</v>
+      </c>
+      <c r="H55" s="32" t="inlineStr">
+        <is>
+          <t>10/1/2019</t>
+        </is>
+      </c>
+      <c r="I55" s="32" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="J55" s="32" t="inlineStr">
+        <is>
+          <t>As of 12/31/23</t>
+        </is>
+      </c>
+      <c r="K55" s="41" t="n"/>
+      <c r="L55" s="41" t="n"/>
+      <c r="M55" s="32" t="inlineStr">
+        <is>
+          <t>85,253 SF. Monthly net rent $0.4510/SF; steps to $0.4600 by 06/01/24.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B56" s="32" t="inlineStr">
+        <is>
+          <t>VACANT</t>
+        </is>
+      </c>
+      <c r="C56" s="32" t="inlineStr">
+        <is>
+          <t>Vacant suite — 50,002 SF (24.99% of building)</t>
+        </is>
+      </c>
+      <c r="D56" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="32" t="n"/>
+      <c r="I56" s="32" t="n"/>
+      <c r="J56" s="32" t="inlineStr">
+        <is>
+          <t>As of 12/31/23</t>
+        </is>
+      </c>
+      <c r="K56" s="41" t="n"/>
+      <c r="L56" s="41" t="n"/>
+      <c r="M56" s="32" t="inlineStr">
+        <is>
+          <t>No rent; 150,088 SF occupied of 200,090 SF (75.01%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B57" s="38" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C57" s="38" t="inlineStr">
+        <is>
+          <t>Grand total — Project Commercenter #22 LLC</t>
+        </is>
+      </c>
+      <c r="D57" s="38" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E57" s="39">
+        <f>SUM(E54:E56)</f>
+        <v/>
+      </c>
+      <c r="F57" s="40">
+        <f>SUM(F54:F56)</f>
+        <v/>
+      </c>
+      <c r="G57" s="39" t="n"/>
+      <c r="H57" s="38" t="n"/>
+      <c r="I57" s="38" t="n"/>
+      <c r="J57" s="38" t="inlineStr">
+        <is>
+          <t>As of 12/31/23</t>
+        </is>
+      </c>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="39" t="n"/>
+      <c r="M57" s="38" t="inlineStr">
+        <is>
+          <t>Printed grand total $66,569.61/mo and $798,835.32/yr on 200,090 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B58" s="32" t="inlineStr">
+        <is>
+          <t>Bldg 22 / 206422</t>
+        </is>
+      </c>
+      <c r="C58" s="32" t="inlineStr">
+        <is>
+          <t>Expeditors International of Washington</t>
+        </is>
+      </c>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E58" s="41" t="n">
+        <v>27433.52</v>
+      </c>
+      <c r="F58" s="35" t="n">
+        <v>329202.24</v>
+      </c>
+      <c r="G58" s="41" t="n">
+        <v>5.0775</v>
+      </c>
+      <c r="H58" s="32" t="inlineStr">
+        <is>
+          <t>8/1/2015</t>
+        </is>
+      </c>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="J58" s="32" t="inlineStr">
+        <is>
+          <t>As of 06/30/23</t>
+        </is>
+      </c>
+      <c r="K58" s="41" t="n"/>
+      <c r="L58" s="41" t="n"/>
+      <c r="M58" s="32" t="inlineStr">
+        <is>
+          <t>64,835 SF. Monthly net rent $0.4231/SF; steps to $0.4337 by 12/31/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B59" s="32" t="inlineStr">
+        <is>
+          <t>Bldg 22 / 206422</t>
+        </is>
+      </c>
+      <c r="C59" s="32" t="inlineStr">
+        <is>
+          <t>Steelcase, Inc.</t>
+        </is>
+      </c>
+      <c r="D59" s="32" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E59" s="41" t="n">
+        <v>38450.25</v>
+      </c>
+      <c r="F59" s="35" t="n">
+        <v>461403</v>
+      </c>
+      <c r="G59" s="41" t="n">
+        <v>5.4122</v>
+      </c>
+      <c r="H59" s="32" t="inlineStr">
+        <is>
+          <t>10/1/2019</t>
+        </is>
+      </c>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>12/31/2024</t>
+        </is>
+      </c>
+      <c r="J59" s="32" t="inlineStr">
+        <is>
+          <t>As of 06/30/23</t>
+        </is>
+      </c>
+      <c r="K59" s="41" t="n"/>
+      <c r="L59" s="41" t="n"/>
+      <c r="M59" s="32" t="inlineStr">
+        <is>
+          <t>85,253 SF. Monthly net rent $0.4510/SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B60" s="32" t="inlineStr">
+        <is>
+          <t>VACANT</t>
+        </is>
+      </c>
+      <c r="C60" s="32" t="inlineStr">
+        <is>
+          <t>Vacant suite — 50,002 SF (24.99% of building)</t>
+        </is>
+      </c>
+      <c r="D60" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E60" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="32" t="n"/>
+      <c r="I60" s="32" t="n"/>
+      <c r="J60" s="32" t="inlineStr">
+        <is>
+          <t>As of 06/30/23</t>
+        </is>
+      </c>
+      <c r="K60" s="41" t="n"/>
+      <c r="L60" s="41" t="n"/>
+      <c r="M60" s="32" t="inlineStr">
+        <is>
+          <t>No rent; 150,088 SF occupied of 200,090 SF (75.01%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22</t>
+        </is>
+      </c>
+      <c r="B61" s="38" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C61" s="38" t="inlineStr">
+        <is>
+          <t>Grand total — Project Commercenter #22 LLC</t>
+        </is>
+      </c>
+      <c r="D61" s="38" t="inlineStr">
+        <is>
+          <t>Multi-Tenant Net</t>
+        </is>
+      </c>
+      <c r="E61" s="39">
+        <f>SUM(E58:E60)</f>
+        <v/>
+      </c>
+      <c r="F61" s="40">
+        <f>SUM(F58:F60)</f>
+        <v/>
+      </c>
+      <c r="G61" s="39" t="n"/>
+      <c r="H61" s="38" t="n"/>
+      <c r="I61" s="38" t="n"/>
+      <c r="J61" s="38" t="inlineStr">
+        <is>
+          <t>As of 06/30/23</t>
+        </is>
+      </c>
+      <c r="K61" s="39" t="n"/>
+      <c r="L61" s="39" t="n"/>
+      <c r="M61" s="38" t="inlineStr">
+        <is>
+          <t>Printed grand total $65,883.77/mo and $790,605.24/yr on 200,090 SF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>Commercenter #22 rents are triple-net base rents from the "Rent Roll Master Industrial" report; the annual net rent PSF column is printed on the roll itself. Only two suites are leased — the 50,002 SF balance is vacant at every date shown, so the property totals are 75.01% of building area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="33" t="inlineStr">
         <is>
           <t>Rent PSF is annual base rent ÷ leasable SF as printed on each rent roll. Denver Distribution Center rents are billed monthly per SF ($0.54 → $0.56); the annual PSF shown here is 12× that rate. 2780 N. Tower Road has no rent roll in the file — its rent is taken from the P&amp;L income line and divided by the 377,729 SF in the document title.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
     <mergeCell ref="A18:M18"/>
+    <mergeCell ref="A62:M62"/>
     <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A65:M65"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A49:M49"/>
   </mergeCells>
@@ -4367,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4602,238 +5404,301 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 (R0132030)</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C11" s="35" t="n"/>
+      <c r="D11" s="41" t="n"/>
+      <c r="E11" s="35" t="n">
+        <v>13402900</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="G11" s="35" t="n"/>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>R0132030 Exhibit H (proforma)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1"/>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="21" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="20" t="n"/>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="21" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="21" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>4832500</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>17608 E. 24th Dr</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>209100</v>
+        <v>359394</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>-10455</v>
+        <v>-17970</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>198645</v>
+        <v>341424</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>-15892</v>
+        <v>-27314</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>182753</v>
+        <v>314110</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="H17" s="14" t="n">
-        <v>3050000</v>
+        <v>4832500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>12260 Pennsylvania St</t>
+          <t>17608 E. 24th Dr</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>237290</v>
+        <v>209100</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>-16610</v>
+        <v>-10455</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>220680</v>
+        <v>198645</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>-22068</v>
+        <v>-15892</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>198612</v>
+        <v>182753</v>
       </c>
       <c r="G18" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="H18" s="14" t="n">
-        <v>2837000</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>6770 E. 56th Ave</t>
+          <t>12260 Pennsylvania St</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>115824</v>
+        <v>237290</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>-5791</v>
+        <v>-16610</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>110033</v>
+        <v>220680</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>-5502</v>
+        <v>-22068</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>104531</v>
+        <v>198612</v>
       </c>
       <c r="G19" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>1493302</v>
+        <v>2837000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>1493302</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B21" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C21" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D21" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E21" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F21" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G21" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H21" s="14" t="n">
         <v>2460577</v>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 (R0132030)</t>
+        </is>
+      </c>
+      <c r="B22" s="35" t="n">
+        <v>1250563</v>
+      </c>
+      <c r="C22" s="35" t="n">
+        <v>-125056</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>1125506</v>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>-56275</v>
+      </c>
+      <c r="F22" s="35" t="n">
+        <v>1069231</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>0.07630000000000001</v>
+      </c>
+      <c r="H22" s="35" t="n">
+        <v>14013512</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
         </is>
       </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="21" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>Commercenter #22 (R0132030): the petitioner's proforma uses PGI $6.25/SF on 200,090 SF, 10% vacancy and collection loss, a 5% expense allowance, and a 7.63% loaded cap rate (7.00% market cap + 0.63% ETR at 41.259 Metro District mills), giving $14,013,512 as-if-stabilized ($70.04/SF, rounded $14,013,500). A further "Adjustment for 67% Vacancy" of $(610,600) yields the $13,402,900 indicated 2025 value shown in section A ($66.99/SF). The 67% label is as printed and does not match the 24.99% vacancy on the rent roll. No assessor/county value appears in the document, so that column is left blank.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
+  <mergeCells count="7">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4845,7 +5710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -5115,23 +5980,45 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 (R0132030) — FY2024</t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="n">
+        <v>1648443.25</v>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>872475.4300000001</v>
+      </c>
+      <c r="D15" s="35">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>Accrual 12-month detail income statement. Net = operating income $775,967.82 (printed). Excludes $457,397.92 mortgage interest and $743,031.13 other (income)/expense — after those the printed bottom line is a net loss of $(424,461.23).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
         </is>
       </c>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="21" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5143,7 +6030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E206"/>
+  <dimension ref="A1:E276"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9450,7 +10337,1457 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="33" t="inlineStr">
+      <c r="A206" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B206" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C206" s="32" t="inlineStr">
+        <is>
+          <t>4015 Industrial Rental Income</t>
+        </is>
+      </c>
+      <c r="D206" s="41" t="n">
+        <v>865747.0600000001</v>
+      </c>
+      <c r="E206" s="32" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B207" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C207" s="32" t="inlineStr">
+        <is>
+          <t>4035 Rent Concessions</t>
+        </is>
+      </c>
+      <c r="D207" s="41" t="n">
+        <v>35897.03</v>
+      </c>
+      <c r="E207" s="32" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B208" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C208" s="32" t="inlineStr">
+        <is>
+          <t>4040 Rent Amortization</t>
+        </is>
+      </c>
+      <c r="D208" s="41" t="n">
+        <v>-39646.92</v>
+      </c>
+      <c r="E208" s="32" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B209" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C209" s="32" t="inlineStr">
+        <is>
+          <t>4037 Rent Above/Below Market</t>
+        </is>
+      </c>
+      <c r="D209" s="41" t="n">
+        <v>10078.57</v>
+      </c>
+      <c r="E209" s="32" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B210" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C210" s="32" t="inlineStr">
+        <is>
+          <t>4135 Common Area Reimbursement</t>
+        </is>
+      </c>
+      <c r="D210" s="41" t="n">
+        <v>80298.07000000001</v>
+      </c>
+      <c r="E210" s="32" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B211" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C211" s="32" t="inlineStr">
+        <is>
+          <t>4140 Insurance Reimbursement</t>
+        </is>
+      </c>
+      <c r="D211" s="41" t="n">
+        <v>21465.97</v>
+      </c>
+      <c r="E211" s="32" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B212" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C212" s="32" t="inlineStr">
+        <is>
+          <t>4145 Real Estate Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D212" s="41" t="n">
+        <v>496749.45</v>
+      </c>
+      <c r="E212" s="32" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B213" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C213" s="32" t="inlineStr">
+        <is>
+          <t>4150 Utilities Reimbursement</t>
+        </is>
+      </c>
+      <c r="D213" s="41" t="n">
+        <v>39775.44</v>
+      </c>
+      <c r="E213" s="32" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B214" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C214" s="32" t="inlineStr">
+        <is>
+          <t>4158 Direct Tenant Reimbursement</t>
+        </is>
+      </c>
+      <c r="D214" s="41" t="n">
+        <v>8775</v>
+      </c>
+      <c r="E214" s="32" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B215" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C215" s="32" t="inlineStr">
+        <is>
+          <t>4160 Management Fee Reimbursement</t>
+        </is>
+      </c>
+      <c r="D215" s="41" t="n">
+        <v>49158.85</v>
+      </c>
+      <c r="E215" s="32" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B216" s="32" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C216" s="32" t="inlineStr">
+        <is>
+          <t>4175 Reserve Income</t>
+        </is>
+      </c>
+      <c r="D216" s="41" t="n">
+        <v>80144.73</v>
+      </c>
+      <c r="E216" s="32" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B217" s="38" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C217" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE</t>
+        </is>
+      </c>
+      <c r="D217" s="39">
+        <f>SUM(D206:D216)</f>
+        <v/>
+      </c>
+      <c r="E217" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $1,648,443.25. Base industrial rent $865,747.06 = $4.33/SF on 200,090 SF; reimbursements and reserve income make up the balance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B218" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C218" s="32" t="inlineStr">
+        <is>
+          <t>5115 Insurance-Fire &amp; Extended</t>
+        </is>
+      </c>
+      <c r="D218" s="41" t="n">
+        <v>19673</v>
+      </c>
+      <c r="E218" s="32" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B219" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C219" s="32" t="inlineStr">
+        <is>
+          <t>5120 Insurance-Liability</t>
+        </is>
+      </c>
+      <c r="D219" s="41" t="n">
+        <v>6635</v>
+      </c>
+      <c r="E219" s="32" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B220" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C220" s="32" t="inlineStr">
+        <is>
+          <t>5205 Backflow Testing &amp; Repair</t>
+        </is>
+      </c>
+      <c r="D220" s="41" t="n">
+        <v>360</v>
+      </c>
+      <c r="E220" s="32" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B221" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C221" s="32" t="inlineStr">
+        <is>
+          <t>5235 Door Repairs</t>
+        </is>
+      </c>
+      <c r="D221" s="41" t="n">
+        <v>-1795.72</v>
+      </c>
+      <c r="E221" s="32" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B222" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C222" s="32" t="inlineStr">
+        <is>
+          <t>5250 Fire Life Safety</t>
+        </is>
+      </c>
+      <c r="D222" s="41" t="n">
+        <v>6070.35</v>
+      </c>
+      <c r="E222" s="32" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B223" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C223" s="32" t="inlineStr">
+        <is>
+          <t>5275 HVAC</t>
+        </is>
+      </c>
+      <c r="D223" s="41" t="n">
+        <v>3979.14</v>
+      </c>
+      <c r="E223" s="32" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B224" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C224" s="32" t="inlineStr">
+        <is>
+          <t>5280 Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D224" s="41" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="E224" s="32" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B225" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C225" s="32" t="inlineStr">
+        <is>
+          <t>5285 Keys/Card Access</t>
+        </is>
+      </c>
+      <c r="D225" s="41" t="n">
+        <v>467.53</v>
+      </c>
+      <c r="E225" s="32" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B226" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C226" s="32" t="inlineStr">
+        <is>
+          <t>5290 Landscaping</t>
+        </is>
+      </c>
+      <c r="D226" s="41" t="n">
+        <v>20192.54</v>
+      </c>
+      <c r="E226" s="32" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B227" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C227" s="32" t="inlineStr">
+        <is>
+          <t>5305 Lighting</t>
+        </is>
+      </c>
+      <c r="D227" s="41" t="n">
+        <v>1264.71</v>
+      </c>
+      <c r="E227" s="32" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B228" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C228" s="32" t="inlineStr">
+        <is>
+          <t>5312 Other-DTR</t>
+        </is>
+      </c>
+      <c r="D228" s="41" t="n">
+        <v>5868</v>
+      </c>
+      <c r="E228" s="32" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B229" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C229" s="32" t="inlineStr">
+        <is>
+          <t>5315 Painting</t>
+        </is>
+      </c>
+      <c r="D229" s="41" t="n">
+        <v>1285</v>
+      </c>
+      <c r="E229" s="32" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B230" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C230" s="32" t="inlineStr">
+        <is>
+          <t>5320 Parking Lot</t>
+        </is>
+      </c>
+      <c r="D230" s="41" t="n">
+        <v>41800.84</v>
+      </c>
+      <c r="E230" s="32" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B231" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C231" s="32" t="inlineStr">
+        <is>
+          <t>5345 Repairs</t>
+        </is>
+      </c>
+      <c r="D231" s="41" t="n">
+        <v>2466.5</v>
+      </c>
+      <c r="E231" s="32" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B232" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C232" s="32" t="inlineStr">
+        <is>
+          <t>5350 Roof</t>
+        </is>
+      </c>
+      <c r="D232" s="41" t="n">
+        <v>9690.92</v>
+      </c>
+      <c r="E232" s="32" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B233" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C233" s="32" t="inlineStr">
+        <is>
+          <t>5365 Signs</t>
+        </is>
+      </c>
+      <c r="D233" s="41" t="n">
+        <v>481.36</v>
+      </c>
+      <c r="E233" s="32" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B234" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C234" s="32" t="inlineStr">
+        <is>
+          <t>5370 Snow Removal</t>
+        </is>
+      </c>
+      <c r="D234" s="41" t="n">
+        <v>20425.46</v>
+      </c>
+      <c r="E234" s="32" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B235" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C235" s="32" t="inlineStr">
+        <is>
+          <t>5380 Sweeping</t>
+        </is>
+      </c>
+      <c r="D235" s="41" t="n">
+        <v>2713.1</v>
+      </c>
+      <c r="E235" s="32" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B236" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C236" s="32" t="inlineStr">
+        <is>
+          <t>5385 Window Washing</t>
+        </is>
+      </c>
+      <c r="D236" s="41" t="n">
+        <v>520</v>
+      </c>
+      <c r="E236" s="32" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B237" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C237" s="32" t="inlineStr">
+        <is>
+          <t>5400 Management Fees</t>
+        </is>
+      </c>
+      <c r="D237" s="41" t="n">
+        <v>48882.34</v>
+      </c>
+      <c r="E237" s="32" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B238" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C238" s="32" t="inlineStr">
+        <is>
+          <t>5500 Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D238" s="41" t="n">
+        <v>440287.09</v>
+      </c>
+      <c r="E238" s="32" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B239" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C239" s="32" t="inlineStr">
+        <is>
+          <t>5610 Utilities - Electricity</t>
+        </is>
+      </c>
+      <c r="D239" s="41" t="n">
+        <v>10996.47</v>
+      </c>
+      <c r="E239" s="32" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B240" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C240" s="32" t="inlineStr">
+        <is>
+          <t>5615 Utilities-Fire Service</t>
+        </is>
+      </c>
+      <c r="D240" s="41" t="n">
+        <v>478.25</v>
+      </c>
+      <c r="E240" s="32" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B241" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C241" s="32" t="inlineStr">
+        <is>
+          <t>5620 Utilities-Gas/Heating</t>
+        </is>
+      </c>
+      <c r="D241" s="41" t="n">
+        <v>22902.64</v>
+      </c>
+      <c r="E241" s="32" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B242" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C242" s="32" t="inlineStr">
+        <is>
+          <t>5635 Utilities-Water</t>
+        </is>
+      </c>
+      <c r="D242" s="41" t="n">
+        <v>30337.63</v>
+      </c>
+      <c r="E242" s="32" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B243" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C243" s="32" t="inlineStr">
+        <is>
+          <t>6235 Door Repairs</t>
+        </is>
+      </c>
+      <c r="D243" s="41" t="n">
+        <v>1860</v>
+      </c>
+      <c r="E243" s="32" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B244" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C244" s="32" t="inlineStr">
+        <is>
+          <t>6275 HVAC</t>
+        </is>
+      </c>
+      <c r="D244" s="41" t="n">
+        <v>3152.6</v>
+      </c>
+      <c r="E244" s="32" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B245" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C245" s="32" t="inlineStr">
+        <is>
+          <t>6280 Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D245" s="41" t="n">
+        <v>1715.8</v>
+      </c>
+      <c r="E245" s="32" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B246" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C246" s="32" t="inlineStr">
+        <is>
+          <t>6305 Lighting</t>
+        </is>
+      </c>
+      <c r="D246" s="41" t="n">
+        <v>451.92</v>
+      </c>
+      <c r="E246" s="32" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B247" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C247" s="32" t="inlineStr">
+        <is>
+          <t>6315 Painting</t>
+        </is>
+      </c>
+      <c r="D247" s="41" t="n">
+        <v>5570</v>
+      </c>
+      <c r="E247" s="32" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B248" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C248" s="32" t="inlineStr">
+        <is>
+          <t>6320 Parking Lot</t>
+        </is>
+      </c>
+      <c r="D248" s="41" t="n">
+        <v>2652</v>
+      </c>
+      <c r="E248" s="32" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B249" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C249" s="32" t="inlineStr">
+        <is>
+          <t>6335 Plumbing</t>
+        </is>
+      </c>
+      <c r="D249" s="41" t="n">
+        <v>679.79</v>
+      </c>
+      <c r="E249" s="32" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B250" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C250" s="32" t="inlineStr">
+        <is>
+          <t>6345 Repairs</t>
+        </is>
+      </c>
+      <c r="D250" s="41" t="n">
+        <v>17200.71</v>
+      </c>
+      <c r="E250" s="32" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B251" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C251" s="32" t="inlineStr">
+        <is>
+          <t>6500 Property Taxes</t>
+        </is>
+      </c>
+      <c r="D251" s="41" t="n">
+        <v>120240</v>
+      </c>
+      <c r="E251" s="32" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B252" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C252" s="32" t="inlineStr">
+        <is>
+          <t>6610 Utilities - Electricity</t>
+        </is>
+      </c>
+      <c r="D252" s="41" t="n">
+        <v>7170.4</v>
+      </c>
+      <c r="E252" s="32" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B253" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C253" s="32" t="inlineStr">
+        <is>
+          <t>6640 Utilities-Other</t>
+        </is>
+      </c>
+      <c r="D253" s="41" t="n">
+        <v>238.73</v>
+      </c>
+      <c r="E253" s="32" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B254" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C254" s="32" t="inlineStr">
+        <is>
+          <t>8225 Tenant Relations</t>
+        </is>
+      </c>
+      <c r="D254" s="41" t="n">
+        <v>253.8</v>
+      </c>
+      <c r="E254" s="32" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B255" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C255" s="32" t="inlineStr">
+        <is>
+          <t>8420 Prof Service-Legal</t>
+        </is>
+      </c>
+      <c r="D255" s="41" t="n">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="E255" s="32" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B256" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C256" s="32" t="inlineStr">
+        <is>
+          <t>8430 Prof Service-Tax Prep</t>
+        </is>
+      </c>
+      <c r="D256" s="41" t="n">
+        <v>8614.52</v>
+      </c>
+      <c r="E256" s="32" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B257" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C257" s="32" t="inlineStr">
+        <is>
+          <t>8435 Prof Service-Other</t>
+        </is>
+      </c>
+      <c r="D257" s="41" t="n">
+        <v>747.22</v>
+      </c>
+      <c r="E257" s="32" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B258" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C258" s="32" t="inlineStr">
+        <is>
+          <t>8445 Prof Service-Legal (Leasing)</t>
+        </is>
+      </c>
+      <c r="D258" s="41" t="n">
+        <v>5390</v>
+      </c>
+      <c r="E258" s="32" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B259" s="32" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C259" s="32" t="inlineStr">
+        <is>
+          <t>8450 Prof Service-Other Environ</t>
+        </is>
+      </c>
+      <c r="D259" s="41" t="n">
+        <v>447.63</v>
+      </c>
+      <c r="E259" s="32" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B260" s="38" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C260" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="D260" s="39">
+        <f>SUM(D218:D259)</f>
+        <v/>
+      </c>
+      <c r="E260" s="38" t="inlineStr">
+        <is>
+          <t>Printed total: $872,475.43. Real estate taxes $440,287.09 + property taxes $120,240.00 are 64.2% of operating expense. Operating income/(loss) $775,967.82.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B261" s="32" t="inlineStr">
+        <is>
+          <t>Non-operating</t>
+        </is>
+      </c>
+      <c r="C261" s="32" t="inlineStr">
+        <is>
+          <t>6805 Interest - Mortgage</t>
+        </is>
+      </c>
+      <c r="D261" s="41" t="n">
+        <v>457397.92</v>
+      </c>
+      <c r="E261" s="32" t="inlineStr">
+        <is>
+          <t>Printed Total Interest Expense: $457,397.92.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B262" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C262" s="32" t="inlineStr">
+        <is>
+          <t>4605 Interest Income Taxable</t>
+        </is>
+      </c>
+      <c r="D262" s="41" t="n">
+        <v>-21280.12</v>
+      </c>
+      <c r="E262" s="32" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B263" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C263" s="32" t="inlineStr">
+        <is>
+          <t>4860 Insurance Proceeds</t>
+        </is>
+      </c>
+      <c r="D263" s="41" t="n">
+        <v>-35331</v>
+      </c>
+      <c r="E263" s="32" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B264" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C264" s="32" t="inlineStr">
+        <is>
+          <t>8660 Amort-Loan Fees</t>
+        </is>
+      </c>
+      <c r="D264" s="41" t="n">
+        <v>4148.36</v>
+      </c>
+      <c r="E264" s="32" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B265" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C265" s="32" t="inlineStr">
+        <is>
+          <t>8670 Amort-Start Up Costs</t>
+        </is>
+      </c>
+      <c r="D265" s="41" t="n">
+        <v>79290.7</v>
+      </c>
+      <c r="E265" s="32" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B266" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C266" s="32" t="inlineStr">
+        <is>
+          <t>8675 Amort-Capitalized Other</t>
+        </is>
+      </c>
+      <c r="D266" s="41" t="n">
+        <v>1257.25</v>
+      </c>
+      <c r="E266" s="32" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B267" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C267" s="32" t="inlineStr">
+        <is>
+          <t>8680 Amort-Commissions</t>
+        </is>
+      </c>
+      <c r="D267" s="41" t="n">
+        <v>48443.44</v>
+      </c>
+      <c r="E267" s="32" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B268" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C268" s="32" t="inlineStr">
+        <is>
+          <t>8755 Depr-Land Improvements</t>
+        </is>
+      </c>
+      <c r="D268" s="41" t="n">
+        <v>129064.76</v>
+      </c>
+      <c r="E268" s="32" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B269" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C269" s="32" t="inlineStr">
+        <is>
+          <t>8765 Depr-Buildings</t>
+        </is>
+      </c>
+      <c r="D269" s="41" t="n">
+        <v>145543.35</v>
+      </c>
+      <c r="E269" s="32" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B270" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C270" s="32" t="inlineStr">
+        <is>
+          <t>8767 Depr-Buildings Step Up</t>
+        </is>
+      </c>
+      <c r="D270" s="41" t="n">
+        <v>-359014.83</v>
+      </c>
+      <c r="E270" s="32" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="32" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B271" s="32" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C271" s="32" t="inlineStr">
+        <is>
+          <t>8770 Depr-Tenant Improvements</t>
+        </is>
+      </c>
+      <c r="D271" s="41" t="n">
+        <v>32879.56</v>
+      </c>
+      <c r="E271" s="32" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B272" s="38" t="inlineStr">
+        <is>
+          <t>Other (inc)/exp</t>
+        </is>
+      </c>
+      <c r="C272" s="38" t="inlineStr">
+        <is>
+          <t>TOTAL OTHER (INCOME)/EXPENSE — as printed</t>
+        </is>
+      </c>
+      <c r="D272" s="39" t="n">
+        <v>743031.13</v>
+      </c>
+      <c r="E272" s="38" t="inlineStr">
+        <is>
+          <t>Entered as the printed subtotal, NOT as a sum of the lines above: the ten printed line items add to $25,001.47, while the report prints $743,031.13. The $718,029.66 gap is exactly twice the $(359,014.83) Depr-Buildings Step Up credit, i.e. the report adds that credit instead of subtracting it. The printed subtotal is the one consistent with the printed net loss, so it is reproduced here and the line items are reproduced as printed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="38" t="inlineStr">
+        <is>
+          <t>Commercenter #22 — FY2024</t>
+        </is>
+      </c>
+      <c r="B273" s="38" t="inlineStr">
+        <is>
+          <t>Bottom line</t>
+        </is>
+      </c>
+      <c r="C273" s="38" t="inlineStr">
+        <is>
+          <t>NET INCOME/(LOSS)</t>
+        </is>
+      </c>
+      <c r="D273" s="39" t="n">
+        <v>-424461.23</v>
+      </c>
+      <c r="E273" s="38" t="inlineStr">
+        <is>
+          <t>Printed: $(424,461.23) = operating income $775,967.82 − interest $457,397.92 − other $743,031.13. Verified to the cent against the printed figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="33" t="inlineStr">
         <is>
           <t>Denver Distribution Center and Majestic Commercenter figures are accrual, year-to-date, and exclude debt service from the operating-expense totals (financing is listed separately). 2780 N. Tower Road totals follow the owner's QuickBooks P&amp;L and DO include depreciation and amortization inside Total Expense; interest is shown separately as non-operating.</t>
         </is>
@@ -9460,7 +11797,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A206:E206"/>
+    <mergeCell ref="A276:E276"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -656,11 +656,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-07-30  |  8 subject properties, all Adams County, Colorado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Prepared for Carter Equities  |  Updated 2026-08-18  |  22 subject properties, all Adams County, Colorado</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,35 +969,499 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0213618.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Ground Lease (original) — Scannell/Performance Food Group</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Cast Transportation Sub. (R0213618)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Eff. 12/9/2021 (20-yr term + 2x5-yr opt.)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Scannell Properties #534, LLC / Performance Food Group, Inc.</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0213618 2.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Assignment and Assumption of Lease</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Cast Transportation Sub. (R0213618)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>5/24/2024</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Scannell Properties #534, LLC -&gt; Bel Commerce LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0179014.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>1010 Lousell Blvd (Grand Lake), Westminster</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Low Down LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0179050.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal (cost approach) cover letter + cost summary + lease</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>8510 Brighton Rd, Adams County</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Consultus Asset Valuation, Inc. (Jason Letman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>R0100117.pdf</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>3580 W. 72nd Ave, Westminster</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Bohan Family LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>R0100737.pdf</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Valuation protest letter + rent roll + CoStar sale comp</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd, Denver</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025 (rent roll 7/1/2024)</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services, Inc. (Dan George)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>R0099649.pdf</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Petition for Abatement/Refund + income proforma summary</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave, Denver</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2024</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates Cost Reduction Specialists, LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>R0092740.pdf</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St, Commerce City</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / DSP LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>R0085560.pdf</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Valuation protest letter + 4-yr P&amp;L recap + rent rolls</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>14891 East Colfax Avenue</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025 (val. 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services, Inc. (Mike Walter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>R0077963.pdf</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>1750 74th Ave, Commerce City</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Diamond Beall Development LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>R0077789.pdf</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85, Commerce City</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / B and M Equipment Company</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>R0075352.pdf</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>(address illegible), Adams County</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / RJR Investments LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>R0037193.pdf</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>(address illegible), Northglenn area</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Baizer Properties LLC</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>R0030089.pdf</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Valuation protest letter + operating statement + letter of authority</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St, Denver</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2023</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>1st Net Real Estate Services, Inc. (Dan George) / Wallace Associates, Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>R0030085.pdf</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>County Commercial-Industrial Income &amp; Expense Survey</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St, Denver</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Adams County Assessor / Peerless Tyre Co</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
-        </is>
-      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated. R0179050 original 8.4MB PDF could not be downloaded in this session (repeated Google Drive MCP timeout); its data is transcribed from Google Drive's server-side OCR text extract only. Several 325-folder County Income &amp; Expense Survey scans (R0075352, R0037193, R0179014, R0092740) have partially illegible handwritten $ figures per OCR; illegible fields are left blank and flagged in Property Master / Income-Expense notes rather than guessed.</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="21" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed. R0030085/R0030088/R0030089 share adjacent Adams Co. schedule numbers (1719-03-0-05-xxx) suggesting units in the same Huron St. complex; relationship noted in Related Parcels but not confirmed from a plat.</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A31:F31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1517,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2049,6 +2511,1474 @@
       <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>R0092302.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R0213618</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>R0213618</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>R0213618</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Cast Transportation Sub. (BTS)</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Cast Transportation Subdivision (exact street not in extract)</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Bel Commerce LLC (was Scannell Properties #534, LLC)</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Performance Food Group, Inc.</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution (BTS)</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Single (Performance Food Group)</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>28.47</v>
+      </c>
+      <c r="O13" s="8" t="n"/>
+      <c r="P13" s="6" t="n">
+        <v>274992</v>
+      </c>
+      <c r="Q13" s="8" t="n">
+        <v>274992</v>
+      </c>
+      <c r="R13" s="6" t="n"/>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>100% (single tenant)</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>R0213618.pdf; R0213618 2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>R0179014</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>R0179014</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0182505219006 / 0182505219005 (footer; discrepancy)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Grand Lake</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>1010 Lousell Blvd</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>80030 (est.)</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Low Down LLC</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Low Down LLC</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Warehouse / Light Industrial</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (NNN)</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="8" t="n"/>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="n"/>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>R0179014.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>R0179050</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0179050</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>R0179050</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>8500 Brighton Partners (GRNT-AD-002)</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>8510 Brighton Rd</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>8500 Brighton Partners LLC</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>8500 Brighton Partners LLC</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Vehicle Auction/Storage (metal warehouse + paved yard)</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (Insurance Auto Auctions Inc.)</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="8" t="n">
+        <v>1587544</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>11200</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>11200</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>14971919</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>12908000</v>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>R0179050.pdf (Drive OCR text only; 8.4MB PDF download failed repeatedly in session)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>R0100117</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0100117</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>0182505224001</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Bohan Family — Auto Body</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>3580 W. 72nd Ave</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Westminster</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>80030</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Bohan Family Limited Partnership</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Bohan Family Limited Partnership</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Auto Body Shop</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied (portion; grid partly illegible)</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="n"/>
+      <c r="O16" s="8" t="n"/>
+      <c r="P16" s="6" t="n"/>
+      <c r="Q16" s="8" t="n"/>
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>Partial owner-occ. (~688 SF bldg noted; rest illegible)</t>
+        </is>
+      </c>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y16" s="6" t="inlineStr">
+        <is>
+          <t>R0100117.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>R0100737</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0100737</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>1973-35-2-41-001 (cover); Sch. R0017000001</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Northlawn Auto Center</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>80221</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>2626 Sarikov LLC (Mordakhay Sarikov)</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>2626 Sarikov LLC</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Retail - Auto Repair/Service (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant (4 tenants)</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>54014</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v>17458</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>14211</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>1964</v>
+      </c>
+      <c r="S17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T17" s="6" t="inlineStr">
+        <is>
+          <t>100% (per 2024 rent roll)</t>
+        </is>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>2602500</v>
+      </c>
+      <c r="V17" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y17" s="6" t="inlineStr">
+        <is>
+          <t>R0100737.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>R0099649</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0099649</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>182504402007</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Digby Family — 1225 W 64th</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Digby Family LLLP (owner); Navajo Express Inc. (tenant/petitioner)</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>Digby Family LLLP</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>854882</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v>29600</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>29600</v>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v>1974</v>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>8998894</v>
+      </c>
+      <c r="V18" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>R0099649.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>R0092740</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>R0092740</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0182317405014</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>DSP LLC — Newport St</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>80022</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>DSP LLC (c/o Greg Danenhauer)</t>
+        </is>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>DSP LLC</t>
+        </is>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>Industrial / Warehouse</t>
+        </is>
+      </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (3-yr term; new lease 7/1/22-6/30/24)</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="8" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="8" t="n"/>
+      <c r="R19" s="6" t="n"/>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="9" t="n"/>
+      <c r="V19" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X19" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y19" s="6" t="inlineStr">
+        <is>
+          <t>R0092740.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>R0085560</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>R0085560</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>R0085560</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Meineke Car Care — Colfax Ave</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>14891 East Colfax Avenue</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>D Irey Econo Lube LLC et al</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>D Irey Econo Lube LLC et al</t>
+        </is>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>Retail - Auto Service (Meineke Car Care)</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="n"/>
+      <c r="O20" s="8" t="n"/>
+      <c r="P20" s="6" t="n">
+        <v>4264</v>
+      </c>
+      <c r="Q20" s="8" t="n">
+        <v>4264</v>
+      </c>
+      <c r="R20" s="6" t="n"/>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="6" t="inlineStr">
+        <is>
+          <t>100% (per rent roll as of 6/30/24)</t>
+        </is>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>1172600</v>
+      </c>
+      <c r="V20" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="n">
+        <v>870000</v>
+      </c>
+      <c r="X20" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y20" s="6" t="inlineStr">
+        <is>
+          <t>R0085560.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>R0077963</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>R0077963</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>0172131402020</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Diamond Beall Dev — 74th Ave</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>1750 74th Ave</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>80022</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Diamond Beall Development LLC</t>
+        </is>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>Diamond Beall Development LLC</t>
+        </is>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>Industrial (Tank Trailer/Truck Parts &amp; Service)</t>
+        </is>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (NNN)</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="8" t="n"/>
+      <c r="P21" s="6" t="n">
+        <v>18720</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>18720</v>
+      </c>
+      <c r="R21" s="6" t="n"/>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T21" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="U21" s="9" t="n"/>
+      <c r="V21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y21" s="6" t="inlineStr">
+        <is>
+          <t>R0077963.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>R0077789</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>R0077789</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>0172131110004</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>B and M Equipment — Hwy 85</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Commerce City</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>B and M Equipment Company</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>B and M Equipment Company</t>
+        </is>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>Industrial (Recycle Asphalt &amp; Concrete)</t>
+        </is>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied (100%)</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n"/>
+      <c r="P22" s="6" t="n"/>
+      <c r="Q22" s="8" t="n"/>
+      <c r="R22" s="6" t="n"/>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="6" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied</t>
+        </is>
+      </c>
+      <c r="U22" s="9" t="n"/>
+      <c r="V22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y22" s="6" t="inlineStr">
+        <is>
+          <t>R0077789.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>R0075352</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>R0075352</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0172116004003</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>RJR Investments — Adams Co.</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>(address illegible in OCR)</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>RJR Investments LLC (mailing: 8155 Moore St, Arvada CO)</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>RJR Investments LLC</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Warehouse / Office / Shop / Outside Storage</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied (100%, per survey)</t>
+        </is>
+      </c>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="8" t="n"/>
+      <c r="P23" s="6" t="n">
+        <v>12916</v>
+      </c>
+      <c r="Q23" s="8" t="n">
+        <v>12916</v>
+      </c>
+      <c r="R23" s="6" t="n"/>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="6" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied (grid amounts illegible)</t>
+        </is>
+      </c>
+      <c r="U23" s="9" t="n"/>
+      <c r="V23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X23" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y23" s="6" t="inlineStr">
+        <is>
+          <t>R0075352.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>R0037193</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>R0037193</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>0171910307020</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Baizer Properties — Collision Repair</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>(address illegible in OCR; Northglenn, CO 80234 area)</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>Northglenn</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>80234 (est.)</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Baizer Properties LLC</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>Baizer Properties LLC</t>
+        </is>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>Collision Repair Shop</t>
+        </is>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>Single-tenant (NNN)</t>
+        </is>
+      </c>
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n"/>
+      <c r="P24" s="6" t="n"/>
+      <c r="Q24" s="8" t="n"/>
+      <c r="R24" s="6" t="n"/>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="6" t="inlineStr">
+        <is>
+          <t>100% leased</t>
+        </is>
+      </c>
+      <c r="U24" s="9" t="n"/>
+      <c r="V24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X24" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y24" s="6" t="inlineStr">
+        <is>
+          <t>R0037193.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>R0030089</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>R0030089</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>1719-03-0-05-016, 019 (covers R0030088 &amp; R0030089)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (Wallace Associates)</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St / 11450 N. Huron</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Wallace Associates, Inc. (Drake Asset Management LLC, mgr. agent)</t>
+        </is>
+      </c>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>Wallace Associates, Inc.</t>
+        </is>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>Office / Medical (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>Multi-tenant</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="8" t="n"/>
+      <c r="P25" s="6" t="n">
+        <v>30782</v>
+      </c>
+      <c r="Q25" s="8" t="n">
+        <v>30782</v>
+      </c>
+      <c r="R25" s="6" t="n"/>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U25" s="9" t="n">
+        <v>5987885</v>
+      </c>
+      <c r="V25" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="X25" s="6" t="inlineStr">
+        <is>
+          <t>Drake Asset Management LLC</t>
+        </is>
+      </c>
+      <c r="Y25" s="6" t="inlineStr">
+        <is>
+          <t>R0030089.pdf (also covers related R0030088, not in this folder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>R0030085</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>R0030085</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>0171903005007</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Peerless Tyre Co — Huron St</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St, Unit 144 (est.; OCR unclear — parcel numbering suggests same complex as R0030089)</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>80239 (est.)</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Peerless Tyre Co</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>Peerless Tyre Co</t>
+        </is>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>Retail - Tire Store / Light Mechanical Repair</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied (100%)</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="n"/>
+      <c r="O26" s="8" t="n"/>
+      <c r="P26" s="6" t="n">
+        <v>3840</v>
+      </c>
+      <c r="Q26" s="8" t="n">
+        <v>3840</v>
+      </c>
+      <c r="R26" s="6" t="n"/>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T26" s="6" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied</t>
+        </is>
+      </c>
+      <c r="U26" s="9" t="n"/>
+      <c r="V26" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="X26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Y26" s="6" t="inlineStr">
+        <is>
+          <t>R0030085.pdf</t>
         </is>
       </c>
     </row>
@@ -2067,7 +3997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2100,7 +4030,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3131,13 +5060,830 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Cast Transportation Sub., Commerce City (R0213618) — Ground Lease (ex. Scannell Properties #534 LLC, now Bel Commerce LLC)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="20" t="n"/>
+      <c r="M27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Cast Transportation Sub. (R0213618)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>Whole (BTS)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Performance Food Group, Inc.</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>NNN (Ground Lease)</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="6" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>12/9/2021 (Effective; Commencement = 30 days after Substantial Completion)</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>20 yrs from Commencement Date + 2x5-yr options</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>20-yr initial + 2x5-yr ext.</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Landlord interest assigned Scannell Properties #534, LLC -&gt; Bel Commerce LLC 5/24/2024. Building 274,992 SF (28,962 office / 108,989 dry wh / 31,318 cooler / 42,616 cool dock / 49,403 freezer / 4,039 equip / 9,665 veh maint) on 28.47 AC. Rent amount not present in extracted lease text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>8510 Brighton Rd, Adams County (R0179050) — Lease (Lessor: 8500 Brighton LLC)</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="20" t="n"/>
+      <c r="J29" s="20" t="n"/>
+      <c r="K29" s="20" t="n"/>
+      <c r="L29" s="20" t="n"/>
+      <c r="M29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>8510 Brighton Rd (R0179050)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Insurance Auto Auctions, Inc.</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="6" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>11/7/2013</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>240 mos. (20 yrs) from Commencement Date</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>20-yr initial term</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Premises 45.97 gross AC (Initial Phase 29.75 AC w/ ~11,270 RSF bldg + Additional Phase 16.22 AC). Lessee pays Taxes directly as Additional Rent. Rent amount not present in extracted lease text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave, Denver (R0099649) — Fee-Simple Income Proforma (Stevens &amp; Associates appeal)</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="20" t="n"/>
+      <c r="M31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Navajo Express Inc. (actual occupant / petitioner)</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Proforma NNN</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>170200</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>PGI $170,200 (NNN $5.75/sf indicated lease rate); 5% vac.; 8% OpEx; 2% reserves (Stevens &amp; Associates appeal proforma).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd, Denver — Northlawn Auto Center (R0100737) — Rent Roll (as of 7/1/2024)</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="20" t="n"/>
+      <c r="D33" s="20" t="n"/>
+      <c r="E33" s="20" t="n"/>
+      <c r="F33" s="20" t="n"/>
+      <c r="G33" s="20" t="n"/>
+      <c r="H33" s="20" t="n"/>
+      <c r="I33" s="20" t="n"/>
+      <c r="J33" s="20" t="n"/>
+      <c r="K33" s="20" t="n"/>
+      <c r="L33" s="20" t="n"/>
+      <c r="M33" s="21" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737)</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>Ste A (2,550 SF)</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Martinez Auto Repair</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>25200</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>5/31/2027</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>36-mo term</t>
+        </is>
+      </c>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" s="6" t="n"/>
+      <c r="M34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>Ste B (5,631 SF)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Tokayos</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>66000</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>5/31/2027</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>36-mo term</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Ste C (2,550 SF)</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Auto Expert Service LLC</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>38400</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>15.06</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>5/31/2027</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>36-mo term</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737)</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Ste D (3,480 SF)</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>David Gonzalez</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>3400</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>40800</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>11.72</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>6/1/2024</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>5/31/2027</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>36-mo term</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="n"/>
+      <c r="L37" s="6" t="n"/>
+      <c r="M37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737)</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>TOTALS</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Total Rental Income (14,211 SF)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="9">
+        <f>SUM(E34:E37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="6">
+        <f>SUM(F34:F37)</f>
+        <v/>
+      </c>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="5" t="n"/>
+      <c r="K38" s="9" t="n"/>
+      <c r="L38" s="6" t="n"/>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $14,200/mo, $170,400/yr, 100% occupied (per rent roll).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>14891 East Colfax Avenue (R0085560) — Meineke Car Care lease (rent roll as of 6/30/24)</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" s="20" t="n"/>
+      <c r="D39" s="20" t="n"/>
+      <c r="E39" s="20" t="n"/>
+      <c r="F39" s="20" t="n"/>
+      <c r="G39" s="20" t="n"/>
+      <c r="H39" s="20" t="n"/>
+      <c r="I39" s="20" t="n"/>
+      <c r="J39" s="20" t="n"/>
+      <c r="K39" s="20" t="n"/>
+      <c r="L39" s="20" t="n"/>
+      <c r="M39" s="21" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>COLFX14891</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Meineke Car Care (Meineke CE)</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Actual (NNN w/ CAM/tax reimbursement)</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="n">
+        <v>6338.96</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>76067.52</v>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>17.84</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>12/1/2021</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>7/31/2026</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Rent escalates annually to $18.93/sf by 2025-26</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>3017.69</v>
+      </c>
+      <c r="L40" s="6" t="n"/>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>4,264 SF, 100% occupied. Monthly CAM/tax reimb. $3,017.69 (~$36,212/yr) ties closely to 2024 Real Estate Taxes expense line in P&amp;L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>1750 74th Ave, Commerce City (R0077963) — Diamond Beall Development LLC (tenant name not stated)</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="n"/>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+      <c r="G41" s="20" t="n"/>
+      <c r="H41" s="20" t="n"/>
+      <c r="I41" s="20" t="n"/>
+      <c r="J41" s="20" t="n"/>
+      <c r="K41" s="20" t="n"/>
+      <c r="L41" s="20" t="n"/>
+      <c r="M41" s="21" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>1750 74th Ave (R0077963)</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>(unnamed — Tank Trailer/Truck Parts &amp; Service)</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="inlineStr">
+        <is>
+          <t>22,000 (2023) / 22,500 (2024)</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n">
+        <v>264000</v>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>7/31/2027 (renewal term #2)</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Renewal Term #2, 5 yrs (2023-2027)</t>
+        </is>
+      </c>
+      <c r="K42" s="9" t="n"/>
+      <c r="L42" s="6" t="n"/>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>18,720 SF, 100% leased. Scheduled rent $14.10/sf; actual rent $264,000/yr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>1010 Lousell Blvd, Westminster (R0179014) — Grand Lake / Low Down LLC (tenant name not stated)</t>
+        </is>
+      </c>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
+      <c r="E43" s="20" t="n"/>
+      <c r="F43" s="20" t="n"/>
+      <c r="G43" s="20" t="n"/>
+      <c r="H43" s="20" t="n"/>
+      <c r="I43" s="20" t="n"/>
+      <c r="J43" s="20" t="n"/>
+      <c r="K43" s="20" t="n"/>
+      <c r="L43" s="20" t="n"/>
+      <c r="M43" s="21" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>1010 Lousell Blvd (R0179014)</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>(unnamed — single tenant)</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="6" t="n"/>
+      <c r="G44" s="6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="L44" s="6" t="n"/>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>OCR of handwritten survey partly illegible: "Scheduled Rent $2.60/sf" and "CAM Fee $5.99/sf" as printed; actual-rent figure illegible. Figures reproduced as-is, not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>1975 Newport St, Commerce City (R0092740) — DSP LLC (tenant name not stated)</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n"/>
+      <c r="C45" s="20" t="n"/>
+      <c r="D45" s="20" t="n"/>
+      <c r="E45" s="20" t="n"/>
+      <c r="F45" s="20" t="n"/>
+      <c r="G45" s="20" t="n"/>
+      <c r="H45" s="20" t="n"/>
+      <c r="I45" s="20" t="n"/>
+      <c r="J45" s="20" t="n"/>
+      <c r="K45" s="20" t="n"/>
+      <c r="L45" s="20" t="n"/>
+      <c r="M45" s="21" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St (R0092740)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>(unnamed)</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="6" t="n"/>
+      <c r="G46" s="6" t="n"/>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>3-yr term; new lease 7/1/22-6/30/24</t>
+        </is>
+      </c>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" s="6" t="n"/>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>Scheduled/actual rent illegible in OCR. Owner-side expense grid reported Building Insurance $4,600; Leasing Commissions $24,748; Utilities $22,336 (period unclear).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>(address illegible), Northglenn area (R0037193) — Baizer Properties LLC — Collision Repair Shop (tenant name not stated)</t>
+        </is>
+      </c>
+      <c r="B47" s="20" t="n"/>
+      <c r="C47" s="20" t="n"/>
+      <c r="D47" s="20" t="n"/>
+      <c r="E47" s="20" t="n"/>
+      <c r="F47" s="20" t="n"/>
+      <c r="G47" s="20" t="n"/>
+      <c r="H47" s="20" t="n"/>
+      <c r="I47" s="20" t="n"/>
+      <c r="J47" s="20" t="n"/>
+      <c r="K47" s="20" t="n"/>
+      <c r="L47" s="20" t="n"/>
+      <c r="M47" s="21" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>R0037193 (Baizer Properties LLC)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Whole</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>(unnamed — Collision Repair Shop)</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>NNN</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>26638.7</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>319664.4</v>
+      </c>
+      <c r="G48" s="6" t="n"/>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="n"/>
+      <c r="L48" s="6" t="n"/>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>Tenant pays own NNN items directly (amounts not reported to owner). Owner-side Building Insurance $5,176.30.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="14">
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A45:M45"/>
     <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A33:M33"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A29:M29"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A41:M41"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A47:M47"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3149,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3176,7 +5922,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,7 +6130,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -3400,7 +6144,6 @@
       <c r="G12" s="20" t="n"/>
       <c r="H12" s="21" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -3597,7 +6340,6 @@
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -3612,14 +6354,416 @@
       <c r="G22" s="20" t="n"/>
       <c r="H22" s="21" t="n"/>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>C. Assessed / County Values — 325 Folder Batch</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="20" t="n"/>
+      <c r="G24" s="20" t="n"/>
+      <c r="H24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Assess/Tax Yr</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Assessor / County Value</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Value PSF</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Taxpayer / Petitioner Opinion</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Opinion PSF</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Prior-Yr Value</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>8510 Brighton Rd (R0179050)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>14971919</v>
+      </c>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="9" t="n">
+        <v>12908000</v>
+      </c>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>R0179050 (cost-approach summary sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>2602500</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>183.14</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="F27" s="16" t="n">
+        <v>147.77</v>
+      </c>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>R0100737</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649)</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="n">
+        <v>8998894</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>304.02</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>152.03</v>
+      </c>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>R0099649</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560)</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>2025 (val. 6/30/24)</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1172600</v>
+      </c>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="9" t="n">
+        <v>870000</v>
+      </c>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>R0085560</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089, incl. R0030088)</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="n">
+        <v>5987885</v>
+      </c>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="9" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>R0030089</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>R0179050 TAV ($14,971,919) is printed as-is on the Marshall &amp; Swift cost-approach summary sheet (2025 Land $11,906,580 + 2025 Imps $3,065,339); the taxpayer's own cost-approach conclusion on the same sheet reads $12,905,080, while the cover letter requests $12,908,000 — all three reproduced as printed. R0100737 &amp; R0099649 PSF figures computed from GBA/NRA in Property Master; R0085560 &amp; R0030089 PSF not computed (GBA uncertain / multi-parcel).</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="n"/>
+      <c r="C32" s="20" t="n"/>
+      <c r="D32" s="20" t="n"/>
+      <c r="E32" s="20" t="n"/>
+      <c r="F32" s="20" t="n"/>
+      <c r="G32" s="20" t="n"/>
+      <c r="H32" s="21" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>D. Income-Approach Proformas — 325 Folder Batch</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="21" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>PGI</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Vacancy</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>EGI</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Operating Exp</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>NOI</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Cap Rate</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Indicated Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — bldg only</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>170200</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>-8510</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>161690</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>-16169</v>
+      </c>
+      <c r="F36" s="16" t="n">
+        <v>145521</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>2238785</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — + excess land</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="6" t="n">
+        <v>2298247</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737) — petitioner proforma</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>170532</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>-8527</v>
+      </c>
+      <c r="D38" s="16" t="n">
+        <v>162005</v>
+      </c>
+      <c r="E38" s="9" t="n">
+        <v>-12960</v>
+      </c>
+      <c r="F38" s="16" t="n">
+        <v>149045</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>2129214</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021 actual</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>388340</v>
+      </c>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="9" t="n">
+        <v>-219538</v>
+      </c>
+      <c r="F39" s="16" t="n">
+        <v>168802</v>
+      </c>
+      <c r="G39" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>2411453</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022 actual</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>503431</v>
+      </c>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="9" t="n">
+        <v>-247634</v>
+      </c>
+      <c r="F40" s="16" t="n">
+        <v>255797</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>3654247</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>R0099649: capitalized building value $2,238,785 (NOI/6.5%) + excess land value $2,298,247 (at $3.00/sf) = total reconciled value $4,537,032, rounded to requested $4,500,000 (Stevens &amp; Associates). R0100737: petitioner's (1st Net) own proforma using actual 2024 rent roll; indicated value $2,129,214 vs. requested $2,100,000. R0085560 protest letter states assumptions only (rent $17.85/sf, 7% vac., 8% exp., 7.5% cap -&gt; indicated $868,290) without a printed PGI/EGI/NOI table, so it is not itemized here — see letter cited in Source Documents. R0030089 EGI/vacancy not broken out in source; Operating Exp shown = Total Actual Operating Revenue less Net Income from Rental Real Estate, as printed.</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="20" t="n"/>
+      <c r="D42" s="20" t="n"/>
+      <c r="E42" s="20" t="n"/>
+      <c r="F42" s="20" t="n"/>
+      <c r="G42" s="20" t="n"/>
+      <c r="H42" s="21" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="10">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +6775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +6799,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +6913,258 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2021 (cash)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>5975.08</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>P&amp;L 4-yr recap (cash basis)</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2022 (cash)</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>103401.75</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>25245.32</v>
+      </c>
+      <c r="D10" s="23">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>P&amp;L 4-yr recap (cash basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023 (cash)</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>97149.27</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>24931.34</v>
+      </c>
+      <c r="D11" s="23">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>P&amp;L 4-yr recap (cash basis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024 (cash)</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>113858.69</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>36212.3</v>
+      </c>
+      <c r="D12" s="23">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>P&amp;L 4-yr recap (cash basis); Total Expense = Real Estate Taxes only (no other operating exp. reported)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737) — 2024 (petitioner proforma)</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>170532</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>12960</v>
+      </c>
+      <c r="D13" s="23">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>1st Net proforma from 2024 rent roll; NNN (mgmt 3% + reserves/owner exp 5% only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>170200</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>16169</v>
+      </c>
+      <c r="D14" s="23">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates fee-simple proforma (8% OpEx + 2% reserves)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>1975 Newport St (R0092740) — 2023 (partial)</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n">
+        <v>51684</v>
+      </c>
+      <c r="D15" s="23">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Adams Co. survey; owner-side items only (Bldg Ins. $4,600 + Leasing Comm. $24,748 + Utilities $22,336); income illegible in OCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 (owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="n"/>
+      <c r="C16" s="22" t="n">
+        <v>56150</v>
+      </c>
+      <c r="D16" s="23">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Adams Co. survey; 100% owner-occupied, OpEx only</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="n">
+        <v>388340</v>
+      </c>
+      <c r="C17" s="22" t="n">
+        <v>219538</v>
+      </c>
+      <c r="D17" s="23">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1st Net operating statement (recoverable + owner's expenses)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="n">
+        <v>503431</v>
+      </c>
+      <c r="C18" s="22" t="n">
+        <v>247634</v>
+      </c>
+      <c r="D18" s="23">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>1st Net operating statement; Total Expense = Revenue - Net Income as printed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>490 Huron St (R0030085) — 2023-24 (owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="n"/>
+      <c r="C19" s="22" t="n">
+        <v>64535.04</v>
+      </c>
+      <c r="D19" s="23">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Adams Co. survey; 100% owner-occupied, OpEx only</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas. 325-folder additions: R0085560 4-yr cash P&amp;L; R0100737 &amp; R0099649 are proforma (not actual full-year statements); R0092740, R0077789 &amp; R0030085 report Operating Expenses only per the Adams Co. survey (no income reported / owner-occupied); R0030089 Total Expense = printed Total Actual Operating Revenue less printed Net Income from Rental Real Estate (component detail in Income-Expense Detail tab).</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A21:E21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +7176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +7200,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5207,6 +8584,1775 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2021</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>4000 - Rent/Lease Income</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>5975.08</v>
+      </c>
+      <c r="E66" s="6" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2021</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D67" s="22">
+        <f>SUM(D66:D66)</f>
+        <v/>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $5,975.08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2021</t>
+        </is>
+      </c>
+      <c r="B68" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>6010 - Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2021</t>
+        </is>
+      </c>
+      <c r="B69" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D69" s="22">
+        <f>SUM(D68:D68)</f>
+        <v/>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $0.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2022</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>4000 - Rent/Lease Income</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>72597.21000000001</v>
+      </c>
+      <c r="E70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2022</t>
+        </is>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>4020 - Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="n">
+        <v>30804.54</v>
+      </c>
+      <c r="E71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2022</t>
+        </is>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D72" s="22">
+        <f>SUM(D70:D71)</f>
+        <v/>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $103,401.75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2022</t>
+        </is>
+      </c>
+      <c r="B73" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>6010 - Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="n">
+        <v>25245.32</v>
+      </c>
+      <c r="E73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2022</t>
+        </is>
+      </c>
+      <c r="B74" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D74" s="22">
+        <f>SUM(D73:D73)</f>
+        <v/>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $25,245.32.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>4000 - Rent/Lease Income</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>74775.11</v>
+      </c>
+      <c r="E75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>4015 - CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>-3155</v>
+      </c>
+      <c r="E76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>4020 - Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>25529.16</v>
+      </c>
+      <c r="E77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D78" s="22">
+        <f>SUM(D75:D77)</f>
+        <v/>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $97,149.27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023</t>
+        </is>
+      </c>
+      <c r="B79" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>6010 - Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>24931.34</v>
+      </c>
+      <c r="E79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2023</t>
+        </is>
+      </c>
+      <c r="B80" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D80" s="22">
+        <f>SUM(D79:D79)</f>
+        <v/>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $24,931.34.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>4000 - Rent/Lease Income</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="n">
+        <v>77018.37</v>
+      </c>
+      <c r="E81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>4015 - CAM Reconciliation</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="n">
+        <v>-13.88</v>
+      </c>
+      <c r="E82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>4020 - Tax Reimbursement</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>36182.9</v>
+      </c>
+      <c r="E83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>4140 - Expense Reimbursement</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>671.3</v>
+      </c>
+      <c r="E84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D85" s="22">
+        <f>SUM(D81:D84)</f>
+        <v/>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $113,858.69.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B86" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>6010 - Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="n">
+        <v>36212.3</v>
+      </c>
+      <c r="E86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — FY2024</t>
+        </is>
+      </c>
+      <c r="B87" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D87" s="22">
+        <f>SUM(D86:D86)</f>
+        <v/>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $36,212.30.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B88" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>9009 - Reimbursable Expenses</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="n">
+        <v>4131.3</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>2021-24 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B89" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>9010 - Bank Charges</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>2021-24 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B90" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>9011 - Postage/Delivery - Owner</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>2021-24 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B91" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>9035 - Management Fees</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>24140</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>2021-24 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B92" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>9036 - Check Printing Fees</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>2021-24 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B93" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>9100 - Broker Commissions</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>7627.95</v>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>2021-24 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>14891 E Colfax Ave (R0085560) — 4-yr N/O Expense detail (all years)</t>
+        </is>
+      </c>
+      <c r="B94" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D94" s="22">
+        <f>SUM(D88:D93)</f>
+        <v/>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $35,921.25. Non-operating items below the NOI line; NOI $233,995.83 less N/O Expense $35,921.25 = Net Income $198,074.58 (4-yr total, cash basis).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737) — 2024 proforma</t>
+        </is>
+      </c>
+      <c r="B95" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Management (3% of EGI)</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>4860</v>
+      </c>
+      <c r="E95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737) — 2024 proforma</t>
+        </is>
+      </c>
+      <c r="B96" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Reserves &amp; Owner Exp (5% of EGI)</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>8100</v>
+      </c>
+      <c r="E96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>6500 N. Federal Blvd (R0100737) — 2024 proforma</t>
+        </is>
+      </c>
+      <c r="B97" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D97" s="22">
+        <f>SUM(D95:D96)</f>
+        <v/>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $12,960.00. PGI $170,532 (2024 actual); Vacancy 5% ($8,527); EGI $162,005; NOI $149,045; Cap Rate 7.00%; Indicated Value $2,129,214 (1st Net petitioner proforma).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>Potential Gross Income (NNN $5.75/sf x 29,600 SF)</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>170200</v>
+      </c>
+      <c r="E98" s="6" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D99" s="22">
+        <f>SUM(D98:D98)</f>
+        <v/>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $170,200.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B100" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Vacancy &amp; Collection Loss (5.00%)</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>8510</v>
+      </c>
+      <c r="E100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B101" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Operating Expenses - CAM/Mgmt/etc. (8.00% of EGI)</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>12935</v>
+      </c>
+      <c r="E101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B102" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Reserves (2.00% of EGI)</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>3234</v>
+      </c>
+      <c r="E102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave (R0099649) — income proforma</t>
+        </is>
+      </c>
+      <c r="B103" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D103" s="22">
+        <f>SUM(D100:D102)</f>
+        <v/>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $24,679.00. EGI $161,690; NOI $145,521; Cap Rate 6.5% -&gt; capitalized bldg value $2,238,785; + Excess Land value $2,298,247 ($3.00/sf) = Total Value $4,537,032; reconciled/requested $4,500,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St (R0092740) — 2023 survey (owner-side; period as reported)</t>
+        </is>
+      </c>
+      <c r="B104" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>4600</v>
+      </c>
+      <c r="E104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St (R0092740) — 2023 survey (owner-side; period as reported)</t>
+        </is>
+      </c>
+      <c r="B105" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Leasing Commissions</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>24748</v>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>as printed; unusually high for owner-paid column, reproduced as-is</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St (R0092740) — 2023 survey (owner-side; period as reported)</t>
+        </is>
+      </c>
+      <c r="B106" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>22336</v>
+      </c>
+      <c r="E106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>1975 Newport St (R0092740) — 2023 survey (owner-side; period as reported)</t>
+        </is>
+      </c>
+      <c r="B107" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D107" s="22">
+        <f>SUM(D104:D106)</f>
+        <v/>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $51,684.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B108" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>10572</v>
+      </c>
+      <c r="E108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B109" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Building Repair &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>11645</v>
+      </c>
+      <c r="E109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B110" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Ground Maintenance</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>4663</v>
+      </c>
+      <c r="E110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B111" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>7570</v>
+      </c>
+      <c r="E111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B112" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Snow/Trash Removal</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>4800</v>
+      </c>
+      <c r="E112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B113" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>16900</v>
+      </c>
+      <c r="E113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>7908 Highway 85 (R0077789) — 2023 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B114" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D114" s="22">
+        <f>SUM(D108:D113)</f>
+        <v/>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $56,150.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>R0037193 (Baizer Properties LLC) — 2023 survey (owner-side)</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Scheduled/Actual Rent (NNN, 100% leased)</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>319664.4</v>
+      </c>
+      <c r="E115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>R0037193 (Baizer Properties LLC) — 2023 survey (owner-side)</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D116" s="22">
+        <f>SUM(D115:D115)</f>
+        <v/>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $319,664.40.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>R0037193 (Baizer Properties LLC) — 2023 survey (owner-side)</t>
+        </is>
+      </c>
+      <c r="B117" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Building Insurance</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>5176.3</v>
+      </c>
+      <c r="E117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>R0037193 (Baizer Properties LLC) — 2023 survey (owner-side)</t>
+        </is>
+      </c>
+      <c r="B118" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D118" s="22">
+        <f>SUM(D117:D117)</f>
+        <v/>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $5,176.30. NNN lease; tenant pays other operating items directly (amounts not reported to owner).</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B119" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Management Fee (owner)</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>16800</v>
+      </c>
+      <c r="E119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B120" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes (recoverable)</t>
+        </is>
+      </c>
+      <c r="D120" s="22" t="n">
+        <v>106368</v>
+      </c>
+      <c r="E120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B121" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Trash Pickup Contract</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>3762</v>
+      </c>
+      <c r="E121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B122" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>Owner Accounting Fee</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="n">
+        <v>1650</v>
+      </c>
+      <c r="E122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B123" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>Owner Amortization Expense</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>2963</v>
+      </c>
+      <c r="E123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B124" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>Owner Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>16511</v>
+      </c>
+      <c r="E124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B125" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Owner Legal Fees</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>8379</v>
+      </c>
+      <c r="E125" s="6" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B126" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>Owner Miscellaneous Admin.</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E126" s="6" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B127" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>Owner Quarterly Estimated Tax</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E127" s="6" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B128" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>Owner Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>6520</v>
+      </c>
+      <c r="E128" s="6" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B129" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Capital Expenditures - Lease Commissions</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="n">
+        <v>6668</v>
+      </c>
+      <c r="E129" s="6" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B130" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Other / not individually legible in OCR</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>45197</v>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>Balancing figure: printed Total Expenses $219,538 (PSF $7.13) less legible itemized lines above (dense financial grid; some line items illegible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2021</t>
+        </is>
+      </c>
+      <c r="B131" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D131" s="22">
+        <f>SUM(D119:D130)</f>
+        <v/>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $219,538.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B132" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Management Fee (owner)</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n">
+        <v>16800</v>
+      </c>
+      <c r="E132" s="6" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B133" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes (recoverable)</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>106007</v>
+      </c>
+      <c r="E133" s="6" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B134" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Trash Pickup Contract</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="n">
+        <v>8309</v>
+      </c>
+      <c r="E134" s="6" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B135" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Owner Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>6900</v>
+      </c>
+      <c r="E135" s="6" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B136" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Capital Expenditures / General Building</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="n">
+        <v>22340</v>
+      </c>
+      <c r="E136" s="6" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B137" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>Other / not individually legible in OCR</t>
+        </is>
+      </c>
+      <c r="D137" s="22" t="n">
+        <v>87277</v>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>Balancing figure: printed Total Expenses $247,633 (PSF $8.04) less legible itemized lines above (dense financial grid; some line items illegible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (R0030089) — 2022</t>
+        </is>
+      </c>
+      <c r="B138" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D138" s="22">
+        <f>SUM(D132:D137)</f>
+        <v/>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $247,633.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St (R0030085) — 2023-24 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B139" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>Building Repair &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D139" s="22" t="n">
+        <v>43573.1</v>
+      </c>
+      <c r="E139" s="6" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St (R0030085) — 2023-24 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B140" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>Ground Maintenance</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="n">
+        <v>3391.8</v>
+      </c>
+      <c r="E140" s="6" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St (R0030085) — 2023-24 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B141" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>Janitorial Services</t>
+        </is>
+      </c>
+      <c r="D141" s="22" t="n">
+        <v>12393.31</v>
+      </c>
+      <c r="E141" s="6" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St (R0030085) — 2023-24 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B142" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>Snow/Trash Removal</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="n">
+        <v>5176.83</v>
+      </c>
+      <c r="E142" s="6" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>490 Huron St (R0030085) — 2023-24 survey (100% owner-occ.)</t>
+        </is>
+      </c>
+      <c r="B143" s="27" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D143" s="22">
+        <f>SUM(D139:D142)</f>
+        <v/>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $64,535.04. Building Insurance noted as "included in total" (not broken out separately).</t>
         </is>
       </c>
     </row>
@@ -5225,7 +10371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5249,7 +10395,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,23 +10530,130 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Digby Family LLLP</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>R0099649</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>1225 W 64th Ave</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager).</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Digby Family LLLP</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>R0153542</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>1400 W 64th Ave</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Wallace Associates, Inc.</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>R0030088</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St (not in 325 folder)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Wallace Associates, Inc.</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>R0030089</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>11450 Huron St</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager). Digby Family LLLP: both parcels covered by the same Stevens &amp; Associates agency agreement / abatement petition (Exhibit A); only R0099649 (1225 W 64th Ave) has a source document in the 325 folder. Wallace Associates: R0030088 and R0030089 (11450 Huron St) are protested together in the same 1st Net Real Estate Services letter; only R0030089 has a source document in this folder. R0030085 (Peerless Tyre, 490 Huron St) shares the 1719-03-0-05-xxx schedule-number series with R0030088/89, suggesting the same Huron St. complex, but this is not confirmed from a plat or ownership record.</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n"/>
+      <c r="C14" s="20" t="n"/>
+      <c r="D14" s="20" t="n"/>
+      <c r="E14" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Self-Storage Comparison" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,8 +75,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -110,6 +117,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,7 +200,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -269,6 +286,73 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -656,11 +740,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-07-30  |  8 subject properties, all Adams County, Colorado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Prepared for Carter Equities  |  Updated 2026-08-19  |  11 subject properties, all Adams County, Colorado</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,23 +1053,142 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Appeal docs R0040829.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal - income approach + auth letter (self storage)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington Street (R0040829)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2026</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / Dahn Corp (PTA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0040829 self storage.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Duplicate of Appeal docs R0040829.pdf (identical content)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington Street (R0040829)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2026</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / Dahn Corp (PTA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0086010 - 15413 E 18th Avenue.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal - income approach + actual income statement + abatement petition</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave, Aurora (R0086010)</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2026 (petition tax yr 2025)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / CubeSmart (store 6730)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0085571 - 1540 Altura Blvd.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal - income approach + actual income statement</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd, Aurora (R0085571)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2025/2026 (as printed)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (D. Fassig) / CubeSmart (store 6731)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
         </is>
@@ -995,10 +1197,10 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1256,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2049,6 +2250,331 @@
       <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>R0092302.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R0040829</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>R0040829</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>0171914201013</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Thornton (TH) - Dahn - 21548</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington Street</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund B</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund B</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Specialty - Self Storage</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Single (proforma; blanket self-storage lease)</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>127395</v>
+      </c>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="n">
+        <v>48250</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>1985</v>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>84% actual / 85% stabilized (Jun 2024)</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>5428808</v>
+      </c>
+      <c r="V13" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>Dahn Corporation (PTA)</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>Appeal docs R0040829.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>R0086010</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>R0086010</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0182132318001</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Aurora - 18th Avenue - CS - 6730</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 730</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 730</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Specialty - Self Storage</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Single (proforma; blanket self-storage lease)</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>203817</v>
+      </c>
+      <c r="P14" s="8" t="n"/>
+      <c r="Q14" s="8" t="n">
+        <v>57742</v>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v>1984</v>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>87% actual / 88% stabilized (Jun 2024)</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>8187500</v>
+      </c>
+      <c r="V14" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>6610000</v>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart (store 6730)</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>R0086010 - 15413 E 18th Avenue.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>R0085571</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0085571</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>0182131405022</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Aurora Altura Boulevard CS 6731</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 731</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Specialty - Self Storage</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Single (proforma; blanket self-storage lease)</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>89298</v>
+      </c>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="n">
+        <v>27139</v>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v>1978</v>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>3.29:1</t>
+        </is>
+      </c>
+      <c r="T15" s="6" t="inlineStr">
+        <is>
+          <t>100% assumed in proforma (0% vacancy loss)</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>3309468</v>
+      </c>
+      <c r="V15" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>2546900</v>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart (store 6731)</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>R0085571 - 1540 Altura Blvd.pdf</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2626,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3149,7 +3674,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3176,7 +3701,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,241 +3909,414 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>5428808</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <v>112.51</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>93.47</v>
+      </c>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>R0040829</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>8187500</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>141.79</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>6610000</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>114.47</v>
+      </c>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>R0086010</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>3309468</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>121.95</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>2546900</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>93.84999999999999</v>
+      </c>
+      <c r="G13" s="9" t="n">
+        <v>3571199</v>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>R0085571</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="21" t="n"/>
-    </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="20" t="n"/>
+      <c r="F15" s="20" t="n"/>
+      <c r="G15" s="20" t="n"/>
+      <c r="H15" s="21" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
+      <c r="E17" s="20" t="n"/>
+      <c r="F17" s="20" t="n"/>
+      <c r="G17" s="20" t="n"/>
+      <c r="H17" s="21" t="n"/>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>4832500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Dr</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>209100</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>-10455</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>198645</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>182753</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>12260 Pennsylvania St</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>237290</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>-16610</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>220680</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>-22068</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>198612</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>2837000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>6770 E. 56th Ave</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>115824</v>
+        <v>359394</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>-5791</v>
+        <v>-17970</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>110033</v>
+        <v>341424</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>-5502</v>
+        <v>-27314</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>104531</v>
+        <v>314110</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="H19" s="14" t="n">
-        <v>1493302</v>
+        <v>4832500</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
+          <t>17608 E. 24th Dr</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>209100</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>-10455</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>198645</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>-15892</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>182753</v>
+      </c>
+      <c r="G20" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>3050000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>-16610</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>220680</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-22068</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>198612</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>2837000</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>1493302</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
           <t>5970 Marion Drive (mkt)</t>
         </is>
       </c>
-      <c r="B20" s="9" t="n">
+      <c r="B23" s="9" t="n">
         <v>172800</v>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C23" s="9" t="n">
         <v>-8640</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D23" s="9" t="n">
         <v>164160</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E23" s="9" t="n">
         <v>-4223</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F23" s="14" t="n">
         <v>159937</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G23" s="19" t="n">
         <v>0.065</v>
       </c>
-      <c r="H20" s="14" t="n">
+      <c r="H23" s="14" t="n">
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="21" t="n"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St (proforma)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>796125</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-119419</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>676706</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-372188</v>
+      </c>
+      <c r="F24" s="32" t="n">
+        <v>304518</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="H24" s="32" t="n">
+        <v>4510000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (proforma)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="n">
+        <v>750646</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>-90078</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>660568</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>-231199</v>
+      </c>
+      <c r="F25" s="32" t="n">
+        <v>429370</v>
+      </c>
+      <c r="G25" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H25" s="32" t="n">
+        <v>6610000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (proforma)</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>413870</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>413870</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>-248322</v>
+      </c>
+      <c r="F26" s="32" t="n">
+        <v>165548</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H26" s="32" t="n">
+        <v>2546900</v>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="18" t="inlineStr">
+        <is>
+          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).  Self-storage proformas (10350 Washington, 15413 E 18th, 1540 Altura) are Ryan LLC income-capitalization appeals valuing the 100% NNN-leased self-storage facility as a single blanket tenancy, not unit-level rent rolls. Altura Blvd doc header prints 'Assessment Year: 2026' but its own value table is labeled 2025 (reproduced as printed).</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="n"/>
+      <c r="C28" s="20" t="n"/>
+      <c r="D28" s="20" t="n"/>
+      <c r="E28" s="20" t="n"/>
+      <c r="F28" s="20" t="n"/>
+      <c r="G28" s="20" t="n"/>
+      <c r="H28" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +4328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +4352,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +4466,88 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829) — 2026 proforma</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>676706</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>372188</v>
+      </c>
+      <c r="D9" s="32">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Ryan appeal income-cap proforma (EGI/non-reimb. exp.); no actual P&amp;L in source</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>783123.25</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>499759.18</v>
+      </c>
+      <c r="D10" s="32">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart consolidated income statement, store 6730 (YTD through Dec 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>414633.83</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>328355.94</v>
+      </c>
+      <c r="D11" s="32">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart consolidated income statement, store 6731 (YTD through Dec 2024)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas. 10350 Washington's actual on-site P&amp;L was not included in its appeal package — only the income-cap proforma is available, so its 'income/expense' here are EGI and non-reimbursable opex from that proforma, not a real P&amp;L. The two Winner Storage/CubeSmart comps report true YTD actuals.</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n"/>
+      <c r="C13" s="20" t="n"/>
+      <c r="D13" s="20" t="n"/>
+      <c r="E13" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +4559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +4583,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5207,6 +5967,825 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="33" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829) — 2026 Proforma</t>
+        </is>
+      </c>
+      <c r="B66" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C66" s="33" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent (Base Rent, NNN, $16.50/SF)</t>
+        </is>
+      </c>
+      <c r="D66" s="34" t="n">
+        <v>796125</v>
+      </c>
+      <c r="E66" s="33" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="33" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829) — 2026 Proforma</t>
+        </is>
+      </c>
+      <c r="B67" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="33" t="inlineStr">
+        <is>
+          <t>Less: Vacancy &amp; Credit Loss (15%)</t>
+        </is>
+      </c>
+      <c r="D67" s="34" t="n">
+        <v>-119419</v>
+      </c>
+      <c r="E67" s="33" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="33" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829) — 2026 Proforma</t>
+        </is>
+      </c>
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C68" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D68" s="34">
+        <f>SUM(D66:D67)</f>
+        <v/>
+      </c>
+      <c r="E68" s="33" t="inlineStr">
+        <is>
+          <t>Printed total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="33" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829) — 2026 Proforma</t>
+        </is>
+      </c>
+      <c r="B69" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C69" s="33" t="inlineStr">
+        <is>
+          <t>Non-Reimbursable Expenses (55% of EGI)</t>
+        </is>
+      </c>
+      <c r="D69" s="34" t="n">
+        <v>372188</v>
+      </c>
+      <c r="E69" s="33" t="inlineStr">
+        <is>
+          <t>Yields NOI $304,518 at 6.75% cap = $4,510,000 indicated value</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="33" t="inlineStr">
+        <is>
+          <t>10350 Washington St (R0040829) — 2026 Proforma</t>
+        </is>
+      </c>
+      <c r="B70" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C70" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D70" s="34">
+        <f>SUM(D69:D69)</f>
+        <v/>
+      </c>
+      <c r="E70" s="33" t="inlineStr">
+        <is>
+          <t>Printed total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C72" s="33" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
+      </c>
+      <c r="D72" s="34" t="n">
+        <v>731252.08</v>
+      </c>
+      <c r="E72" s="33" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B73" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C73" s="33" t="inlineStr">
+        <is>
+          <t>Total Fees (admin/late/other, net of waivers &amp; chargebacks)</t>
+        </is>
+      </c>
+      <c r="D73" s="34" t="n">
+        <v>51871.17</v>
+      </c>
+      <c r="E73" s="33" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B74" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C74" s="33" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D74" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="33" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B75" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C75" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D75" s="34">
+        <f>SUM(D72:D74)</f>
+        <v/>
+      </c>
+      <c r="E75" s="33" t="inlineStr">
+        <is>
+          <t>Printed total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B76" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C76" s="33" t="inlineStr">
+        <is>
+          <t>Payroll Expense</t>
+        </is>
+      </c>
+      <c r="D76" s="34" t="n">
+        <v>84368.25</v>
+      </c>
+      <c r="E76" s="33" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B77" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C77" s="33" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D77" s="34" t="n">
+        <v>20743.13</v>
+      </c>
+      <c r="E77" s="33" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B78" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C78" s="33" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D78" s="34" t="n">
+        <v>17362.79</v>
+      </c>
+      <c r="E78" s="33" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B79" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="33" t="inlineStr">
+        <is>
+          <t>Other Controllable Expenses</t>
+        </is>
+      </c>
+      <c r="D79" s="34" t="n">
+        <v>48137.71</v>
+      </c>
+      <c r="E79" s="33" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B80" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="33" t="inlineStr">
+        <is>
+          <t>Marketing Expense</t>
+        </is>
+      </c>
+      <c r="D80" s="34" t="n">
+        <v>25974.66</v>
+      </c>
+      <c r="E80" s="33" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C81" s="33" t="inlineStr">
+        <is>
+          <t>Snow Removal &amp; Salting</t>
+        </is>
+      </c>
+      <c r="D81" s="34" t="n">
+        <v>3890</v>
+      </c>
+      <c r="E81" s="33" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B82" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C82" s="33" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="D82" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="E82" s="33" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B83" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C83" s="33" t="inlineStr">
+        <is>
+          <t>Third-Party Management Fees</t>
+        </is>
+      </c>
+      <c r="D83" s="34" t="n">
+        <v>41598.27</v>
+      </c>
+      <c r="E83" s="33" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B84" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C84" s="33" t="inlineStr">
+        <is>
+          <t>Less: Other Income (Sales Tax Collection Allowance)</t>
+        </is>
+      </c>
+      <c r="D84" s="34" t="n">
+        <v>-14.31</v>
+      </c>
+      <c r="E84" s="33" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B85" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C85" s="33" t="inlineStr">
+        <is>
+          <t>Property Tax Expense (Gross Receipts Tax)</t>
+        </is>
+      </c>
+      <c r="D85" s="34" t="n">
+        <v>246826.26</v>
+      </c>
+      <c r="E85" s="33" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B86" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="33" t="inlineStr">
+        <is>
+          <t>Insurance Expense</t>
+        </is>
+      </c>
+      <c r="D86" s="34" t="n">
+        <v>10522.42</v>
+      </c>
+      <c r="E86" s="33" t="inlineStr">
+        <is>
+          <t>CubeSmart consolidated income statement, store 6730</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="33" t="inlineStr">
+        <is>
+          <t>15413 E 18th Ave (R0086010) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B87" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C87" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D87" s="34">
+        <f>SUM(D76:D86)</f>
+        <v/>
+      </c>
+      <c r="E87" s="33" t="inlineStr">
+        <is>
+          <t>Printed total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B89" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C89" s="33" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
+      </c>
+      <c r="D89" s="34" t="n">
+        <v>383165.98</v>
+      </c>
+      <c r="E89" s="33" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B90" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C90" s="33" t="inlineStr">
+        <is>
+          <t>Total Fees (admin/late/other, net of waivers &amp; chargebacks)</t>
+        </is>
+      </c>
+      <c r="D90" s="34" t="n">
+        <v>31467.84</v>
+      </c>
+      <c r="E90" s="33" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B91" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C91" s="33" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="D91" s="34" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E91" s="33" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B92" s="33" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C92" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D92" s="34">
+        <f>SUM(D89:D91)</f>
+        <v/>
+      </c>
+      <c r="E92" s="33" t="inlineStr">
+        <is>
+          <t>Printed total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B93" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="33" t="inlineStr">
+        <is>
+          <t>Payroll Expense</t>
+        </is>
+      </c>
+      <c r="D93" s="34" t="n">
+        <v>69477.36</v>
+      </c>
+      <c r="E93" s="33" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B94" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C94" s="33" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D94" s="34" t="n">
+        <v>15848.82</v>
+      </c>
+      <c r="E94" s="33" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B95" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C95" s="33" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="D95" s="34" t="n">
+        <v>25497.14</v>
+      </c>
+      <c r="E95" s="33" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B96" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C96" s="33" t="inlineStr">
+        <is>
+          <t>Other Controllable Expenses</t>
+        </is>
+      </c>
+      <c r="D96" s="34" t="n">
+        <v>40436.57</v>
+      </c>
+      <c r="E96" s="33" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B97" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C97" s="33" t="inlineStr">
+        <is>
+          <t>Marketing Expense</t>
+        </is>
+      </c>
+      <c r="D97" s="34" t="n">
+        <v>24474.39</v>
+      </c>
+      <c r="E97" s="33" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B98" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C98" s="33" t="inlineStr">
+        <is>
+          <t>Snow Removal &amp; Salting</t>
+        </is>
+      </c>
+      <c r="D98" s="34" t="n">
+        <v>2180</v>
+      </c>
+      <c r="E98" s="33" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B99" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C99" s="33" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="D99" s="34" t="n">
+        <v>350</v>
+      </c>
+      <c r="E99" s="33" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B100" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="33" t="inlineStr">
+        <is>
+          <t>Third-Party Management Fees</t>
+        </is>
+      </c>
+      <c r="D100" s="34" t="n">
+        <v>22457.4</v>
+      </c>
+      <c r="E100" s="33" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B101" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="33" t="inlineStr">
+        <is>
+          <t>Less: Other Income (Sales Tax Collection Allowance)</t>
+        </is>
+      </c>
+      <c r="D101" s="34" t="n">
+        <v>-12.01</v>
+      </c>
+      <c r="E101" s="33" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B102" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="33" t="inlineStr">
+        <is>
+          <t>Property Tax Expense (Gross Receipts Tax)</t>
+        </is>
+      </c>
+      <c r="D102" s="34" t="n">
+        <v>121803.84</v>
+      </c>
+      <c r="E102" s="33" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B103" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="33" t="inlineStr">
+        <is>
+          <t>Insurance Expense</t>
+        </is>
+      </c>
+      <c r="D103" s="34" t="n">
+        <v>5842.43</v>
+      </c>
+      <c r="E103" s="33" t="inlineStr">
+        <is>
+          <t>CubeSmart consolidated income statement, store 6731</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="33" t="inlineStr">
+        <is>
+          <t>1540 Altura Blvd (R0085571) — Actual Dec 2024 YTD</t>
+        </is>
+      </c>
+      <c r="B104" s="33" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="33" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D104" s="34">
+        <f>SUM(D93:D103)</f>
+        <v/>
+      </c>
+      <c r="E104" s="33" t="inlineStr">
+        <is>
+          <t>Printed total.</t>
         </is>
       </c>
     </row>
@@ -5249,7 +6828,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,7 +6963,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>
@@ -5405,4 +6982,750 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>SELF-STORAGE INCOME &amp; EXPENSE COMPARISON — DECEMBER HEARINGS</t>
+        </is>
+      </c>
+      <c r="B1" s="36" t="n"/>
+      <c r="C1" s="36" t="n"/>
+      <c r="D1" s="36" t="n"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="37" t="inlineStr">
+        <is>
+          <t>Subject: 10350 Washington Street (R0040829) vs. comparable Adams County self-storage appeals in the same folder  |  Updated 2026-08-19</t>
+        </is>
+      </c>
+      <c r="B2" s="36" t="n"/>
+      <c r="C2" s="36" t="n"/>
+      <c r="D2" s="36" t="n"/>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="38" t="inlineStr"/>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>SUBJECT
+10350 Washington St
+(R0040829)</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>COMP 1
+15413 E 18th Ave, Aurora
+(R0086010)</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>COMP 2
+1540 Altura Blvd, Aurora
+(R0085571)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>PROPERTY PROFILE</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="n"/>
+      <c r="C5" s="40" t="n"/>
+      <c r="D5" s="40" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="41" t="inlineStr">
+        <is>
+          <t>Owner / Client</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="inlineStr">
+        <is>
+          <t>DSI Special Situations Fund B</t>
+        </is>
+      </c>
+      <c r="C6" s="43" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 730</t>
+        </is>
+      </c>
+      <c r="D6" s="43" t="inlineStr">
+        <is>
+          <t>Winner Storage LLC / PTA USI No 731</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Parcel Number</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="inlineStr">
+        <is>
+          <t>0171914201013</t>
+        </is>
+      </c>
+      <c r="C7" s="43" t="inlineStr">
+        <is>
+          <t>0182132318001</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>0182131405022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Year Built</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n">
+        <v>1985</v>
+      </c>
+      <c r="C8" s="43" t="n">
+        <v>1984</v>
+      </c>
+      <c r="D8" s="43" t="n">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="41" t="inlineStr">
+        <is>
+          <t>Net Leasable Area (SF)</t>
+        </is>
+      </c>
+      <c r="B9" s="44" t="n">
+        <v>48250</v>
+      </c>
+      <c r="C9" s="45" t="n">
+        <v>57742</v>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>27139</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
+          <t>Site Area (Acres)</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C10" s="47" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="D10" s="47" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Occupancy (Jun 2024, per appeal)</t>
+        </is>
+      </c>
+      <c r="B11" s="42" t="inlineStr">
+        <is>
+          <t>84% actual / 85% stabilized</t>
+        </is>
+      </c>
+      <c r="C11" s="43" t="inlineStr">
+        <is>
+          <t>87% actual / 88% stabilized</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>0% vacancy assumed in proforma</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>ASSESSED VALUE</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="n"/>
+      <c r="C12" s="40" t="n"/>
+      <c r="D12" s="40" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="41" t="inlineStr">
+        <is>
+          <t>Assessor's Value</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="n">
+        <v>5428808</v>
+      </c>
+      <c r="C13" s="49" t="n">
+        <v>8187500</v>
+      </c>
+      <c r="D13" s="49" t="n">
+        <v>3309468</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>Value per SF</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="n">
+        <v>112.5141554404145</v>
+      </c>
+      <c r="C14" s="51" t="n">
+        <v>141.7945343077829</v>
+      </c>
+      <c r="D14" s="51" t="n">
+        <v>121.9450974612182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Taxpayer's Opinion of Value</t>
+        </is>
+      </c>
+      <c r="B15" s="48" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="C15" s="49" t="n">
+        <v>6610000</v>
+      </c>
+      <c r="D15" s="49" t="n">
+        <v>2546900</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Opinion per SF</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="n">
+        <v>93.47150259067358</v>
+      </c>
+      <c r="C16" s="51" t="n">
+        <v>114.4747324304666</v>
+      </c>
+      <c r="D16" s="51" t="n">
+        <v>93.84649397545967</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Assessment / Tax Year</t>
+        </is>
+      </c>
+      <c r="B17" s="42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="C17" s="43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr">
+        <is>
+          <t>2025 (per value table; header says 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>INCOME-APPROACH PROFORMA (Ryan LLC appeal — all three)</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>Gross Potential Rent</t>
+        </is>
+      </c>
+      <c r="B19" s="48" t="n">
+        <v>796125</v>
+      </c>
+      <c r="C19" s="49" t="n">
+        <v>750646</v>
+      </c>
+      <c r="D19" s="49" t="n">
+        <v>413870</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Base Rent per SF</t>
+        </is>
+      </c>
+      <c r="B20" s="50" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C20" s="51" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" s="51" t="n">
+        <v>15.25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="41" t="inlineStr">
+        <is>
+          <t>Vacancy &amp; Credit Loss</t>
+        </is>
+      </c>
+      <c r="B21" s="42" t="inlineStr">
+        <is>
+          <t>15% / $119,419</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="inlineStr">
+        <is>
+          <t>12% / $90,078</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>0% / $0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>Effective Gross Income (EGI)</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="n">
+        <v>676706</v>
+      </c>
+      <c r="C22" s="49" t="n">
+        <v>660568</v>
+      </c>
+      <c r="D22" s="49" t="n">
+        <v>413870</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="41" t="inlineStr">
+        <is>
+          <t>Operating / Non-Reimbursable Expenses</t>
+        </is>
+      </c>
+      <c r="B23" s="42" t="inlineStr">
+        <is>
+          <t>55% EGI / $372,188</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>35% EGI / $231,199</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>60% EGI / $248,322</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="52" t="inlineStr">
+        <is>
+          <t>Net Operating Income (NOI)</t>
+        </is>
+      </c>
+      <c r="B24" s="53" t="n">
+        <v>304518</v>
+      </c>
+      <c r="C24" s="54" t="n">
+        <v>429370</v>
+      </c>
+      <c r="D24" s="54" t="n">
+        <v>165548</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>NOI per SF</t>
+        </is>
+      </c>
+      <c r="B25" s="50" t="n">
+        <v>6.311253886010363</v>
+      </c>
+      <c r="C25" s="51" t="n">
+        <v>7.436008451387205</v>
+      </c>
+      <c r="D25" s="51" t="n">
+        <v>6.100003684734147</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>Cap Rate</t>
+        </is>
+      </c>
+      <c r="B26" s="55" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="C26" s="56" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="D26" s="56" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="52" t="inlineStr">
+        <is>
+          <t>Indicated Value (Income Approach)</t>
+        </is>
+      </c>
+      <c r="B27" s="53" t="n">
+        <v>4510000</v>
+      </c>
+      <c r="C27" s="54" t="n">
+        <v>6610000</v>
+      </c>
+      <c r="D27" s="54" t="n">
+        <v>2546900</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>ACTUAL OPERATING STATEMENT — Dec 2024 YTD (CubeSmart-managed comps only)</t>
+        </is>
+      </c>
+      <c r="B28" s="40" t="n"/>
+      <c r="C28" s="40" t="n"/>
+      <c r="D28" s="40" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Net Rental Income</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n">
+        <v>731252.08</v>
+      </c>
+      <c r="D29" s="49" t="n">
+        <v>383165.98</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Fees &amp; Other Income</t>
+        </is>
+      </c>
+      <c r="B30" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n">
+        <v>51871.17</v>
+      </c>
+      <c r="D30" s="49" t="n">
+        <v>31467.85</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="52" t="inlineStr">
+        <is>
+          <t>TOTAL ACTUAL INCOME</t>
+        </is>
+      </c>
+      <c r="B31" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="54" t="n">
+        <v>783123.25</v>
+      </c>
+      <c r="D31" s="54" t="n">
+        <v>414633.83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>Payroll Expense</t>
+        </is>
+      </c>
+      <c r="B32" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="n">
+        <v>84368.25</v>
+      </c>
+      <c r="D32" s="49" t="n">
+        <v>69477.36</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B33" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n">
+        <v>20743.13</v>
+      </c>
+      <c r="D33" s="49" t="n">
+        <v>15848.82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="41" t="inlineStr">
+        <is>
+          <t>Repairs &amp; Maintenance</t>
+        </is>
+      </c>
+      <c r="B34" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="n">
+        <v>17362.79</v>
+      </c>
+      <c r="D34" s="49" t="n">
+        <v>25497.14</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B35" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C35" s="49" t="n">
+        <v>25974.66</v>
+      </c>
+      <c r="D35" s="49" t="n">
+        <v>24474.39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Other Controllable Expenses</t>
+        </is>
+      </c>
+      <c r="B36" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="n">
+        <v>48137.71</v>
+      </c>
+      <c r="D36" s="49" t="n">
+        <v>40436.57</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="41" t="inlineStr">
+        <is>
+          <t>Property Tax (Gross Receipts Tax)</t>
+        </is>
+      </c>
+      <c r="B37" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C37" s="49" t="n">
+        <v>246826.26</v>
+      </c>
+      <c r="D37" s="49" t="n">
+        <v>121803.84</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B38" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="n">
+        <v>10522.42</v>
+      </c>
+      <c r="D38" s="49" t="n">
+        <v>5842.43</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="41" t="inlineStr">
+        <is>
+          <t>Mgmt Fee, Snow Removal, Prof. Fees (net)</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C39" s="49" t="n">
+        <v>45823.96</v>
+      </c>
+      <c r="D39" s="49" t="n">
+        <v>24975.39</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="52" t="inlineStr">
+        <is>
+          <t>TOTAL ACTUAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="B40" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C40" s="54" t="n">
+        <v>499759.18</v>
+      </c>
+      <c r="D40" s="54" t="n">
+        <v>328355.94</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="52" t="inlineStr">
+        <is>
+          <t>ACTUAL NET OPERATING INCOME</t>
+        </is>
+      </c>
+      <c r="B41" s="57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C41" s="54" t="n">
+        <v>283364.07</v>
+      </c>
+      <c r="D41" s="54" t="n">
+        <v>86277.89</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Actual NOI per SF</t>
+        </is>
+      </c>
+      <c r="B42" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C42" s="51" t="n">
+        <v>4.907416958193343</v>
+      </c>
+      <c r="D42" s="51" t="n">
+        <v>3.179110873650466</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Actual Expense Ratio (Exp / Total Income)</t>
+        </is>
+      </c>
+      <c r="B43" s="42" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C43" s="56" t="n">
+        <v>0.6381615920610197</v>
+      </c>
+      <c r="D43" s="56" t="n">
+        <v>0.7919178712455759</v>
+      </c>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="58" t="inlineStr">
+        <is>
+          <t>Notes: All three properties are Adams County self-storage tax appeals prepared by Ryan LLC (Declan Fassig), valued as of 6/30/2024, from the 'R0040829 - 10350 Washington Street' folder under December Hearings. Proforma figures (income-approach appeal) are apples-to-apples across all three. Actual operating statements are only available for the two Winner Storage/CubeSmart comps (15413 E 18th Ave and 1540 Altura Blvd) — 10350 Washington's appeal package did not include an actual P&amp;L, only the income-cap proforma, so its actual-statement cells are marked '—'. 1540 Altura Blvd's header prints 'Assessment Year: 2026' but its own value table and income statement are labeled 2025 — reproduced as printed. Full line-item detail and source citations are in the 'Assessments &amp; Valuation' and 'Income-Expense Detail' tabs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -13,23 +13,27 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense Comps ($ per SF)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Expense Comps ($ per SF)'!$A$4:$Q$22</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="#,##0.###"/>
     <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);-"/>
     <numFmt numFmtId="168" formatCode="$0.00"/>
+    <numFmt numFmtId="169" formatCode="$0.00;($0.00);&quot;n/a&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +84,11 @@
       <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -190,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -295,6 +304,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -14991,6 +15018,1511 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="60" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="46" t="inlineStr">
+        <is>
+          <t>EXPENSE COMPS — $ PER SQUARE FOOT</t>
+        </is>
+      </c>
+      <c r="B1" s="47" t="n"/>
+      <c r="C1" s="47" t="n"/>
+      <c r="D1" s="47" t="n"/>
+      <c r="E1" s="47" t="n"/>
+      <c r="F1" s="47" t="n"/>
+      <c r="G1" s="47" t="n"/>
+      <c r="H1" s="47" t="n"/>
+      <c r="I1" s="47" t="n"/>
+      <c r="J1" s="47" t="n"/>
+      <c r="K1" s="47" t="n"/>
+      <c r="L1" s="47" t="n"/>
+      <c r="M1" s="47" t="n"/>
+      <c r="N1" s="47" t="n"/>
+      <c r="O1" s="47" t="n"/>
+      <c r="P1" s="47" t="n"/>
+      <c r="Q1" s="47" t="n"/>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="48" t="inlineStr">
+        <is>
+          <t>Insurance, Utilities, CAM+Repairs &amp; Maintenance, and Management costs per SF — organize/filter by OCC Code and Size (SF) to build comp sets</t>
+        </is>
+      </c>
+      <c r="B2" s="47" t="n"/>
+      <c r="C2" s="47" t="n"/>
+      <c r="D2" s="47" t="n"/>
+      <c r="E2" s="47" t="n"/>
+      <c r="F2" s="47" t="n"/>
+      <c r="G2" s="47" t="n"/>
+      <c r="H2" s="47" t="n"/>
+      <c r="I2" s="47" t="n"/>
+      <c r="J2" s="47" t="n"/>
+      <c r="K2" s="47" t="n"/>
+      <c r="L2" s="47" t="n"/>
+      <c r="M2" s="47" t="n"/>
+      <c r="N2" s="47" t="n"/>
+      <c r="O2" s="47" t="n"/>
+      <c r="P2" s="47" t="n"/>
+      <c r="Q2" s="47" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>Property</t>
+        </is>
+      </c>
+      <c r="B4" s="49" t="inlineStr">
+        <is>
+          <t>OCC Code</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="inlineStr">
+        <is>
+          <t>Property Type / Use</t>
+        </is>
+      </c>
+      <c r="D4" s="49" t="inlineStr">
+        <is>
+          <t>Size (SF)</t>
+        </is>
+      </c>
+      <c r="E4" s="49" t="inlineStr">
+        <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="F4" s="49" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="G4" s="49" t="inlineStr">
+        <is>
+          <t>Occupancy</t>
+        </is>
+      </c>
+      <c r="H4" s="49" t="inlineStr">
+        <is>
+          <t>Insurance $</t>
+        </is>
+      </c>
+      <c r="I4" s="49" t="inlineStr">
+        <is>
+          <t>Insurance $/SF</t>
+        </is>
+      </c>
+      <c r="J4" s="49" t="inlineStr">
+        <is>
+          <t>Utilities $</t>
+        </is>
+      </c>
+      <c r="K4" s="49" t="inlineStr">
+        <is>
+          <t>Utilities $/SF</t>
+        </is>
+      </c>
+      <c r="L4" s="49" t="inlineStr">
+        <is>
+          <t>CAM + R&amp;M $</t>
+        </is>
+      </c>
+      <c r="M4" s="49" t="inlineStr">
+        <is>
+          <t>CAM + R&amp;M $/SF</t>
+        </is>
+      </c>
+      <c r="N4" s="49" t="inlineStr">
+        <is>
+          <t>Management $</t>
+        </is>
+      </c>
+      <c r="O4" s="49" t="inlineStr">
+        <is>
+          <t>Management $/SF</t>
+        </is>
+      </c>
+      <c r="P4" s="49" t="inlineStr">
+        <is>
+          <t>Total (4 cats) $/SF</t>
+        </is>
+      </c>
+      <c r="Q4" s="49" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="33" t="inlineStr">
+        <is>
+          <t>125 Bridge St (Broadview)</t>
+        </is>
+      </c>
+      <c r="B5" s="50" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
+      <c r="C5" s="33" t="inlineStr">
+        <is>
+          <t>Commercial (multi-tenant industrial)</t>
+        </is>
+      </c>
+      <c r="D5" s="51" t="n"/>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>2024 (IRS Form 8825)</t>
+        </is>
+      </c>
+      <c r="F5" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G5" s="33" t="inlineStr">
+        <is>
+          <t>Mostly leased (1-2 units vacant)</t>
+        </is>
+      </c>
+      <c r="H5" s="40" t="n">
+        <v>12004</v>
+      </c>
+      <c r="J5" s="40" t="n">
+        <v>4731</v>
+      </c>
+      <c r="L5" s="40" t="n">
+        <v>100279</v>
+      </c>
+      <c r="N5" s="33" t="n"/>
+      <c r="Q5" s="52" t="inlineStr">
+        <is>
+          <t>CAM/R&amp;M = 'Repairs' line per Form 8825. No separate management-fee line on the tax return (bundled in 'Other $39,767' or self-managed). Building SF not captured in Property Master (multi-suite building; unit-level rents only) — $/SF not computable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="33" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Road</t>
+        </is>
+      </c>
+      <c r="B6" s="50" t="inlineStr">
+        <is>
+          <t>IND-DIST</t>
+        </is>
+      </c>
+      <c r="C6" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution (single tenant)</t>
+        </is>
+      </c>
+      <c r="D6" s="53" t="n">
+        <v>386000</v>
+      </c>
+      <c r="E6" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F6" s="33" t="inlineStr">
+        <is>
+          <t>Actual (NNN — tenant-paid)</t>
+        </is>
+      </c>
+      <c r="G6" s="33" t="inlineStr">
+        <is>
+          <t>100% (single tenant)</t>
+        </is>
+      </c>
+      <c r="H6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="54">
+        <f>H6/D6</f>
+        <v/>
+      </c>
+      <c r="J6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="54">
+        <f>J6/D6</f>
+        <v/>
+      </c>
+      <c r="L6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="54">
+        <f>L6/D6</f>
+        <v/>
+      </c>
+      <c r="N6" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="54">
+        <f>N6/D6</f>
+        <v/>
+      </c>
+      <c r="P6" s="55">
+        <f>SUM(H6,J6,L6,N6)/D6</f>
+        <v/>
+      </c>
+      <c r="Q6" s="52" t="inlineStr">
+        <is>
+          <t>Landlord P&amp;L has NO Insurance/Utilities/CAM/Management GL lines — this is a true NNN lease where the tenant pays all operating costs directly. Landlord-side costs are limited to G&amp;A (bank fees, legal, accounting), interest, and depreciation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>2780 N. Tower Road</t>
+        </is>
+      </c>
+      <c r="B7" s="50" t="inlineStr">
+        <is>
+          <t>IND-DIST</t>
+        </is>
+      </c>
+      <c r="C7" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution (single tenant)</t>
+        </is>
+      </c>
+      <c r="D7" s="53" t="n">
+        <v>386000</v>
+      </c>
+      <c r="E7" s="33" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F7" s="33" t="inlineStr">
+        <is>
+          <t>Actual (NNN — tenant-paid)</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="inlineStr">
+        <is>
+          <t>100% (single tenant)</t>
+        </is>
+      </c>
+      <c r="H7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="54">
+        <f>H7/D7</f>
+        <v/>
+      </c>
+      <c r="J7" s="40" t="n">
+        <v>687</v>
+      </c>
+      <c r="K7" s="54">
+        <f>J7/D7</f>
+        <v/>
+      </c>
+      <c r="L7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="54">
+        <f>L7/D7</f>
+        <v/>
+      </c>
+      <c r="N7" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="54">
+        <f>N7/D7</f>
+        <v/>
+      </c>
+      <c r="P7" s="55">
+        <f>SUM(H7,J7,L7,N7)/D7</f>
+        <v/>
+      </c>
+      <c r="Q7" s="52" t="inlineStr">
+        <is>
+          <t>Same NNN structure as FY2024; $687 utilities appears to be a minor landlord-side true-up, not a recurring cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="33" t="inlineStr">
+        <is>
+          <t>2011 E 58th Ave (TempTee)</t>
+        </is>
+      </c>
+      <c r="B8" s="50" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Mfg / Food Processing</t>
+        </is>
+      </c>
+      <c r="D8" s="53" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E8" s="33" t="inlineStr">
+        <is>
+          <t>2024 survey (Oct'23-Sep'24)</t>
+        </is>
+      </c>
+      <c r="F8" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied</t>
+        </is>
+      </c>
+      <c r="H8" s="40" t="n">
+        <v>14050</v>
+      </c>
+      <c r="I8" s="54">
+        <f>H8/D8</f>
+        <v/>
+      </c>
+      <c r="J8" s="40" t="n">
+        <v>102000</v>
+      </c>
+      <c r="K8" s="54">
+        <f>J8/D8</f>
+        <v/>
+      </c>
+      <c r="L8" s="40" t="n">
+        <v>22000</v>
+      </c>
+      <c r="M8" s="54">
+        <f>L8/D8</f>
+        <v/>
+      </c>
+      <c r="N8" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="54">
+        <f>N8/D8</f>
+        <v/>
+      </c>
+      <c r="P8" s="55">
+        <f>SUM(H8,J8,L8,N8)/D8</f>
+        <v/>
+      </c>
+      <c r="Q8" s="52" t="inlineStr">
+        <is>
+          <t>CAM/R&amp;M = Building R&amp;M $10,000 + Snow/Trash Removal $12,000. Ground Maintenance &amp; Janitorial reported 'in house' = $0 (not truly zero cost, just unreported/self-performed). No 3rd-party management fee (owner-occupied).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>TrusTile Doors</t>
+        </is>
+      </c>
+      <c r="B9" s="50" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Manufacturing (doors)</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="n"/>
+      <c r="E9" s="33" t="inlineStr">
+        <is>
+          <t>Oct'23-Sep'24 survey</t>
+        </is>
+      </c>
+      <c r="F9" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G9" s="33" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied</t>
+        </is>
+      </c>
+      <c r="H9" s="40" t="n">
+        <v>361160</v>
+      </c>
+      <c r="J9" s="40" t="n">
+        <v>1031487</v>
+      </c>
+      <c r="L9" s="40" t="n">
+        <v>1695350</v>
+      </c>
+      <c r="N9" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="52" t="inlineStr">
+        <is>
+          <t>CAM/R&amp;M = Building R&amp;M $796,122 + Janitorial $150,032 + Snow/Trash Removal $749,196. No management fee (owner-occupied, no leasing). Building SF not stated on the county survey form — $/SF not computable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>5970 Marion Drive</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - 2-unit</t>
+        </is>
+      </c>
+      <c r="D10" s="53" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E10" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F10" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G10" s="33" t="inlineStr">
+        <is>
+          <t>100% (2 units)</t>
+        </is>
+      </c>
+      <c r="H10" s="40" t="n">
+        <v>10241.26</v>
+      </c>
+      <c r="I10" s="54">
+        <f>H10/D10</f>
+        <v/>
+      </c>
+      <c r="J10" s="40" t="n">
+        <v>2569.85</v>
+      </c>
+      <c r="K10" s="54">
+        <f>J10/D10</f>
+        <v/>
+      </c>
+      <c r="L10" s="40" t="n">
+        <v>1227.47</v>
+      </c>
+      <c r="M10" s="54">
+        <f>L10/D10</f>
+        <v/>
+      </c>
+      <c r="N10" s="40" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O10" s="54">
+        <f>N10/D10</f>
+        <v/>
+      </c>
+      <c r="P10" s="55">
+        <f>SUM(H10,J10,L10,N10)/D10</f>
+        <v/>
+      </c>
+      <c r="Q10" s="52" t="inlineStr">
+        <is>
+          <t>Utilities = Water $2,175.55 + Sewer $394.30. CAM/R&amp;M = Inspection &amp; Compliance $100 + Snow Removal $927.47 + Common Area Clean $200. Mgmt: Deerwoods Management.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>5970 Marion Drive</t>
+        </is>
+      </c>
+      <c r="B11" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C11" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - 2-unit</t>
+        </is>
+      </c>
+      <c r="D11" s="53" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E11" s="33" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F11" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G11" s="33" t="inlineStr">
+        <is>
+          <t>100% (2 units)</t>
+        </is>
+      </c>
+      <c r="H11" s="40" t="n">
+        <v>8640.99</v>
+      </c>
+      <c r="I11" s="54">
+        <f>H11/D11</f>
+        <v/>
+      </c>
+      <c r="J11" s="40" t="n">
+        <v>2308.09</v>
+      </c>
+      <c r="K11" s="54">
+        <f>J11/D11</f>
+        <v/>
+      </c>
+      <c r="L11" s="40" t="n">
+        <v>50376.31</v>
+      </c>
+      <c r="M11" s="54">
+        <f>L11/D11</f>
+        <v/>
+      </c>
+      <c r="N11" s="40" t="n">
+        <v>6000</v>
+      </c>
+      <c r="O11" s="54">
+        <f>N11/D11</f>
+        <v/>
+      </c>
+      <c r="P11" s="55">
+        <f>SUM(H11,J11,L11,N11)/D11</f>
+        <v/>
+      </c>
+      <c r="Q11" s="52" t="inlineStr">
+        <is>
+          <t>Utilities = Water $2,157.08 + Trash $151.01. CAM/R&amp;M = Electrical Repairs &amp; Lighting $1,550 + Roofing Repairs $47,000 (one-off) + Drywall Repairs $810 + Snow Removal $1,016.31 + Inspection &amp; Compliance $110 — large roof repair skews this year high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 26</t>
+        </is>
+      </c>
+      <c r="B12" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D12" s="53" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E12" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F12" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G12" s="33" t="inlineStr">
+        <is>
+          <t>100% (single tenant)</t>
+        </is>
+      </c>
+      <c r="H12" s="40" t="n">
+        <v>30594</v>
+      </c>
+      <c r="I12" s="54">
+        <f>H12/D12</f>
+        <v/>
+      </c>
+      <c r="J12" s="40" t="n">
+        <v>477.83</v>
+      </c>
+      <c r="K12" s="54">
+        <f>J12/D12</f>
+        <v/>
+      </c>
+      <c r="L12" s="40" t="n">
+        <v>95782.41</v>
+      </c>
+      <c r="M12" s="54">
+        <f>L12/D12</f>
+        <v/>
+      </c>
+      <c r="N12" s="40" t="n">
+        <v>36084.88</v>
+      </c>
+      <c r="O12" s="54">
+        <f>N12/D12</f>
+        <v/>
+      </c>
+      <c r="P12" s="55">
+        <f>SUM(H12,J12,L12,N12)/D12</f>
+        <v/>
+      </c>
+      <c r="Q12" s="52" t="inlineStr">
+        <is>
+          <t>Utilities landlord-side captured only 'Fire Service' — single-tenant NNN, tenant pays electricity/gas/water directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 22</t>
+        </is>
+      </c>
+      <c r="B13" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D13" s="53" t="n">
+        <v>200090</v>
+      </c>
+      <c r="E13" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F13" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G13" s="33" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H13" s="40" t="n">
+        <v>26308</v>
+      </c>
+      <c r="I13" s="54">
+        <f>H13/D13</f>
+        <v/>
+      </c>
+      <c r="J13" s="40" t="n">
+        <v>72124.12</v>
+      </c>
+      <c r="K13" s="54">
+        <f>J13/D13</f>
+        <v/>
+      </c>
+      <c r="L13" s="40" t="n">
+        <v>149100.03</v>
+      </c>
+      <c r="M13" s="54">
+        <f>L13/D13</f>
+        <v/>
+      </c>
+      <c r="N13" s="40" t="n">
+        <v>48882.34</v>
+      </c>
+      <c r="O13" s="54">
+        <f>N13/D13</f>
+        <v/>
+      </c>
+      <c r="P13" s="55">
+        <f>SUM(H13,J13,L13,N13)/D13</f>
+        <v/>
+      </c>
+      <c r="Q13" s="52" t="inlineStr">
+        <is>
+          <t>Only building in this batch with partial (75%) actual occupancy at DOV. GL carries two account series (5xxx and 6xxx) suggesting two building sections; both rolled together here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="33" t="inlineStr">
+        <is>
+          <t>Broadway Logistics Center</t>
+        </is>
+      </c>
+      <c r="B14" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D14" s="53" t="n">
+        <v>201025</v>
+      </c>
+      <c r="E14" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G14" s="33" t="inlineStr">
+        <is>
+          <t>0% (100% vacant)</t>
+        </is>
+      </c>
+      <c r="H14" s="40" t="n">
+        <v>32411.18</v>
+      </c>
+      <c r="I14" s="54">
+        <f>H14/D14</f>
+        <v/>
+      </c>
+      <c r="J14" s="40" t="n">
+        <v>11508.48</v>
+      </c>
+      <c r="K14" s="54">
+        <f>J14/D14</f>
+        <v/>
+      </c>
+      <c r="L14" s="40" t="n">
+        <v>9383.52</v>
+      </c>
+      <c r="M14" s="54">
+        <f>L14/D14</f>
+        <v/>
+      </c>
+      <c r="N14" s="40" t="n">
+        <v>12500</v>
+      </c>
+      <c r="O14" s="54">
+        <f>N14/D14</f>
+        <v/>
+      </c>
+      <c r="P14" s="55">
+        <f>SUM(H14,J14,L14,N14)/D14</f>
+        <v/>
+      </c>
+      <c r="Q14" s="52" t="inlineStr">
+        <is>
+          <t>Utilities = Recoverable $11,084.46 + Non-Recoverable 'Electricity Vacant' $424.02. CAM/R&amp;M = Repair &amp; Maint $3,639.29 + Contract Services (Fire Alarm/Sweeping/Janitorial) $5,744.23. Building 100% vacant all year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 24</t>
+        </is>
+      </c>
+      <c r="B15" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C15" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D15" s="53" t="n">
+        <v>215030</v>
+      </c>
+      <c r="E15" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G15" s="33" t="inlineStr">
+        <is>
+          <t>100% (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="H15" s="40" t="n">
+        <v>30832</v>
+      </c>
+      <c r="I15" s="54">
+        <f>H15/D15</f>
+        <v/>
+      </c>
+      <c r="J15" s="40" t="n">
+        <v>101924.33</v>
+      </c>
+      <c r="K15" s="54">
+        <f>J15/D15</f>
+        <v/>
+      </c>
+      <c r="L15" s="40" t="n">
+        <v>127450.06</v>
+      </c>
+      <c r="M15" s="54">
+        <f>L15/D15</f>
+        <v/>
+      </c>
+      <c r="N15" s="40" t="n">
+        <v>71320.8</v>
+      </c>
+      <c r="O15" s="54">
+        <f>N15/D15</f>
+        <v/>
+      </c>
+      <c r="P15" s="55">
+        <f>SUM(H15,J15,L15,N15)/D15</f>
+        <v/>
+      </c>
+      <c r="Q15" s="52" t="inlineStr">
+        <is>
+          <t>Full electricity/gas/water utilities present (multi-tenant, landlord pays and recovers via CAM). CAM/R&amp;M includes a '5312 Other-DTR' pass-through line ($5,821.17).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 11</t>
+        </is>
+      </c>
+      <c r="B16" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D16" s="53" t="n">
+        <v>244920</v>
+      </c>
+      <c r="E16" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G16" s="33" t="inlineStr">
+        <is>
+          <t>0% (100% vacant)</t>
+        </is>
+      </c>
+      <c r="H16" s="40" t="n">
+        <v>9460.52</v>
+      </c>
+      <c r="I16" s="54">
+        <f>H16/D16</f>
+        <v/>
+      </c>
+      <c r="J16" s="40" t="n">
+        <v>67358.14999999999</v>
+      </c>
+      <c r="K16" s="54">
+        <f>J16/D16</f>
+        <v/>
+      </c>
+      <c r="L16" s="40" t="n">
+        <v>43289.06</v>
+      </c>
+      <c r="M16" s="54">
+        <f>L16/D16</f>
+        <v/>
+      </c>
+      <c r="N16" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="54">
+        <f>N16/D16</f>
+        <v/>
+      </c>
+      <c r="P16" s="55">
+        <f>SUM(H16,J16,L16,N16)/D16</f>
+        <v/>
+      </c>
+      <c r="Q16" s="52" t="inlineStr">
+        <is>
+          <t>Self-managed by Majestic Realty — no 3rd-party management-fee GL line. Building 100% vacant all year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="33" t="inlineStr">
+        <is>
+          <t>Shamrock Foods</t>
+        </is>
+      </c>
+      <c r="B17" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C17" s="33" t="inlineStr">
+        <is>
+          <t>Warehouse</t>
+        </is>
+      </c>
+      <c r="D17" s="53" t="n">
+        <v>329903</v>
+      </c>
+      <c r="E17" s="33" t="inlineStr">
+        <is>
+          <t>TY2025 appeal</t>
+        </is>
+      </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>Proforma Assumption (not actual — owner-occupied, no tenant)</t>
+        </is>
+      </c>
+      <c r="G17" s="33" t="inlineStr">
+        <is>
+          <t>100% Owner-Occupied</t>
+        </is>
+      </c>
+      <c r="H17" s="40" t="n">
+        <v>56908</v>
+      </c>
+      <c r="I17" s="54">
+        <f>H17/D17</f>
+        <v/>
+      </c>
+      <c r="J17" s="33" t="n"/>
+      <c r="L17" s="33" t="n"/>
+      <c r="N17" s="40" t="n">
+        <v>56908</v>
+      </c>
+      <c r="O17" s="54">
+        <f>N17/D17</f>
+        <v/>
+      </c>
+      <c r="Q17" s="52" t="inlineStr">
+        <is>
+          <t>Insurance &amp; Management are the appeal's hypothetical fee-simple pro forma assumptions (3% of EGI each). Utilities and CAM/R&amp;M were not broken out separately — folded into the pro forma's blanket operating-expense load.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="33" t="inlineStr">
+        <is>
+          <t>22100 E 26th Ave (ASB)</t>
+        </is>
+      </c>
+      <c r="B18" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>406959</v>
+      </c>
+      <c r="E18" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G18" s="33" t="inlineStr">
+        <is>
+          <t>28% (6/30/2024)</t>
+        </is>
+      </c>
+      <c r="H18" s="40" t="n">
+        <v>201387.56</v>
+      </c>
+      <c r="I18" s="54">
+        <f>H18/D18</f>
+        <v/>
+      </c>
+      <c r="J18" s="40" t="n">
+        <v>124809.5</v>
+      </c>
+      <c r="K18" s="54">
+        <f>J18/D18</f>
+        <v/>
+      </c>
+      <c r="L18" s="40" t="n">
+        <v>97166.52</v>
+      </c>
+      <c r="M18" s="54">
+        <f>L18/D18</f>
+        <v/>
+      </c>
+      <c r="N18" s="40" t="n">
+        <v>36000</v>
+      </c>
+      <c r="O18" s="54">
+        <f>N18/D18</f>
+        <v/>
+      </c>
+      <c r="P18" s="55">
+        <f>SUM(H18,J18,L18,N18)/D18</f>
+        <v/>
+      </c>
+      <c r="Q18" s="52" t="inlineStr">
+        <is>
+          <t>CAM/R&amp;M = Cleaning $2,250 + Repairs &amp; Maintenance $17,250 + Roads &amp; Grounds $49,573.29 + Security &amp; Life Safety $28,093.23. Monthly-column OCR on this statement was unreliable (already flagged in Income-Expense Detail); these are the clean category-level annual TOTAL lines, which do not net perfectly to the statement's overall Total Operating Expense due to that OCR issue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="33" t="inlineStr">
+        <is>
+          <t>22100 E 26th Ave (ASB)</t>
+        </is>
+      </c>
+      <c r="B19" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C19" s="33" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="D19" s="53" t="n">
+        <v>406959</v>
+      </c>
+      <c r="E19" s="33" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G19" s="33" t="inlineStr">
+        <is>
+          <t>~22% (largely vacant, pre-Vederra lease)</t>
+        </is>
+      </c>
+      <c r="H19" s="40" t="n">
+        <v>140115.36</v>
+      </c>
+      <c r="I19" s="54">
+        <f>H19/D19</f>
+        <v/>
+      </c>
+      <c r="J19" s="40" t="n">
+        <v>200928.77</v>
+      </c>
+      <c r="K19" s="54">
+        <f>J19/D19</f>
+        <v/>
+      </c>
+      <c r="L19" s="40" t="n">
+        <v>58649.22</v>
+      </c>
+      <c r="M19" s="54">
+        <f>L19/D19</f>
+        <v/>
+      </c>
+      <c r="N19" s="40" t="n">
+        <v>36000</v>
+      </c>
+      <c r="O19" s="54">
+        <f>N19/D19</f>
+        <v/>
+      </c>
+      <c r="P19" s="55">
+        <f>SUM(H19,J19,L19,N19)/D19</f>
+        <v/>
+      </c>
+      <c r="Q19" s="52" t="inlineStr">
+        <is>
+          <t>CAM/R&amp;M = Cleaning $3,480 + Repairs &amp; Maintenance $21,396.45 + Roads &amp; Grounds $25,320.33 + Security &amp; Life Safety $8,452.44.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 29</t>
+        </is>
+      </c>
+      <c r="B20" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D20" s="53" t="n">
+        <v>452400</v>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G20" s="33" t="inlineStr">
+        <is>
+          <t>100% (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="H20" s="40" t="n">
+        <v>69076</v>
+      </c>
+      <c r="I20" s="54">
+        <f>H20/D20</f>
+        <v/>
+      </c>
+      <c r="J20" s="40" t="n">
+        <v>1080.84</v>
+      </c>
+      <c r="K20" s="54">
+        <f>J20/D20</f>
+        <v/>
+      </c>
+      <c r="L20" s="40" t="n">
+        <v>170658.68</v>
+      </c>
+      <c r="M20" s="54">
+        <f>L20/D20</f>
+        <v/>
+      </c>
+      <c r="N20" s="40" t="n">
+        <v>123809.45</v>
+      </c>
+      <c r="O20" s="54">
+        <f>N20/D20</f>
+        <v/>
+      </c>
+      <c r="P20" s="55">
+        <f>SUM(H20,J20,L20,N20)/D20</f>
+        <v/>
+      </c>
+      <c r="Q20" s="52" t="inlineStr">
+        <is>
+          <t>Utilities landlord-side captured only 'Fire Service' ($1,080.84) — electricity/gas/water appear tenant-billed direct or routed through a '5312 Other-DTR' pass-through account ($118,064.60, not classified into the 4 categories here). CAM/R&amp;M includes an unusually large $94,602 'Painting' line item (reproduced as printed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 12</t>
+        </is>
+      </c>
+      <c r="B21" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C21" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D21" s="53" t="n">
+        <v>461580</v>
+      </c>
+      <c r="E21" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F21" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G21" s="33" t="inlineStr">
+        <is>
+          <t>0% (100% vacant)</t>
+        </is>
+      </c>
+      <c r="H21" s="40" t="n">
+        <v>16527.93</v>
+      </c>
+      <c r="I21" s="54">
+        <f>H21/D21</f>
+        <v/>
+      </c>
+      <c r="J21" s="40" t="n">
+        <v>20820.4</v>
+      </c>
+      <c r="K21" s="54">
+        <f>J21/D21</f>
+        <v/>
+      </c>
+      <c r="L21" s="40" t="n">
+        <v>42752.71</v>
+      </c>
+      <c r="M21" s="54">
+        <f>L21/D21</f>
+        <v/>
+      </c>
+      <c r="N21" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="54">
+        <f>N21/D21</f>
+        <v/>
+      </c>
+      <c r="P21" s="55">
+        <f>SUM(H21,J21,L21,N21)/D21</f>
+        <v/>
+      </c>
+      <c r="Q21" s="52" t="inlineStr">
+        <is>
+          <t>Self-managed by Majestic Realty — no 3rd-party management-fee GL line. Building 100% vacant all year; costs are pure carrying costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>Majestic Commercenter Bldg 15</t>
+        </is>
+      </c>
+      <c r="B22" s="50" t="inlineStr">
+        <is>
+          <t>IND-WHSE</t>
+        </is>
+      </c>
+      <c r="C22" s="33" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="D22" s="53" t="n">
+        <v>702491</v>
+      </c>
+      <c r="E22" s="33" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F22" s="33" t="inlineStr">
+        <is>
+          <t>Actual</t>
+        </is>
+      </c>
+      <c r="G22" s="33" t="inlineStr">
+        <is>
+          <t>100% (single tenant)</t>
+        </is>
+      </c>
+      <c r="H22" s="40" t="n">
+        <v>96706</v>
+      </c>
+      <c r="I22" s="54">
+        <f>H22/D22</f>
+        <v/>
+      </c>
+      <c r="J22" s="40" t="n">
+        <v>3616.47</v>
+      </c>
+      <c r="K22" s="54">
+        <f>J22/D22</f>
+        <v/>
+      </c>
+      <c r="L22" s="40" t="n">
+        <v>79483.92</v>
+      </c>
+      <c r="M22" s="54">
+        <f>L22/D22</f>
+        <v/>
+      </c>
+      <c r="N22" s="40" t="n">
+        <v>123015.72</v>
+      </c>
+      <c r="O22" s="54">
+        <f>N22/D22</f>
+        <v/>
+      </c>
+      <c r="P22" s="55">
+        <f>SUM(H22,J22,L22,N22)/D22</f>
+        <v/>
+      </c>
+      <c r="Q22" s="52" t="inlineStr">
+        <is>
+          <t>Utilities landlord-side are minimal (Fire Service + a small 'Other' line) — consistent with a single-tenant NNN building where the tenant pays electricity/gas/water directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>NNN leases excluded from $/SF comps (tenant pays Insurance/Utilities/CAM/Management directly — no landlord-side actuals in the source documents)</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="n"/>
+      <c r="C24" s="39" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="39" t="n"/>
+      <c r="H24" s="39" t="n"/>
+      <c r="I24" s="39" t="n"/>
+      <c r="J24" s="39" t="n"/>
+      <c r="K24" s="39" t="n"/>
+      <c r="L24" s="39" t="n"/>
+      <c r="M24" s="39" t="n"/>
+      <c r="N24" s="39" t="n"/>
+      <c r="O24" s="39" t="n"/>
+      <c r="P24" s="39" t="n"/>
+      <c r="Q24" s="39" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="33" t="inlineStr">
+        <is>
+          <t>DEN3 - Bull Crossing</t>
+        </is>
+      </c>
+      <c r="B25" s="33" t="inlineStr">
+        <is>
+          <t>R0198789</t>
+        </is>
+      </c>
+      <c r="Q25" s="52" t="inlineStr">
+        <is>
+          <t>NNN — Amazon pays all opex directly; landlord pro forma uses a blanket 5% expense load, not itemized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="33" t="inlineStr">
+        <is>
+          <t>DEN7</t>
+        </is>
+      </c>
+      <c r="B26" s="33" t="inlineStr">
+        <is>
+          <t>R0198530</t>
+        </is>
+      </c>
+      <c r="Q26" s="52" t="inlineStr">
+        <is>
+          <t>NNN — Amazon pays all opex directly; landlord pro forma uses a blanket 5% expense load, not itemized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>DEN2 - PR Park 70</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>R0191292</t>
+        </is>
+      </c>
+      <c r="Q27" s="52" t="inlineStr">
+        <is>
+          <t>NNN — Amazon pays all opex directly; landlord pro forma uses a blanket 5% expense load, not itemized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="33" t="inlineStr">
+        <is>
+          <t>Home Depot Denver</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t>R0180551</t>
+        </is>
+      </c>
+      <c r="Q28" s="52" t="inlineStr">
+        <is>
+          <t>NNN — Home Depot pays all opex directly; no landlord-side actual $ in the appeal package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="52" t="inlineStr">
+        <is>
+          <t>How to use: click any header and use Data &gt; Filter (or the AutoFilter arrows already enabled) to sort/filter by OCC Code or Size (SF) and build a comp set for a subject property of similar use and size. 'Basis' distinguishes actual-statement figures from the one proforma-assumption row (Shamrock Foods, owner-occupied). $/SF is blank ('n/a') where a $ amount exists but the property's building SF wasn't captured in Property Master, or where the category wasn't reported/applicable. OCC Code is a simple use-based classification inferred from each property's Property Type / Use in this database (IND-WHSE = industrial warehouse, IND-DIST = industrial distribution, IND-MFG = industrial manufacturing, IND-FLEX = industrial/flex, COM-MT = commercial multi-tenant) — it is NOT an official Adams County CAMA occupancy code; map/replace with the official code if one is needed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q22"/>
+  <mergeCells count="4">
+    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A30:Q30"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Property Master" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tenants &amp; Leases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assessments &amp; Valuation" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income-Expense Detail" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Related Parcels" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Source Documents" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OCCC Legend" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Property Master" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Tenants &amp; Leases" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Assessments &amp; Valuation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Income-Expense Summary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Income-Expense Detail" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Related Parcels" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'OCCC Legend'!$A$4:$C$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Property Master'!$A$4:$Z$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Income-Expense Summary'!$A$4:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Income-Expense Detail'!$A$4:$F$65</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -183,7 +189,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -270,6 +276,8 @@
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -660,7 +668,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,7 +977,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -1010,7 +1016,164 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>OCCC CODE LEGEND</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="33" t="inlineStr">
+        <is>
+          <t>Occupancy Classification Codes -- assigned in this workbook from each property's Property Type / Use (Property Master tab). No such code existed in the source documents; rename/remap here if your organization uses a different OCCC scheme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>OCCC Code</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Commercial (multi-tenant industrial)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Broadview</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - 2-unit (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion Drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>IND-DIST</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Distribution</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>(7194) CO-Aurora</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>IND-FLEX</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Industrial / Flex (multi-tenant)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Washington Business Park</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Mfg / Food Processing</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>TempTee Brand Steaks</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>IND-WH</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Warehouse</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>7205 Gilpin Way, SGS - Pennsylvania Industrial, 6770 E. 56th Ave</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:C10"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1038,6 +1201,7 @@
     <col width="18" customWidth="1" min="23" max="23"/>
     <col width="22" customWidth="1" min="24" max="24"/>
     <col width="26" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -1054,7 +1218,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1179,6 +1342,11 @@
       <c r="Y4" s="4" t="inlineStr">
         <is>
           <t>Source File</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>OCCC Code</t>
         </is>
       </c>
     </row>
@@ -1292,6 +1460,11 @@
           <t>R0178308.pdf</t>
         </is>
       </c>
+      <c r="Z5" s="6" t="inlineStr">
+        <is>
+          <t>IND-WH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1401,6 +1574,11 @@
       <c r="Y6" s="6" t="inlineStr">
         <is>
           <t>R0169133.pdf</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="inlineStr">
+        <is>
+          <t>IND-DIST</t>
         </is>
       </c>
     </row>
@@ -1508,6 +1686,11 @@
           <t>R0103792.pdf</t>
         </is>
       </c>
+      <c r="Z7" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -1615,6 +1798,11 @@
           <t>5970 Marion P&amp;L/CF/xlsx</t>
         </is>
       </c>
+      <c r="Z8" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1726,6 +1914,11 @@
       <c r="Y9" s="6" t="inlineStr">
         <is>
           <t>5650_Washington_St.docx</t>
+        </is>
+      </c>
+      <c r="Z9" s="6" t="inlineStr">
+        <is>
+          <t>IND-FLEX</t>
         </is>
       </c>
     </row>
@@ -1835,6 +2028,11 @@
       <c r="Y10" s="6" t="inlineStr">
         <is>
           <t>R0024442.pdf</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
+        <is>
+          <t>IND-WH</t>
         </is>
       </c>
     </row>
@@ -1940,6 +2138,11 @@
           <t>R0002819.pdf</t>
         </is>
       </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2051,17 +2254,23 @@
           <t>R0092302.pdf</t>
         </is>
       </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>IND-WH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:Z12"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A1:Z1"/>
+    <mergeCell ref="A2:Z2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2100,7 +2309,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3143,7 +3351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3176,7 +3384,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,7 +3592,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="18" t="inlineStr">
         <is>
@@ -3400,7 +3606,6 @@
       <c r="G12" s="20" t="n"/>
       <c r="H12" s="21" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -3597,7 +3802,6 @@
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
     <row r="22" ht="28" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
@@ -3625,13 +3829,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3639,6 +3843,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3655,7 +3860,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3680,6 +3884,11 @@
       <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Basis / Source</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>OCCC Code</t>
         </is>
       </c>
     </row>
@@ -3704,6 +3913,11 @@
           <t>5970_Marion 2024 P&amp;L (cash; incl. debt svc &amp; taxes)</t>
         </is>
       </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -3726,6 +3940,11 @@
           <t>2023 Cash Flow (cash; incl. debt svc &amp; taxes)</t>
         </is>
       </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -3747,6 +3966,11 @@
           <t>Owner-occupied; reported OpEx only ('in house' items = $0)</t>
         </is>
       </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -3769,6 +3993,11 @@
           <t>IRS Form 8825 (tax basis; incl. depreciation, amort. &amp; interest)</t>
         </is>
       </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="9"/>
     <row r="10" ht="28" customHeight="1">
@@ -3780,25 +4009,27 @@
       <c r="B10" s="20" t="n"/>
       <c r="C10" s="20" t="n"/>
       <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="E10" s="20" t="n"/>
+      <c r="F10" s="21" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F10"/>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3806,6 +4037,7 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3822,7 +4054,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3849,6 +4080,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>OCCC Code</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -3874,6 +4110,11 @@
           <t>Whatever It Takes Transmissions + Integrated Turf Solutions</t>
         </is>
       </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -3897,6 +4138,11 @@
       <c r="E6" s="6" t="inlineStr">
         <is>
           <t>CAM recoveries</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
         </is>
       </c>
     </row>
@@ -3925,6 +4171,11 @@
           <t>Printed total: $249,672.20.</t>
         </is>
       </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -3946,6 +4197,11 @@
         <v>2175.55</v>
       </c>
       <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -3967,6 +4223,11 @@
         <v>394.3</v>
       </c>
       <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -3988,6 +4249,11 @@
         <v>100</v>
       </c>
       <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4009,6 +4275,11 @@
         <v>927.47</v>
       </c>
       <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4030,6 +4301,11 @@
         <v>200</v>
       </c>
       <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4055,6 +4331,11 @@
           <t>Deerwoods</t>
         </is>
       </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4080,6 +4361,11 @@
           <t>net $0</t>
         </is>
       </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4105,6 +4391,11 @@
           <t>Farmers</t>
         </is>
       </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4130,6 +4421,11 @@
           <t>Adams Co.</t>
         </is>
       </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4151,6 +4447,11 @@
         <v>800</v>
       </c>
       <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4176,6 +4477,11 @@
           <t>Alpine Bank</t>
         </is>
       </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4201,6 +4507,11 @@
           <t>Alpine Bank</t>
         </is>
       </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4222,6 +4533,11 @@
         <v>465</v>
       </c>
       <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -4243,6 +4559,11 @@
         <v>293.68</v>
       </c>
       <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -4269,6 +4590,11 @@
           <t>Printed total: $162,774.36. cash basis; incl. debt service &amp; property taxes</t>
         </is>
       </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -4290,6 +4616,11 @@
         <v>89143.03999999999</v>
       </c>
       <c r="E23" s="6" t="inlineStr"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -4311,6 +4642,11 @@
         <v>523.01</v>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -4332,6 +4668,11 @@
         <v>500</v>
       </c>
       <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -4353,6 +4694,11 @@
         <v>157145.5</v>
       </c>
       <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -4379,6 +4725,11 @@
           <t>Printed total: $247,311.55.</t>
         </is>
       </c>
+      <c r="F27" s="18" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -4400,6 +4751,11 @@
         <v>1550</v>
       </c>
       <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -4421,6 +4777,11 @@
         <v>47000</v>
       </c>
       <c r="E29" s="6" t="inlineStr"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -4442,6 +4803,11 @@
         <v>810</v>
       </c>
       <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -4463,6 +4829,11 @@
         <v>1016.31</v>
       </c>
       <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -4484,6 +4855,11 @@
         <v>2157.08</v>
       </c>
       <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -4505,6 +4881,11 @@
         <v>151.01</v>
       </c>
       <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -4526,6 +4907,11 @@
         <v>110</v>
       </c>
       <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -4547,6 +4933,11 @@
         <v>6000</v>
       </c>
       <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -4568,6 +4959,11 @@
         <v>180</v>
       </c>
       <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -4589,6 +4985,11 @@
         <v>8640.99</v>
       </c>
       <c r="E37" s="6" t="inlineStr"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -4610,6 +5011,11 @@
         <v>37726.76</v>
       </c>
       <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -4631,6 +5037,11 @@
         <v>4968.83</v>
       </c>
       <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -4652,6 +5063,11 @@
         <v>26699.59</v>
       </c>
       <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -4673,6 +5089,11 @@
         <v>51624.89</v>
       </c>
       <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -4699,6 +5120,11 @@
           <t>Printed total: $188,635.46. cash basis; Owner Draw $100,000 (financing) excluded</t>
         </is>
       </c>
+      <c r="F42" s="18" t="inlineStr">
+        <is>
+          <t>IND-2U</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -4720,6 +5146,11 @@
         <v>0</v>
       </c>
       <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -4741,6 +5172,11 @@
         <v>14050</v>
       </c>
       <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -4762,6 +5198,11 @@
         <v>10000</v>
       </c>
       <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -4787,6 +5228,11 @@
           <t>'in house'</t>
         </is>
       </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -4812,6 +5258,11 @@
           <t>'in house'</t>
         </is>
       </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -4833,6 +5284,11 @@
         <v>0</v>
       </c>
       <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -4854,6 +5310,11 @@
         <v>0</v>
       </c>
       <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -4875,6 +5336,11 @@
         <v>12000</v>
       </c>
       <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -4896,6 +5362,11 @@
         <v>102000</v>
       </c>
       <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -4922,6 +5393,11 @@
           <t>Printed total: $138,050.00. Adams Co. survey; 100% owner-occupied (~17,000 SF); 'in house' items = $0</t>
         </is>
       </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>IND-MFG</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -4945,6 +5421,11 @@
       <c r="E53" s="6" t="inlineStr">
         <is>
           <t>IRS Form 8825, Property A (125 Bridge St, COMMERCIAL)</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
         </is>
       </c>
     </row>
@@ -4973,6 +5454,11 @@
           <t>Printed total: $307,817.00.</t>
         </is>
       </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -4994,6 +5480,11 @@
         <v>776</v>
       </c>
       <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -5015,6 +5506,11 @@
         <v>12004</v>
       </c>
       <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -5036,6 +5532,11 @@
         <v>10211</v>
       </c>
       <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -5057,6 +5558,11 @@
         <v>98058</v>
       </c>
       <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -5078,6 +5584,11 @@
         <v>100279</v>
       </c>
       <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -5099,6 +5610,11 @@
         <v>4731</v>
       </c>
       <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -5120,6 +5636,11 @@
         <v>47109</v>
       </c>
       <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -5141,6 +5662,11 @@
         <v>1080</v>
       </c>
       <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -5162,6 +5688,11 @@
         <v>2166</v>
       </c>
       <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -5183,6 +5714,11 @@
         <v>39767</v>
       </c>
       <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
@@ -5209,17 +5745,23 @@
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
         </is>
       </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>COM-MT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:F65"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5249,7 +5791,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,7 +5926,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="18" t="inlineStr">
         <is>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -28,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="$#,##0.00"/>
     <numFmt numFmtId="167" formatCode="$#,##0.00;($#,##0.00);-"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +73,11 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -183,7 +188,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -269,6 +274,9 @@
     </xf>
     <xf numFmtId="166" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -635,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -656,11 +664,10 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-07-30  |  8 subject properties, all Adams County, Colorado</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Prepared for Carter Equities  |  Updated 2026-09-04  |  12 subject properties, all Adams County, Colorado</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -970,35 +977,169 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0102989.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal — income approach (proforma) + rent roll</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage, 4911 West 58th Ave., Arvada</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Assess. Yr 2023 (val. 6/30/2022)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (B. Henkels)</t>
+        </is>
+      </c>
+    </row>
     <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0169115.pdf</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Tax appeal — income approach (proforma) + actual P&amp;L + NSA/Securcare auth. schedule</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>11210 E 104th Avenue</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Value Yr 2025</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (M. Poling)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0099616.pdf</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Protest inquiry forms + property analysis (income approach, 6-schedule economic unit)</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage, 1777 W. 68th Ave., Denver</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025-2026 (val. 6/30/2024)</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>R.H. Jacobson &amp; Co. (D. Berger)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0085523.pdf</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Appeal cover letter + BAA Final Agency Order + Management Summaries</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage - Fitzsimons, 1520 N Fitzsimons Pkwy, Aurora</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2026 appeal (2023 BAA order on file)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists (D. Jaramillo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed.</t>
-        </is>
-      </c>
+      <c r="B20" s="20" t="n"/>
+      <c r="C20" s="20" t="n"/>
+      <c r="D20" s="20" t="n"/>
+      <c r="E20" s="20" t="n"/>
+      <c r="F20" s="21" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated. R0099616's six schedules (R0099616, R0099615, R0099617, R0180917, R0099618, R0180918) function as one economic unit per the taxpayer's analysis; combined 2025 notice value $7,659,751. R0085523's 2023 value was set at $5,200,000 by BAA Order (Docket 2023BAA2761), $200,000 allocated residential; the 2026 appeal requests $3,395,400 ($213,000 residential).</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n"/>
+      <c r="C21" s="20" t="n"/>
+      <c r="D21" s="20" t="n"/>
+      <c r="E21" s="20" t="n"/>
+      <c r="F21" s="21" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed. R0169115's Exhibit C authorization schedule lists ~29 other Colorado self-storage parcels under the NSA/Securcare family (see Related Parcels tab) that are NOT part of this economic unit — reproduced for reference only. R0102989 pages 6-22 (self-storage cap-rate survey / Denver market comps) and R0085523 pages 27-28 (CoStar apartment sale comps) were out of scope and skipped per extraction rules.</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n"/>
+      <c r="C22" s="20" t="n"/>
+      <c r="D22" s="20" t="n"/>
+      <c r="E22" s="20" t="n"/>
+      <c r="F22" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1010,7 +1151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y12"/>
+  <dimension ref="A1:Y16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1054,7 +1195,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="42" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -2049,6 +2189,424 @@
       <c r="Y12" s="6" t="inlineStr">
         <is>
           <t>R0092302.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>R0102989</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>R0102989</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>R0102989</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>4911 West 58th Ave.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Arvada</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>80002</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>MFP-Simply Storage Holdings Colorado, LLC</t>
+        </is>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage Holdings Colorado LLC</t>
+        </is>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>Self-Storage</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>Multi (self-storage, 524 units)</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>106286</v>
+      </c>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="8" t="n">
+        <v>84687</v>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>1.26:1</t>
+        </is>
+      </c>
+      <c r="T13" s="6" t="inlineStr">
+        <is>
+          <t>76.3% economic (as of 6/30/2022)</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>8150000</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="W13" s="9" t="n">
+        <v>5970000</v>
+      </c>
+      <c r="X13" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Bryce Henkels)</t>
+        </is>
+      </c>
+      <c r="Y13" s="6" t="inlineStr">
+        <is>
+          <t>R0102989.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>R0169115</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>R0169115</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0172114202001</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock Self Storage #20</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>11210 E 104th Avenue</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-lock Partners No. 20 LLC (PTA: National Storage Affiliates)</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-lock Partners No. 20 LLC</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>Self-Storage</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Multi (self-storage, NNN)</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="n"/>
+      <c r="O14" s="8" t="n"/>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="8" t="n">
+        <v>75430</v>
+      </c>
+      <c r="R14" s="6" t="n"/>
+      <c r="S14" s="6" t="n"/>
+      <c r="T14" s="6" t="n"/>
+      <c r="U14" s="9" t="n">
+        <v>7942335</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W14" s="9" t="n">
+        <v>6540000</v>
+      </c>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>Ryan LLC (Matt Poling)</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>R0169115.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>R0099616</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>R0099616 (+ R0099615, R0099617, R0180917, R0099618, R0180918)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>0182504223005 (+related)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1777 W. 68th Avenue</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>80221</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Self-Storage + Office/Residential (mixed use)</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Multi (self-storage + resident manager)</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>220762</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v>73500</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>73500</v>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>1985 &amp; 2001 (two bldgs)</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="n"/>
+      <c r="T15" s="6" t="n"/>
+      <c r="U15" s="9" t="n">
+        <v>7659751</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W15" s="9" t="n">
+        <v>6250000</v>
+      </c>
+      <c r="X15" s="6" t="inlineStr">
+        <is>
+          <t>R.H. Jacobson &amp; Co. (David G. Berger)</t>
+        </is>
+      </c>
+      <c r="Y15" s="6" t="inlineStr">
+        <is>
+          <t>R0099616.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>R0085523</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>R0085523</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>R0085523</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage - Fitzsimons</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>1520 N Fitzsimons Parkway</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>80011</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Mountain View (Fitzsimons) LLC</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>Mountain View (Fitzsimons) LLC</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Self-Storage (non-climate) + Manager Residence</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Multi (420 units) + residential apt</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>110350</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v>38423</v>
+      </c>
+      <c r="Q16" s="8" t="n">
+        <v>38423</v>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v>1973</v>
+      </c>
+      <c r="S16" s="6" t="n"/>
+      <c r="T16" s="6" t="inlineStr">
+        <is>
+          <t>85.2% units / 88.2% area (12/31/2023)</t>
+        </is>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="V16" s="5" t="inlineStr">
+        <is>
+          <t>2023 (BAA Order); 2026 appeal pending</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="n">
+        <v>3395400</v>
+      </c>
+      <c r="X16" s="6" t="inlineStr">
+        <is>
+          <t>Sterling Property Tax Specialists (Darla K. Jaramillo)</t>
+        </is>
+      </c>
+      <c r="Y16" s="6" t="inlineStr">
+        <is>
+          <t>R0085523.pdf</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2100,7 +2658,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3131,12 +3688,400 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Simply Storage, 4911 W 58th Ave, Arvada (R0102989) — self-storage rent roll (full unit detail on file, 524 units, as of 6/30/2022)</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="n"/>
+      <c r="C27" s="20" t="n"/>
+      <c r="D27" s="20" t="n"/>
+      <c r="E27" s="20" t="n"/>
+      <c r="F27" s="20" t="n"/>
+      <c r="G27" s="20" t="n"/>
+      <c r="H27" s="20" t="n"/>
+      <c r="I27" s="20" t="n"/>
+      <c r="J27" s="20" t="n"/>
+      <c r="K27" s="20" t="n"/>
+      <c r="L27" s="20" t="n"/>
+      <c r="M27" s="21" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>ALL UNITS (524)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage — multiple individual renters</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage / month-to-month</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>80463</v>
+      </c>
+      <c r="F28" s="6">
+        <f>E28*12</f>
+        <v/>
+      </c>
+      <c r="G28" s="6">
+        <f>F28/84687</f>
+        <v/>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" s="6" t="n"/>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>Actual standard/rental totals as of 6/30/2022 rent roll (11 pages). Economic occupancy 76.3%. PGI at 100% occ. $1,209,882/yr ($14.29 PSF); standard (asking) rate total $105,477/mo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock Self Storage #20, 11210 E 104th Ave (R0169115) — NNN self-storage, actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="n"/>
+      <c r="C29" s="20" t="n"/>
+      <c r="D29" s="20" t="n"/>
+      <c r="E29" s="20" t="n"/>
+      <c r="F29" s="20" t="n"/>
+      <c r="G29" s="20" t="n"/>
+      <c r="H29" s="20" t="n"/>
+      <c r="I29" s="20" t="n"/>
+      <c r="J29" s="20" t="n"/>
+      <c r="K29" s="20" t="n"/>
+      <c r="L29" s="20" t="n"/>
+      <c r="M29" s="21" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock Partners #20 (R0169115)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>ALL UNITS</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage — multiple individual renters</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage NNN / month-to-month</t>
+        </is>
+      </c>
+      <c r="E30" s="9">
+        <f>F30/12</f>
+        <v/>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>1155957.87</v>
+      </c>
+      <c r="G30" s="6">
+        <f>F30/75430</f>
+        <v/>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="9" t="n"/>
+      <c r="L30" s="6" t="n"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Actual 2024 rental income (Storage/Parking Rent) per operating P&amp;L. 2025 appeal proforma: GPR $1,206,880/yr ($16.00 PSF NNN); 12% vacancy; EGI $1,062,054; indicated value $6,540,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>All American Mini Storage, 1777 W 68th Ave, Denver (R0099616 economic unit, 6 schedules) — self-storage + resident manager</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="n"/>
+      <c r="C31" s="20" t="n"/>
+      <c r="D31" s="20" t="n"/>
+      <c r="E31" s="20" t="n"/>
+      <c r="F31" s="20" t="n"/>
+      <c r="G31" s="20" t="n"/>
+      <c r="H31" s="20" t="n"/>
+      <c r="I31" s="20" t="n"/>
+      <c r="J31" s="20" t="n"/>
+      <c r="K31" s="20" t="n"/>
+      <c r="L31" s="20" t="n"/>
+      <c r="M31" s="21" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>ALL UNITS + Office</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage — multiple individual renters</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage</t>
+        </is>
+      </c>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>226004</v>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K32" s="9" t="n"/>
+      <c r="L32" s="6" t="n"/>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>2024 Rental Income $226,004; plus Credit Card Deposits $600,338 and Misc. Income $8,016 (Total Income per Income Analysis exhibit $834,358 — see Income-Expense tabs). Building 73,500 SF (59,000 SF built 1985 + 14,500 SF built 2001) on 220,762 SF land incl. 2 drainage parcels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>Office/Residence Bldg</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>On-site manager residence + leasing office (non-rented)</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied / mixed use</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K33" s="9" t="n"/>
+      <c r="L33" s="6" t="n"/>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>County has valued 2 of the 6 schedules as vacant/detention-pond land; taxpayer requests $1,000 minimal value each. Requested value allocated $200,000 residential / $4,515,008 commercial for R0099616.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>IN Self Storage - Fitzsimons, 1520 N Fitzsimons Pkwy, Aurora (R0085523) — self-storage + manager apartment</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="n"/>
+      <c r="C34" s="20" t="n"/>
+      <c r="D34" s="20" t="n"/>
+      <c r="E34" s="20" t="n"/>
+      <c r="F34" s="20" t="n"/>
+      <c r="G34" s="20" t="n"/>
+      <c r="H34" s="20" t="n"/>
+      <c r="I34" s="20" t="n"/>
+      <c r="J34" s="20" t="n"/>
+      <c r="K34" s="20" t="n"/>
+      <c r="L34" s="20" t="n"/>
+      <c r="M34" s="21" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage - Fitzsimons (R0085523)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>ALL STORAGE UNITS (420)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage — multiple individual renters</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Self-storage / month-to-month, non-climate</t>
+        </is>
+      </c>
+      <c r="E35" s="9">
+        <f>F35/12</f>
+        <v/>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>532214.86</v>
+      </c>
+      <c r="G35" s="6">
+        <f>F35/38423</f>
+        <v/>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K35" s="9" t="n"/>
+      <c r="L35" s="6" t="n"/>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>Actual 2024 rental income per operating P&amp;L (420 units, 9 buildings, built 1973). Occupied 82.7% of units as of 12/31/2024 vs. 85.2% as of 12/31/2023 (Management Summary).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage - Fitzsimons (R0085523)</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Manager Apartment</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>On-site manager residence (non-rented)</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Owner-occupied / residential</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="6" t="n"/>
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K36" s="9" t="n"/>
+      <c r="L36" s="6" t="n"/>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>1,100 SF, 2BR/1BA. BAA Order (Docket 2023BAA2761/2024BAA2539) allocated $200,000 residential value within the 2023 ordered actual value of $5,200,000; 2026 appeal requests $213,000 residential allocation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A27:M27"/>
+    <mergeCell ref="A31:M31"/>
+    <mergeCell ref="A34:M34"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="A21:M21"/>
+    <mergeCell ref="A29:M29"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3149,7 +4094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3176,7 +4121,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -3385,241 +4329,462 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="21" t="n"/>
-    </row>
-    <row r="13"/>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>4911 West 58th Ave (Simply Storage) (R0102989)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>8150000</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>5970000</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>70.48999999999999</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>6251900</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>R0102989</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>11210 E 104th Ave (Stor-n-Lock #20) (R0169115)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>7942335</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>105.28</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>6540000</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>87</v>
+      </c>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>R0169115</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (All American Mini Storage) (R0099616, 6-schedule econ. unit)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>7659751</v>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>104.22</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>6250000</v>
+      </c>
+      <c r="F14" s="16" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>R0099616 (+5 related schedules)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>1520 N Fitzsimons Pkwy (IN Self Storage-Fitzsimons) (R0085523)</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>2023 (BAA)</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="D15" s="16" t="n">
+        <v>135.36</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>3395400</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>6998300</v>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>R0085523</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Historical detail — R0178308: 2025 Land $1,125,150 / Imp $4,025,175 / Total $5,150,325; 2024 Total $4,999,770.  R0169133: 2025 Land $992,519 / Imp $2,122,296 / schedule Total $3,114,815 (cover shows $3,408,546); 2024 Total $2,900,000.  R0024442: 2024 County $2,000,000 → 2025 $3,876,387 (+93.8%).  R0102989: 2023 Assessor $8,150,000 ($96.24/SF) vs. 2022 $6,251,900 ($73.82/SF), +30.36%. R0169115: 2025 Assessor $7,942,335. R0099616 economic unit (6 schedules): current 2025 total $7,659,751 = R0099616 $5,637,471 + R0099615 $375,616 + R0099617 $518,976 + R0180917 $638,400 + R0099618 $300,384 (drainage) + R0180918 $188,904 (drainage); requested $6,250,000 allocated $200,000 residential / $4,515,008 commercial to R0099616, with the 2 drainage parcels reduced to $1,000 each. R0085523: 2023 CBOE value $6,998,300 reduced to $5,200,000 by BAA Order (Docket 2023BAA2761), $200,000 of which allocated residential (Order 2024BAA2539); 2026 appeal requests $3,395,400 ($213,000 residential / $3,182,400 commercial).</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="n"/>
+      <c r="C16" s="20" t="n"/>
+      <c r="D16" s="20" t="n"/>
+      <c r="E16" s="20" t="n"/>
+      <c r="F16" s="20" t="n"/>
+      <c r="G16" s="20" t="n"/>
+      <c r="H16" s="21" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>B. Income-Approach Proformas</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="21" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="B18" s="20" t="n"/>
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20" t="n"/>
+      <c r="E18" s="20" t="n"/>
+      <c r="F18" s="20" t="n"/>
+      <c r="G18" s="20" t="n"/>
+      <c r="H18" s="21" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Property</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>PGI</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Vacancy</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>EGI</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Operating Exp</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>NOI</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Cap Rate</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Indicated Value</t>
         </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>7205 Gilpin Way</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="n">
-        <v>359394</v>
-      </c>
-      <c r="C16" s="9" t="n">
-        <v>-17970</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>341424</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <v>-27314</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>314110</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>4832500</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>17608 E. 24th Dr</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="n">
-        <v>209100</v>
-      </c>
-      <c r="C17" s="9" t="n">
-        <v>-10455</v>
-      </c>
-      <c r="D17" s="9" t="n">
-        <v>198645</v>
-      </c>
-      <c r="E17" s="9" t="n">
-        <v>-15892</v>
-      </c>
-      <c r="F17" s="14" t="n">
-        <v>182753</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>3050000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>12260 Pennsylvania St</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="n">
-        <v>237290</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <v>-16610</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>220680</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>-22068</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>198612</v>
-      </c>
-      <c r="G18" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>2837000</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>6770 E. 56th Ave</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n">
-        <v>115824</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>-5791</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>110033</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>-5502</v>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>104531</v>
-      </c>
-      <c r="G19" s="19" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H19" s="14" t="n">
-        <v>1493302</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>5970 Marion Drive (mkt)</t>
+          <t>7205 Gilpin Way</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>172800</v>
+        <v>359394</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>-8640</v>
+        <v>-17970</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>164160</v>
+        <v>341424</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>-4223</v>
+        <v>-27314</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>159937</v>
+        <v>314110</v>
       </c>
       <c r="G20" s="19" t="n">
         <v>0.065</v>
       </c>
       <c r="H20" s="14" t="n">
+        <v>4832500</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>17608 E. 24th Dr</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>209100</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>-10455</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>198645</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>-15892</v>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>182753</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H21" s="14" t="n">
+        <v>3050000</v>
+      </c>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>12260 Pennsylvania St</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>237290</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>-16610</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>220680</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>-22068</v>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>198612</v>
+      </c>
+      <c r="G22" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H22" s="14" t="n">
+        <v>2837000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>6770 E. 56th Ave</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>115824</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>-5791</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>110033</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>-5502</v>
+      </c>
+      <c r="F23" s="14" t="n">
+        <v>104531</v>
+      </c>
+      <c r="G23" s="19" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H23" s="14" t="n">
+        <v>1493302</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>5970 Marion Drive (mkt)</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n">
+        <v>172800</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>-8640</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>164160</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>-4223</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>159937</v>
+      </c>
+      <c r="G24" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H24" s="14" t="n">
         <v>2460577</v>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="21" t="n"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989)</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="n">
+        <v>1209882</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>-286984</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>922898</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>-369159</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <v>553739</v>
+      </c>
+      <c r="G26" s="19" t="n">
+        <v>0.09279999999999999</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <v>5970000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115)</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="n">
+        <v>1206880</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>-144826</v>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1062054</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <v>-637233</v>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>424822</v>
+      </c>
+      <c r="G27" s="19" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="H27" s="14" t="n">
+        <v>6540000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616, stabilized)</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>800000</v>
+      </c>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>-165000</v>
+      </c>
+      <c r="F28" s="14" t="n">
+        <v>635000</v>
+      </c>
+      <c r="G28" s="19" t="n">
+        <v>0.1023</v>
+      </c>
+      <c r="H28" s="14" t="n">
+        <v>6094050</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523, avg 2023-24 actual)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n">
+        <v>539835.5</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>-200300</v>
+      </c>
+      <c r="F29" s="14" t="n">
+        <v>339535</v>
+      </c>
+      <c r="G29" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H29" s="14" t="n">
+        <v>3395400</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Proforma vacancy/EGI figures as reported by each preparer (Ryan, Property Tax Advisors, or owner's analysis). 5970 Marion figures are from the owner's income-approach block in the 2024 P&amp;L workbook (PGI $172,800, 95% occ, NOI $159,938, 6.5% cap → $2,460,577; assigned $2,527,915).  R0102989 (Simply Storage): NOI is capitalized at a loaded overall rate of 9.28% (6.00% base cap rate + 3.28% effective tax rate load) rather than being taxed separately; PGI/EGI reflect actual 2022 economic occupancy (76.28%). R0169115 (Stor-n-Lock #20): NNN proforma, 12% vacancy, 60% non-reimbursable expense ratio. R0099616 (All American Mini Storage): stabilized column from the taxpayer's 4-year income analysis (2021-2024 actual), 10.23% loaded cap rate (7.00% + 3.23% ETR); value shown excludes taxes from the expense line (taxes loaded into the rate) — an alternate calc with taxes as an expense (7.00% flat rate) gives $6,571,429. R0085523 (IN Self Storage-Fitzsimons): NOI is the average of actual 2023 ($384,712) and 2024 ($294,359) adjusted NOI (actual EGI less actual expenses net of property tax, plus a 3% capital-replacement reserve, per Sterling Property Tax Specialists' 2026 appeal); loaded rate 10.00% (7.00% cap + 3.00% ETR).</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
+      <c r="E30" s="20" t="n"/>
+      <c r="F30" s="20" t="n"/>
+      <c r="G30" s="20" t="n"/>
+      <c r="H30" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A22:H22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3631,7 +4796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -3655,7 +4820,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -3770,23 +4934,154 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="n">
+        <v>922898</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>677550</v>
+      </c>
+      <c r="D9" s="23">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Ryan appeal notes (2022 P&amp;L not included in file); NOI $245,348 stated directly, expense derived as EGI−NOI (incl. property tax)</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas.</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="n">
+        <v>1206603.08</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>688345.26</v>
+      </c>
+      <c r="D10" s="23">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Operating P&amp;L (cash basis); excludes interest income, mortgage interest &amp; depreciation (see Detail tab for those)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="n">
+        <v>834358</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <v>388298</v>
+      </c>
+      <c r="D11" s="23">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Income Analysis exhibit; income incl. credit card deposits; expense incl. RE taxes $176,136</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2023</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>750575</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <v>317929</v>
+      </c>
+      <c r="D12" s="23">
+        <f>B12-C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Income Analysis exhibit; income incl. credit card deposits; expense incl. RE taxes $171,843</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="n">
+        <v>532214.86</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <v>371033.04</v>
+      </c>
+      <c r="D13" s="23">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Operating P&amp;L (cash basis); excludes debt-service interest &amp; member distributions (see Detail tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>547455.6800000001</v>
+      </c>
+      <c r="C14" s="22" t="n">
+        <v>297826.34</v>
+      </c>
+      <c r="D14" s="23">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Operating P&amp;L (cash basis); excludes debt-service interest (see Detail tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>Net = Total Income − Total Expense as printed. Bases differ: 5970 Marion &amp; Broadview totals include financing/depreciation, so they are cash-flow / tax figures, not NOI. TempTee reported operating expenses only. See 'Assessments &amp; Valuation' tab for stabilized NOI proformas. R0102989/R0169115/R0099616/R0085523 add self-storage tax-appeal properties. R0169115 &amp; R0085523 totals are operating-only (excl. financing/depreciation, cash basis); R0099616 totals include RE taxes as an expense per the taxpayer's own Income Analysis exhibit.</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n"/>
+      <c r="C15" s="20" t="n"/>
+      <c r="D15" s="20" t="n"/>
+      <c r="E15" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3798,7 +5093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3822,7 +5117,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5207,6 +6501,1604 @@
       <c r="E65" s="18" t="inlineStr">
         <is>
           <t>Printed total: $316,181.00. IRS Form 8825; net rental loss $(8,364). Tax basis (incl. depreciation, amortization &amp; interest).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Effective Gross Income (actual, net of refunds)</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>922898</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>Per Ryan appeal proforma notes; source 2022 P&amp;L not included in this file</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D67" s="22">
+        <f>SUM(D66:D66)</f>
+        <v/>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>Printed as EGI $922,898</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Total Operating Expenses (incl. property tax)</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>677550</v>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>Derived: EGI $922,898 − stated NOI $245,348</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D69" s="22">
+        <f>SUM(D68:D68)</f>
+        <v/>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>Derived, not printed directly</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>NOI (as stated, incl. property tax)</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="n">
+        <v>245348</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>Actual YE2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>NOI excl. property tax</t>
+        </is>
+      </c>
+      <c r="D71" s="22" t="n">
+        <v>403718.35</v>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>Actual YE2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Simply Storage (R0102989) — Actual 2022</t>
+        </is>
+      </c>
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>NOI excl. property tax &amp; Taxes-Escrow line</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="n">
+        <v>508528.9</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>Actual YE2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
+      <c r="D73" s="22" t="n">
+        <v>1155957.87</v>
+      </c>
+      <c r="E73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B74" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>Late Fee Income</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="n">
+        <v>24921.03</v>
+      </c>
+      <c r="E74" s="6" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B75" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Locks &amp; Misc Income</t>
+        </is>
+      </c>
+      <c r="D75" s="22" t="n">
+        <v>3947.95</v>
+      </c>
+      <c r="E75" s="6" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B76" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>Administrative Income</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E76" s="6" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Other Property Income</t>
+        </is>
+      </c>
+      <c r="D77" s="22" t="n">
+        <v>15796.23</v>
+      </c>
+      <c r="E77" s="6" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B78" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D78" s="22">
+        <f>SUM(D73:D77)</f>
+        <v/>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $1,206,603.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B79" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Employment Expenses (salaries, payroll tax, benefits)</t>
+        </is>
+      </c>
+      <c r="D79" s="22" t="n">
+        <v>106696.02</v>
+      </c>
+      <c r="E79" s="6" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B80" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>Office &amp; Site Expenses</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="n">
+        <v>34608.63</v>
+      </c>
+      <c r="E80" s="6" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B81" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="D81" s="22" t="n">
+        <v>18344.37</v>
+      </c>
+      <c r="E81" s="6" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B82" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="n">
+        <v>1927.8</v>
+      </c>
+      <c r="E82" s="6" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B83" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D83" s="22" t="n">
+        <v>16957</v>
+      </c>
+      <c r="E83" s="6" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B84" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>Snow Removal</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="n">
+        <v>7653.04</v>
+      </c>
+      <c r="E84" s="6" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B85" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Administrative Expenses (legal, mgmt fee, dues)</t>
+        </is>
+      </c>
+      <c r="D85" s="22" t="n">
+        <v>87155.08</v>
+      </c>
+      <c r="E85" s="6" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B86" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="n">
+        <v>13024.73</v>
+      </c>
+      <c r="E86" s="6" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B87" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Property Expenses (Taxes $389,500.16 + Insurance $12,478.43)</t>
+        </is>
+      </c>
+      <c r="D87" s="22" t="n">
+        <v>401978.59</v>
+      </c>
+      <c r="E87" s="6" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B88" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE</t>
+        </is>
+      </c>
+      <c r="D88" s="22">
+        <f>SUM(D79:D87)</f>
+        <v/>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $688,345.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B89" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Net Ordinary Income (operating)</t>
+        </is>
+      </c>
+      <c r="D89" s="22" t="n">
+        <v>518257.82</v>
+      </c>
+      <c r="E89" s="6" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B90" s="25" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>Interest Earned</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>13497.86</v>
+      </c>
+      <c r="E90" s="6" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B91" s="25" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Maintenance - Other</t>
+        </is>
+      </c>
+      <c r="D91" s="22" t="n">
+        <v>28640.65</v>
+      </c>
+      <c r="E91" s="6" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B92" s="25" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>Mortgage Interest</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="n">
+        <v>134793.9</v>
+      </c>
+      <c r="E92" s="6" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B93" s="25" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>Depreciation/Amortization</t>
+        </is>
+      </c>
+      <c r="D93" s="22" t="n">
+        <v>54137</v>
+      </c>
+      <c r="E93" s="6" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>Stor-n-Lock #20 (R0169115) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B94" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>Net Income (all-in)</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="n">
+        <v>314184.13</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Printed total</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B95" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>Rental Income</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="n">
+        <v>226004</v>
+      </c>
+      <c r="E95" s="6" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B96" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>Credit Card Deposits</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>600338</v>
+      </c>
+      <c r="E96" s="6" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B97" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>Miscellaneous Income</t>
+        </is>
+      </c>
+      <c r="D97" s="22" t="n">
+        <v>8016</v>
+      </c>
+      <c r="E97" s="6" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B98" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="D98" s="22">
+        <f>SUM(D95:D97)</f>
+        <v/>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $834,358</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B99" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>18408</v>
+      </c>
+      <c r="E99" s="6" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B100" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>Accounting</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="n">
+        <v>3590</v>
+      </c>
+      <c r="E100" s="6" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B101" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>Credit Card Fees</t>
+        </is>
+      </c>
+      <c r="D101" s="22" t="n">
+        <v>16172</v>
+      </c>
+      <c r="E101" s="6" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B102" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>Bank Charges</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="n">
+        <v>287</v>
+      </c>
+      <c r="E102" s="6" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B103" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D103" s="22" t="n">
+        <v>23000</v>
+      </c>
+      <c r="E103" s="6" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B104" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>Medical Insurance</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="n">
+        <v>8685</v>
+      </c>
+      <c r="E104" s="6" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B105" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>Federal Taxes Withholding</t>
+        </is>
+      </c>
+      <c r="D105" s="22" t="n">
+        <v>2685</v>
+      </c>
+      <c r="E105" s="6" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B106" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>State Taxes Withholding</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>390</v>
+      </c>
+      <c r="E106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B107" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>Unemployment Tax</t>
+        </is>
+      </c>
+      <c r="D107" s="22" t="n">
+        <v>533</v>
+      </c>
+      <c r="E107" s="6" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B108" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>Workman's Compensation</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="n">
+        <v>1472</v>
+      </c>
+      <c r="E108" s="6" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B109" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>Payroll</t>
+        </is>
+      </c>
+      <c r="D109" s="22" t="n">
+        <v>41277</v>
+      </c>
+      <c r="E109" s="6" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B110" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>Advertising</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="n">
+        <v>168</v>
+      </c>
+      <c r="E110" s="6" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B111" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>IT / Phone</t>
+        </is>
+      </c>
+      <c r="D111" s="22" t="n">
+        <v>3925</v>
+      </c>
+      <c r="E111" s="6" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B112" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>Supplies</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>828</v>
+      </c>
+      <c r="E112" s="6" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B113" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>6434</v>
+      </c>
+      <c r="E113" s="6" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B114" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>Water / Sewer</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="n">
+        <v>2126</v>
+      </c>
+      <c r="E114" s="6" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B115" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>Trash</t>
+        </is>
+      </c>
+      <c r="D115" s="22" t="n">
+        <v>4770</v>
+      </c>
+      <c r="E115" s="6" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B116" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="n">
+        <v>3382</v>
+      </c>
+      <c r="E116" s="6" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>Building Maintenance</t>
+        </is>
+      </c>
+      <c r="D117" s="22" t="n">
+        <v>24753</v>
+      </c>
+      <c r="E117" s="6" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>Fire / Security</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="n">
+        <v>497</v>
+      </c>
+      <c r="E118" s="6" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>Miscellaneous (3 lines)</t>
+        </is>
+      </c>
+      <c r="D119" s="22" t="n">
+        <v>48780</v>
+      </c>
+      <c r="E119" s="6" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B120" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>Subtotal Operating Expenses (excl. RE taxes)</t>
+        </is>
+      </c>
+      <c r="D120" s="22">
+        <f>SUM(D99:D119)</f>
+        <v/>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $212,162</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>Real Estate Taxes</t>
+        </is>
+      </c>
+      <c r="D121" s="22" t="n">
+        <v>176136</v>
+      </c>
+      <c r="E121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE (incl. RE taxes)</t>
+        </is>
+      </c>
+      <c r="D122" s="22">
+        <f>D120+D121</f>
+        <v/>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: $388,298</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>NOI excl. RE taxes</t>
+        </is>
+      </c>
+      <c r="D123" s="22" t="n">
+        <v>622196</v>
+      </c>
+      <c r="E123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
+        <is>
+          <t>All American Mini Storage (R0099616 econ. unit) — Actual 2024</t>
+        </is>
+      </c>
+      <c r="B124" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>NOI incl. RE taxes (as expense)</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="n">
+        <v>446060</v>
+      </c>
+      <c r="E124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B125" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>Storage/Parking Rent</t>
+        </is>
+      </c>
+      <c r="D125" s="22" t="n">
+        <v>547455.6800000001</v>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME (printed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B126" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="n">
+        <v>170192.4</v>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>Included within TOTAL EXPENSE below</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B127" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE (operating, cash basis, printed)</t>
+        </is>
+      </c>
+      <c r="D127" s="22" t="n">
+        <v>297826.34</v>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>Printed total; see Assessors Exhibit B for full line-item budget-vs-actual detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B128" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>Net Operating Income (operating)</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="n">
+        <v>249629.34</v>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: Income − Total Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B129" s="25" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>Debt Service - Interest Expense</t>
+        </is>
+      </c>
+      <c r="D129" s="22" t="n">
+        <v>117371.63</v>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>Non-operating; excluded from operating NOI above</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2023 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B130" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>Net Income (all-in, incl. debt service &amp; other)</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="n">
+        <v>131613.65</v>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>2024 figure includes a $99,000 member dividend distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B131" s="25" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>Storage/Parking Rent</t>
+        </is>
+      </c>
+      <c r="D131" s="22" t="n">
+        <v>532214.86</v>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL INCOME (printed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B132" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>Property Taxes</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="n">
+        <v>209139.14</v>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>Included within TOTAL EXPENSE below</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B133" s="25" t="inlineStr">
+        <is>
+          <t>Expense</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL EXPENSE (operating, cash basis, printed)</t>
+        </is>
+      </c>
+      <c r="D133" s="22" t="n">
+        <v>371033.04</v>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>Printed total; see Assessors Exhibit B for full line-item budget-vs-actual detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B134" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>Net Operating Income (operating)</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="n">
+        <v>161181.82</v>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>Printed total: Income − Total Expense</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B135" s="25" t="inlineStr">
+        <is>
+          <t>Other Expense</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>Debt Service - Interest Expense</t>
+        </is>
+      </c>
+      <c r="D135" s="22" t="n">
+        <v>115773.01</v>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>Non-operating; excluded from operating NOI above</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>IN Self Storage-Fitzsimons (R0085523) — Actual 2024 P&amp;L</t>
+        </is>
+      </c>
+      <c r="B136" s="25" t="inlineStr">
+        <is>
+          <t>Memo</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>Net Income (all-in, incl. debt service &amp; other)</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="n">
+        <v>-55489.94</v>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>2024 figure includes a $99,000 member dividend distribution</t>
         </is>
       </c>
     </row>
@@ -5225,7 +8117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5249,7 +8141,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -5385,23 +8276,967 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>R0099616</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (Lot 1) — primary appeal subject</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager).</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="21" t="n"/>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>R0099615</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (Lot 4)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>R0099617</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (Lot 3)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>R0180917</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (Lot 4, 2nd schedule)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>R0099618</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (Lot 2, drainage parcel)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Kekake Hale LLC</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>R0180918</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>1777 W 68th Ave (Lot 2, drainage parcel, 2nd schedule)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Adams County</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties II LLC</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>1573-32-1-22-001</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>2460 E Midway Blvd</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Broomfield County &amp; City</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties II LLC</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>1573-32-1-22-002</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>2430 W 128th Ave</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Broomfield County &amp; City</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties II LLC</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>1573-32-1-22-003</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>2410 E Midway Blvd</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Broomfield County &amp; City</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Nsa Property Holdings, LLC</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>6402218002</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>2345 Academy Pl</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties II R LLC</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>6426420013</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>4615 Astrozon Blvd</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>6304203003</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>1408 Chapel Hills Dr</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Portfolio Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>6430100037</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>320 E Saint Elmo Ave</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Colorado III LLC</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>6315412037</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>3420 Vickers Dr</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>6304216001</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Jamboree Dr</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Colorado III LLC</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>7402408073</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>2005 King St</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Maizeland Storage LLC</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>6403101003</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>3737 Maizeland Rd</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Maizeland Storage LLC</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>6403101006</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>3728 Alpine Pl</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>6330100120</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>4215-4225 N Nevada Ave</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties I LLC</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>6423202007</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>777 S Academy Blvd</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Portfolio Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>6419413057</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>1545 S Nevada Ave</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>6524119025</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>7112 Alegre St</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>6524119035</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>639 Carson Blvd</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>6524404013</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>7102 Alegre St</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties I LLC</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>9601161001</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>4815 Boardwalk Dr</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Larimer County</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties I LLC</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>8731422001</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>1961 Caribou Dr</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Larimer County</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Securcare Properties I LLC</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>8731451001</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>1961 Caribou Dr</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Larimer County</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Town Center Self Storage LLC</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>R0496304</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>855 Sgt Jon Stiles Dr</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Douglas County</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>7111304021</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>1895 Deer Creek Rd</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>N S A Property Holdings LLC; C/o Securcare Storage</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>1523001001</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>90 Greenhorn Dr</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>Pueblo County</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Nsa Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>146719365001</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>1012 Carbon Ct</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Weld County</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Nsa Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>601006009</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>517 E Industrial Blvd</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Pueblo County</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>7115201001</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>605 Highway 105</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>7115201012</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>2810 Roberts Dr</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>NSA Property Holdings LLC</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>7115201013</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>2925 Peak View Blvd</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>El Paso County</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
+        <is>
+          <t>Highlighted row (R0178308 / 7205 Gilpin Way) is the primary appeal subject; the other three parcels are co-listed on the same authorization schedule. Appeal owner of record: Center Land Properties (signed by Ken R. Lombardi, Manager). Kekake Hale LLC rows: the 6 schedules that make up the All American Mini Storage economic unit (R0099616 appeal); R0099618 &amp; R0180918 are the 2 detention-pond "drainage" parcels the taxpayer contends are over-valued as buildable land. NSA/Securcare rows (from "Securcare Properties II LLC" through "2925 Peak View Blvd"): the National Storage Affiliates / Securcare portfolio of ~29 other Colorado self-storage parcels listed on the Letter of Authorization (Exhibit C) attached to the R0169115 (Stor-n-Lock Partners #20) appeal — separate ownership entities within the NSA family, reproduced for reference; none is part of the R0169115 economic unit or valuation.</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="20" t="n"/>
+      <c r="D44" s="20" t="n"/>
+      <c r="E44" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A44:E44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Master_Property_Database.xlsx
+++ b/Master_Property_Database.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -664,7 +664,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for Carter Equities  |  Updated 2026-09-04  |  12 subject properties, all Adams County, Colorado</t>
+          <t>Prepared for Carter Equities  |  Updated 2026-09-04  |  15 subject properties, all Adams County, Colorado</t>
         </is>
       </c>
     </row>
@@ -1098,48 +1098,138 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>R0071007.pdf</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>SB 11-119 income/expense disclosure: cover letter + IRS Form 8825 (2023 &amp; 2024) + 2023 &amp; H1-2024 rent rolls</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Warehouse and Storage Building(s), N. Pecos Ave, Denver (T &amp; G Pecos LLC)</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>2023-2024</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>R0055143.pdf</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Real Property Protest Form + Letter of Agency + 26-Month Rolling Income Statement + 36-Month Activity Summary</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Blvd, Denver (8700 Devonshire Storage LLC / CubeSmart-managed)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Tax Yr 2025 (data Aug 2023-Feb 2025)</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>National Bureau Property Advisors (Evan Lantz)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>R0043569.pdf</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Monthly P&amp;L export (Actuals)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Public Storage #08214, Thornton / 104th &amp; Quivas St</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>Public Storage (internal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Notes: Figures transcribed from the source documents. Total / net / average cells are live formulas (SUM/AVERAGE) verified against the printed totals; they populate on open in Excel/Sheets.</t>
         </is>
       </c>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="21" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated. R0099616's six schedules (R0099616, R0099615, R0099617, R0180917, R0099618, R0180918) function as one economic unit per the taxpayer's analysis; combined 2025 notice value $7,659,751. R0085523's 2023 value was set at $5,200,000 by BAA Order (Docket 2023BAA2761), $200,000 allocated residential; the 2026 appeal requests $3,395,400 ($213,000 residential).</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="21" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed. R0169115's Exhibit C authorization schedule lists ~29 other Colorado self-storage parcels under the NSA/Securcare family (see Related Parcels tab) that are NOT part of this economic unit — reproduced for reference only. R0102989 pages 6-22 (self-storage cap-rate survey / Denver market comps) and R0085523 pages 27-28 (CoStar apartment sale comps) were out of scope and skipped per extraction rules.</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="21" t="n"/>
+      <c r="B24" s="20" t="n"/>
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20" t="n"/>
+      <c r="E24" s="20" t="n"/>
+      <c r="F24" s="21" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>'in house' on the TempTee survey = owner self-performs the service (no $ reported), entered as $0. 5650 Washington St concluded value, rent-roll grid, and income proforma are embedded as EMF vector images in the DOCX and were not text-extractable; narrative figures are captured where stated. R0099616's six schedules (R0099616, R0099615, R0099617, R0180917, R0099618, R0180918) function as one economic unit per the taxpayer's analysis; combined 2025 notice value $7,659,751. R0085523's 2023 value was set at $5,200,000 by BAA Order (Docket 2023BAA2761), $200,000 allocated residential; the 2026 appeal requests $3,395,400 ($213,000 residential). R0071007 (T &amp; G Pecos LLC) is an outdoor/indoor multi-tenant storage-yard property (~90 individual bays/units, Buildings A-G) leased to a mix of individuals and small trade businesses; not enumerated tenant-by-tenant here given the count — see the Tenants &amp; Leases tab for an aggregate line and the source PDF for the full rent roll. R0055143's 26-month rolling income statement is a dense, rotated scanned table; only clearly-legible subtotals (Total Income, Total Expense, Net Operating Income, and the post-debt-service Net Profit/Loss) were transcribed — line-item categories were not, to avoid transcription error. R0043569 (Public Storage #08214) came with no cover letter/appeal — only a FY2024 monthly Actuals P&amp;L; no assessor or taxpayer opinion value is available for it in this file.</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="20" t="n"/>
+      <c r="D25" s="20" t="n"/>
+      <c r="E25" s="20" t="n"/>
+      <c r="F25" s="21" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>5970 Marion cash-basis 'expense' includes mortgage P&amp;I and property taxes (cash flow, not NOI). R0169133 cover value ($3,408,546) differs from its schedule total ($3,114,815); both reproduced as printed. R0169115's Exhibit C authorization schedule lists ~29 other Colorado self-storage parcels under the NSA/Securcare family (see Related Parcels tab) that are NOT part of this economic unit — reproduced for reference only. R0102989 pages 6-22 (self-storage cap-rate survey / Denver market comps) and R0085523 pages 27-28 (CoStar apartment sale comps) were out of scope and skipped per extraction rules. R0071007, R0055143 and R0043569 have no assessor 'current value' or protest ask in their source files except R0055143, whose Real Property Protest Form gives a taxpayer estimate of $2,000,000 (as of 6/30) with no county notice value shown; none is added to the Assessments &amp; Valuation 'Income-Approach Proformas' section since none of the three includes a PGI/vacancy/cap-rate proforma (all are actual-P&amp;L / rent-roll documents, not income-approach appeal exhibits).</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="n"/>
+      <c r="C26" s="20" t="n"/>
+      <c r="D26" s="20" t="n"/>
+      <c r="E26" s="20" t="n"/>
+      <c r="F26" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1151,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2610,6 +2700,275 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>R0071007</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>R0071007</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>0171935302010</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Warehouse and Storage Building(s)</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>N. Pecos Ave</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>80221</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>T &amp; G Pecos, LLC</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>T &amp; G Pecos, LLC</t>
+        </is>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>Industrial - Multi-Tenant Storage/Warehouse Bays</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>Multi (~90 units/bays, Buildings A-G)</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="8" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="8" t="n"/>
+      <c r="R17" s="6" t="n"/>
+      <c r="S17" s="6" t="n"/>
+      <c r="T17" s="6" t="n"/>
+      <c r="U17" s="9" t="n"/>
+      <c r="V17" s="5" t="n"/>
+      <c r="W17" s="9" t="n"/>
+      <c r="X17" s="6" t="inlineStr">
+        <is>
+          <t>Stevens &amp; Associates (SB 11-119 filing agent)</t>
+        </is>
+      </c>
+      <c r="Y17" s="6" t="inlineStr">
+        <is>
+          <t>R0071007.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>R0055143</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R0055143</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>R0055143</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Storage</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Blvd</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Denver</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>80229</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Adams</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Storage LLC (Richard Kessler / TAM Capital, Asset Mgr)</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>8700 Devonshire Storage LLC</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>Self-Storage</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>Multi (self-storage, ~278-290 units)</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="n"/>
+      <c r="O18" s="8" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="8" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
+      <c r="T18" s="6" t="inlineStr">
+        <is>
+          <t>68.29% units (Feb-2025) vs. 75.17% (2023), declining</t>
+        </is>
+      </c>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="W18" s="9" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="X18" s="6" t="inlineStr">
+        <is>
+          <t>CubeSmart (property mgr) / National Bureau Property Advisors (Evan Lantz, tax agent)</t>
+        </is>
+      </c>
+      <c r="Y18" s="6" t="inlineStr">
+        <is>
+          <t>R0055143.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">